--- a/clang-x64/Scattered successful looukp.xlsx
+++ b/clang-x64/Scattered successful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>5.08765</v>
+        <v>3.8876</v>
       </c>
       <c r="C2" t="n">
-        <v>4.92265</v>
+        <v>3.03299</v>
       </c>
       <c r="D2" t="n">
-        <v>7.36635</v>
+        <v>6.86728</v>
       </c>
       <c r="E2" t="n">
-        <v>4.57181</v>
+        <v>3.90764</v>
       </c>
       <c r="F2" t="n">
-        <v>4.88283</v>
+        <v>3.8325</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>4.58211</v>
+        <v>3.8974</v>
       </c>
       <c r="C3" t="n">
-        <v>4.98558</v>
+        <v>3.02384</v>
       </c>
       <c r="D3" t="n">
-        <v>8.05251</v>
+        <v>7.36644</v>
       </c>
       <c r="E3" t="n">
-        <v>4.66628</v>
+        <v>3.92463</v>
       </c>
       <c r="F3" t="n">
-        <v>4.92265</v>
+        <v>3.86085</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>4.63644</v>
+        <v>3.98966</v>
       </c>
       <c r="C4" t="n">
-        <v>5.08802</v>
+        <v>3.07527</v>
       </c>
       <c r="D4" t="n">
-        <v>8.93915</v>
+        <v>8.30997</v>
       </c>
       <c r="E4" t="n">
-        <v>4.60515</v>
+        <v>3.93774</v>
       </c>
       <c r="F4" t="n">
-        <v>4.76153</v>
+        <v>3.82741</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>4.65471</v>
+        <v>3.99012</v>
       </c>
       <c r="C5" t="n">
-        <v>5.06127</v>
+        <v>3.10014</v>
       </c>
       <c r="D5" t="n">
-        <v>9.65856</v>
+        <v>9.11819</v>
       </c>
       <c r="E5" t="n">
-        <v>4.61737</v>
+        <v>3.94542</v>
       </c>
       <c r="F5" t="n">
-        <v>4.96204</v>
+        <v>3.83907</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>4.63073</v>
+        <v>4.06462</v>
       </c>
       <c r="C6" t="n">
-        <v>5.1062</v>
+        <v>3.15721</v>
       </c>
       <c r="D6" t="n">
-        <v>10.3758</v>
+        <v>9.8583</v>
       </c>
       <c r="E6" t="n">
-        <v>4.64217</v>
+        <v>4.01464</v>
       </c>
       <c r="F6" t="n">
-        <v>5.02337</v>
+        <v>3.87662</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>4.63977</v>
+        <v>4.08516</v>
       </c>
       <c r="C7" t="n">
-        <v>5.15549</v>
+        <v>3.20325</v>
       </c>
       <c r="D7" t="n">
-        <v>6.04566</v>
+        <v>5.9212</v>
       </c>
       <c r="E7" t="n">
-        <v>4.7074</v>
+        <v>4.03067</v>
       </c>
       <c r="F7" t="n">
-        <v>5.15791</v>
+        <v>3.96638</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>4.72931</v>
+        <v>4.07026</v>
       </c>
       <c r="C8" t="n">
-        <v>5.19208</v>
+        <v>3.47474</v>
       </c>
       <c r="D8" t="n">
-        <v>6.46623</v>
+        <v>6.16503</v>
       </c>
       <c r="E8" t="n">
-        <v>4.98078</v>
+        <v>4.15589</v>
       </c>
       <c r="F8" t="n">
-        <v>5.26348</v>
+        <v>4.15991</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77251</v>
+        <v>4.05403</v>
       </c>
       <c r="C9" t="n">
-        <v>5.17962</v>
+        <v>3.86895</v>
       </c>
       <c r="D9" t="n">
-        <v>6.99979</v>
+        <v>6.80041</v>
       </c>
       <c r="E9" t="n">
-        <v>4.88042</v>
+        <v>4.84027</v>
       </c>
       <c r="F9" t="n">
-        <v>4.81301</v>
+        <v>4.12124</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>5.39842</v>
+        <v>4.77143</v>
       </c>
       <c r="C10" t="n">
-        <v>5.15688</v>
+        <v>3.52128</v>
       </c>
       <c r="D10" t="n">
-        <v>7.11797</v>
+        <v>7.31636</v>
       </c>
       <c r="E10" t="n">
-        <v>4.95105</v>
+        <v>5.04395</v>
       </c>
       <c r="F10" t="n">
-        <v>4.82632</v>
+        <v>4.14912</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>5.50298</v>
+        <v>4.88658</v>
       </c>
       <c r="C11" t="n">
-        <v>5.1811</v>
+        <v>3.78443</v>
       </c>
       <c r="D11" t="n">
-        <v>7.76206</v>
+        <v>7.96809</v>
       </c>
       <c r="E11" t="n">
-        <v>4.95988</v>
+        <v>5.0765</v>
       </c>
       <c r="F11" t="n">
-        <v>4.84461</v>
+        <v>4.1769</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>5.50052</v>
+        <v>4.8495</v>
       </c>
       <c r="C12" t="n">
-        <v>5.20653</v>
+        <v>3.80281</v>
       </c>
       <c r="D12" t="n">
-        <v>8.35173</v>
+        <v>8.505520000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>4.98531</v>
+        <v>4.94719</v>
       </c>
       <c r="F12" t="n">
-        <v>4.86862</v>
+        <v>4.20408</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>5.4946</v>
+        <v>5.01412</v>
       </c>
       <c r="C13" t="n">
-        <v>5.21133</v>
+        <v>3.83299</v>
       </c>
       <c r="D13" t="n">
-        <v>8.938370000000001</v>
+        <v>9.110239999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>5.19808</v>
+        <v>4.94311</v>
       </c>
       <c r="F13" t="n">
-        <v>4.90776</v>
+        <v>4.22725</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>5.60141</v>
+        <v>5.35376</v>
       </c>
       <c r="C14" t="n">
-        <v>5.21205</v>
+        <v>3.95298</v>
       </c>
       <c r="D14" t="n">
-        <v>9.537929999999999</v>
+        <v>9.68995</v>
       </c>
       <c r="E14" t="n">
-        <v>5.10355</v>
+        <v>5.19039</v>
       </c>
       <c r="F14" t="n">
-        <v>4.94648</v>
+        <v>4.258</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>5.57804</v>
+        <v>5.71706</v>
       </c>
       <c r="C15" t="n">
-        <v>5.23316</v>
+        <v>3.74009</v>
       </c>
       <c r="D15" t="n">
-        <v>9.94788</v>
+        <v>10.1775</v>
       </c>
       <c r="E15" t="n">
-        <v>5.08706</v>
+        <v>5.15687</v>
       </c>
       <c r="F15" t="n">
-        <v>4.97045</v>
+        <v>4.30668</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>5.59386</v>
+        <v>5.85735</v>
       </c>
       <c r="C16" t="n">
-        <v>5.26336</v>
+        <v>3.93594</v>
       </c>
       <c r="D16" t="n">
-        <v>10.4647</v>
+        <v>10.6791</v>
       </c>
       <c r="E16" t="n">
-        <v>5.17513</v>
+        <v>5.2658</v>
       </c>
       <c r="F16" t="n">
-        <v>5.01522</v>
+        <v>4.32247</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>5.61311</v>
+        <v>5.05015</v>
       </c>
       <c r="C17" t="n">
-        <v>5.29118</v>
+        <v>3.99379</v>
       </c>
       <c r="D17" t="n">
-        <v>10.9133</v>
+        <v>11.1503</v>
       </c>
       <c r="E17" t="n">
-        <v>5.16373</v>
+        <v>4.96366</v>
       </c>
       <c r="F17" t="n">
-        <v>5.03577</v>
+        <v>4.36066</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>5.83532</v>
+        <v>5.40781</v>
       </c>
       <c r="C18" t="n">
-        <v>5.32872</v>
+        <v>4.08548</v>
       </c>
       <c r="D18" t="n">
-        <v>11.4402</v>
+        <v>11.6771</v>
       </c>
       <c r="E18" t="n">
-        <v>5.29173</v>
+        <v>5.17042</v>
       </c>
       <c r="F18" t="n">
-        <v>5.08449</v>
+        <v>4.37277</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>5.59667</v>
+        <v>5.08501</v>
       </c>
       <c r="C19" t="n">
-        <v>5.38199</v>
+        <v>4.07393</v>
       </c>
       <c r="D19" t="n">
-        <v>11.8697</v>
+        <v>12.1208</v>
       </c>
       <c r="E19" t="n">
-        <v>5.3107</v>
+        <v>5.03821</v>
       </c>
       <c r="F19" t="n">
-        <v>5.19376</v>
+        <v>4.43014</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>5.57896</v>
+        <v>5.79191</v>
       </c>
       <c r="C20" t="n">
-        <v>5.3725</v>
+        <v>3.89461</v>
       </c>
       <c r="D20" t="n">
-        <v>12.2139</v>
+        <v>12.5493</v>
       </c>
       <c r="E20" t="n">
-        <v>5.27632</v>
+        <v>4.95751</v>
       </c>
       <c r="F20" t="n">
-        <v>5.21549</v>
+        <v>4.495</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>5.61837</v>
+        <v>5.8239</v>
       </c>
       <c r="C21" t="n">
-        <v>5.4018</v>
+        <v>3.93377</v>
       </c>
       <c r="D21" t="n">
-        <v>8.46785</v>
+        <v>8.71912</v>
       </c>
       <c r="E21" t="n">
-        <v>5.62325</v>
+        <v>5.07028</v>
       </c>
       <c r="F21" t="n">
-        <v>5.6118</v>
+        <v>4.69208</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>5.66505</v>
+        <v>5.86642</v>
       </c>
       <c r="C22" t="n">
-        <v>5.62667</v>
+        <v>3.73931</v>
       </c>
       <c r="D22" t="n">
-        <v>8.82687</v>
+        <v>9.04875</v>
       </c>
       <c r="E22" t="n">
-        <v>5.94174</v>
+        <v>5.73998</v>
       </c>
       <c r="F22" t="n">
-        <v>6.21226</v>
+        <v>5.95683</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>5.73568</v>
+        <v>5.75276</v>
       </c>
       <c r="C23" t="n">
-        <v>5.97542</v>
+        <v>3.78856</v>
       </c>
       <c r="D23" t="n">
-        <v>9.21528</v>
+        <v>9.4215</v>
       </c>
       <c r="E23" t="n">
-        <v>5.50005</v>
+        <v>4.85864</v>
       </c>
       <c r="F23" t="n">
-        <v>5.51306</v>
+        <v>5.0748</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>6.01521</v>
+        <v>5.59322</v>
       </c>
       <c r="C24" t="n">
-        <v>6.0179</v>
+        <v>3.81981</v>
       </c>
       <c r="D24" t="n">
-        <v>9.558059999999999</v>
+        <v>9.75919</v>
       </c>
       <c r="E24" t="n">
-        <v>5.52828</v>
+        <v>4.82992</v>
       </c>
       <c r="F24" t="n">
-        <v>5.54933</v>
+        <v>5.09767</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>6.04991</v>
+        <v>5.69754</v>
       </c>
       <c r="C25" t="n">
-        <v>6.03123</v>
+        <v>3.80654</v>
       </c>
       <c r="D25" t="n">
-        <v>9.93618</v>
+        <v>10.1942</v>
       </c>
       <c r="E25" t="n">
-        <v>5.59205</v>
+        <v>4.89602</v>
       </c>
       <c r="F25" t="n">
-        <v>5.57372</v>
+        <v>5.14402</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>6.04214</v>
+        <v>5.60996</v>
       </c>
       <c r="C26" t="n">
-        <v>6.03327</v>
+        <v>3.8495</v>
       </c>
       <c r="D26" t="n">
-        <v>10.3507</v>
+        <v>10.5988</v>
       </c>
       <c r="E26" t="n">
-        <v>5.60069</v>
+        <v>4.96977</v>
       </c>
       <c r="F26" t="n">
-        <v>5.59521</v>
+        <v>4.97687</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>6.06188</v>
+        <v>5.58265</v>
       </c>
       <c r="C27" t="n">
-        <v>6.03904</v>
+        <v>3.87503</v>
       </c>
       <c r="D27" t="n">
-        <v>10.7412</v>
+        <v>10.937</v>
       </c>
       <c r="E27" t="n">
-        <v>5.67555</v>
+        <v>4.9952</v>
       </c>
       <c r="F27" t="n">
-        <v>5.61699</v>
+        <v>5.02265</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>6.08285</v>
+        <v>5.75653</v>
       </c>
       <c r="C28" t="n">
-        <v>6.09346</v>
+        <v>3.81894</v>
       </c>
       <c r="D28" t="n">
-        <v>11.1435</v>
+        <v>11.39</v>
       </c>
       <c r="E28" t="n">
-        <v>5.65063</v>
+        <v>5.03068</v>
       </c>
       <c r="F28" t="n">
-        <v>5.62894</v>
+        <v>5.04307</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>6.09766</v>
+        <v>5.77589</v>
       </c>
       <c r="C29" t="n">
-        <v>6.06648</v>
+        <v>3.84399</v>
       </c>
       <c r="D29" t="n">
-        <v>11.5154</v>
+        <v>11.7734</v>
       </c>
       <c r="E29" t="n">
-        <v>5.7989</v>
+        <v>5.07355</v>
       </c>
       <c r="F29" t="n">
-        <v>5.67287</v>
+        <v>5.081</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>6.1138</v>
+        <v>5.3501</v>
       </c>
       <c r="C30" t="n">
-        <v>6.10295</v>
+        <v>3.94388</v>
       </c>
       <c r="D30" t="n">
-        <v>11.9141</v>
+        <v>12.1671</v>
       </c>
       <c r="E30" t="n">
-        <v>5.79513</v>
+        <v>5.04817</v>
       </c>
       <c r="F30" t="n">
-        <v>5.71038</v>
+        <v>5.27734</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>6.13901</v>
+        <v>5.37248</v>
       </c>
       <c r="C31" t="n">
-        <v>6.11881</v>
+        <v>3.97112</v>
       </c>
       <c r="D31" t="n">
-        <v>12.2853</v>
+        <v>12.5727</v>
       </c>
       <c r="E31" t="n">
-        <v>5.80221</v>
+        <v>5.13979</v>
       </c>
       <c r="F31" t="n">
-        <v>5.77847</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>6.15276</v>
+        <v>5.39146</v>
       </c>
       <c r="C32" t="n">
-        <v>6.18786</v>
+        <v>4.00968</v>
       </c>
       <c r="D32" t="n">
-        <v>12.6122</v>
+        <v>12.8713</v>
       </c>
       <c r="E32" t="n">
-        <v>5.83629</v>
+        <v>5.22731</v>
       </c>
       <c r="F32" t="n">
-        <v>5.83382</v>
+        <v>5.37717</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>6.18048</v>
+        <v>5.41927</v>
       </c>
       <c r="C33" t="n">
-        <v>6.2145</v>
+        <v>4.04984</v>
       </c>
       <c r="D33" t="n">
-        <v>12.9874</v>
+        <v>13.3462</v>
       </c>
       <c r="E33" t="n">
-        <v>5.90417</v>
+        <v>5.22243</v>
       </c>
       <c r="F33" t="n">
-        <v>5.89927</v>
+        <v>5.23954</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>6.21944</v>
+        <v>5.45336</v>
       </c>
       <c r="C34" t="n">
-        <v>6.2203</v>
+        <v>4.09079</v>
       </c>
       <c r="D34" t="n">
-        <v>13.317</v>
+        <v>13.6735</v>
       </c>
       <c r="E34" t="n">
-        <v>5.99517</v>
+        <v>5.3463</v>
       </c>
       <c r="F34" t="n">
-        <v>6.02268</v>
+        <v>5.58933</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>6.22164</v>
+        <v>5.61589</v>
       </c>
       <c r="C35" t="n">
-        <v>6.2539</v>
+        <v>4.09371</v>
       </c>
       <c r="D35" t="n">
-        <v>9.39554</v>
+        <v>9.513030000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>6.345</v>
+        <v>5.55717</v>
       </c>
       <c r="F35" t="n">
-        <v>6.31959</v>
+        <v>5.79077</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>6.29726</v>
+        <v>6.12279</v>
       </c>
       <c r="C36" t="n">
-        <v>6.41156</v>
+        <v>4.10615</v>
       </c>
       <c r="D36" t="n">
-        <v>9.62424</v>
+        <v>9.75132</v>
       </c>
       <c r="E36" t="n">
-        <v>6.99972</v>
+        <v>6.19535</v>
       </c>
       <c r="F36" t="n">
-        <v>6.9931</v>
+        <v>6.57463</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>6.53888</v>
+        <v>5.99959</v>
       </c>
       <c r="C37" t="n">
-        <v>6.66495</v>
+        <v>3.81048</v>
       </c>
       <c r="D37" t="n">
-        <v>9.777609999999999</v>
+        <v>9.88847</v>
       </c>
       <c r="E37" t="n">
-        <v>5.9826</v>
+        <v>5.16476</v>
       </c>
       <c r="F37" t="n">
-        <v>6.01933</v>
+        <v>4.94795</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>6.68413</v>
+        <v>5.40201</v>
       </c>
       <c r="C38" t="n">
-        <v>6.89486</v>
+        <v>4.15689</v>
       </c>
       <c r="D38" t="n">
-        <v>10.067</v>
+        <v>10.2138</v>
       </c>
       <c r="E38" t="n">
-        <v>6.09185</v>
+        <v>5.21153</v>
       </c>
       <c r="F38" t="n">
-        <v>6.04724</v>
+        <v>4.98007</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>6.68471</v>
+        <v>5.41473</v>
       </c>
       <c r="C39" t="n">
-        <v>6.90239</v>
+        <v>4.17215</v>
       </c>
       <c r="D39" t="n">
-        <v>10.4002</v>
+        <v>10.5036</v>
       </c>
       <c r="E39" t="n">
-        <v>6.13058</v>
+        <v>5.35279</v>
       </c>
       <c r="F39" t="n">
-        <v>6.07921</v>
+        <v>5.00895</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>6.6956</v>
+        <v>5.84012</v>
       </c>
       <c r="C40" t="n">
-        <v>6.91018</v>
+        <v>3.95468</v>
       </c>
       <c r="D40" t="n">
-        <v>10.732</v>
+        <v>10.8482</v>
       </c>
       <c r="E40" t="n">
-        <v>6.17003</v>
+        <v>5.44138</v>
       </c>
       <c r="F40" t="n">
-        <v>6.11484</v>
+        <v>5.12946</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>6.70406</v>
+        <v>5.83691</v>
       </c>
       <c r="C41" t="n">
-        <v>6.92243</v>
+        <v>4.19106</v>
       </c>
       <c r="D41" t="n">
-        <v>11.1096</v>
+        <v>11.2347</v>
       </c>
       <c r="E41" t="n">
-        <v>6.23534</v>
+        <v>5.3494</v>
       </c>
       <c r="F41" t="n">
-        <v>6.1426</v>
+        <v>5.07716</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>6.72532</v>
+        <v>5.44482</v>
       </c>
       <c r="C42" t="n">
-        <v>6.93932</v>
+        <v>4.2382</v>
       </c>
       <c r="D42" t="n">
-        <v>11.4471</v>
+        <v>11.5763</v>
       </c>
       <c r="E42" t="n">
-        <v>6.26077</v>
+        <v>5.30416</v>
       </c>
       <c r="F42" t="n">
-        <v>6.17842</v>
+        <v>5.10375</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>6.7374</v>
+        <v>5.45517</v>
       </c>
       <c r="C43" t="n">
-        <v>6.95499</v>
+        <v>4.26145</v>
       </c>
       <c r="D43" t="n">
-        <v>11.8603</v>
+        <v>11.9215</v>
       </c>
       <c r="E43" t="n">
-        <v>6.31464</v>
+        <v>5.55366</v>
       </c>
       <c r="F43" t="n">
-        <v>6.23214</v>
+        <v>5.14724</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>6.75055</v>
+        <v>5.47378</v>
       </c>
       <c r="C44" t="n">
-        <v>6.95792</v>
+        <v>4.29122</v>
       </c>
       <c r="D44" t="n">
-        <v>12.2533</v>
+        <v>12.3099</v>
       </c>
       <c r="E44" t="n">
-        <v>6.35102</v>
+        <v>5.60372</v>
       </c>
       <c r="F44" t="n">
-        <v>6.27752</v>
+        <v>5.19482</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>6.77096</v>
+        <v>5.49458</v>
       </c>
       <c r="C45" t="n">
-        <v>6.99144</v>
+        <v>4.3301</v>
       </c>
       <c r="D45" t="n">
-        <v>12.6353</v>
+        <v>12.6982</v>
       </c>
       <c r="E45" t="n">
-        <v>6.41213</v>
+        <v>5.70904</v>
       </c>
       <c r="F45" t="n">
-        <v>6.27823</v>
+        <v>5.5482</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>6.7916</v>
+        <v>6.00797</v>
       </c>
       <c r="C46" t="n">
-        <v>7.02437</v>
+        <v>4.3526</v>
       </c>
       <c r="D46" t="n">
-        <v>12.9746</v>
+        <v>13.0782</v>
       </c>
       <c r="E46" t="n">
-        <v>6.48558</v>
+        <v>5.77182</v>
       </c>
       <c r="F46" t="n">
-        <v>6.38293</v>
+        <v>5.70761</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>6.79738</v>
+        <v>5.55052</v>
       </c>
       <c r="C47" t="n">
-        <v>7.06668</v>
+        <v>4.42148</v>
       </c>
       <c r="D47" t="n">
-        <v>13.3077</v>
+        <v>13.4162</v>
       </c>
       <c r="E47" t="n">
-        <v>6.64228</v>
+        <v>5.93051</v>
       </c>
       <c r="F47" t="n">
-        <v>6.55677</v>
+        <v>5.97877</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>6.86444</v>
+        <v>5.89767</v>
       </c>
       <c r="C48" t="n">
-        <v>7.10979</v>
+        <v>4.16304</v>
       </c>
       <c r="D48" t="n">
-        <v>13.6798</v>
+        <v>13.8057</v>
       </c>
       <c r="E48" t="n">
-        <v>6.86998</v>
+        <v>6.15209</v>
       </c>
       <c r="F48" t="n">
-        <v>6.72696</v>
+        <v>5.89018</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>6.93623</v>
+        <v>5.89851</v>
       </c>
       <c r="C49" t="n">
-        <v>7.1786</v>
+        <v>4.23216</v>
       </c>
       <c r="D49" t="n">
-        <v>13.9915</v>
+        <v>14.1343</v>
       </c>
       <c r="E49" t="n">
-        <v>7.21305</v>
+        <v>6.50221</v>
       </c>
       <c r="F49" t="n">
-        <v>7.14408</v>
+        <v>6.363</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>7.08651</v>
+        <v>5.93188</v>
       </c>
       <c r="C50" t="n">
-        <v>7.23885</v>
+        <v>4.76383</v>
       </c>
       <c r="D50" t="n">
-        <v>9.816409999999999</v>
+        <v>11.2027</v>
       </c>
       <c r="E50" t="n">
-        <v>7.64697</v>
+        <v>6.38875</v>
       </c>
       <c r="F50" t="n">
-        <v>7.64688</v>
+        <v>7.07611</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>7.43591</v>
+        <v>6.43102</v>
       </c>
       <c r="C51" t="n">
-        <v>7.68187</v>
+        <v>4.14063</v>
       </c>
       <c r="D51" t="n">
-        <v>10.0142</v>
+        <v>11.6261</v>
       </c>
       <c r="E51" t="n">
-        <v>6.51089</v>
+        <v>5.23514</v>
       </c>
       <c r="F51" t="n">
-        <v>6.32239</v>
+        <v>5.66701</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>7.88546</v>
+        <v>7.58265</v>
       </c>
       <c r="C52" t="n">
-        <v>8.406370000000001</v>
+        <v>4.19229</v>
       </c>
       <c r="D52" t="n">
-        <v>10.2601</v>
+        <v>11.7768</v>
       </c>
       <c r="E52" t="n">
-        <v>6.44022</v>
+        <v>5.37343</v>
       </c>
       <c r="F52" t="n">
-        <v>6.35389</v>
+        <v>5.5301</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>7.41505</v>
+        <v>6.26432</v>
       </c>
       <c r="C53" t="n">
-        <v>7.56462</v>
+        <v>4.20806</v>
       </c>
       <c r="D53" t="n">
-        <v>10.5423</v>
+        <v>12.3047</v>
       </c>
       <c r="E53" t="n">
-        <v>6.43541</v>
+        <v>5.41163</v>
       </c>
       <c r="F53" t="n">
-        <v>6.38422</v>
+        <v>5.62604</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>7.4219</v>
+        <v>6.24727</v>
       </c>
       <c r="C54" t="n">
-        <v>7.58701</v>
+        <v>4.22762</v>
       </c>
       <c r="D54" t="n">
-        <v>10.8877</v>
+        <v>12.8448</v>
       </c>
       <c r="E54" t="n">
-        <v>6.65003</v>
+        <v>5.48053</v>
       </c>
       <c r="F54" t="n">
-        <v>6.42808</v>
+        <v>5.70683</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>7.4195</v>
+        <v>6.28843</v>
       </c>
       <c r="C55" t="n">
-        <v>7.60045</v>
+        <v>4.25307</v>
       </c>
       <c r="D55" t="n">
-        <v>11.2492</v>
+        <v>13.6271</v>
       </c>
       <c r="E55" t="n">
-        <v>6.67068</v>
+        <v>5.52146</v>
       </c>
       <c r="F55" t="n">
-        <v>6.472</v>
+        <v>6.02071</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>7.43884</v>
+        <v>6.27141</v>
       </c>
       <c r="C56" t="n">
-        <v>7.60592</v>
+        <v>4.27087</v>
       </c>
       <c r="D56" t="n">
-        <v>11.6175</v>
+        <v>13.8818</v>
       </c>
       <c r="E56" t="n">
-        <v>6.71998</v>
+        <v>5.59096</v>
       </c>
       <c r="F56" t="n">
-        <v>6.53251</v>
+        <v>5.81953</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>7.40122</v>
+        <v>6.2439</v>
       </c>
       <c r="C57" t="n">
-        <v>7.62358</v>
+        <v>4.27885</v>
       </c>
       <c r="D57" t="n">
-        <v>12.0638</v>
+        <v>15.8462</v>
       </c>
       <c r="E57" t="n">
-        <v>6.65609</v>
+        <v>5.67032</v>
       </c>
       <c r="F57" t="n">
-        <v>6.60637</v>
+        <v>6.09713</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>7.45337</v>
+        <v>6.22175</v>
       </c>
       <c r="C58" t="n">
-        <v>7.59781</v>
+        <v>4.31203</v>
       </c>
       <c r="D58" t="n">
-        <v>12.4435</v>
+        <v>16.0716</v>
       </c>
       <c r="E58" t="n">
-        <v>6.8519</v>
+        <v>5.72314</v>
       </c>
       <c r="F58" t="n">
-        <v>6.65232</v>
+        <v>5.91382</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>7.46518</v>
+        <v>6.25217</v>
       </c>
       <c r="C59" t="n">
-        <v>7.64422</v>
+        <v>4.34748</v>
       </c>
       <c r="D59" t="n">
-        <v>12.7692</v>
+        <v>16.3593</v>
       </c>
       <c r="E59" t="n">
-        <v>6.93356</v>
+        <v>5.8226</v>
       </c>
       <c r="F59" t="n">
-        <v>6.76855</v>
+        <v>5.99171</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>7.46681</v>
+        <v>6.31877</v>
       </c>
       <c r="C60" t="n">
-        <v>7.67959</v>
+        <v>4.40794</v>
       </c>
       <c r="D60" t="n">
-        <v>13.1256</v>
+        <v>17.2287</v>
       </c>
       <c r="E60" t="n">
-        <v>7.07264</v>
+        <v>5.83922</v>
       </c>
       <c r="F60" t="n">
-        <v>6.9368</v>
+        <v>6.15691</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>7.5382</v>
+        <v>6.32808</v>
       </c>
       <c r="C61" t="n">
-        <v>7.69555</v>
+        <v>4.44073</v>
       </c>
       <c r="D61" t="n">
-        <v>13.5583</v>
+        <v>17.3969</v>
       </c>
       <c r="E61" t="n">
-        <v>7.20513</v>
+        <v>6.07225</v>
       </c>
       <c r="F61" t="n">
-        <v>7.1526</v>
+        <v>6.84392</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>7.60505</v>
+        <v>6.44851</v>
       </c>
       <c r="C62" t="n">
-        <v>7.80956</v>
+        <v>4.52326</v>
       </c>
       <c r="D62" t="n">
-        <v>13.9904</v>
+        <v>17.8435</v>
       </c>
       <c r="E62" t="n">
-        <v>7.53493</v>
+        <v>6.31018</v>
       </c>
       <c r="F62" t="n">
-        <v>7.41612</v>
+        <v>6.95747</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>7.72328</v>
+        <v>6.50203</v>
       </c>
       <c r="C63" t="n">
-        <v>7.95244</v>
+        <v>4.63868</v>
       </c>
       <c r="D63" t="n">
-        <v>14.4074</v>
+        <v>18.0845</v>
       </c>
       <c r="E63" t="n">
-        <v>7.83172</v>
+        <v>6.59662</v>
       </c>
       <c r="F63" t="n">
-        <v>7.8467</v>
+        <v>7.36094</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>7.87333</v>
+        <v>6.65941</v>
       </c>
       <c r="C64" t="n">
-        <v>8.147640000000001</v>
+        <v>4.80784</v>
       </c>
       <c r="D64" t="n">
-        <v>10.8898</v>
+        <v>13.8272</v>
       </c>
       <c r="E64" t="n">
-        <v>8.195959999999999</v>
+        <v>6.99021</v>
       </c>
       <c r="F64" t="n">
-        <v>8.363659999999999</v>
+        <v>7.54005</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>8.137639999999999</v>
+        <v>6.96244</v>
       </c>
       <c r="C65" t="n">
-        <v>8.54585</v>
+        <v>6.091</v>
       </c>
       <c r="D65" t="n">
-        <v>11.108</v>
+        <v>12.8352</v>
       </c>
       <c r="E65" t="n">
-        <v>8.843389999999999</v>
+        <v>7.59437</v>
       </c>
       <c r="F65" t="n">
-        <v>9.1228</v>
+        <v>8.433070000000001</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>8.58291</v>
+        <v>7.36759</v>
       </c>
       <c r="C66" t="n">
-        <v>9.059699999999999</v>
+        <v>6.2948</v>
       </c>
       <c r="D66" t="n">
-        <v>11.589</v>
+        <v>14.3084</v>
       </c>
       <c r="E66" t="n">
-        <v>6.92845</v>
+        <v>6.11047</v>
       </c>
       <c r="F66" t="n">
-        <v>7.00451</v>
+        <v>6.59833</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>8.604089999999999</v>
+        <v>8.505330000000001</v>
       </c>
       <c r="C67" t="n">
-        <v>8.576269999999999</v>
+        <v>6.14488</v>
       </c>
       <c r="D67" t="n">
-        <v>12.2469</v>
+        <v>14.9122</v>
       </c>
       <c r="E67" t="n">
-        <v>7.02751</v>
+        <v>6.12158</v>
       </c>
       <c r="F67" t="n">
-        <v>7.09578</v>
+        <v>6.69057</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>8.467180000000001</v>
+        <v>8.522919999999999</v>
       </c>
       <c r="C68" t="n">
-        <v>8.62604</v>
+        <v>6.22882</v>
       </c>
       <c r="D68" t="n">
-        <v>12.7926</v>
+        <v>16.3849</v>
       </c>
       <c r="E68" t="n">
-        <v>7.02476</v>
+        <v>6.14506</v>
       </c>
       <c r="F68" t="n">
-        <v>7.15993</v>
+        <v>6.87683</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>8.47148</v>
+        <v>8.768359999999999</v>
       </c>
       <c r="C69" t="n">
-        <v>8.68268</v>
+        <v>6.43776</v>
       </c>
       <c r="D69" t="n">
-        <v>13.3232</v>
+        <v>16.4845</v>
       </c>
       <c r="E69" t="n">
-        <v>7.08103</v>
+        <v>6.2644</v>
       </c>
       <c r="F69" t="n">
-        <v>7.25903</v>
+        <v>6.85636</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>8.561859999999999</v>
+        <v>8.71794</v>
       </c>
       <c r="C70" t="n">
-        <v>8.66962</v>
+        <v>6.45594</v>
       </c>
       <c r="D70" t="n">
-        <v>14.0868</v>
+        <v>17.51</v>
       </c>
       <c r="E70" t="n">
-        <v>7.13624</v>
+        <v>6.38567</v>
       </c>
       <c r="F70" t="n">
-        <v>7.31106</v>
+        <v>6.9929</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>8.503349999999999</v>
+        <v>10.4687</v>
       </c>
       <c r="C71" t="n">
-        <v>8.877090000000001</v>
+        <v>8.01365</v>
       </c>
       <c r="D71" t="n">
-        <v>15.0176</v>
+        <v>17.9268</v>
       </c>
       <c r="E71" t="n">
-        <v>7.22934</v>
+        <v>6.38178</v>
       </c>
       <c r="F71" t="n">
-        <v>7.41562</v>
+        <v>7.20047</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>8.751810000000001</v>
+        <v>8.76117</v>
       </c>
       <c r="C72" t="n">
-        <v>8.947150000000001</v>
+        <v>6.44567</v>
       </c>
       <c r="D72" t="n">
-        <v>15.7969</v>
+        <v>18.8661</v>
       </c>
       <c r="E72" t="n">
-        <v>7.30987</v>
+        <v>6.45318</v>
       </c>
       <c r="F72" t="n">
-        <v>7.55202</v>
+        <v>7.36612</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>8.619809999999999</v>
+        <v>8.922370000000001</v>
       </c>
       <c r="C73" t="n">
-        <v>8.99145</v>
+        <v>6.60933</v>
       </c>
       <c r="D73" t="n">
-        <v>16.6073</v>
+        <v>18.9987</v>
       </c>
       <c r="E73" t="n">
-        <v>7.41247</v>
+        <v>6.56339</v>
       </c>
       <c r="F73" t="n">
-        <v>7.73996</v>
+        <v>7.53016</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>8.4818</v>
+        <v>11.1556</v>
       </c>
       <c r="C74" t="n">
-        <v>9.109069999999999</v>
+        <v>8.58553</v>
       </c>
       <c r="D74" t="n">
-        <v>17.5128</v>
+        <v>20.546</v>
       </c>
       <c r="E74" t="n">
-        <v>7.51749</v>
+        <v>8.87595</v>
       </c>
       <c r="F74" t="n">
-        <v>7.96819</v>
+        <v>7.24074</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>8.52383</v>
+        <v>11.182</v>
       </c>
       <c r="C75" t="n">
-        <v>9.056319999999999</v>
+        <v>8.55442</v>
       </c>
       <c r="D75" t="n">
-        <v>18.4737</v>
+        <v>21.4432</v>
       </c>
       <c r="E75" t="n">
-        <v>7.69005</v>
+        <v>7.48722</v>
       </c>
       <c r="F75" t="n">
-        <v>8.22856</v>
+        <v>8.45993</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>8.605359999999999</v>
+        <v>11.2998</v>
       </c>
       <c r="C76" t="n">
-        <v>9.23573</v>
+        <v>8.66262</v>
       </c>
       <c r="D76" t="n">
-        <v>19.14</v>
+        <v>21.5363</v>
       </c>
       <c r="E76" t="n">
-        <v>7.90698</v>
+        <v>8.67891</v>
       </c>
       <c r="F76" t="n">
-        <v>8.637890000000001</v>
+        <v>8.05776</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>8.820690000000001</v>
+        <v>9.22231</v>
       </c>
       <c r="C77" t="n">
-        <v>9.42184</v>
+        <v>6.9873</v>
       </c>
       <c r="D77" t="n">
-        <v>20.185</v>
+        <v>22.5883</v>
       </c>
       <c r="E77" t="n">
-        <v>8.20016</v>
+        <v>9.018549999999999</v>
       </c>
       <c r="F77" t="n">
-        <v>9.07437</v>
+        <v>8.726610000000001</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>8.972939999999999</v>
+        <v>12.4709</v>
       </c>
       <c r="C78" t="n">
-        <v>9.82798</v>
+        <v>9.885490000000001</v>
       </c>
       <c r="D78" t="n">
-        <v>20.1168</v>
+        <v>21.0895</v>
       </c>
       <c r="E78" t="n">
-        <v>8.55078</v>
+        <v>8.80688</v>
       </c>
       <c r="F78" t="n">
-        <v>9.542719999999999</v>
+        <v>11.5836</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>9.184139999999999</v>
+        <v>11.2956</v>
       </c>
       <c r="C79" t="n">
-        <v>10.2318</v>
+        <v>15.4164</v>
       </c>
       <c r="D79" t="n">
-        <v>20.8274</v>
+        <v>21.6377</v>
       </c>
       <c r="E79" t="n">
-        <v>9.21477</v>
+        <v>9.34774</v>
       </c>
       <c r="F79" t="n">
-        <v>10.3943</v>
+        <v>9.72649</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>9.56903</v>
+        <v>13.0209</v>
       </c>
       <c r="C80" t="n">
-        <v>10.8748</v>
+        <v>15.8949</v>
       </c>
       <c r="D80" t="n">
-        <v>21.6737</v>
+        <v>22.6957</v>
       </c>
       <c r="E80" t="n">
-        <v>11.8216</v>
+        <v>10.9196</v>
       </c>
       <c r="F80" t="n">
-        <v>12.4205</v>
+        <v>13.6809</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>21.2802</v>
+        <v>20.0831</v>
       </c>
       <c r="C81" t="n">
-        <v>17.0509</v>
+        <v>16.3034</v>
       </c>
       <c r="D81" t="n">
-        <v>22.9515</v>
+        <v>23.6112</v>
       </c>
       <c r="E81" t="n">
-        <v>12.1536</v>
+        <v>12.0988</v>
       </c>
       <c r="F81" t="n">
-        <v>12.4518</v>
+        <v>15.3371</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>21.4301</v>
+        <v>19.8435</v>
       </c>
       <c r="C82" t="n">
-        <v>17.1075</v>
+        <v>16.0757</v>
       </c>
       <c r="D82" t="n">
-        <v>23.8585</v>
+        <v>24.2952</v>
       </c>
       <c r="E82" t="n">
-        <v>12.4575</v>
+        <v>12.4252</v>
       </c>
       <c r="F82" t="n">
-        <v>12.5723</v>
+        <v>15.1182</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>21.9814</v>
+        <v>20.0145</v>
       </c>
       <c r="C83" t="n">
-        <v>17.1241</v>
+        <v>16.2639</v>
       </c>
       <c r="D83" t="n">
-        <v>24.8767</v>
+        <v>25.8981</v>
       </c>
       <c r="E83" t="n">
-        <v>12.49</v>
+        <v>12.7694</v>
       </c>
       <c r="F83" t="n">
-        <v>12.7455</v>
+        <v>15.5835</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>21.6587</v>
+        <v>20.0398</v>
       </c>
       <c r="C84" t="n">
-        <v>17.2238</v>
+        <v>16.2921</v>
       </c>
       <c r="D84" t="n">
-        <v>26.0695</v>
+        <v>26.9269</v>
       </c>
       <c r="E84" t="n">
-        <v>12.9492</v>
+        <v>13.0468</v>
       </c>
       <c r="F84" t="n">
-        <v>12.7333</v>
+        <v>15.6099</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>21.6732</v>
+        <v>20.2023</v>
       </c>
       <c r="C85" t="n">
-        <v>17.2646</v>
+        <v>16.459</v>
       </c>
       <c r="D85" t="n">
-        <v>26.5555</v>
+        <v>28.9316</v>
       </c>
       <c r="E85" t="n">
-        <v>13.1692</v>
+        <v>12.5353</v>
       </c>
       <c r="F85" t="n">
-        <v>12.2832</v>
+        <v>12.6809</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>21.7714</v>
+        <v>20.4575</v>
       </c>
       <c r="C86" t="n">
-        <v>17.3731</v>
+        <v>16.7364</v>
       </c>
       <c r="D86" t="n">
-        <v>28.0755</v>
+        <v>29.8653</v>
       </c>
       <c r="E86" t="n">
-        <v>13.4304</v>
+        <v>12.8493</v>
       </c>
       <c r="F86" t="n">
-        <v>12.4429</v>
+        <v>12.899</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>21.8227</v>
+        <v>20.3531</v>
       </c>
       <c r="C87" t="n">
-        <v>17.4353</v>
+        <v>16.6356</v>
       </c>
       <c r="D87" t="n">
-        <v>28.7345</v>
+        <v>31.256</v>
       </c>
       <c r="E87" t="n">
-        <v>13.5763</v>
+        <v>12.9942</v>
       </c>
       <c r="F87" t="n">
-        <v>12.6418</v>
+        <v>12.9953</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>21.8189</v>
+        <v>19.7273</v>
       </c>
       <c r="C88" t="n">
-        <v>17.1697</v>
+        <v>16.1638</v>
       </c>
       <c r="D88" t="n">
-        <v>30.1396</v>
+        <v>31.994</v>
       </c>
       <c r="E88" t="n">
-        <v>13.8178</v>
+        <v>13.4591</v>
       </c>
       <c r="F88" t="n">
-        <v>13.2765</v>
+        <v>16.1505</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>21.8592</v>
+        <v>19.9469</v>
       </c>
       <c r="C89" t="n">
-        <v>17.3438</v>
+        <v>16.3104</v>
       </c>
       <c r="D89" t="n">
-        <v>31.3091</v>
+        <v>33.1497</v>
       </c>
       <c r="E89" t="n">
-        <v>14.1699</v>
+        <v>13.7407</v>
       </c>
       <c r="F89" t="n">
-        <v>13.5373</v>
+        <v>16.4738</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>21.8681</v>
+        <v>19.8563</v>
       </c>
       <c r="C90" t="n">
-        <v>17.7375</v>
+        <v>16.3165</v>
       </c>
       <c r="D90" t="n">
-        <v>32.452</v>
+        <v>34.3402</v>
       </c>
       <c r="E90" t="n">
-        <v>14.393</v>
+        <v>14.0344</v>
       </c>
       <c r="F90" t="n">
-        <v>13.7072</v>
+        <v>17.6738</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>21.9183</v>
+        <v>20.1514</v>
       </c>
       <c r="C91" t="n">
-        <v>17.7873</v>
+        <v>16.4686</v>
       </c>
       <c r="D91" t="n">
-        <v>33.7114</v>
+        <v>34.4799</v>
       </c>
       <c r="E91" t="n">
-        <v>14.7733</v>
+        <v>15.1023</v>
       </c>
       <c r="F91" t="n">
-        <v>13.652</v>
+        <v>14.9106</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>22.0483</v>
+        <v>20.1276</v>
       </c>
       <c r="C92" t="n">
-        <v>17.7829</v>
+        <v>16.6443</v>
       </c>
       <c r="D92" t="n">
-        <v>32.0212</v>
+        <v>32.9637</v>
       </c>
       <c r="E92" t="n">
-        <v>14.8314</v>
+        <v>14.9193</v>
       </c>
       <c r="F92" t="n">
-        <v>14.3141</v>
+        <v>14.717</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>22.1729</v>
+        <v>20.2457</v>
       </c>
       <c r="C93" t="n">
-        <v>18.3873</v>
+        <v>16.8151</v>
       </c>
       <c r="D93" t="n">
-        <v>32.7134</v>
+        <v>33.7748</v>
       </c>
       <c r="E93" t="n">
-        <v>15.3372</v>
+        <v>15.0673</v>
       </c>
       <c r="F93" t="n">
-        <v>15.1439</v>
+        <v>15.2981</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>22.3072</v>
+        <v>20.5583</v>
       </c>
       <c r="C94" t="n">
-        <v>18.998</v>
+        <v>21.448</v>
       </c>
       <c r="D94" t="n">
-        <v>33.4336</v>
+        <v>34.5503</v>
       </c>
       <c r="E94" t="n">
-        <v>23.6021</v>
+        <v>22.2305</v>
       </c>
       <c r="F94" t="n">
-        <v>23.2065</v>
+        <v>22.5599</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>29.921</v>
+        <v>26.0679</v>
       </c>
       <c r="C95" t="n">
-        <v>26.6679</v>
+        <v>21.4768</v>
       </c>
       <c r="D95" t="n">
-        <v>34.1108</v>
+        <v>35.0727</v>
       </c>
       <c r="E95" t="n">
-        <v>23.7445</v>
+        <v>22.6079</v>
       </c>
       <c r="F95" t="n">
-        <v>23.3183</v>
+        <v>22.6822</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>29.8974</v>
+        <v>26.2619</v>
       </c>
       <c r="C96" t="n">
-        <v>26.7033</v>
+        <v>21.5122</v>
       </c>
       <c r="D96" t="n">
-        <v>35.0325</v>
+        <v>35.7025</v>
       </c>
       <c r="E96" t="n">
-        <v>24.0385</v>
+        <v>22.9476</v>
       </c>
       <c r="F96" t="n">
-        <v>23.4758</v>
+        <v>22.7105</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>29.8999</v>
+        <v>26.2463</v>
       </c>
       <c r="C97" t="n">
-        <v>26.7559</v>
+        <v>21.5973</v>
       </c>
       <c r="D97" t="n">
-        <v>36.1915</v>
+        <v>37.0588</v>
       </c>
       <c r="E97" t="n">
-        <v>24.1977</v>
+        <v>22.9928</v>
       </c>
       <c r="F97" t="n">
-        <v>23.5799</v>
+        <v>22.9231</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>29.9432</v>
+        <v>26.2586</v>
       </c>
       <c r="C98" t="n">
-        <v>26.7744</v>
+        <v>21.5684</v>
       </c>
       <c r="D98" t="n">
-        <v>36.8011</v>
+        <v>37.49</v>
       </c>
       <c r="E98" t="n">
-        <v>24.4391</v>
+        <v>23.1992</v>
       </c>
       <c r="F98" t="n">
-        <v>23.6594</v>
+        <v>23.0143</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>29.9356</v>
+        <v>26.2394</v>
       </c>
       <c r="C99" t="n">
-        <v>26.8203</v>
+        <v>21.5913</v>
       </c>
       <c r="D99" t="n">
-        <v>37.7519</v>
+        <v>38.5151</v>
       </c>
       <c r="E99" t="n">
-        <v>24.4003</v>
+        <v>23.3509</v>
       </c>
       <c r="F99" t="n">
-        <v>23.7966</v>
+        <v>23.024</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>30.0183</v>
+        <v>26.2406</v>
       </c>
       <c r="C100" t="n">
-        <v>26.8524</v>
+        <v>21.6914</v>
       </c>
       <c r="D100" t="n">
-        <v>38.857</v>
+        <v>39.4029</v>
       </c>
       <c r="E100" t="n">
-        <v>24.6199</v>
+        <v>23.5579</v>
       </c>
       <c r="F100" t="n">
-        <v>23.9691</v>
+        <v>23.1978</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>29.9914</v>
+        <v>26.2557</v>
       </c>
       <c r="C101" t="n">
-        <v>26.9355</v>
+        <v>21.68</v>
       </c>
       <c r="D101" t="n">
-        <v>39.6803</v>
+        <v>40.4679</v>
       </c>
       <c r="E101" t="n">
-        <v>25.0596</v>
+        <v>23.6722</v>
       </c>
       <c r="F101" t="n">
-        <v>24.1258</v>
+        <v>23.357</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>29.9826</v>
+        <v>26.2893</v>
       </c>
       <c r="C102" t="n">
-        <v>26.9816</v>
+        <v>21.6247</v>
       </c>
       <c r="D102" t="n">
-        <v>40.8413</v>
+        <v>41.6667</v>
       </c>
       <c r="E102" t="n">
-        <v>25.3567</v>
+        <v>23.8684</v>
       </c>
       <c r="F102" t="n">
-        <v>24.295</v>
+        <v>23.6302</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>30.0459</v>
+        <v>26.2787</v>
       </c>
       <c r="C103" t="n">
-        <v>27.0898</v>
+        <v>21.6952</v>
       </c>
       <c r="D103" t="n">
-        <v>41.8984</v>
+        <v>42.723</v>
       </c>
       <c r="E103" t="n">
-        <v>25.6195</v>
+        <v>24.0487</v>
       </c>
       <c r="F103" t="n">
-        <v>24.4341</v>
+        <v>24.58</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>30.0924</v>
+        <v>26.4508</v>
       </c>
       <c r="C104" t="n">
-        <v>27.1197</v>
+        <v>21.7759</v>
       </c>
       <c r="D104" t="n">
-        <v>43.0874</v>
+        <v>43.6669</v>
       </c>
       <c r="E104" t="n">
-        <v>25.8727</v>
+        <v>24.2793</v>
       </c>
       <c r="F104" t="n">
-        <v>24.8674</v>
+        <v>24.1219</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>30.167</v>
+        <v>26.4595</v>
       </c>
       <c r="C105" t="n">
-        <v>27.4284</v>
+        <v>21.8879</v>
       </c>
       <c r="D105" t="n">
-        <v>44.1338</v>
+        <v>44.6309</v>
       </c>
       <c r="E105" t="n">
-        <v>26.0309</v>
+        <v>24.5058</v>
       </c>
       <c r="F105" t="n">
-        <v>25.2308</v>
+        <v>25.0421</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>30.2864</v>
+        <v>26.6149</v>
       </c>
       <c r="C106" t="n">
-        <v>27.5327</v>
+        <v>21.9865</v>
       </c>
       <c r="D106" t="n">
-        <v>45.4685</v>
+        <v>46.1753</v>
       </c>
       <c r="E106" t="n">
-        <v>26.5386</v>
+        <v>24.7948</v>
       </c>
       <c r="F106" t="n">
-        <v>25.5444</v>
+        <v>24.7946</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>30.4499</v>
+        <v>26.763</v>
       </c>
       <c r="C107" t="n">
-        <v>27.9487</v>
+        <v>22.1561</v>
       </c>
       <c r="D107" t="n">
-        <v>38.5288</v>
+        <v>40.1194</v>
       </c>
       <c r="E107" t="n">
-        <v>26.9956</v>
+        <v>25.2577</v>
       </c>
       <c r="F107" t="n">
-        <v>26.2139</v>
+        <v>25.6369</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>30.6155</v>
+        <v>27.0249</v>
       </c>
       <c r="C108" t="n">
-        <v>28.483</v>
+        <v>23.0631</v>
       </c>
       <c r="D108" t="n">
-        <v>39.1404</v>
+        <v>40.3819</v>
       </c>
       <c r="E108" t="n">
-        <v>29.6292</v>
+        <v>29.0132</v>
       </c>
       <c r="F108" t="n">
-        <v>28.9932</v>
+        <v>29.0602</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>30.8754</v>
+        <v>27.4242</v>
       </c>
       <c r="C109" t="n">
-        <v>29.4455</v>
+        <v>23.122</v>
       </c>
       <c r="D109" t="n">
-        <v>40.1823</v>
+        <v>41.0959</v>
       </c>
       <c r="E109" t="n">
-        <v>30.2894</v>
+        <v>29.351</v>
       </c>
       <c r="F109" t="n">
-        <v>29.2678</v>
+        <v>29.3385</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>33.8152</v>
+        <v>29.7837</v>
       </c>
       <c r="C110" t="n">
-        <v>33.7764</v>
+        <v>23.2195</v>
       </c>
       <c r="D110" t="n">
-        <v>40.9089</v>
+        <v>41.7324</v>
       </c>
       <c r="E110" t="n">
-        <v>30.5922</v>
+        <v>29.714</v>
       </c>
       <c r="F110" t="n">
-        <v>29.5537</v>
+        <v>29.5597</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>33.9609</v>
+        <v>29.9386</v>
       </c>
       <c r="C111" t="n">
-        <v>33.6154</v>
+        <v>23.2857</v>
       </c>
       <c r="D111" t="n">
-        <v>41.5856</v>
+        <v>42.5116</v>
       </c>
       <c r="E111" t="n">
-        <v>30.824</v>
+        <v>29.9018</v>
       </c>
       <c r="F111" t="n">
-        <v>29.7209</v>
+        <v>29.4496</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>34.0407</v>
+        <v>29.8874</v>
       </c>
       <c r="C112" t="n">
-        <v>33.7478</v>
+        <v>23.2502</v>
       </c>
       <c r="D112" t="n">
-        <v>41.8706</v>
+        <v>43.2905</v>
       </c>
       <c r="E112" t="n">
-        <v>31.1119</v>
+        <v>29.9756</v>
       </c>
       <c r="F112" t="n">
-        <v>29.3176</v>
+        <v>30.0536</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>33.9002</v>
+        <v>29.5619</v>
       </c>
       <c r="C113" t="n">
-        <v>33.8267</v>
+        <v>23.3592</v>
       </c>
       <c r="D113" t="n">
-        <v>43.5028</v>
+        <v>44.2501</v>
       </c>
       <c r="E113" t="n">
-        <v>31.4207</v>
+        <v>30.436</v>
       </c>
       <c r="F113" t="n">
-        <v>30.1533</v>
+        <v>30.2451</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>34.3096</v>
+        <v>29.3793</v>
       </c>
       <c r="C114" t="n">
-        <v>33.7527</v>
+        <v>23.4213</v>
       </c>
       <c r="D114" t="n">
-        <v>44.2905</v>
+        <v>45.1635</v>
       </c>
       <c r="E114" t="n">
-        <v>31.515</v>
+        <v>30.8242</v>
       </c>
       <c r="F114" t="n">
-        <v>30.2169</v>
+        <v>30.5815</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>34.0053</v>
+        <v>29.8722</v>
       </c>
       <c r="C115" t="n">
-        <v>33.8709</v>
+        <v>23.5057</v>
       </c>
       <c r="D115" t="n">
-        <v>45.2833</v>
+        <v>45.9296</v>
       </c>
       <c r="E115" t="n">
-        <v>32.027</v>
+        <v>31.021</v>
       </c>
       <c r="F115" t="n">
-        <v>30.7942</v>
+        <v>30.8598</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>33.497</v>
+        <v>29.933</v>
       </c>
       <c r="C116" t="n">
-        <v>34.1105</v>
+        <v>23.5934</v>
       </c>
       <c r="D116" t="n">
-        <v>45.6286</v>
+        <v>46.999</v>
       </c>
       <c r="E116" t="n">
-        <v>32.277</v>
+        <v>31.232</v>
       </c>
       <c r="F116" t="n">
-        <v>30.9402</v>
+        <v>30.6196</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>34.159</v>
+        <v>30.0986</v>
       </c>
       <c r="C117" t="n">
-        <v>34.1331</v>
+        <v>23.6387</v>
       </c>
       <c r="D117" t="n">
-        <v>46.8362</v>
+        <v>48.0971</v>
       </c>
       <c r="E117" t="n">
-        <v>32.4579</v>
+        <v>31.4711</v>
       </c>
       <c r="F117" t="n">
-        <v>31.3345</v>
+        <v>31.4887</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>34.1987</v>
+        <v>30.1021</v>
       </c>
       <c r="C118" t="n">
-        <v>34.3041</v>
+        <v>23.7378</v>
       </c>
       <c r="D118" t="n">
-        <v>48.7162</v>
+        <v>49.8198</v>
       </c>
       <c r="E118" t="n">
-        <v>33.1597</v>
+        <v>31.6893</v>
       </c>
       <c r="F118" t="n">
-        <v>31.7865</v>
+        <v>31.9123</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>34.179</v>
+        <v>30.1108</v>
       </c>
       <c r="C119" t="n">
-        <v>34.5332</v>
+        <v>23.9248</v>
       </c>
       <c r="D119" t="n">
-        <v>49.8348</v>
+        <v>51.0852</v>
       </c>
       <c r="E119" t="n">
-        <v>33.5726</v>
+        <v>32.147</v>
       </c>
       <c r="F119" t="n">
-        <v>32.2437</v>
+        <v>32.4854</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>34.432</v>
+        <v>30.3064</v>
       </c>
       <c r="C120" t="n">
-        <v>34.7174</v>
+        <v>24.114</v>
       </c>
       <c r="D120" t="n">
-        <v>51.0287</v>
+        <v>52.2246</v>
       </c>
       <c r="E120" t="n">
-        <v>34.1489</v>
+        <v>32.572</v>
       </c>
       <c r="F120" t="n">
-        <v>33.3987</v>
+        <v>33.0579</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>34.5646</v>
+        <v>30.3951</v>
       </c>
       <c r="C121" t="n">
-        <v>35.1232</v>
+        <v>24.4051</v>
       </c>
       <c r="D121" t="n">
-        <v>41.7292</v>
+        <v>43.0591</v>
       </c>
       <c r="E121" t="n">
-        <v>34.7698</v>
+        <v>32.5839</v>
       </c>
       <c r="F121" t="n">
-        <v>34.1889</v>
+        <v>33.9613</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>34.8426</v>
+        <v>30.5711</v>
       </c>
       <c r="C122" t="n">
-        <v>35.7719</v>
+        <v>25.2828</v>
       </c>
       <c r="D122" t="n">
-        <v>42.1413</v>
+        <v>43.7786</v>
       </c>
       <c r="E122" t="n">
-        <v>35.6622</v>
+        <v>33.0797</v>
       </c>
       <c r="F122" t="n">
-        <v>35.0182</v>
+        <v>35.1284</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>35.1542</v>
+        <v>30.9571</v>
       </c>
       <c r="C123" t="n">
-        <v>36.0892</v>
+        <v>25.3846</v>
       </c>
       <c r="D123" t="n">
-        <v>42.8431</v>
+        <v>43.8297</v>
       </c>
       <c r="E123" t="n">
-        <v>34.183</v>
+        <v>35.185</v>
       </c>
       <c r="F123" t="n">
-        <v>33.8778</v>
+        <v>33.6735</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>43.2891</v>
+        <v>38.1446</v>
       </c>
       <c r="C124" t="n">
-        <v>43.297</v>
+        <v>25.5396</v>
       </c>
       <c r="D124" t="n">
-        <v>44.2278</v>
+        <v>45.255</v>
       </c>
       <c r="E124" t="n">
-        <v>34.8581</v>
+        <v>35.5732</v>
       </c>
       <c r="F124" t="n">
-        <v>34.0459</v>
+        <v>33.7136</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>43.2927</v>
+        <v>38.5128</v>
       </c>
       <c r="C125" t="n">
-        <v>43.3197</v>
+        <v>25.6167</v>
       </c>
       <c r="D125" t="n">
-        <v>44.4342</v>
+        <v>45.9649</v>
       </c>
       <c r="E125" t="n">
-        <v>35.2444</v>
+        <v>35.9075</v>
       </c>
       <c r="F125" t="n">
-        <v>34.1246</v>
+        <v>33.9451</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>43.27</v>
+        <v>38.3359</v>
       </c>
       <c r="C126" t="n">
-        <v>43.7362</v>
+        <v>25.7243</v>
       </c>
       <c r="D126" t="n">
-        <v>44.9856</v>
+        <v>46.5896</v>
       </c>
       <c r="E126" t="n">
-        <v>35.5942</v>
+        <v>36.2813</v>
       </c>
       <c r="F126" t="n">
-        <v>34.4045</v>
+        <v>34.3534</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>43.5803</v>
+        <v>38.4416</v>
       </c>
       <c r="C127" t="n">
-        <v>44.216</v>
+        <v>25.9101</v>
       </c>
       <c r="D127" t="n">
-        <v>46.7846</v>
+        <v>47.412</v>
       </c>
       <c r="E127" t="n">
-        <v>36.0444</v>
+        <v>36.5846</v>
       </c>
       <c r="F127" t="n">
-        <v>34.9697</v>
+        <v>34.7179</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>43.5917</v>
+        <v>38.4252</v>
       </c>
       <c r="C128" t="n">
-        <v>44.2576</v>
+        <v>26.0737</v>
       </c>
       <c r="D128" t="n">
-        <v>47.6935</v>
+        <v>48.128</v>
       </c>
       <c r="E128" t="n">
-        <v>36.3705</v>
+        <v>36.9298</v>
       </c>
       <c r="F128" t="n">
-        <v>34.9786</v>
+        <v>35.0702</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>43.3762</v>
+        <v>38.4414</v>
       </c>
       <c r="C129" t="n">
-        <v>43.6904</v>
+        <v>26.2116</v>
       </c>
       <c r="D129" t="n">
-        <v>48.6391</v>
+        <v>49.5105</v>
       </c>
       <c r="E129" t="n">
-        <v>36.6965</v>
+        <v>37.2571</v>
       </c>
       <c r="F129" t="n">
-        <v>35.5692</v>
+        <v>35.4177</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>43.4455</v>
+        <v>38.5215</v>
       </c>
       <c r="C130" t="n">
-        <v>44.5812</v>
+        <v>26.4482</v>
       </c>
       <c r="D130" t="n">
-        <v>49.3308</v>
+        <v>50.5265</v>
       </c>
       <c r="E130" t="n">
-        <v>36.6359</v>
+        <v>37.6668</v>
       </c>
       <c r="F130" t="n">
-        <v>36.0601</v>
+        <v>35.9998</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>43.5428</v>
+        <v>38.545</v>
       </c>
       <c r="C131" t="n">
-        <v>44.5574</v>
+        <v>26.6063</v>
       </c>
       <c r="D131" t="n">
-        <v>50.5301</v>
+        <v>51.4986</v>
       </c>
       <c r="E131" t="n">
-        <v>37.5419</v>
+        <v>38.0388</v>
       </c>
       <c r="F131" t="n">
-        <v>36.4253</v>
+        <v>36.4372</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>42.5473</v>
+        <v>38.6665</v>
       </c>
       <c r="C132" t="n">
-        <v>44.6327</v>
+        <v>26.7818</v>
       </c>
       <c r="D132" t="n">
-        <v>51.6288</v>
+        <v>52.6228</v>
       </c>
       <c r="E132" t="n">
-        <v>38.0901</v>
+        <v>38.5031</v>
       </c>
       <c r="F132" t="n">
-        <v>37.0842</v>
+        <v>37.0228</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>43.8417</v>
+        <v>38.6881</v>
       </c>
       <c r="C133" t="n">
-        <v>44.9601</v>
+        <v>27.2089</v>
       </c>
       <c r="D133" t="n">
-        <v>52.892</v>
+        <v>53.7423</v>
       </c>
       <c r="E133" t="n">
-        <v>38.575</v>
+        <v>38.9091</v>
       </c>
       <c r="F133" t="n">
-        <v>37.7808</v>
+        <v>37.631</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>43.6968</v>
+        <v>38.8623</v>
       </c>
       <c r="C134" t="n">
-        <v>45.2612</v>
+        <v>27.4228</v>
       </c>
       <c r="D134" t="n">
-        <v>53.8773</v>
+        <v>54.9631</v>
       </c>
       <c r="E134" t="n">
-        <v>39.2795</v>
+        <v>39.4864</v>
       </c>
       <c r="F134" t="n">
-        <v>38.7985</v>
+        <v>38.3291</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>42.957</v>
+        <v>38.2752</v>
       </c>
       <c r="C135" t="n">
-        <v>45.4029</v>
+        <v>27.8575</v>
       </c>
       <c r="D135" t="n">
-        <v>43.3707</v>
+        <v>44.9592</v>
       </c>
       <c r="E135" t="n">
-        <v>40.1109</v>
+        <v>40.2456</v>
       </c>
       <c r="F135" t="n">
-        <v>40.0714</v>
+        <v>39.5887</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>44.0003</v>
+        <v>39.2482</v>
       </c>
       <c r="C136" t="n">
-        <v>46.1662</v>
+        <v>27.5587</v>
       </c>
       <c r="D136" t="n">
-        <v>43.784</v>
+        <v>45.4949</v>
       </c>
       <c r="E136" t="n">
-        <v>41.2711</v>
+        <v>41.19</v>
       </c>
       <c r="F136" t="n">
-        <v>41.4874</v>
+        <v>41.0888</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>44.4298</v>
+        <v>39.806</v>
       </c>
       <c r="C137" t="n">
-        <v>47.0242</v>
+        <v>27.725</v>
       </c>
       <c r="D137" t="n">
-        <v>44.7834</v>
+        <v>45.9045</v>
       </c>
       <c r="E137" t="n">
-        <v>36.9645</v>
+        <v>38.4248</v>
       </c>
       <c r="F137" t="n">
-        <v>36.1637</v>
+        <v>36.1463</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>49.5879</v>
+        <v>44.0982</v>
       </c>
       <c r="C138" t="n">
-        <v>50.0676</v>
+        <v>27.8933</v>
       </c>
       <c r="D138" t="n">
-        <v>45.2057</v>
+        <v>47.0691</v>
       </c>
       <c r="E138" t="n">
-        <v>37.3694</v>
+        <v>38.7587</v>
       </c>
       <c r="F138" t="n">
-        <v>36.4293</v>
+        <v>36.3223</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>49.247</v>
+        <v>44.1154</v>
       </c>
       <c r="C139" t="n">
-        <v>50.1245</v>
+        <v>28.0518</v>
       </c>
       <c r="D139" t="n">
-        <v>46.3953</v>
+        <v>47.6132</v>
       </c>
       <c r="E139" t="n">
-        <v>37.6632</v>
+        <v>39.0844</v>
       </c>
       <c r="F139" t="n">
-        <v>36.6948</v>
+        <v>36.7105</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>49.3307</v>
+        <v>44.1313</v>
       </c>
       <c r="C140" t="n">
-        <v>49.6105</v>
+        <v>28.2001</v>
       </c>
       <c r="D140" t="n">
-        <v>47.5014</v>
+        <v>48.1061</v>
       </c>
       <c r="E140" t="n">
-        <v>38.0285</v>
+        <v>39.4773</v>
       </c>
       <c r="F140" t="n">
-        <v>37.0949</v>
+        <v>36.9849</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>49.7133</v>
+        <v>44.1471</v>
       </c>
       <c r="C141" t="n">
-        <v>50.2909</v>
+        <v>28.4045</v>
       </c>
       <c r="D141" t="n">
-        <v>47.8598</v>
+        <v>49.382</v>
       </c>
       <c r="E141" t="n">
-        <v>38.5706</v>
+        <v>39.7917</v>
       </c>
       <c r="F141" t="n">
-        <v>37.5623</v>
+        <v>37.1801</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>49.7858</v>
+        <v>44.1986</v>
       </c>
       <c r="C142" t="n">
-        <v>50.3661</v>
+        <v>28.6145</v>
       </c>
       <c r="D142" t="n">
-        <v>49.3062</v>
+        <v>49.9659</v>
       </c>
       <c r="E142" t="n">
-        <v>38.9728</v>
+        <v>40.1834</v>
       </c>
       <c r="F142" t="n">
-        <v>37.9786</v>
+        <v>37.5564</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>49.8851</v>
+        <v>43.5373</v>
       </c>
       <c r="C143" t="n">
-        <v>50.5508</v>
+        <v>28.8174</v>
       </c>
       <c r="D143" t="n">
-        <v>49.5605</v>
+        <v>51.3086</v>
       </c>
       <c r="E143" t="n">
-        <v>39.2054</v>
+        <v>40.5128</v>
       </c>
       <c r="F143" t="n">
-        <v>38.4143</v>
+        <v>38.024</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Scattered successful looukp.xlsx
+++ b/clang-x64/Scattered successful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>3.24715</v>
+        <v>3.14974</v>
       </c>
       <c r="C2" t="n">
-        <v>2.62469</v>
+        <v>2.50136</v>
       </c>
       <c r="D2" t="n">
-        <v>7.04187</v>
+        <v>7.12657</v>
       </c>
       <c r="E2" t="n">
-        <v>3.24972</v>
+        <v>3.19139</v>
       </c>
       <c r="F2" t="n">
-        <v>3.32863</v>
+        <v>3.25974</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>3.22217</v>
+        <v>3.17228</v>
       </c>
       <c r="C3" t="n">
-        <v>2.60201</v>
+        <v>2.55042</v>
       </c>
       <c r="D3" t="n">
-        <v>7.805</v>
+        <v>7.89143</v>
       </c>
       <c r="E3" t="n">
-        <v>3.26572</v>
+        <v>3.10488</v>
       </c>
       <c r="F3" t="n">
-        <v>3.31642</v>
+        <v>3.28496</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>3.23222</v>
+        <v>2.949</v>
       </c>
       <c r="C4" t="n">
-        <v>2.61646</v>
+        <v>2.47997</v>
       </c>
       <c r="D4" t="n">
-        <v>8.668189999999999</v>
+        <v>8.666740000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>3.28815</v>
+        <v>3.09599</v>
       </c>
       <c r="F4" t="n">
-        <v>3.26437</v>
+        <v>3.37306</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.31046</v>
+        <v>3.21146</v>
       </c>
       <c r="C5" t="n">
-        <v>2.67581</v>
+        <v>2.5783</v>
       </c>
       <c r="D5" t="n">
-        <v>9.24802</v>
+        <v>9.372210000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>3.31435</v>
+        <v>3.14622</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3303</v>
+        <v>3.39274</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>3.29391</v>
+        <v>3.17833</v>
       </c>
       <c r="C6" t="n">
-        <v>2.67399</v>
+        <v>2.58216</v>
       </c>
       <c r="D6" t="n">
-        <v>9.93524</v>
+        <v>10.0093</v>
       </c>
       <c r="E6" t="n">
-        <v>3.21338</v>
+        <v>3.22824</v>
       </c>
       <c r="F6" t="n">
-        <v>3.41979</v>
+        <v>3.33747</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>3.12787</v>
+        <v>3.23599</v>
       </c>
       <c r="C7" t="n">
-        <v>2.62913</v>
+        <v>2.65032</v>
       </c>
       <c r="D7" t="n">
-        <v>6.13737</v>
+        <v>6.10527</v>
       </c>
       <c r="E7" t="n">
-        <v>3.35207</v>
+        <v>3.80674</v>
       </c>
       <c r="F7" t="n">
-        <v>3.43364</v>
+        <v>3.36962</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>3.22523</v>
+        <v>3.24991</v>
       </c>
       <c r="C8" t="n">
-        <v>2.98291</v>
+        <v>3.03173</v>
       </c>
       <c r="D8" t="n">
-        <v>6.34276</v>
+        <v>6.32032</v>
       </c>
       <c r="E8" t="n">
-        <v>3.44342</v>
+        <v>3.88675</v>
       </c>
       <c r="F8" t="n">
-        <v>3.60383</v>
+        <v>3.39784</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>3.33011</v>
+        <v>3.07679</v>
       </c>
       <c r="C9" t="n">
-        <v>2.92878</v>
+        <v>3.18735</v>
       </c>
       <c r="D9" t="n">
-        <v>7.00254</v>
+        <v>6.99772</v>
       </c>
       <c r="E9" t="n">
-        <v>3.94631</v>
+        <v>3.91409</v>
       </c>
       <c r="F9" t="n">
-        <v>3.48692</v>
+        <v>3.43481</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>3.93827</v>
+        <v>4.04715</v>
       </c>
       <c r="C10" t="n">
-        <v>3.00725</v>
+        <v>3.20415</v>
       </c>
       <c r="D10" t="n">
-        <v>7.45146</v>
+        <v>7.43546</v>
       </c>
       <c r="E10" t="n">
-        <v>3.99165</v>
+        <v>3.95147</v>
       </c>
       <c r="F10" t="n">
-        <v>3.52997</v>
+        <v>3.45692</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>4.00698</v>
+        <v>4.24653</v>
       </c>
       <c r="C11" t="n">
-        <v>3.00179</v>
+        <v>3.06305</v>
       </c>
       <c r="D11" t="n">
-        <v>7.9952</v>
+        <v>7.95412</v>
       </c>
       <c r="E11" t="n">
-        <v>4.01257</v>
+        <v>4.263</v>
       </c>
       <c r="F11" t="n">
-        <v>3.54308</v>
+        <v>3.50358</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>4.01389</v>
+        <v>3.97542</v>
       </c>
       <c r="C12" t="n">
-        <v>3.01447</v>
+        <v>3.15875</v>
       </c>
       <c r="D12" t="n">
-        <v>8.653840000000001</v>
+        <v>8.62452</v>
       </c>
       <c r="E12" t="n">
-        <v>3.99852</v>
+        <v>4.30914</v>
       </c>
       <c r="F12" t="n">
-        <v>3.55928</v>
+        <v>3.51648</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>3.91687</v>
+        <v>4.27534</v>
       </c>
       <c r="C13" t="n">
-        <v>2.95485</v>
+        <v>3.10544</v>
       </c>
       <c r="D13" t="n">
-        <v>9.15193</v>
+        <v>9.080069999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>4.0404</v>
+        <v>4.16242</v>
       </c>
       <c r="F13" t="n">
-        <v>3.6167</v>
+        <v>3.56851</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>4.27141</v>
+        <v>4.35761</v>
       </c>
       <c r="C14" t="n">
-        <v>3.09504</v>
+        <v>3.1704</v>
       </c>
       <c r="D14" t="n">
-        <v>9.702310000000001</v>
+        <v>9.662089999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>4.11902</v>
+        <v>4.07</v>
       </c>
       <c r="F14" t="n">
-        <v>3.63377</v>
+        <v>3.56363</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>3.94958</v>
+        <v>4.29168</v>
       </c>
       <c r="C15" t="n">
-        <v>3.07476</v>
+        <v>3.15009</v>
       </c>
       <c r="D15" t="n">
-        <v>10.2047</v>
+        <v>10.1338</v>
       </c>
       <c r="E15" t="n">
-        <v>4.05271</v>
+        <v>4.17096</v>
       </c>
       <c r="F15" t="n">
-        <v>3.65729</v>
+        <v>3.60705</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>4.26067</v>
+        <v>4.37781</v>
       </c>
       <c r="C16" t="n">
-        <v>3.13685</v>
+        <v>3.21256</v>
       </c>
       <c r="D16" t="n">
-        <v>10.6702</v>
+        <v>10.6088</v>
       </c>
       <c r="E16" t="n">
-        <v>4.11668</v>
+        <v>4.51033</v>
       </c>
       <c r="F16" t="n">
-        <v>3.66987</v>
+        <v>3.63345</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>4.38262</v>
+        <v>4.30951</v>
       </c>
       <c r="C17" t="n">
-        <v>3.14764</v>
+        <v>3.19893</v>
       </c>
       <c r="D17" t="n">
-        <v>11.1913</v>
+        <v>11.1407</v>
       </c>
       <c r="E17" t="n">
-        <v>4.23051</v>
+        <v>4.15607</v>
       </c>
       <c r="F17" t="n">
-        <v>3.68882</v>
+        <v>3.62993</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>4.31868</v>
+        <v>4.32802</v>
       </c>
       <c r="C18" t="n">
-        <v>3.20344</v>
+        <v>3.23256</v>
       </c>
       <c r="D18" t="n">
-        <v>11.6419</v>
+        <v>11.5878</v>
       </c>
       <c r="E18" t="n">
-        <v>4.2811</v>
+        <v>4.52954</v>
       </c>
       <c r="F18" t="n">
-        <v>3.70198</v>
+        <v>3.66275</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>4.33114</v>
+        <v>4.33735</v>
       </c>
       <c r="C19" t="n">
-        <v>3.23568</v>
+        <v>3.26835</v>
       </c>
       <c r="D19" t="n">
-        <v>12.1273</v>
+        <v>12.0728</v>
       </c>
       <c r="E19" t="n">
-        <v>4.20086</v>
+        <v>4.30975</v>
       </c>
       <c r="F19" t="n">
-        <v>3.77838</v>
+        <v>3.69719</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>4.41272</v>
+        <v>4.35838</v>
       </c>
       <c r="C20" t="n">
-        <v>3.23901</v>
+        <v>3.29446</v>
       </c>
       <c r="D20" t="n">
-        <v>12.4448</v>
+        <v>12.3863</v>
       </c>
       <c r="E20" t="n">
-        <v>4.38901</v>
+        <v>4.41041</v>
       </c>
       <c r="F20" t="n">
-        <v>3.83611</v>
+        <v>3.90003</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>4.36502</v>
+        <v>4.37961</v>
       </c>
       <c r="C21" t="n">
-        <v>3.28763</v>
+        <v>3.34038</v>
       </c>
       <c r="D21" t="n">
-        <v>8.67605</v>
+        <v>8.73128</v>
       </c>
       <c r="E21" t="n">
-        <v>4.42078</v>
+        <v>3.88916</v>
       </c>
       <c r="F21" t="n">
-        <v>4.46173</v>
+        <v>4.18994</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>4.36101</v>
+        <v>4.48737</v>
       </c>
       <c r="C22" t="n">
-        <v>3.10978</v>
+        <v>2.99017</v>
       </c>
       <c r="D22" t="n">
-        <v>8.99147</v>
+        <v>9.09071</v>
       </c>
       <c r="E22" t="n">
-        <v>4.84981</v>
+        <v>3.99474</v>
       </c>
       <c r="F22" t="n">
-        <v>4.78078</v>
+        <v>4.31746</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>4.39101</v>
+        <v>4.46783</v>
       </c>
       <c r="C23" t="n">
-        <v>2.96408</v>
+        <v>3.00489</v>
       </c>
       <c r="D23" t="n">
-        <v>9.374219999999999</v>
+        <v>9.490500000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>3.77118</v>
+        <v>3.99396</v>
       </c>
       <c r="F23" t="n">
-        <v>4.22503</v>
+        <v>4.25626</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>4.37853</v>
+        <v>4.71675</v>
       </c>
       <c r="C24" t="n">
-        <v>2.99111</v>
+        <v>3.02143</v>
       </c>
       <c r="D24" t="n">
-        <v>9.75197</v>
+        <v>9.82525</v>
       </c>
       <c r="E24" t="n">
-        <v>3.90185</v>
+        <v>4.04911</v>
       </c>
       <c r="F24" t="n">
-        <v>4.34062</v>
+        <v>4.29405</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>4.52517</v>
+        <v>4.75883</v>
       </c>
       <c r="C25" t="n">
-        <v>3.08101</v>
+        <v>3.03081</v>
       </c>
       <c r="D25" t="n">
-        <v>10.1393</v>
+        <v>10.2381</v>
       </c>
       <c r="E25" t="n">
-        <v>3.835</v>
+        <v>3.99697</v>
       </c>
       <c r="F25" t="n">
-        <v>4.27838</v>
+        <v>4.37586</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>4.51639</v>
+        <v>4.76014</v>
       </c>
       <c r="C26" t="n">
-        <v>3.12487</v>
+        <v>3.04222</v>
       </c>
       <c r="D26" t="n">
-        <v>10.5814</v>
+        <v>10.6177</v>
       </c>
       <c r="E26" t="n">
-        <v>3.95242</v>
+        <v>4.10649</v>
       </c>
       <c r="F26" t="n">
-        <v>4.20367</v>
+        <v>4.11602</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>4.41787</v>
+        <v>4.48167</v>
       </c>
       <c r="C27" t="n">
-        <v>3.14613</v>
+        <v>3.02802</v>
       </c>
       <c r="D27" t="n">
-        <v>10.9417</v>
+        <v>11.0577</v>
       </c>
       <c r="E27" t="n">
-        <v>4.03377</v>
+        <v>3.97933</v>
       </c>
       <c r="F27" t="n">
-        <v>4.23997</v>
+        <v>4.14742</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>4.55058</v>
+        <v>4.566</v>
       </c>
       <c r="C28" t="n">
-        <v>3.12617</v>
+        <v>3.0403</v>
       </c>
       <c r="D28" t="n">
-        <v>11.4051</v>
+        <v>11.4274</v>
       </c>
       <c r="E28" t="n">
-        <v>4.05245</v>
+        <v>4.02098</v>
       </c>
       <c r="F28" t="n">
-        <v>4.25711</v>
+        <v>4.17699</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>4.42212</v>
+        <v>4.52513</v>
       </c>
       <c r="C29" t="n">
-        <v>3.18147</v>
+        <v>3.0684</v>
       </c>
       <c r="D29" t="n">
-        <v>11.7925</v>
+        <v>11.8291</v>
       </c>
       <c r="E29" t="n">
-        <v>4.04433</v>
+        <v>4.04207</v>
       </c>
       <c r="F29" t="n">
-        <v>4.30377</v>
+        <v>4.22106</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>4.45814</v>
+        <v>4.67334</v>
       </c>
       <c r="C30" t="n">
-        <v>3.2021</v>
+        <v>3.22293</v>
       </c>
       <c r="D30" t="n">
-        <v>12.1816</v>
+        <v>12.2454</v>
       </c>
       <c r="E30" t="n">
-        <v>4.12482</v>
+        <v>4.08493</v>
       </c>
       <c r="F30" t="n">
-        <v>4.33221</v>
+        <v>4.24624</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>4.58076</v>
+        <v>4.8204</v>
       </c>
       <c r="C31" t="n">
-        <v>3.22586</v>
+        <v>3.14212</v>
       </c>
       <c r="D31" t="n">
-        <v>12.6272</v>
+        <v>12.6746</v>
       </c>
       <c r="E31" t="n">
-        <v>4.11908</v>
+        <v>4.27236</v>
       </c>
       <c r="F31" t="n">
-        <v>4.37804</v>
+        <v>4.28219</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>4.36538</v>
+        <v>4.58541</v>
       </c>
       <c r="C32" t="n">
-        <v>3.12363</v>
+        <v>3.14836</v>
       </c>
       <c r="D32" t="n">
-        <v>12.8954</v>
+        <v>13.0138</v>
       </c>
       <c r="E32" t="n">
-        <v>4.32515</v>
+        <v>4.1582</v>
       </c>
       <c r="F32" t="n">
-        <v>4.63618</v>
+        <v>4.31884</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.54298</v>
+        <v>4.60002</v>
       </c>
       <c r="C33" t="n">
-        <v>3.17304</v>
+        <v>3.18211</v>
       </c>
       <c r="D33" t="n">
-        <v>13.3478</v>
+        <v>13.413</v>
       </c>
       <c r="E33" t="n">
-        <v>4.24498</v>
+        <v>4.37061</v>
       </c>
       <c r="F33" t="n">
-        <v>4.49993</v>
+        <v>4.4011</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>4.6262</v>
+        <v>4.64066</v>
       </c>
       <c r="C34" t="n">
-        <v>3.28421</v>
+        <v>3.2131</v>
       </c>
       <c r="D34" t="n">
-        <v>13.6885</v>
+        <v>13.7295</v>
       </c>
       <c r="E34" t="n">
-        <v>4.30478</v>
+        <v>4.33489</v>
       </c>
       <c r="F34" t="n">
-        <v>4.38857</v>
+        <v>4.45881</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>4.50359</v>
+        <v>4.92296</v>
       </c>
       <c r="C35" t="n">
-        <v>3.30454</v>
+        <v>3.38297</v>
       </c>
       <c r="D35" t="n">
-        <v>9.34924</v>
+        <v>9.379799999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>4.5909</v>
+        <v>4.14217</v>
       </c>
       <c r="F35" t="n">
-        <v>5.20322</v>
+        <v>4.24018</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>4.55198</v>
+        <v>4.77989</v>
       </c>
       <c r="C36" t="n">
-        <v>3.33737</v>
+        <v>3.32384</v>
       </c>
       <c r="D36" t="n">
-        <v>9.60144</v>
+        <v>9.61469</v>
       </c>
       <c r="E36" t="n">
-        <v>5.13114</v>
+        <v>4.17094</v>
       </c>
       <c r="F36" t="n">
-        <v>5.73184</v>
+        <v>4.26786</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>4.78692</v>
+        <v>4.74295</v>
       </c>
       <c r="C37" t="n">
-        <v>3.10454</v>
+        <v>3.5033</v>
       </c>
       <c r="D37" t="n">
-        <v>9.794829999999999</v>
+        <v>9.817830000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>4.19264</v>
+        <v>4.20528</v>
       </c>
       <c r="F37" t="n">
-        <v>4.41854</v>
+        <v>4.29353</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>4.80652</v>
+        <v>4.8771</v>
       </c>
       <c r="C38" t="n">
-        <v>3.29881</v>
+        <v>3.34618</v>
       </c>
       <c r="D38" t="n">
-        <v>10.1144</v>
+        <v>10.1405</v>
       </c>
       <c r="E38" t="n">
-        <v>4.19515</v>
+        <v>4.22585</v>
       </c>
       <c r="F38" t="n">
-        <v>4.44134</v>
+        <v>4.3256</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>4.46912</v>
+        <v>4.74419</v>
       </c>
       <c r="C39" t="n">
-        <v>3.55423</v>
+        <v>3.25996</v>
       </c>
       <c r="D39" t="n">
-        <v>10.4459</v>
+        <v>10.4652</v>
       </c>
       <c r="E39" t="n">
-        <v>4.58934</v>
+        <v>4.25996</v>
       </c>
       <c r="F39" t="n">
-        <v>4.35525</v>
+        <v>4.35243</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>4.42086</v>
+        <v>4.77071</v>
       </c>
       <c r="C40" t="n">
-        <v>3.60663</v>
+        <v>3.26016</v>
       </c>
       <c r="D40" t="n">
-        <v>10.7779</v>
+        <v>10.7989</v>
       </c>
       <c r="E40" t="n">
-        <v>4.26913</v>
+        <v>4.29639</v>
       </c>
       <c r="F40" t="n">
-        <v>4.50309</v>
+        <v>4.37407</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>4.42351</v>
+        <v>4.6142</v>
       </c>
       <c r="C41" t="n">
-        <v>3.64159</v>
+        <v>3.56587</v>
       </c>
       <c r="D41" t="n">
-        <v>11.1324</v>
+        <v>11.147</v>
       </c>
       <c r="E41" t="n">
-        <v>4.29826</v>
+        <v>4.64564</v>
       </c>
       <c r="F41" t="n">
-        <v>4.52092</v>
+        <v>4.40401</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>4.4658</v>
+        <v>4.62549</v>
       </c>
       <c r="C42" t="n">
-        <v>3.65208</v>
+        <v>3.53855</v>
       </c>
       <c r="D42" t="n">
-        <v>11.5002</v>
+        <v>11.5304</v>
       </c>
       <c r="E42" t="n">
-        <v>4.33474</v>
+        <v>4.36597</v>
       </c>
       <c r="F42" t="n">
-        <v>4.56027</v>
+        <v>4.4539</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>4.62213</v>
+        <v>4.63986</v>
       </c>
       <c r="C43" t="n">
-        <v>3.63781</v>
+        <v>3.64108</v>
       </c>
       <c r="D43" t="n">
-        <v>11.8874</v>
+        <v>11.8977</v>
       </c>
       <c r="E43" t="n">
-        <v>4.74215</v>
+        <v>4.73231</v>
       </c>
       <c r="F43" t="n">
-        <v>4.49161</v>
+        <v>4.48476</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>4.57732</v>
+        <v>4.70111</v>
       </c>
       <c r="C44" t="n">
-        <v>3.66392</v>
+        <v>3.5258</v>
       </c>
       <c r="D44" t="n">
-        <v>12.276</v>
+        <v>12.3009</v>
       </c>
       <c r="E44" t="n">
-        <v>4.41885</v>
+        <v>4.45024</v>
       </c>
       <c r="F44" t="n">
-        <v>4.64297</v>
+        <v>4.53054</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>4.70183</v>
+        <v>4.79793</v>
       </c>
       <c r="C45" t="n">
-        <v>3.65002</v>
+        <v>3.70524</v>
       </c>
       <c r="D45" t="n">
-        <v>12.6703</v>
+        <v>12.689</v>
       </c>
       <c r="E45" t="n">
-        <v>4.81638</v>
+        <v>4.84403</v>
       </c>
       <c r="F45" t="n">
-        <v>4.75312</v>
+        <v>4.58355</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.5627</v>
+        <v>4.75749</v>
       </c>
       <c r="C46" t="n">
-        <v>3.74417</v>
+        <v>3.76474</v>
       </c>
       <c r="D46" t="n">
-        <v>13.0333</v>
+        <v>13.052</v>
       </c>
       <c r="E46" t="n">
-        <v>4.87494</v>
+        <v>4.90295</v>
       </c>
       <c r="F46" t="n">
-        <v>4.84694</v>
+        <v>4.66436</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.55446</v>
+        <v>4.72048</v>
       </c>
       <c r="C47" t="n">
-        <v>3.83276</v>
+        <v>3.72916</v>
       </c>
       <c r="D47" t="n">
-        <v>13.3694</v>
+        <v>13.3918</v>
       </c>
       <c r="E47" t="n">
-        <v>5.00087</v>
+        <v>5.06963</v>
       </c>
       <c r="F47" t="n">
-        <v>5.16286</v>
+        <v>4.82006</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>4.56729</v>
+        <v>4.80766</v>
       </c>
       <c r="C48" t="n">
-        <v>3.64564</v>
+        <v>3.89295</v>
       </c>
       <c r="D48" t="n">
-        <v>13.7483</v>
+        <v>13.7742</v>
       </c>
       <c r="E48" t="n">
-        <v>5.14376</v>
+        <v>5.30954</v>
       </c>
       <c r="F48" t="n">
-        <v>5.09448</v>
+        <v>5.04121</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>4.95139</v>
+        <v>4.78873</v>
       </c>
       <c r="C49" t="n">
-        <v>3.53272</v>
+        <v>3.87545</v>
       </c>
       <c r="D49" t="n">
-        <v>14.0548</v>
+        <v>14.1155</v>
       </c>
       <c r="E49" t="n">
-        <v>5.46326</v>
+        <v>5.62636</v>
       </c>
       <c r="F49" t="n">
-        <v>5.53951</v>
+        <v>5.47714</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>4.81884</v>
+        <v>4.96567</v>
       </c>
       <c r="C50" t="n">
-        <v>4.1062</v>
+        <v>4.007</v>
       </c>
       <c r="D50" t="n">
-        <v>10.5139</v>
+        <v>10.9249</v>
       </c>
       <c r="E50" t="n">
-        <v>5.6548</v>
+        <v>4.52047</v>
       </c>
       <c r="F50" t="n">
-        <v>6.11903</v>
+        <v>5.58495</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>5.95564</v>
+        <v>5.38367</v>
       </c>
       <c r="C51" t="n">
-        <v>3.56691</v>
+        <v>3.54715</v>
       </c>
       <c r="D51" t="n">
-        <v>10.8134</v>
+        <v>11.3797</v>
       </c>
       <c r="E51" t="n">
-        <v>4.50914</v>
+        <v>4.5474</v>
       </c>
       <c r="F51" t="n">
-        <v>4.67532</v>
+        <v>5.55206</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>6.49047</v>
+        <v>6.13883</v>
       </c>
       <c r="C52" t="n">
-        <v>3.58152</v>
+        <v>3.75735</v>
       </c>
       <c r="D52" t="n">
-        <v>11.2011</v>
+        <v>11.8697</v>
       </c>
       <c r="E52" t="n">
-        <v>4.53571</v>
+        <v>4.58563</v>
       </c>
       <c r="F52" t="n">
-        <v>4.81213</v>
+        <v>4.90337</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>5.14623</v>
+        <v>5.5528</v>
       </c>
       <c r="C53" t="n">
-        <v>3.62146</v>
+        <v>3.5613</v>
       </c>
       <c r="D53" t="n">
-        <v>11.3267</v>
+        <v>12.1409</v>
       </c>
       <c r="E53" t="n">
-        <v>4.59433</v>
+        <v>4.61148</v>
       </c>
       <c r="F53" t="n">
-        <v>4.73767</v>
+        <v>5.69415</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>5.13172</v>
+        <v>5.47838</v>
       </c>
       <c r="C54" t="n">
-        <v>3.58939</v>
+        <v>3.55925</v>
       </c>
       <c r="D54" t="n">
-        <v>12.0023</v>
+        <v>12.8941</v>
       </c>
       <c r="E54" t="n">
-        <v>4.5571</v>
+        <v>4.66307</v>
       </c>
       <c r="F54" t="n">
-        <v>4.7856</v>
+        <v>5.62406</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>5.13863</v>
+        <v>5.49962</v>
       </c>
       <c r="C55" t="n">
-        <v>3.61799</v>
+        <v>3.61807</v>
       </c>
       <c r="D55" t="n">
-        <v>12.474</v>
+        <v>13.6874</v>
       </c>
       <c r="E55" t="n">
-        <v>4.7044</v>
+        <v>4.65512</v>
       </c>
       <c r="F55" t="n">
-        <v>5.04318</v>
+        <v>4.88072</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>5.24525</v>
+        <v>5.21187</v>
       </c>
       <c r="C56" t="n">
-        <v>3.6373</v>
+        <v>3.74221</v>
       </c>
       <c r="D56" t="n">
-        <v>12.7589</v>
+        <v>13.2169</v>
       </c>
       <c r="E56" t="n">
-        <v>4.76337</v>
+        <v>4.74152</v>
       </c>
       <c r="F56" t="n">
-        <v>4.99011</v>
+        <v>5.91399</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>5.46529</v>
+        <v>5.54533</v>
       </c>
       <c r="C57" t="n">
-        <v>3.61243</v>
+        <v>3.66227</v>
       </c>
       <c r="D57" t="n">
-        <v>13.4919</v>
+        <v>15.7688</v>
       </c>
       <c r="E57" t="n">
-        <v>4.76793</v>
+        <v>4.75858</v>
       </c>
       <c r="F57" t="n">
-        <v>5.15801</v>
+        <v>5.20428</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>5.17193</v>
+        <v>5.56717</v>
       </c>
       <c r="C58" t="n">
-        <v>3.70242</v>
+        <v>3.70923</v>
       </c>
       <c r="D58" t="n">
-        <v>14.6693</v>
+        <v>16.6429</v>
       </c>
       <c r="E58" t="n">
-        <v>4.83653</v>
+        <v>5.02927</v>
       </c>
       <c r="F58" t="n">
-        <v>5.23825</v>
+        <v>5.23675</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>5.15973</v>
+        <v>5.61232</v>
       </c>
       <c r="C59" t="n">
-        <v>3.71243</v>
+        <v>3.71399</v>
       </c>
       <c r="D59" t="n">
-        <v>15.1475</v>
+        <v>16.2701</v>
       </c>
       <c r="E59" t="n">
-        <v>4.90973</v>
+        <v>4.97015</v>
       </c>
       <c r="F59" t="n">
-        <v>5.20895</v>
+        <v>5.86988</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>5.28327</v>
+        <v>5.24965</v>
       </c>
       <c r="C60" t="n">
-        <v>3.97099</v>
+        <v>3.78291</v>
       </c>
       <c r="D60" t="n">
-        <v>15.5278</v>
+        <v>16.596</v>
       </c>
       <c r="E60" t="n">
-        <v>5.00018</v>
+        <v>5.1475</v>
       </c>
       <c r="F60" t="n">
-        <v>5.73892</v>
+        <v>6.22378</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>5.22756</v>
+        <v>5.70478</v>
       </c>
       <c r="C61" t="n">
-        <v>3.81387</v>
+        <v>3.75648</v>
       </c>
       <c r="D61" t="n">
-        <v>15.8725</v>
+        <v>17.3059</v>
       </c>
       <c r="E61" t="n">
-        <v>5.10171</v>
+        <v>5.30732</v>
       </c>
       <c r="F61" t="n">
-        <v>5.9279</v>
+        <v>6.45032</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>5.43393</v>
+        <v>5.3482</v>
       </c>
       <c r="C62" t="n">
-        <v>4.01929</v>
+        <v>4.11296</v>
       </c>
       <c r="D62" t="n">
-        <v>16.8348</v>
+        <v>17.8171</v>
       </c>
       <c r="E62" t="n">
-        <v>5.30344</v>
+        <v>5.4999</v>
       </c>
       <c r="F62" t="n">
-        <v>6.24664</v>
+        <v>6.4273</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>5.51238</v>
+        <v>5.46341</v>
       </c>
       <c r="C63" t="n">
-        <v>3.97684</v>
+        <v>3.98778</v>
       </c>
       <c r="D63" t="n">
-        <v>16.7814</v>
+        <v>17.8713</v>
       </c>
       <c r="E63" t="n">
-        <v>5.56393</v>
+        <v>5.77833</v>
       </c>
       <c r="F63" t="n">
-        <v>6.39499</v>
+        <v>7.30064</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>5.6595</v>
+        <v>5.97205</v>
       </c>
       <c r="C64" t="n">
-        <v>4.22421</v>
+        <v>4.06378</v>
       </c>
       <c r="D64" t="n">
-        <v>11.6079</v>
+        <v>11.8631</v>
       </c>
       <c r="E64" t="n">
-        <v>5.92575</v>
+        <v>4.93038</v>
       </c>
       <c r="F64" t="n">
-        <v>6.88469</v>
+        <v>5.9048</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>5.88066</v>
+        <v>6.19494</v>
       </c>
       <c r="C65" t="n">
-        <v>5.5398</v>
+        <v>4.95856</v>
       </c>
       <c r="D65" t="n">
-        <v>12.0642</v>
+        <v>12.7954</v>
       </c>
       <c r="E65" t="n">
-        <v>6.51223</v>
+        <v>4.94584</v>
       </c>
       <c r="F65" t="n">
-        <v>7.44002</v>
+        <v>6.00147</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>6.19027</v>
+        <v>6.62203</v>
       </c>
       <c r="C66" t="n">
-        <v>5.46658</v>
+        <v>5.00017</v>
       </c>
       <c r="D66" t="n">
-        <v>13.2592</v>
+        <v>13.7182</v>
       </c>
       <c r="E66" t="n">
-        <v>5.18076</v>
+        <v>5.03432</v>
       </c>
       <c r="F66" t="n">
-        <v>5.7287</v>
+        <v>6.23337</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>7.80946</v>
+        <v>7.08455</v>
       </c>
       <c r="C67" t="n">
-        <v>5.82916</v>
+        <v>5.09184</v>
       </c>
       <c r="D67" t="n">
-        <v>14.2923</v>
+        <v>14.8642</v>
       </c>
       <c r="E67" t="n">
-        <v>4.9772</v>
+        <v>5.09292</v>
       </c>
       <c r="F67" t="n">
-        <v>5.88758</v>
+        <v>6.43752</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>8.355560000000001</v>
+        <v>7.12462</v>
       </c>
       <c r="C68" t="n">
-        <v>6.12859</v>
+        <v>5.19413</v>
       </c>
       <c r="D68" t="n">
-        <v>15.3325</v>
+        <v>16.0759</v>
       </c>
       <c r="E68" t="n">
-        <v>5.1687</v>
+        <v>5.30384</v>
       </c>
       <c r="F68" t="n">
-        <v>6.10565</v>
+        <v>6.6025</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>7.34508</v>
+        <v>7.28394</v>
       </c>
       <c r="C69" t="n">
-        <v>5.41991</v>
+        <v>5.50582</v>
       </c>
       <c r="D69" t="n">
-        <v>16.1614</v>
+        <v>16.5617</v>
       </c>
       <c r="E69" t="n">
-        <v>5.38756</v>
+        <v>5.27844</v>
       </c>
       <c r="F69" t="n">
-        <v>6.2168</v>
+        <v>6.68449</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>7.56529</v>
+        <v>8.34999</v>
       </c>
       <c r="C70" t="n">
-        <v>5.69758</v>
+        <v>6.60674</v>
       </c>
       <c r="D70" t="n">
-        <v>16.4523</v>
+        <v>16.569</v>
       </c>
       <c r="E70" t="n">
-        <v>5.31048</v>
+        <v>5.29682</v>
       </c>
       <c r="F70" t="n">
-        <v>6.33475</v>
+        <v>6.81663</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>7.6359</v>
+        <v>8.731260000000001</v>
       </c>
       <c r="C71" t="n">
-        <v>5.78626</v>
+        <v>6.97931</v>
       </c>
       <c r="D71" t="n">
-        <v>17.0775</v>
+        <v>17.3308</v>
       </c>
       <c r="E71" t="n">
-        <v>5.80141</v>
+        <v>6.04575</v>
       </c>
       <c r="F71" t="n">
-        <v>6.48358</v>
+        <v>6.51822</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>7.64993</v>
+        <v>7.22007</v>
       </c>
       <c r="C72" t="n">
-        <v>5.78804</v>
+        <v>5.34253</v>
       </c>
       <c r="D72" t="n">
-        <v>17.3448</v>
+        <v>18.2277</v>
       </c>
       <c r="E72" t="n">
-        <v>5.90716</v>
+        <v>6.1658</v>
       </c>
       <c r="F72" t="n">
-        <v>6.69249</v>
+        <v>6.666</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>8.524760000000001</v>
+        <v>7.71005</v>
       </c>
       <c r="C73" t="n">
-        <v>6.4368</v>
+        <v>5.97779</v>
       </c>
       <c r="D73" t="n">
-        <v>17.8451</v>
+        <v>19.1217</v>
       </c>
       <c r="E73" t="n">
-        <v>6.03828</v>
+        <v>6.30815</v>
       </c>
       <c r="F73" t="n">
-        <v>6.87528</v>
+        <v>6.89444</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>8.412089999999999</v>
+        <v>7.51305</v>
       </c>
       <c r="C74" t="n">
-        <v>6.4473</v>
+        <v>5.68511</v>
       </c>
       <c r="D74" t="n">
-        <v>18.6604</v>
+        <v>19.9761</v>
       </c>
       <c r="E74" t="n">
-        <v>7.1774</v>
+        <v>7.73012</v>
       </c>
       <c r="F74" t="n">
-        <v>7.02023</v>
+        <v>7.27202</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>9.791919999999999</v>
+        <v>11.1016</v>
       </c>
       <c r="C75" t="n">
-        <v>7.63181</v>
+        <v>9.0488</v>
       </c>
       <c r="D75" t="n">
-        <v>19.7204</v>
+        <v>19.8819</v>
       </c>
       <c r="E75" t="n">
-        <v>7.15838</v>
+        <v>8.12336</v>
       </c>
       <c r="F75" t="n">
-        <v>7.26687</v>
+        <v>7.36937</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>9.909280000000001</v>
+        <v>11.1872</v>
       </c>
       <c r="C76" t="n">
-        <v>7.81149</v>
+        <v>9.220800000000001</v>
       </c>
       <c r="D76" t="n">
-        <v>20.3849</v>
+        <v>20.2102</v>
       </c>
       <c r="E76" t="n">
-        <v>7.26191</v>
+        <v>8.0717</v>
       </c>
       <c r="F76" t="n">
-        <v>7.65755</v>
+        <v>8.1829</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>9.83032</v>
+        <v>11.2556</v>
       </c>
       <c r="C77" t="n">
-        <v>7.78334</v>
+        <v>9.25642</v>
       </c>
       <c r="D77" t="n">
-        <v>21.2729</v>
+        <v>23.2191</v>
       </c>
       <c r="E77" t="n">
-        <v>7.5661</v>
+        <v>8.368869999999999</v>
       </c>
       <c r="F77" t="n">
-        <v>8.142379999999999</v>
+        <v>9.641909999999999</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>9.971909999999999</v>
+        <v>8.33661</v>
       </c>
       <c r="C78" t="n">
-        <v>7.90151</v>
+        <v>6.61041</v>
       </c>
       <c r="D78" t="n">
-        <v>20.9677</v>
+        <v>20.6291</v>
       </c>
       <c r="E78" t="n">
-        <v>7.9806</v>
+        <v>9.775169999999999</v>
       </c>
       <c r="F78" t="n">
-        <v>9.278969999999999</v>
+        <v>12.9898</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>10.22</v>
+        <v>12.3165</v>
       </c>
       <c r="C79" t="n">
-        <v>13.5044</v>
+        <v>13.3439</v>
       </c>
       <c r="D79" t="n">
-        <v>22.8317</v>
+        <v>21.8467</v>
       </c>
       <c r="E79" t="n">
-        <v>8.50794</v>
+        <v>10.5888</v>
       </c>
       <c r="F79" t="n">
-        <v>9.44342</v>
+        <v>12.7566</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>10.6002</v>
+        <v>12.622</v>
       </c>
       <c r="C80" t="n">
-        <v>13.6441</v>
+        <v>13.6568</v>
       </c>
       <c r="D80" t="n">
-        <v>23.3162</v>
+        <v>23.0646</v>
       </c>
       <c r="E80" t="n">
-        <v>10.5195</v>
+        <v>10.4145</v>
       </c>
       <c r="F80" t="n">
-        <v>11.9238</v>
+        <v>13.0598</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>16.543</v>
+        <v>16.8</v>
       </c>
       <c r="C81" t="n">
-        <v>13.4663</v>
+        <v>13.6929</v>
       </c>
       <c r="D81" t="n">
-        <v>24.1452</v>
+        <v>24.1658</v>
       </c>
       <c r="E81" t="n">
-        <v>10.5999</v>
+        <v>10.258</v>
       </c>
       <c r="F81" t="n">
-        <v>12.0169</v>
+        <v>12.4751</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>16.8661</v>
+        <v>16.8682</v>
       </c>
       <c r="C82" t="n">
-        <v>13.7684</v>
+        <v>13.7744</v>
       </c>
       <c r="D82" t="n">
-        <v>25.3907</v>
+        <v>24.9354</v>
       </c>
       <c r="E82" t="n">
-        <v>11.093</v>
+        <v>10.96</v>
       </c>
       <c r="F82" t="n">
-        <v>12.2328</v>
+        <v>13.5987</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>16.6821</v>
+        <v>16.931</v>
       </c>
       <c r="C83" t="n">
-        <v>13.6302</v>
+        <v>13.843</v>
       </c>
       <c r="D83" t="n">
-        <v>25.9707</v>
+        <v>26.1671</v>
       </c>
       <c r="E83" t="n">
-        <v>10.4974</v>
+        <v>11.1622</v>
       </c>
       <c r="F83" t="n">
-        <v>12.3113</v>
+        <v>13.5822</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>17.1147</v>
+        <v>16.9753</v>
       </c>
       <c r="C84" t="n">
-        <v>13.9696</v>
+        <v>13.9171</v>
       </c>
       <c r="D84" t="n">
-        <v>27.2505</v>
+        <v>26.8893</v>
       </c>
       <c r="E84" t="n">
-        <v>11.6688</v>
+        <v>12.3705</v>
       </c>
       <c r="F84" t="n">
-        <v>12.4318</v>
+        <v>13.7357</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>16.8291</v>
+        <v>17.0816</v>
       </c>
       <c r="C85" t="n">
-        <v>13.7743</v>
+        <v>13.9616</v>
       </c>
       <c r="D85" t="n">
-        <v>28.2866</v>
+        <v>28.4206</v>
       </c>
       <c r="E85" t="n">
-        <v>11.3566</v>
+        <v>11.9132</v>
       </c>
       <c r="F85" t="n">
-        <v>11.8398</v>
+        <v>12.3527</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>17.0593</v>
+        <v>17.1303</v>
       </c>
       <c r="C86" t="n">
-        <v>14.004</v>
+        <v>14.0546</v>
       </c>
       <c r="D86" t="n">
-        <v>29.6781</v>
+        <v>29.8906</v>
       </c>
       <c r="E86" t="n">
-        <v>11.6562</v>
+        <v>12.186</v>
       </c>
       <c r="F86" t="n">
-        <v>12.0525</v>
+        <v>12.6763</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>16.9269</v>
+        <v>17.1523</v>
       </c>
       <c r="C87" t="n">
-        <v>13.9079</v>
+        <v>14.1241</v>
       </c>
       <c r="D87" t="n">
-        <v>30.4408</v>
+        <v>30.5501</v>
       </c>
       <c r="E87" t="n">
-        <v>11.8475</v>
+        <v>12.3059</v>
       </c>
       <c r="F87" t="n">
-        <v>12.1703</v>
+        <v>12.5084</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>17.0148</v>
+        <v>17.1681</v>
       </c>
       <c r="C88" t="n">
-        <v>13.984</v>
+        <v>14.1293</v>
       </c>
       <c r="D88" t="n">
-        <v>31.3883</v>
+        <v>31.0952</v>
       </c>
       <c r="E88" t="n">
-        <v>11.7506</v>
+        <v>12.2514</v>
       </c>
       <c r="F88" t="n">
-        <v>13.5468</v>
+        <v>14.6815</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>17.3257</v>
+        <v>17.2227</v>
       </c>
       <c r="C89" t="n">
-        <v>14.2432</v>
+        <v>14.156</v>
       </c>
       <c r="D89" t="n">
-        <v>33.2864</v>
+        <v>31.2948</v>
       </c>
       <c r="E89" t="n">
-        <v>12.0003</v>
+        <v>12.5596</v>
       </c>
       <c r="F89" t="n">
-        <v>12.4915</v>
+        <v>12.651</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>17.1264</v>
+        <v>17.1074</v>
       </c>
       <c r="C90" t="n">
-        <v>14.1524</v>
+        <v>14.1253</v>
       </c>
       <c r="D90" t="n">
-        <v>32.9577</v>
+        <v>34.4172</v>
       </c>
       <c r="E90" t="n">
-        <v>12.2583</v>
+        <v>12.8046</v>
       </c>
       <c r="F90" t="n">
-        <v>12.8584</v>
+        <v>14.9026</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>17.2625</v>
+        <v>17.421</v>
       </c>
       <c r="C91" t="n">
-        <v>14.2115</v>
+        <v>14.434</v>
       </c>
       <c r="D91" t="n">
-        <v>34.196</v>
+        <v>35.5663</v>
       </c>
       <c r="E91" t="n">
-        <v>12.5726</v>
+        <v>13.0602</v>
       </c>
       <c r="F91" t="n">
-        <v>13.1855</v>
+        <v>15.2846</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>17.5012</v>
+        <v>17.5261</v>
       </c>
       <c r="C92" t="n">
-        <v>14.5065</v>
+        <v>14.5687</v>
       </c>
       <c r="D92" t="n">
-        <v>32.4689</v>
+        <v>32.3695</v>
       </c>
       <c r="E92" t="n">
-        <v>13.0379</v>
+        <v>19.5218</v>
       </c>
       <c r="F92" t="n">
-        <v>14.5273</v>
+        <v>18.5066</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>17.4052</v>
+        <v>17.7599</v>
       </c>
       <c r="C93" t="n">
-        <v>14.4675</v>
+        <v>14.7485</v>
       </c>
       <c r="D93" t="n">
-        <v>33.4466</v>
+        <v>33.1598</v>
       </c>
       <c r="E93" t="n">
-        <v>13.472</v>
+        <v>19.7083</v>
       </c>
       <c r="F93" t="n">
-        <v>15.1792</v>
+        <v>18.6418</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>17.6648</v>
+        <v>17.9056</v>
       </c>
       <c r="C94" t="n">
-        <v>17.6947</v>
+        <v>17.6653</v>
       </c>
       <c r="D94" t="n">
-        <v>34.1837</v>
+        <v>33.925</v>
       </c>
       <c r="E94" t="n">
-        <v>19.8065</v>
+        <v>19.8303</v>
       </c>
       <c r="F94" t="n">
-        <v>18.9564</v>
+        <v>18.7496</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>22.0885</v>
+        <v>22.0528</v>
       </c>
       <c r="C95" t="n">
-        <v>17.6618</v>
+        <v>17.6857</v>
       </c>
       <c r="D95" t="n">
-        <v>34.9007</v>
+        <v>34.9093</v>
       </c>
       <c r="E95" t="n">
-        <v>20.058</v>
+        <v>20.0527</v>
       </c>
       <c r="F95" t="n">
-        <v>19.0724</v>
+        <v>18.8243</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>22.1734</v>
+        <v>22.2261</v>
       </c>
       <c r="C96" t="n">
-        <v>17.7049</v>
+        <v>17.7152</v>
       </c>
       <c r="D96" t="n">
-        <v>35.9751</v>
+        <v>35.7653</v>
       </c>
       <c r="E96" t="n">
-        <v>20.1266</v>
+        <v>20.4094</v>
       </c>
       <c r="F96" t="n">
-        <v>19.2075</v>
+        <v>18.9714</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>22.1289</v>
+        <v>22.2651</v>
       </c>
       <c r="C97" t="n">
-        <v>17.7194</v>
+        <v>17.7492</v>
       </c>
       <c r="D97" t="n">
-        <v>36.9627</v>
+        <v>36.7174</v>
       </c>
       <c r="E97" t="n">
-        <v>20.3057</v>
+        <v>20.3464</v>
       </c>
       <c r="F97" t="n">
-        <v>19.3271</v>
+        <v>19.0721</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>22.2619</v>
+        <v>22.2291</v>
       </c>
       <c r="C98" t="n">
-        <v>17.7754</v>
+        <v>17.8372</v>
       </c>
       <c r="D98" t="n">
-        <v>37.7313</v>
+        <v>37.4024</v>
       </c>
       <c r="E98" t="n">
-        <v>20.4422</v>
+        <v>20.5499</v>
       </c>
       <c r="F98" t="n">
-        <v>19.4756</v>
+        <v>19.2146</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>22.1428</v>
+        <v>22.1654</v>
       </c>
       <c r="C99" t="n">
-        <v>17.8428</v>
+        <v>17.7919</v>
       </c>
       <c r="D99" t="n">
-        <v>38.5558</v>
+        <v>38.382</v>
       </c>
       <c r="E99" t="n">
-        <v>20.5684</v>
+        <v>20.6131</v>
       </c>
       <c r="F99" t="n">
-        <v>19.7291</v>
+        <v>19.5547</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>22.1549</v>
+        <v>22.2362</v>
       </c>
       <c r="C100" t="n">
-        <v>17.832</v>
+        <v>17.8559</v>
       </c>
       <c r="D100" t="n">
-        <v>39.9332</v>
+        <v>39.6976</v>
       </c>
       <c r="E100" t="n">
-        <v>20.7966</v>
+        <v>20.3765</v>
       </c>
       <c r="F100" t="n">
-        <v>19.7865</v>
+        <v>18.9167</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>22.1917</v>
+        <v>21.3307</v>
       </c>
       <c r="C101" t="n">
-        <v>17.9005</v>
+        <v>17.0891</v>
       </c>
       <c r="D101" t="n">
-        <v>40.736</v>
+        <v>40.6835</v>
       </c>
       <c r="E101" t="n">
-        <v>20.9113</v>
+        <v>20.5816</v>
       </c>
       <c r="F101" t="n">
-        <v>20.0019</v>
+        <v>19.7779</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>22.232</v>
+        <v>21.4161</v>
       </c>
       <c r="C102" t="n">
-        <v>17.8973</v>
+        <v>17.1621</v>
       </c>
       <c r="D102" t="n">
-        <v>41.9054</v>
+        <v>41.4709</v>
       </c>
       <c r="E102" t="n">
-        <v>20.9956</v>
+        <v>20.6769</v>
       </c>
       <c r="F102" t="n">
-        <v>20.186</v>
+        <v>20.0807</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>22.3583</v>
+        <v>21.4007</v>
       </c>
       <c r="C103" t="n">
-        <v>17.9702</v>
+        <v>17.2424</v>
       </c>
       <c r="D103" t="n">
-        <v>42.7512</v>
+        <v>42.8275</v>
       </c>
       <c r="E103" t="n">
-        <v>21.1229</v>
+        <v>20.907</v>
       </c>
       <c r="F103" t="n">
-        <v>20.4649</v>
+        <v>19.5697</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>22.2813</v>
+        <v>21.4956</v>
       </c>
       <c r="C104" t="n">
-        <v>18.1114</v>
+        <v>17.3462</v>
       </c>
       <c r="D104" t="n">
-        <v>43.814</v>
+        <v>43.652</v>
       </c>
       <c r="E104" t="n">
-        <v>21.3998</v>
+        <v>21.0489</v>
       </c>
       <c r="F104" t="n">
-        <v>20.8248</v>
+        <v>20.589</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>22.4669</v>
+        <v>21.5343</v>
       </c>
       <c r="C105" t="n">
-        <v>18.2276</v>
+        <v>17.4314</v>
       </c>
       <c r="D105" t="n">
-        <v>45.5749</v>
+        <v>44.7267</v>
       </c>
       <c r="E105" t="n">
-        <v>21.6192</v>
+        <v>21.2687</v>
       </c>
       <c r="F105" t="n">
-        <v>21.1826</v>
+        <v>20.9958</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>22.5728</v>
+        <v>21.6804</v>
       </c>
       <c r="C106" t="n">
-        <v>18.364</v>
+        <v>17.5885</v>
       </c>
       <c r="D106" t="n">
-        <v>46.5855</v>
+        <v>45.9424</v>
       </c>
       <c r="E106" t="n">
-        <v>21.9211</v>
+        <v>21.6271</v>
       </c>
       <c r="F106" t="n">
-        <v>21.6452</v>
+        <v>21.257</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>22.7789</v>
+        <v>21.864</v>
       </c>
       <c r="C107" t="n">
-        <v>18.5731</v>
+        <v>17.8336</v>
       </c>
       <c r="D107" t="n">
-        <v>39.8757</v>
+        <v>38.1542</v>
       </c>
       <c r="E107" t="n">
-        <v>22.2846</v>
+        <v>25.3948</v>
       </c>
       <c r="F107" t="n">
-        <v>22.4419</v>
+        <v>23.8179</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>23.0467</v>
+        <v>22.8682</v>
       </c>
       <c r="C108" t="n">
-        <v>18.9854</v>
+        <v>18.4799</v>
       </c>
       <c r="D108" t="n">
-        <v>40.5744</v>
+        <v>39.799</v>
       </c>
       <c r="E108" t="n">
-        <v>25.635</v>
+        <v>25.1362</v>
       </c>
       <c r="F108" t="n">
-        <v>23.9277</v>
+        <v>23.4056</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>23.5089</v>
+        <v>23.2871</v>
       </c>
       <c r="C109" t="n">
-        <v>19.055</v>
+        <v>18.6362</v>
       </c>
       <c r="D109" t="n">
-        <v>41.3062</v>
+        <v>40.498</v>
       </c>
       <c r="E109" t="n">
-        <v>25.8713</v>
+        <v>25.1161</v>
       </c>
       <c r="F109" t="n">
-        <v>24.07</v>
+        <v>23.6634</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>25.3245</v>
+        <v>24.7321</v>
       </c>
       <c r="C110" t="n">
-        <v>19.1514</v>
+        <v>18.7308</v>
       </c>
       <c r="D110" t="n">
-        <v>42.1043</v>
+        <v>41.1245</v>
       </c>
       <c r="E110" t="n">
-        <v>26.0511</v>
+        <v>25.4622</v>
       </c>
       <c r="F110" t="n">
-        <v>24.1704</v>
+        <v>24.0854</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>25.3637</v>
+        <v>24.6547</v>
       </c>
       <c r="C111" t="n">
-        <v>19.1968</v>
+        <v>18.4908</v>
       </c>
       <c r="D111" t="n">
-        <v>43.0527</v>
+        <v>41.5992</v>
       </c>
       <c r="E111" t="n">
-        <v>26.311</v>
+        <v>25.7061</v>
       </c>
       <c r="F111" t="n">
-        <v>24.67</v>
+        <v>24.0558</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>25.4321</v>
+        <v>24.5931</v>
       </c>
       <c r="C112" t="n">
-        <v>19.257</v>
+        <v>18.8314</v>
       </c>
       <c r="D112" t="n">
-        <v>43.7734</v>
+        <v>42.4063</v>
       </c>
       <c r="E112" t="n">
-        <v>26.5278</v>
+        <v>25.8447</v>
       </c>
       <c r="F112" t="n">
-        <v>24.9243</v>
+        <v>24.1199</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>25.5736</v>
+        <v>24.6266</v>
       </c>
       <c r="C113" t="n">
-        <v>19.308</v>
+        <v>18.792</v>
       </c>
       <c r="D113" t="n">
-        <v>45.0281</v>
+        <v>43.4246</v>
       </c>
       <c r="E113" t="n">
-        <v>26.6979</v>
+        <v>26.07</v>
       </c>
       <c r="F113" t="n">
-        <v>25.1991</v>
+        <v>24.2493</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>25.4696</v>
+        <v>24.7274</v>
       </c>
       <c r="C114" t="n">
-        <v>19.4154</v>
+        <v>18.8685</v>
       </c>
       <c r="D114" t="n">
-        <v>45.9023</v>
+        <v>44.3232</v>
       </c>
       <c r="E114" t="n">
-        <v>26.748</v>
+        <v>26.3058</v>
       </c>
       <c r="F114" t="n">
-        <v>25.3975</v>
+        <v>24.5932</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>25.3719</v>
+        <v>24.8602</v>
       </c>
       <c r="C115" t="n">
-        <v>19.5198</v>
+        <v>18.9745</v>
       </c>
       <c r="D115" t="n">
-        <v>47.0201</v>
+        <v>45.3281</v>
       </c>
       <c r="E115" t="n">
-        <v>27.0266</v>
+        <v>26.5565</v>
       </c>
       <c r="F115" t="n">
-        <v>25.8053</v>
+        <v>25.0009</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>25.5021</v>
+        <v>24.8656</v>
       </c>
       <c r="C116" t="n">
-        <v>19.5356</v>
+        <v>19.1532</v>
       </c>
       <c r="D116" t="n">
-        <v>48.0901</v>
+        <v>46.3224</v>
       </c>
       <c r="E116" t="n">
-        <v>27.2571</v>
+        <v>26.6644</v>
       </c>
       <c r="F116" t="n">
-        <v>26.1879</v>
+        <v>25.4768</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>25.5367</v>
+        <v>24.6298</v>
       </c>
       <c r="C117" t="n">
-        <v>19.6825</v>
+        <v>19.0262</v>
       </c>
       <c r="D117" t="n">
-        <v>49.2275</v>
+        <v>47.2852</v>
       </c>
       <c r="E117" t="n">
-        <v>27.5002</v>
+        <v>26.9363</v>
       </c>
       <c r="F117" t="n">
-        <v>26.5628</v>
+        <v>26.0486</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>25.5941</v>
+        <v>24.8415</v>
       </c>
       <c r="C118" t="n">
-        <v>19.8362</v>
+        <v>19.1811</v>
       </c>
       <c r="D118" t="n">
-        <v>50.2092</v>
+        <v>48.5413</v>
       </c>
       <c r="E118" t="n">
-        <v>27.8283</v>
+        <v>27.3186</v>
       </c>
       <c r="F118" t="n">
-        <v>27.1001</v>
+        <v>26.4491</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>25.8179</v>
+        <v>25.2705</v>
       </c>
       <c r="C119" t="n">
-        <v>19.9758</v>
+        <v>19.7628</v>
       </c>
       <c r="D119" t="n">
-        <v>51.4026</v>
+        <v>49.4359</v>
       </c>
       <c r="E119" t="n">
-        <v>27.8061</v>
+        <v>27.7395</v>
       </c>
       <c r="F119" t="n">
-        <v>27.647</v>
+        <v>26.5594</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>25.7645</v>
+        <v>25.7897</v>
       </c>
       <c r="C120" t="n">
-        <v>20.1992</v>
+        <v>19.9339</v>
       </c>
       <c r="D120" t="n">
-        <v>52.2802</v>
+        <v>50.9716</v>
       </c>
       <c r="E120" t="n">
-        <v>28.4983</v>
+        <v>28.0798</v>
       </c>
       <c r="F120" t="n">
-        <v>28.2777</v>
+        <v>27.9629</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>26.0015</v>
+        <v>25.5067</v>
       </c>
       <c r="C121" t="n">
-        <v>20.6313</v>
+        <v>20.2259</v>
       </c>
       <c r="D121" t="n">
-        <v>43.3255</v>
+        <v>41.8497</v>
       </c>
       <c r="E121" t="n">
-        <v>29.1439</v>
+        <v>29.8323</v>
       </c>
       <c r="F121" t="n">
-        <v>29.1998</v>
+        <v>27.6134</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>26.5296</v>
+        <v>26.0447</v>
       </c>
       <c r="C122" t="n">
-        <v>21.4867</v>
+        <v>21.0357</v>
       </c>
       <c r="D122" t="n">
-        <v>43.9316</v>
+        <v>43.0172</v>
       </c>
       <c r="E122" t="n">
-        <v>29.6633</v>
+        <v>30.3838</v>
       </c>
       <c r="F122" t="n">
-        <v>30.3934</v>
+        <v>27.903</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>26.5152</v>
+        <v>26.6864</v>
       </c>
       <c r="C123" t="n">
-        <v>21.5389</v>
+        <v>21.1189</v>
       </c>
       <c r="D123" t="n">
-        <v>44.5054</v>
+        <v>43.7232</v>
       </c>
       <c r="E123" t="n">
-        <v>30.981</v>
+        <v>30.5727</v>
       </c>
       <c r="F123" t="n">
-        <v>28.2956</v>
+        <v>28.0451</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>32.7023</v>
+        <v>32.333</v>
       </c>
       <c r="C124" t="n">
-        <v>21.7092</v>
+        <v>21.5911</v>
       </c>
       <c r="D124" t="n">
-        <v>45.306</v>
+        <v>44.8657</v>
       </c>
       <c r="E124" t="n">
-        <v>30.7608</v>
+        <v>30.8473</v>
       </c>
       <c r="F124" t="n">
-        <v>28.7127</v>
+        <v>28.3659</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>33.1197</v>
+        <v>32.682</v>
       </c>
       <c r="C125" t="n">
-        <v>21.7992</v>
+        <v>21.5765</v>
       </c>
       <c r="D125" t="n">
-        <v>46.1245</v>
+        <v>45.7348</v>
       </c>
       <c r="E125" t="n">
-        <v>31.3549</v>
+        <v>30.9156</v>
       </c>
       <c r="F125" t="n">
-        <v>28.9449</v>
+        <v>28.3883</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>32.6028</v>
+        <v>32.5056</v>
       </c>
       <c r="C126" t="n">
-        <v>21.9897</v>
+        <v>21.7516</v>
       </c>
       <c r="D126" t="n">
-        <v>46.9264</v>
+        <v>46.3857</v>
       </c>
       <c r="E126" t="n">
-        <v>31.6864</v>
+        <v>30.9405</v>
       </c>
       <c r="F126" t="n">
-        <v>29.0556</v>
+        <v>28.535</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>33.2251</v>
+        <v>32.8232</v>
       </c>
       <c r="C127" t="n">
-        <v>22.1097</v>
+        <v>21.8354</v>
       </c>
       <c r="D127" t="n">
-        <v>47.7751</v>
+        <v>47.2738</v>
       </c>
       <c r="E127" t="n">
-        <v>31.8606</v>
+        <v>30.91</v>
       </c>
       <c r="F127" t="n">
-        <v>29.4291</v>
+        <v>29.0612</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>33.1229</v>
+        <v>32.125</v>
       </c>
       <c r="C128" t="n">
-        <v>22.279</v>
+        <v>21.801</v>
       </c>
       <c r="D128" t="n">
-        <v>48.6876</v>
+        <v>48.1389</v>
       </c>
       <c r="E128" t="n">
-        <v>32.1317</v>
+        <v>30.639</v>
       </c>
       <c r="F128" t="n">
-        <v>29.9069</v>
+        <v>28.9198</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>33.1907</v>
+        <v>32.0404</v>
       </c>
       <c r="C129" t="n">
-        <v>22.4201</v>
+        <v>21.9751</v>
       </c>
       <c r="D129" t="n">
-        <v>50.1025</v>
+        <v>49.4636</v>
       </c>
       <c r="E129" t="n">
-        <v>32.3901</v>
+        <v>30.5292</v>
       </c>
       <c r="F129" t="n">
-        <v>30.2749</v>
+        <v>29.7007</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>33.2048</v>
+        <v>32.1547</v>
       </c>
       <c r="C130" t="n">
-        <v>22.5785</v>
+        <v>22.1939</v>
       </c>
       <c r="D130" t="n">
-        <v>50.8501</v>
+        <v>50.5096</v>
       </c>
       <c r="E130" t="n">
-        <v>32.6497</v>
+        <v>31.464</v>
       </c>
       <c r="F130" t="n">
-        <v>30.7045</v>
+        <v>29.9708</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>33.2752</v>
+        <v>32.2799</v>
       </c>
       <c r="C131" t="n">
-        <v>22.9031</v>
+        <v>22.3788</v>
       </c>
       <c r="D131" t="n">
-        <v>52.0364</v>
+        <v>51.5654</v>
       </c>
       <c r="E131" t="n">
-        <v>32.9207</v>
+        <v>31.3799</v>
       </c>
       <c r="F131" t="n">
-        <v>31.0574</v>
+        <v>29.921</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>33.3174</v>
+        <v>32.239</v>
       </c>
       <c r="C132" t="n">
-        <v>23.0561</v>
+        <v>22.5936</v>
       </c>
       <c r="D132" t="n">
-        <v>53.0925</v>
+        <v>52.1884</v>
       </c>
       <c r="E132" t="n">
-        <v>33.0437</v>
+        <v>32.1705</v>
       </c>
       <c r="F132" t="n">
-        <v>31.4687</v>
+        <v>30.7765</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>33.2836</v>
+        <v>32.4966</v>
       </c>
       <c r="C133" t="n">
-        <v>23.3795</v>
+        <v>22.9235</v>
       </c>
       <c r="D133" t="n">
-        <v>54.3057</v>
+        <v>53.7327</v>
       </c>
       <c r="E133" t="n">
-        <v>33.8168</v>
+        <v>32.7181</v>
       </c>
       <c r="F133" t="n">
-        <v>32.4726</v>
+        <v>31.7651</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>33.4863</v>
+        <v>32.4879</v>
       </c>
       <c r="C134" t="n">
-        <v>23.7212</v>
+        <v>23.2877</v>
       </c>
       <c r="D134" t="n">
-        <v>55.7583</v>
+        <v>55.1313</v>
       </c>
       <c r="E134" t="n">
-        <v>34.0291</v>
+        <v>32.7507</v>
       </c>
       <c r="F134" t="n">
-        <v>33.1719</v>
+        <v>32.1399</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>33.4797</v>
+        <v>32.7969</v>
       </c>
       <c r="C135" t="n">
-        <v>24.1806</v>
+        <v>23.7946</v>
       </c>
       <c r="D135" t="n">
-        <v>44.8852</v>
+        <v>44.2533</v>
       </c>
       <c r="E135" t="n">
-        <v>35.0073</v>
+        <v>32.495</v>
       </c>
       <c r="F135" t="n">
-        <v>34.3997</v>
+        <v>30.0205</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>34.2405</v>
+        <v>33.2076</v>
       </c>
       <c r="C136" t="n">
-        <v>23.564</v>
+        <v>23.5154</v>
       </c>
       <c r="D136" t="n">
-        <v>45.6378</v>
+        <v>45.1875</v>
       </c>
       <c r="E136" t="n">
-        <v>35.2066</v>
+        <v>32.7208</v>
       </c>
       <c r="F136" t="n">
-        <v>35.8757</v>
+        <v>30.3352</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>34.3473</v>
+        <v>33.6712</v>
       </c>
       <c r="C137" t="n">
-        <v>24.3037</v>
+        <v>23.7419</v>
       </c>
       <c r="D137" t="n">
-        <v>46.1973</v>
+        <v>45.8587</v>
       </c>
       <c r="E137" t="n">
-        <v>33.119</v>
+        <v>32.8828</v>
       </c>
       <c r="F137" t="n">
-        <v>31.0417</v>
+        <v>30.7729</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>38.4838</v>
+        <v>38.2838</v>
       </c>
       <c r="C138" t="n">
-        <v>24.4526</v>
+        <v>24.1692</v>
       </c>
       <c r="D138" t="n">
-        <v>46.8674</v>
+        <v>46.7377</v>
       </c>
       <c r="E138" t="n">
-        <v>33.324</v>
+        <v>33.1523</v>
       </c>
       <c r="F138" t="n">
-        <v>31.2795</v>
+        <v>31.0012</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>38.4757</v>
+        <v>38.2953</v>
       </c>
       <c r="C139" t="n">
-        <v>24.6308</v>
+        <v>24.3523</v>
       </c>
       <c r="D139" t="n">
-        <v>47.6934</v>
+        <v>47.0155</v>
       </c>
       <c r="E139" t="n">
-        <v>33.0643</v>
+        <v>33.4822</v>
       </c>
       <c r="F139" t="n">
-        <v>31.5726</v>
+        <v>31.0425</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>38.4942</v>
+        <v>38.3036</v>
       </c>
       <c r="C140" t="n">
-        <v>24.8071</v>
+        <v>24.4434</v>
       </c>
       <c r="D140" t="n">
-        <v>48.6608</v>
+        <v>48.1299</v>
       </c>
       <c r="E140" t="n">
-        <v>33.8985</v>
+        <v>33.6456</v>
       </c>
       <c r="F140" t="n">
-        <v>31.8674</v>
+        <v>31.0413</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>38.5017</v>
+        <v>38.3122</v>
       </c>
       <c r="C141" t="n">
-        <v>24.9874</v>
+        <v>24.617</v>
       </c>
       <c r="D141" t="n">
-        <v>49.5628</v>
+        <v>49.1287</v>
       </c>
       <c r="E141" t="n">
-        <v>34.1045</v>
+        <v>33.9678</v>
       </c>
       <c r="F141" t="n">
-        <v>32.1423</v>
+        <v>31.8551</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>38.5022</v>
+        <v>38.2021</v>
       </c>
       <c r="C142" t="n">
-        <v>25.1643</v>
+        <v>24.7992</v>
       </c>
       <c r="D142" t="n">
-        <v>50.4133</v>
+        <v>49.83</v>
       </c>
       <c r="E142" t="n">
-        <v>34.3224</v>
+        <v>34.1938</v>
       </c>
       <c r="F142" t="n">
-        <v>32.4167</v>
+        <v>31.8458</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>38.5373</v>
+        <v>38.3475</v>
       </c>
       <c r="C143" t="n">
-        <v>25.3704</v>
+        <v>25.032</v>
       </c>
       <c r="D143" t="n">
-        <v>51.2486</v>
+        <v>51.2998</v>
       </c>
       <c r="E143" t="n">
-        <v>34.5292</v>
+        <v>34.4099</v>
       </c>
       <c r="F143" t="n">
-        <v>32.728</v>
+        <v>32.5561</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Scattered successful looukp.xlsx
+++ b/clang-x64/Scattered successful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>3.14974</v>
+        <v>3.35276</v>
       </c>
       <c r="C2" t="n">
-        <v>2.50136</v>
+        <v>2.65439</v>
       </c>
       <c r="D2" t="n">
-        <v>7.12657</v>
+        <v>7.02719</v>
       </c>
       <c r="E2" t="n">
-        <v>3.19139</v>
+        <v>3.25904</v>
       </c>
       <c r="F2" t="n">
-        <v>3.25974</v>
+        <v>3.16295</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>3.17228</v>
+        <v>3.38743</v>
       </c>
       <c r="C3" t="n">
-        <v>2.55042</v>
+        <v>2.69068</v>
       </c>
       <c r="D3" t="n">
-        <v>7.89143</v>
+        <v>7.70156</v>
       </c>
       <c r="E3" t="n">
-        <v>3.10488</v>
+        <v>3.19603</v>
       </c>
       <c r="F3" t="n">
-        <v>3.28496</v>
+        <v>3.36646</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>2.949</v>
+        <v>3.14915</v>
       </c>
       <c r="C4" t="n">
-        <v>2.47997</v>
+        <v>2.53571</v>
       </c>
       <c r="D4" t="n">
-        <v>8.666740000000001</v>
+        <v>8.513859999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>3.09599</v>
+        <v>3.17469</v>
       </c>
       <c r="F4" t="n">
-        <v>3.37306</v>
+        <v>3.68198</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.21146</v>
+        <v>3.40277</v>
       </c>
       <c r="C5" t="n">
-        <v>2.5783</v>
+        <v>2.69188</v>
       </c>
       <c r="D5" t="n">
-        <v>9.372210000000001</v>
+        <v>9.2033</v>
       </c>
       <c r="E5" t="n">
-        <v>3.14622</v>
+        <v>3.349</v>
       </c>
       <c r="F5" t="n">
-        <v>3.39274</v>
+        <v>3.59396</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>3.17833</v>
+        <v>3.38382</v>
       </c>
       <c r="C6" t="n">
-        <v>2.58216</v>
+        <v>2.69703</v>
       </c>
       <c r="D6" t="n">
-        <v>10.0093</v>
+        <v>9.999040000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>3.22824</v>
+        <v>3.41952</v>
       </c>
       <c r="F6" t="n">
-        <v>3.33747</v>
+        <v>3.25923</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>3.23599</v>
+        <v>3.44872</v>
       </c>
       <c r="C7" t="n">
-        <v>2.65032</v>
+        <v>2.7967</v>
       </c>
       <c r="D7" t="n">
-        <v>6.10527</v>
+        <v>6.13523</v>
       </c>
       <c r="E7" t="n">
-        <v>3.80674</v>
+        <v>3.70437</v>
       </c>
       <c r="F7" t="n">
-        <v>3.36962</v>
+        <v>3.36661</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>3.24991</v>
+        <v>3.46472</v>
       </c>
       <c r="C8" t="n">
-        <v>3.03173</v>
+        <v>3.16871</v>
       </c>
       <c r="D8" t="n">
-        <v>6.32032</v>
+        <v>6.38959</v>
       </c>
       <c r="E8" t="n">
-        <v>3.88675</v>
+        <v>3.8965</v>
       </c>
       <c r="F8" t="n">
-        <v>3.39784</v>
+        <v>3.40448</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>3.07679</v>
+        <v>3.27952</v>
       </c>
       <c r="C9" t="n">
-        <v>3.18735</v>
+        <v>3.20688</v>
       </c>
       <c r="D9" t="n">
-        <v>6.99772</v>
+        <v>7.03595</v>
       </c>
       <c r="E9" t="n">
-        <v>3.91409</v>
+        <v>3.93118</v>
       </c>
       <c r="F9" t="n">
-        <v>3.43481</v>
+        <v>3.42679</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>4.04715</v>
+        <v>4.18588</v>
       </c>
       <c r="C10" t="n">
-        <v>3.20415</v>
+        <v>3.27633</v>
       </c>
       <c r="D10" t="n">
-        <v>7.43546</v>
+        <v>7.4443</v>
       </c>
       <c r="E10" t="n">
-        <v>3.95147</v>
+        <v>3.96545</v>
       </c>
       <c r="F10" t="n">
-        <v>3.45692</v>
+        <v>3.4575</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>4.24653</v>
+        <v>4.83308</v>
       </c>
       <c r="C11" t="n">
-        <v>3.06305</v>
+        <v>3.22917</v>
       </c>
       <c r="D11" t="n">
-        <v>7.95412</v>
+        <v>7.97543</v>
       </c>
       <c r="E11" t="n">
-        <v>4.263</v>
+        <v>4.23102</v>
       </c>
       <c r="F11" t="n">
-        <v>3.50358</v>
+        <v>3.4513</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>3.97542</v>
+        <v>3.9529</v>
       </c>
       <c r="C12" t="n">
-        <v>3.15875</v>
+        <v>3.25494</v>
       </c>
       <c r="D12" t="n">
-        <v>8.62452</v>
+        <v>8.62487</v>
       </c>
       <c r="E12" t="n">
-        <v>4.30914</v>
+        <v>4.2851</v>
       </c>
       <c r="F12" t="n">
-        <v>3.51648</v>
+        <v>3.4775</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>4.27534</v>
+        <v>4.84135</v>
       </c>
       <c r="C13" t="n">
-        <v>3.10544</v>
+        <v>3.34881</v>
       </c>
       <c r="D13" t="n">
-        <v>9.080069999999999</v>
+        <v>9.087199999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>4.16242</v>
+        <v>4.24184</v>
       </c>
       <c r="F13" t="n">
-        <v>3.56851</v>
+        <v>3.61813</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>4.35761</v>
+        <v>4.84932</v>
       </c>
       <c r="C14" t="n">
-        <v>3.1704</v>
+        <v>3.39409</v>
       </c>
       <c r="D14" t="n">
-        <v>9.662089999999999</v>
+        <v>9.65513</v>
       </c>
       <c r="E14" t="n">
-        <v>4.07</v>
+        <v>4.11287</v>
       </c>
       <c r="F14" t="n">
-        <v>3.56363</v>
+        <v>3.58085</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>4.29168</v>
+        <v>4.86238</v>
       </c>
       <c r="C15" t="n">
-        <v>3.15009</v>
+        <v>3.39499</v>
       </c>
       <c r="D15" t="n">
-        <v>10.1338</v>
+        <v>10.1527</v>
       </c>
       <c r="E15" t="n">
-        <v>4.17096</v>
+        <v>4.2692</v>
       </c>
       <c r="F15" t="n">
-        <v>3.60705</v>
+        <v>3.66193</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>4.37781</v>
+        <v>4.86307</v>
       </c>
       <c r="C16" t="n">
-        <v>3.21256</v>
+        <v>3.43115</v>
       </c>
       <c r="D16" t="n">
-        <v>10.6088</v>
+        <v>10.6428</v>
       </c>
       <c r="E16" t="n">
-        <v>4.51033</v>
+        <v>4.47095</v>
       </c>
       <c r="F16" t="n">
-        <v>3.63345</v>
+        <v>3.69376</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>4.30951</v>
+        <v>4.88007</v>
       </c>
       <c r="C17" t="n">
-        <v>3.19893</v>
+        <v>3.4584</v>
       </c>
       <c r="D17" t="n">
-        <v>11.1407</v>
+        <v>11.164</v>
       </c>
       <c r="E17" t="n">
-        <v>4.15607</v>
+        <v>4.0796</v>
       </c>
       <c r="F17" t="n">
-        <v>3.62993</v>
+        <v>3.66831</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>4.32802</v>
+        <v>4.89666</v>
       </c>
       <c r="C18" t="n">
-        <v>3.23256</v>
+        <v>3.49669</v>
       </c>
       <c r="D18" t="n">
-        <v>11.5878</v>
+        <v>11.5864</v>
       </c>
       <c r="E18" t="n">
-        <v>4.52954</v>
+        <v>4.57679</v>
       </c>
       <c r="F18" t="n">
-        <v>3.66275</v>
+        <v>3.65519</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>4.33735</v>
+        <v>4.90626</v>
       </c>
       <c r="C19" t="n">
-        <v>3.26835</v>
+        <v>3.52596</v>
       </c>
       <c r="D19" t="n">
-        <v>12.0728</v>
+        <v>12.1267</v>
       </c>
       <c r="E19" t="n">
-        <v>4.30975</v>
+        <v>4.40519</v>
       </c>
       <c r="F19" t="n">
-        <v>3.69719</v>
+        <v>3.74565</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>4.35838</v>
+        <v>4.93078</v>
       </c>
       <c r="C20" t="n">
-        <v>3.29446</v>
+        <v>3.57339</v>
       </c>
       <c r="D20" t="n">
-        <v>12.3863</v>
+        <v>12.5012</v>
       </c>
       <c r="E20" t="n">
-        <v>4.41041</v>
+        <v>4.68119</v>
       </c>
       <c r="F20" t="n">
-        <v>3.90003</v>
+        <v>3.86829</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>4.37961</v>
+        <v>4.95493</v>
       </c>
       <c r="C21" t="n">
-        <v>3.34038</v>
+        <v>3.60729</v>
       </c>
       <c r="D21" t="n">
-        <v>8.73128</v>
+        <v>8.72888</v>
       </c>
       <c r="E21" t="n">
-        <v>3.88916</v>
+        <v>3.8156</v>
       </c>
       <c r="F21" t="n">
-        <v>4.18994</v>
+        <v>4.15666</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>4.48737</v>
+        <v>4.98941</v>
       </c>
       <c r="C22" t="n">
-        <v>2.99017</v>
+        <v>3.09673</v>
       </c>
       <c r="D22" t="n">
-        <v>9.09071</v>
+        <v>9.110189999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>3.99474</v>
+        <v>3.83348</v>
       </c>
       <c r="F22" t="n">
-        <v>4.31746</v>
+        <v>4.3336</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>4.46783</v>
+        <v>5.02378</v>
       </c>
       <c r="C23" t="n">
-        <v>3.00489</v>
+        <v>3.09892</v>
       </c>
       <c r="D23" t="n">
-        <v>9.490500000000001</v>
+        <v>9.45173</v>
       </c>
       <c r="E23" t="n">
-        <v>3.99396</v>
+        <v>4.29687</v>
       </c>
       <c r="F23" t="n">
-        <v>4.25626</v>
+        <v>4.26139</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>4.71675</v>
+        <v>4.92528</v>
       </c>
       <c r="C24" t="n">
-        <v>3.02143</v>
+        <v>3.12677</v>
       </c>
       <c r="D24" t="n">
-        <v>9.82525</v>
+        <v>9.792210000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>4.04911</v>
+        <v>4.11011</v>
       </c>
       <c r="F24" t="n">
-        <v>4.29405</v>
+        <v>4.30907</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>4.75883</v>
+        <v>4.94118</v>
       </c>
       <c r="C25" t="n">
-        <v>3.03081</v>
+        <v>3.15927</v>
       </c>
       <c r="D25" t="n">
-        <v>10.2381</v>
+        <v>10.2228</v>
       </c>
       <c r="E25" t="n">
-        <v>3.99697</v>
+        <v>4.07462</v>
       </c>
       <c r="F25" t="n">
-        <v>4.37586</v>
+        <v>4.42513</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>4.76014</v>
+        <v>4.94497</v>
       </c>
       <c r="C26" t="n">
-        <v>3.04222</v>
+        <v>3.16463</v>
       </c>
       <c r="D26" t="n">
-        <v>10.6177</v>
+        <v>10.6263</v>
       </c>
       <c r="E26" t="n">
-        <v>4.10649</v>
+        <v>4.07668</v>
       </c>
       <c r="F26" t="n">
-        <v>4.11602</v>
+        <v>4.11205</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>4.48167</v>
+        <v>4.50249</v>
       </c>
       <c r="C27" t="n">
-        <v>3.02802</v>
+        <v>3.19767</v>
       </c>
       <c r="D27" t="n">
-        <v>11.0577</v>
+        <v>11.04</v>
       </c>
       <c r="E27" t="n">
-        <v>3.97933</v>
+        <v>3.91976</v>
       </c>
       <c r="F27" t="n">
-        <v>4.14742</v>
+        <v>4.14517</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>4.566</v>
+        <v>4.49518</v>
       </c>
       <c r="C28" t="n">
-        <v>3.0403</v>
+        <v>3.21807</v>
       </c>
       <c r="D28" t="n">
-        <v>11.4274</v>
+        <v>11.437</v>
       </c>
       <c r="E28" t="n">
-        <v>4.02098</v>
+        <v>4.11428</v>
       </c>
       <c r="F28" t="n">
-        <v>4.17699</v>
+        <v>4.16531</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>4.52513</v>
+        <v>4.50459</v>
       </c>
       <c r="C29" t="n">
-        <v>3.0684</v>
+        <v>3.26364</v>
       </c>
       <c r="D29" t="n">
-        <v>11.8291</v>
+        <v>11.8441</v>
       </c>
       <c r="E29" t="n">
-        <v>4.04207</v>
+        <v>4.16562</v>
       </c>
       <c r="F29" t="n">
-        <v>4.22106</v>
+        <v>4.21135</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>4.67334</v>
+        <v>4.96037</v>
       </c>
       <c r="C30" t="n">
-        <v>3.22293</v>
+        <v>3.42804</v>
       </c>
       <c r="D30" t="n">
-        <v>12.2454</v>
+        <v>12.2804</v>
       </c>
       <c r="E30" t="n">
-        <v>4.08493</v>
+        <v>4.21171</v>
       </c>
       <c r="F30" t="n">
-        <v>4.24624</v>
+        <v>4.24838</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>4.8204</v>
+        <v>5.01065</v>
       </c>
       <c r="C31" t="n">
-        <v>3.14212</v>
+        <v>3.27585</v>
       </c>
       <c r="D31" t="n">
-        <v>12.6746</v>
+        <v>12.7398</v>
       </c>
       <c r="E31" t="n">
-        <v>4.27236</v>
+        <v>4.28784</v>
       </c>
       <c r="F31" t="n">
-        <v>4.28219</v>
+        <v>4.29358</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>4.58541</v>
+        <v>4.56781</v>
       </c>
       <c r="C32" t="n">
-        <v>3.14836</v>
+        <v>3.34639</v>
       </c>
       <c r="D32" t="n">
-        <v>13.0138</v>
+        <v>13.0819</v>
       </c>
       <c r="E32" t="n">
-        <v>4.1582</v>
+        <v>4.3056</v>
       </c>
       <c r="F32" t="n">
-        <v>4.31884</v>
+        <v>4.37372</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.60002</v>
+        <v>4.57103</v>
       </c>
       <c r="C33" t="n">
-        <v>3.18211</v>
+        <v>3.3811</v>
       </c>
       <c r="D33" t="n">
-        <v>13.413</v>
+        <v>13.4937</v>
       </c>
       <c r="E33" t="n">
-        <v>4.37061</v>
+        <v>4.40406</v>
       </c>
       <c r="F33" t="n">
-        <v>4.4011</v>
+        <v>4.49473</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>4.64066</v>
+        <v>4.60817</v>
       </c>
       <c r="C34" t="n">
-        <v>3.2131</v>
+        <v>3.42161</v>
       </c>
       <c r="D34" t="n">
-        <v>13.7295</v>
+        <v>13.7911</v>
       </c>
       <c r="E34" t="n">
-        <v>4.33489</v>
+        <v>4.27655</v>
       </c>
       <c r="F34" t="n">
-        <v>4.45881</v>
+        <v>4.55285</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>4.92296</v>
+        <v>5.06978</v>
       </c>
       <c r="C35" t="n">
-        <v>3.38297</v>
+        <v>3.50283</v>
       </c>
       <c r="D35" t="n">
-        <v>9.379799999999999</v>
+        <v>9.41188</v>
       </c>
       <c r="E35" t="n">
-        <v>4.14217</v>
+        <v>3.99271</v>
       </c>
       <c r="F35" t="n">
-        <v>4.24018</v>
+        <v>4.0808</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>4.77989</v>
+        <v>4.73165</v>
       </c>
       <c r="C36" t="n">
-        <v>3.32384</v>
+        <v>3.48194</v>
       </c>
       <c r="D36" t="n">
-        <v>9.61469</v>
+        <v>9.685639999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>4.17094</v>
+        <v>4.14916</v>
       </c>
       <c r="F36" t="n">
-        <v>4.26786</v>
+        <v>4.1045</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>4.74295</v>
+        <v>4.83012</v>
       </c>
       <c r="C37" t="n">
-        <v>3.5033</v>
+        <v>3.65966</v>
       </c>
       <c r="D37" t="n">
-        <v>9.817830000000001</v>
+        <v>10.0454</v>
       </c>
       <c r="E37" t="n">
-        <v>4.20528</v>
+        <v>4.18726</v>
       </c>
       <c r="F37" t="n">
-        <v>4.29353</v>
+        <v>4.13054</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>4.8771</v>
+        <v>4.83317</v>
       </c>
       <c r="C38" t="n">
-        <v>3.34618</v>
+        <v>3.43029</v>
       </c>
       <c r="D38" t="n">
-        <v>10.1405</v>
+        <v>10.2091</v>
       </c>
       <c r="E38" t="n">
-        <v>4.22585</v>
+        <v>4.20851</v>
       </c>
       <c r="F38" t="n">
-        <v>4.3256</v>
+        <v>4.17034</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>4.74419</v>
+        <v>4.75254</v>
       </c>
       <c r="C39" t="n">
-        <v>3.25996</v>
+        <v>3.47439</v>
       </c>
       <c r="D39" t="n">
-        <v>10.4652</v>
+        <v>10.6598</v>
       </c>
       <c r="E39" t="n">
-        <v>4.25996</v>
+        <v>4.25205</v>
       </c>
       <c r="F39" t="n">
-        <v>4.35243</v>
+        <v>4.22606</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>4.77071</v>
+        <v>4.73956</v>
       </c>
       <c r="C40" t="n">
-        <v>3.26016</v>
+        <v>3.49434</v>
       </c>
       <c r="D40" t="n">
-        <v>10.7989</v>
+        <v>11.1597</v>
       </c>
       <c r="E40" t="n">
-        <v>4.29639</v>
+        <v>4.27888</v>
       </c>
       <c r="F40" t="n">
-        <v>4.37407</v>
+        <v>4.22129</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>4.6142</v>
+        <v>4.69747</v>
       </c>
       <c r="C41" t="n">
-        <v>3.56587</v>
+        <v>3.73256</v>
       </c>
       <c r="D41" t="n">
-        <v>11.147</v>
+        <v>11.5212</v>
       </c>
       <c r="E41" t="n">
-        <v>4.64564</v>
+        <v>4.45215</v>
       </c>
       <c r="F41" t="n">
-        <v>4.40401</v>
+        <v>4.40362</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>4.62549</v>
+        <v>4.62893</v>
       </c>
       <c r="C42" t="n">
-        <v>3.53855</v>
+        <v>3.79592</v>
       </c>
       <c r="D42" t="n">
-        <v>11.5304</v>
+        <v>11.9102</v>
       </c>
       <c r="E42" t="n">
-        <v>4.36597</v>
+        <v>4.39255</v>
       </c>
       <c r="F42" t="n">
-        <v>4.4539</v>
+        <v>4.43869</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>4.63986</v>
+        <v>4.79771</v>
       </c>
       <c r="C43" t="n">
-        <v>3.64108</v>
+        <v>3.79406</v>
       </c>
       <c r="D43" t="n">
-        <v>11.8977</v>
+        <v>12.2183</v>
       </c>
       <c r="E43" t="n">
-        <v>4.73231</v>
+        <v>4.54404</v>
       </c>
       <c r="F43" t="n">
-        <v>4.48476</v>
+        <v>4.49511</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>4.70111</v>
+        <v>4.67926</v>
       </c>
       <c r="C44" t="n">
-        <v>3.5258</v>
+        <v>3.81852</v>
       </c>
       <c r="D44" t="n">
-        <v>12.3009</v>
+        <v>12.5911</v>
       </c>
       <c r="E44" t="n">
-        <v>4.45024</v>
+        <v>4.45903</v>
       </c>
       <c r="F44" t="n">
-        <v>4.53054</v>
+        <v>4.53769</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>4.79793</v>
+        <v>5.00713</v>
       </c>
       <c r="C45" t="n">
-        <v>3.70524</v>
+        <v>3.88959</v>
       </c>
       <c r="D45" t="n">
-        <v>12.689</v>
+        <v>12.9039</v>
       </c>
       <c r="E45" t="n">
-        <v>4.84403</v>
+        <v>4.69672</v>
       </c>
       <c r="F45" t="n">
-        <v>4.58355</v>
+        <v>4.56179</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.75749</v>
+        <v>4.75168</v>
       </c>
       <c r="C46" t="n">
-        <v>3.76474</v>
+        <v>3.9641</v>
       </c>
       <c r="D46" t="n">
-        <v>13.052</v>
+        <v>13.3097</v>
       </c>
       <c r="E46" t="n">
-        <v>4.90295</v>
+        <v>4.76607</v>
       </c>
       <c r="F46" t="n">
-        <v>4.66436</v>
+        <v>4.65379</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.72048</v>
+        <v>4.80753</v>
       </c>
       <c r="C47" t="n">
-        <v>3.72916</v>
+        <v>3.93399</v>
       </c>
       <c r="D47" t="n">
-        <v>13.3918</v>
+        <v>13.614</v>
       </c>
       <c r="E47" t="n">
-        <v>5.06963</v>
+        <v>4.91588</v>
       </c>
       <c r="F47" t="n">
-        <v>4.82006</v>
+        <v>4.98988</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>4.80766</v>
+        <v>4.80687</v>
       </c>
       <c r="C48" t="n">
-        <v>3.89295</v>
+        <v>4.16548</v>
       </c>
       <c r="D48" t="n">
-        <v>13.7742</v>
+        <v>14.1245</v>
       </c>
       <c r="E48" t="n">
-        <v>5.30954</v>
+        <v>5.14125</v>
       </c>
       <c r="F48" t="n">
-        <v>5.04121</v>
+        <v>5.22671</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>4.78873</v>
+        <v>4.91292</v>
       </c>
       <c r="C49" t="n">
-        <v>3.87545</v>
+        <v>4.04271</v>
       </c>
       <c r="D49" t="n">
-        <v>14.1155</v>
+        <v>14.546</v>
       </c>
       <c r="E49" t="n">
-        <v>5.62636</v>
+        <v>5.47378</v>
       </c>
       <c r="F49" t="n">
-        <v>5.47714</v>
+        <v>5.66089</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>4.96567</v>
+        <v>5.09304</v>
       </c>
       <c r="C50" t="n">
-        <v>4.007</v>
+        <v>4.18136</v>
       </c>
       <c r="D50" t="n">
-        <v>10.9249</v>
+        <v>11.7729</v>
       </c>
       <c r="E50" t="n">
-        <v>4.52047</v>
+        <v>4.32615</v>
       </c>
       <c r="F50" t="n">
-        <v>5.58495</v>
+        <v>6.41853</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>5.38367</v>
+        <v>5.21625</v>
       </c>
       <c r="C51" t="n">
-        <v>3.54715</v>
+        <v>3.63211</v>
       </c>
       <c r="D51" t="n">
-        <v>11.3797</v>
+        <v>12.1278</v>
       </c>
       <c r="E51" t="n">
-        <v>4.5474</v>
+        <v>4.3801</v>
       </c>
       <c r="F51" t="n">
-        <v>5.55206</v>
+        <v>6.27912</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>6.13883</v>
+        <v>6.01921</v>
       </c>
       <c r="C52" t="n">
-        <v>3.75735</v>
+        <v>3.62887</v>
       </c>
       <c r="D52" t="n">
-        <v>11.8697</v>
+        <v>12.8662</v>
       </c>
       <c r="E52" t="n">
-        <v>4.58563</v>
+        <v>4.41748</v>
       </c>
       <c r="F52" t="n">
-        <v>4.90337</v>
+        <v>5.10549</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>5.5528</v>
+        <v>5.44223</v>
       </c>
       <c r="C53" t="n">
-        <v>3.5613</v>
+        <v>3.59368</v>
       </c>
       <c r="D53" t="n">
-        <v>12.1409</v>
+        <v>13.4815</v>
       </c>
       <c r="E53" t="n">
-        <v>4.61148</v>
+        <v>4.50177</v>
       </c>
       <c r="F53" t="n">
-        <v>5.69415</v>
+        <v>6.56384</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>5.47838</v>
+        <v>5.42145</v>
       </c>
       <c r="C54" t="n">
-        <v>3.55925</v>
+        <v>3.62459</v>
       </c>
       <c r="D54" t="n">
-        <v>12.8941</v>
+        <v>14.5418</v>
       </c>
       <c r="E54" t="n">
-        <v>4.66307</v>
+        <v>4.49353</v>
       </c>
       <c r="F54" t="n">
-        <v>5.62406</v>
+        <v>6.46507</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>5.49962</v>
+        <v>5.4352</v>
       </c>
       <c r="C55" t="n">
-        <v>3.61807</v>
+        <v>3.70441</v>
       </c>
       <c r="D55" t="n">
-        <v>13.6874</v>
+        <v>15.4387</v>
       </c>
       <c r="E55" t="n">
-        <v>4.65512</v>
+        <v>4.87119</v>
       </c>
       <c r="F55" t="n">
-        <v>4.88072</v>
+        <v>4.94623</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>5.21187</v>
+        <v>5.47454</v>
       </c>
       <c r="C56" t="n">
-        <v>3.74221</v>
+        <v>3.64172</v>
       </c>
       <c r="D56" t="n">
-        <v>13.2169</v>
+        <v>14.6661</v>
       </c>
       <c r="E56" t="n">
-        <v>4.74152</v>
+        <v>4.58778</v>
       </c>
       <c r="F56" t="n">
-        <v>5.91399</v>
+        <v>6.71879</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>5.54533</v>
+        <v>5.48281</v>
       </c>
       <c r="C57" t="n">
-        <v>3.66227</v>
+        <v>3.64104</v>
       </c>
       <c r="D57" t="n">
-        <v>15.7688</v>
+        <v>17.8019</v>
       </c>
       <c r="E57" t="n">
-        <v>4.75858</v>
+        <v>4.98745</v>
       </c>
       <c r="F57" t="n">
-        <v>5.20428</v>
+        <v>5.33888</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>5.56717</v>
+        <v>5.47524</v>
       </c>
       <c r="C58" t="n">
-        <v>3.70923</v>
+        <v>3.81454</v>
       </c>
       <c r="D58" t="n">
-        <v>16.6429</v>
+        <v>18.4773</v>
       </c>
       <c r="E58" t="n">
-        <v>5.02927</v>
+        <v>5.04333</v>
       </c>
       <c r="F58" t="n">
-        <v>5.23675</v>
+        <v>5.21705</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>5.61232</v>
+        <v>5.53239</v>
       </c>
       <c r="C59" t="n">
-        <v>3.71399</v>
+        <v>3.71227</v>
       </c>
       <c r="D59" t="n">
-        <v>16.2701</v>
+        <v>18.3551</v>
       </c>
       <c r="E59" t="n">
-        <v>4.97015</v>
+        <v>4.88502</v>
       </c>
       <c r="F59" t="n">
-        <v>5.86988</v>
+        <v>6.0693</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>5.24965</v>
+        <v>5.37081</v>
       </c>
       <c r="C60" t="n">
-        <v>3.78291</v>
+        <v>3.82001</v>
       </c>
       <c r="D60" t="n">
-        <v>16.596</v>
+        <v>18.1</v>
       </c>
       <c r="E60" t="n">
-        <v>5.1475</v>
+        <v>4.96881</v>
       </c>
       <c r="F60" t="n">
-        <v>6.22378</v>
+        <v>6.15383</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>5.70478</v>
+        <v>5.59978</v>
       </c>
       <c r="C61" t="n">
-        <v>3.75648</v>
+        <v>3.84077</v>
       </c>
       <c r="D61" t="n">
-        <v>17.3059</v>
+        <v>18.6232</v>
       </c>
       <c r="E61" t="n">
-        <v>5.30732</v>
+        <v>5.28948</v>
       </c>
       <c r="F61" t="n">
-        <v>6.45032</v>
+        <v>6.50487</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>5.3482</v>
+        <v>5.37095</v>
       </c>
       <c r="C62" t="n">
-        <v>4.11296</v>
+        <v>3.82687</v>
       </c>
       <c r="D62" t="n">
-        <v>17.8171</v>
+        <v>18.9466</v>
       </c>
       <c r="E62" t="n">
-        <v>5.4999</v>
+        <v>5.49553</v>
       </c>
       <c r="F62" t="n">
-        <v>6.4273</v>
+        <v>6.44343</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>5.46341</v>
+        <v>5.55412</v>
       </c>
       <c r="C63" t="n">
-        <v>3.98778</v>
+        <v>3.99968</v>
       </c>
       <c r="D63" t="n">
-        <v>17.8713</v>
+        <v>18.6477</v>
       </c>
       <c r="E63" t="n">
-        <v>5.77833</v>
+        <v>5.795</v>
       </c>
       <c r="F63" t="n">
-        <v>7.30064</v>
+        <v>7.60281</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>5.97205</v>
+        <v>5.91536</v>
       </c>
       <c r="C64" t="n">
-        <v>4.06378</v>
+        <v>4.12676</v>
       </c>
       <c r="D64" t="n">
-        <v>11.8631</v>
+        <v>12.9591</v>
       </c>
       <c r="E64" t="n">
-        <v>4.93038</v>
+        <v>5.26215</v>
       </c>
       <c r="F64" t="n">
-        <v>5.9048</v>
+        <v>5.60187</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>6.19494</v>
+        <v>6.23023</v>
       </c>
       <c r="C65" t="n">
-        <v>4.95856</v>
+        <v>6.59601</v>
       </c>
       <c r="D65" t="n">
-        <v>12.7954</v>
+        <v>13.902</v>
       </c>
       <c r="E65" t="n">
-        <v>4.94584</v>
+        <v>5.40887</v>
       </c>
       <c r="F65" t="n">
-        <v>6.00147</v>
+        <v>5.74859</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>6.62203</v>
+        <v>6.6663</v>
       </c>
       <c r="C66" t="n">
-        <v>5.00017</v>
+        <v>6.73312</v>
       </c>
       <c r="D66" t="n">
-        <v>13.7182</v>
+        <v>15.4066</v>
       </c>
       <c r="E66" t="n">
-        <v>5.03432</v>
+        <v>5.96234</v>
       </c>
       <c r="F66" t="n">
-        <v>6.23337</v>
+        <v>5.96067</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>7.08455</v>
+        <v>8.52154</v>
       </c>
       <c r="C67" t="n">
-        <v>5.09184</v>
+        <v>6.64099</v>
       </c>
       <c r="D67" t="n">
-        <v>14.8642</v>
+        <v>15.8514</v>
       </c>
       <c r="E67" t="n">
-        <v>5.09292</v>
+        <v>5.94135</v>
       </c>
       <c r="F67" t="n">
-        <v>6.43752</v>
+        <v>6.10036</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>7.12462</v>
+        <v>8.24175</v>
       </c>
       <c r="C68" t="n">
-        <v>5.19413</v>
+        <v>6.32505</v>
       </c>
       <c r="D68" t="n">
-        <v>16.0759</v>
+        <v>16.7731</v>
       </c>
       <c r="E68" t="n">
-        <v>5.30384</v>
+        <v>6.55969</v>
       </c>
       <c r="F68" t="n">
-        <v>6.6025</v>
+        <v>6.23616</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>7.28394</v>
+        <v>8.87785</v>
       </c>
       <c r="C69" t="n">
-        <v>5.50582</v>
+        <v>6.8849</v>
       </c>
       <c r="D69" t="n">
-        <v>16.5617</v>
+        <v>17.4786</v>
       </c>
       <c r="E69" t="n">
-        <v>5.27844</v>
+        <v>5.82919</v>
       </c>
       <c r="F69" t="n">
-        <v>6.68449</v>
+        <v>6.4245</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>8.34999</v>
+        <v>9.089169999999999</v>
       </c>
       <c r="C70" t="n">
-        <v>6.60674</v>
+        <v>7.03391</v>
       </c>
       <c r="D70" t="n">
-        <v>16.569</v>
+        <v>17.5186</v>
       </c>
       <c r="E70" t="n">
-        <v>5.29682</v>
+        <v>6.84516</v>
       </c>
       <c r="F70" t="n">
-        <v>6.81663</v>
+        <v>6.44565</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>8.731260000000001</v>
+        <v>9.12818</v>
       </c>
       <c r="C71" t="n">
-        <v>6.97931</v>
+        <v>7.04302</v>
       </c>
       <c r="D71" t="n">
-        <v>17.3308</v>
+        <v>18.2416</v>
       </c>
       <c r="E71" t="n">
-        <v>6.04575</v>
+        <v>6.93523</v>
       </c>
       <c r="F71" t="n">
-        <v>6.51822</v>
+        <v>6.47724</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>7.22007</v>
+        <v>9.12504</v>
       </c>
       <c r="C72" t="n">
-        <v>5.34253</v>
+        <v>7.09163</v>
       </c>
       <c r="D72" t="n">
-        <v>18.2277</v>
+        <v>18.929</v>
       </c>
       <c r="E72" t="n">
-        <v>6.1658</v>
+        <v>7.02837</v>
       </c>
       <c r="F72" t="n">
-        <v>6.666</v>
+        <v>6.68087</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>7.71005</v>
+        <v>9.12696</v>
       </c>
       <c r="C73" t="n">
-        <v>5.97779</v>
+        <v>7.02345</v>
       </c>
       <c r="D73" t="n">
-        <v>19.1217</v>
+        <v>19.1502</v>
       </c>
       <c r="E73" t="n">
-        <v>6.30815</v>
+        <v>7.12791</v>
       </c>
       <c r="F73" t="n">
-        <v>6.89444</v>
+        <v>6.8323</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>7.51305</v>
+        <v>7.92502</v>
       </c>
       <c r="C74" t="n">
-        <v>5.68511</v>
+        <v>6.04574</v>
       </c>
       <c r="D74" t="n">
-        <v>19.9761</v>
+        <v>19.6246</v>
       </c>
       <c r="E74" t="n">
-        <v>7.73012</v>
+        <v>6.77293</v>
       </c>
       <c r="F74" t="n">
-        <v>7.27202</v>
+        <v>6.88478</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>11.1016</v>
+        <v>8.931789999999999</v>
       </c>
       <c r="C75" t="n">
-        <v>9.0488</v>
+        <v>6.68027</v>
       </c>
       <c r="D75" t="n">
-        <v>19.8819</v>
+        <v>19.5962</v>
       </c>
       <c r="E75" t="n">
-        <v>8.12336</v>
+        <v>6.76698</v>
       </c>
       <c r="F75" t="n">
-        <v>7.36937</v>
+        <v>7.21659</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>11.1872</v>
+        <v>8.43201</v>
       </c>
       <c r="C76" t="n">
-        <v>9.220800000000001</v>
+        <v>6.36369</v>
       </c>
       <c r="D76" t="n">
-        <v>20.2102</v>
+        <v>20.2433</v>
       </c>
       <c r="E76" t="n">
-        <v>8.0717</v>
+        <v>6.66756</v>
       </c>
       <c r="F76" t="n">
-        <v>8.1829</v>
+        <v>8.233790000000001</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>11.2556</v>
+        <v>8.29532</v>
       </c>
       <c r="C77" t="n">
-        <v>9.25642</v>
+        <v>6.32712</v>
       </c>
       <c r="D77" t="n">
-        <v>23.2191</v>
+        <v>23.2555</v>
       </c>
       <c r="E77" t="n">
-        <v>8.368869999999999</v>
+        <v>6.95118</v>
       </c>
       <c r="F77" t="n">
-        <v>9.641909999999999</v>
+        <v>9.601889999999999</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>8.33661</v>
+        <v>9.55219</v>
       </c>
       <c r="C78" t="n">
-        <v>6.61041</v>
+        <v>7.43858</v>
       </c>
       <c r="D78" t="n">
-        <v>20.6291</v>
+        <v>19.8254</v>
       </c>
       <c r="E78" t="n">
-        <v>9.775169999999999</v>
+        <v>11.5094</v>
       </c>
       <c r="F78" t="n">
-        <v>12.9898</v>
+        <v>11.0013</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>12.3165</v>
+        <v>8.386850000000001</v>
       </c>
       <c r="C79" t="n">
-        <v>13.3439</v>
+        <v>12.7305</v>
       </c>
       <c r="D79" t="n">
-        <v>21.8467</v>
+        <v>20.6355</v>
       </c>
       <c r="E79" t="n">
-        <v>10.5888</v>
+        <v>11.7738</v>
       </c>
       <c r="F79" t="n">
-        <v>12.7566</v>
+        <v>10.5571</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>12.622</v>
+        <v>8.68215</v>
       </c>
       <c r="C80" t="n">
-        <v>13.6568</v>
+        <v>13.029</v>
       </c>
       <c r="D80" t="n">
-        <v>23.0646</v>
+        <v>21.8848</v>
       </c>
       <c r="E80" t="n">
-        <v>10.4145</v>
+        <v>11.7866</v>
       </c>
       <c r="F80" t="n">
-        <v>13.0598</v>
+        <v>10.9344</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>16.8</v>
+        <v>16.1238</v>
       </c>
       <c r="C81" t="n">
-        <v>13.6929</v>
+        <v>13.0833</v>
       </c>
       <c r="D81" t="n">
-        <v>24.1658</v>
+        <v>22.8407</v>
       </c>
       <c r="E81" t="n">
-        <v>10.258</v>
+        <v>11.5267</v>
       </c>
       <c r="F81" t="n">
-        <v>12.4751</v>
+        <v>10.9834</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>16.8682</v>
+        <v>16.1983</v>
       </c>
       <c r="C82" t="n">
-        <v>13.7744</v>
+        <v>13.1504</v>
       </c>
       <c r="D82" t="n">
-        <v>24.9354</v>
+        <v>23.6516</v>
       </c>
       <c r="E82" t="n">
-        <v>10.96</v>
+        <v>12.0824</v>
       </c>
       <c r="F82" t="n">
-        <v>13.5987</v>
+        <v>11.1942</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>16.931</v>
+        <v>16.2604</v>
       </c>
       <c r="C83" t="n">
-        <v>13.843</v>
+        <v>13.1897</v>
       </c>
       <c r="D83" t="n">
-        <v>26.1671</v>
+        <v>25.0328</v>
       </c>
       <c r="E83" t="n">
-        <v>11.1622</v>
+        <v>12.1716</v>
       </c>
       <c r="F83" t="n">
-        <v>13.5822</v>
+        <v>11.2992</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>16.9753</v>
+        <v>16.327</v>
       </c>
       <c r="C84" t="n">
-        <v>13.9171</v>
+        <v>13.2642</v>
       </c>
       <c r="D84" t="n">
-        <v>26.8893</v>
+        <v>25.6509</v>
       </c>
       <c r="E84" t="n">
-        <v>12.3705</v>
+        <v>12.4763</v>
       </c>
       <c r="F84" t="n">
-        <v>13.7357</v>
+        <v>11.3344</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>17.0816</v>
+        <v>16.4127</v>
       </c>
       <c r="C85" t="n">
-        <v>13.9616</v>
+        <v>13.331</v>
       </c>
       <c r="D85" t="n">
-        <v>28.4206</v>
+        <v>27.1807</v>
       </c>
       <c r="E85" t="n">
-        <v>11.9132</v>
+        <v>12.4789</v>
       </c>
       <c r="F85" t="n">
-        <v>12.3527</v>
+        <v>12.3812</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>17.1303</v>
+        <v>16.4613</v>
       </c>
       <c r="C86" t="n">
-        <v>14.0546</v>
+        <v>13.3414</v>
       </c>
       <c r="D86" t="n">
-        <v>29.8906</v>
+        <v>28.1064</v>
       </c>
       <c r="E86" t="n">
-        <v>12.186</v>
+        <v>12.6461</v>
       </c>
       <c r="F86" t="n">
-        <v>12.6763</v>
+        <v>12.5794</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>17.1523</v>
+        <v>16.5086</v>
       </c>
       <c r="C87" t="n">
-        <v>14.1241</v>
+        <v>13.4053</v>
       </c>
       <c r="D87" t="n">
-        <v>30.5501</v>
+        <v>28.8852</v>
       </c>
       <c r="E87" t="n">
-        <v>12.3059</v>
+        <v>12.604</v>
       </c>
       <c r="F87" t="n">
-        <v>12.5084</v>
+        <v>12.2681</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>17.1681</v>
+        <v>16.5517</v>
       </c>
       <c r="C88" t="n">
-        <v>14.1293</v>
+        <v>13.433</v>
       </c>
       <c r="D88" t="n">
-        <v>31.0952</v>
+        <v>30.9779</v>
       </c>
       <c r="E88" t="n">
-        <v>12.2514</v>
+        <v>12.5955</v>
       </c>
       <c r="F88" t="n">
-        <v>14.6815</v>
+        <v>15.0049</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>17.2227</v>
+        <v>16.5097</v>
       </c>
       <c r="C89" t="n">
-        <v>14.156</v>
+        <v>13.2862</v>
       </c>
       <c r="D89" t="n">
-        <v>31.2948</v>
+        <v>30.4941</v>
       </c>
       <c r="E89" t="n">
-        <v>12.5596</v>
+        <v>12.6333</v>
       </c>
       <c r="F89" t="n">
-        <v>12.651</v>
+        <v>12.3242</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>17.1074</v>
+        <v>16.496</v>
       </c>
       <c r="C90" t="n">
-        <v>14.1253</v>
+        <v>13.227</v>
       </c>
       <c r="D90" t="n">
-        <v>34.4172</v>
+        <v>32.3849</v>
       </c>
       <c r="E90" t="n">
-        <v>12.8046</v>
+        <v>12.8377</v>
       </c>
       <c r="F90" t="n">
-        <v>14.9026</v>
+        <v>12.4784</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>17.421</v>
+        <v>16.7644</v>
       </c>
       <c r="C91" t="n">
-        <v>14.434</v>
+        <v>13.6041</v>
       </c>
       <c r="D91" t="n">
-        <v>35.5663</v>
+        <v>33.764</v>
       </c>
       <c r="E91" t="n">
-        <v>13.0602</v>
+        <v>13.1202</v>
       </c>
       <c r="F91" t="n">
-        <v>15.2846</v>
+        <v>13.1563</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>17.5261</v>
+        <v>16.8204</v>
       </c>
       <c r="C92" t="n">
-        <v>14.5687</v>
+        <v>13.674</v>
       </c>
       <c r="D92" t="n">
-        <v>32.3695</v>
+        <v>31.2479</v>
       </c>
       <c r="E92" t="n">
-        <v>19.5218</v>
+        <v>18.8075</v>
       </c>
       <c r="F92" t="n">
-        <v>18.5066</v>
+        <v>17.889</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>17.7599</v>
+        <v>17.1121</v>
       </c>
       <c r="C93" t="n">
-        <v>14.7485</v>
+        <v>13.8454</v>
       </c>
       <c r="D93" t="n">
-        <v>33.1598</v>
+        <v>31.9706</v>
       </c>
       <c r="E93" t="n">
-        <v>19.7083</v>
+        <v>18.7497</v>
       </c>
       <c r="F93" t="n">
-        <v>18.6418</v>
+        <v>18.0052</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>17.9056</v>
+        <v>17.2077</v>
       </c>
       <c r="C94" t="n">
-        <v>17.6653</v>
+        <v>17.008</v>
       </c>
       <c r="D94" t="n">
-        <v>33.925</v>
+        <v>32.7701</v>
       </c>
       <c r="E94" t="n">
-        <v>19.8303</v>
+        <v>18.911</v>
       </c>
       <c r="F94" t="n">
-        <v>18.7496</v>
+        <v>18.1027</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>22.0528</v>
+        <v>21.4618</v>
       </c>
       <c r="C95" t="n">
-        <v>17.6857</v>
+        <v>17.1521</v>
       </c>
       <c r="D95" t="n">
-        <v>34.9093</v>
+        <v>33.7568</v>
       </c>
       <c r="E95" t="n">
-        <v>20.0527</v>
+        <v>19.2829</v>
       </c>
       <c r="F95" t="n">
-        <v>18.8243</v>
+        <v>18.223</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>22.2261</v>
+        <v>21.4458</v>
       </c>
       <c r="C96" t="n">
-        <v>17.7152</v>
+        <v>17.1716</v>
       </c>
       <c r="D96" t="n">
-        <v>35.7653</v>
+        <v>34.5941</v>
       </c>
       <c r="E96" t="n">
-        <v>20.4094</v>
+        <v>19.3571</v>
       </c>
       <c r="F96" t="n">
-        <v>18.9714</v>
+        <v>18.3008</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>22.2651</v>
+        <v>21.4791</v>
       </c>
       <c r="C97" t="n">
-        <v>17.7492</v>
+        <v>17.2472</v>
       </c>
       <c r="D97" t="n">
-        <v>36.7174</v>
+        <v>35.6018</v>
       </c>
       <c r="E97" t="n">
-        <v>20.3464</v>
+        <v>19.5544</v>
       </c>
       <c r="F97" t="n">
-        <v>19.0721</v>
+        <v>18.4371</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>22.2291</v>
+        <v>21.4862</v>
       </c>
       <c r="C98" t="n">
-        <v>17.8372</v>
+        <v>17.2499</v>
       </c>
       <c r="D98" t="n">
-        <v>37.4024</v>
+        <v>36.3049</v>
       </c>
       <c r="E98" t="n">
-        <v>20.5499</v>
+        <v>19.6942</v>
       </c>
       <c r="F98" t="n">
-        <v>19.2146</v>
+        <v>18.5531</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>22.1654</v>
+        <v>21.5214</v>
       </c>
       <c r="C99" t="n">
-        <v>17.7919</v>
+        <v>17.2716</v>
       </c>
       <c r="D99" t="n">
-        <v>38.382</v>
+        <v>37.2918</v>
       </c>
       <c r="E99" t="n">
-        <v>20.6131</v>
+        <v>19.9509</v>
       </c>
       <c r="F99" t="n">
-        <v>19.5547</v>
+        <v>18.7676</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>22.2362</v>
+        <v>21.5106</v>
       </c>
       <c r="C100" t="n">
-        <v>17.8559</v>
+        <v>17.335</v>
       </c>
       <c r="D100" t="n">
-        <v>39.6976</v>
+        <v>38.2997</v>
       </c>
       <c r="E100" t="n">
-        <v>20.3765</v>
+        <v>20.0956</v>
       </c>
       <c r="F100" t="n">
-        <v>18.9167</v>
+        <v>18.9424</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>21.3307</v>
+        <v>21.5598</v>
       </c>
       <c r="C101" t="n">
-        <v>17.0891</v>
+        <v>17.3537</v>
       </c>
       <c r="D101" t="n">
-        <v>40.6835</v>
+        <v>39.6882</v>
       </c>
       <c r="E101" t="n">
-        <v>20.5816</v>
+        <v>20.4117</v>
       </c>
       <c r="F101" t="n">
-        <v>19.7779</v>
+        <v>19.0824</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>21.4161</v>
+        <v>21.618</v>
       </c>
       <c r="C102" t="n">
-        <v>17.1621</v>
+        <v>17.4516</v>
       </c>
       <c r="D102" t="n">
-        <v>41.4709</v>
+        <v>40.4941</v>
       </c>
       <c r="E102" t="n">
-        <v>20.6769</v>
+        <v>20.6489</v>
       </c>
       <c r="F102" t="n">
-        <v>20.0807</v>
+        <v>19.2069</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>21.4007</v>
+        <v>21.6119</v>
       </c>
       <c r="C103" t="n">
-        <v>17.2424</v>
+        <v>17.4923</v>
       </c>
       <c r="D103" t="n">
-        <v>42.8275</v>
+        <v>41.7952</v>
       </c>
       <c r="E103" t="n">
-        <v>20.907</v>
+        <v>20.9537</v>
       </c>
       <c r="F103" t="n">
-        <v>19.5697</v>
+        <v>19.5142</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>21.4956</v>
+        <v>21.6458</v>
       </c>
       <c r="C104" t="n">
-        <v>17.3462</v>
+        <v>17.609</v>
       </c>
       <c r="D104" t="n">
-        <v>43.652</v>
+        <v>42.7554</v>
       </c>
       <c r="E104" t="n">
-        <v>21.0489</v>
+        <v>21.1828</v>
       </c>
       <c r="F104" t="n">
-        <v>20.589</v>
+        <v>19.7259</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>21.5343</v>
+        <v>21.7336</v>
       </c>
       <c r="C105" t="n">
-        <v>17.4314</v>
+        <v>17.6532</v>
       </c>
       <c r="D105" t="n">
-        <v>44.7267</v>
+        <v>43.8256</v>
       </c>
       <c r="E105" t="n">
-        <v>21.2687</v>
+        <v>21.4651</v>
       </c>
       <c r="F105" t="n">
-        <v>20.9958</v>
+        <v>20.0952</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>21.6804</v>
+        <v>21.8927</v>
       </c>
       <c r="C106" t="n">
-        <v>17.5885</v>
+        <v>17.8232</v>
       </c>
       <c r="D106" t="n">
-        <v>45.9424</v>
+        <v>45.2285</v>
       </c>
       <c r="E106" t="n">
-        <v>21.6271</v>
+        <v>21.952</v>
       </c>
       <c r="F106" t="n">
-        <v>21.257</v>
+        <v>20.5061</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>21.864</v>
+        <v>22.0529</v>
       </c>
       <c r="C107" t="n">
-        <v>17.8336</v>
+        <v>18.0069</v>
       </c>
       <c r="D107" t="n">
-        <v>38.1542</v>
+        <v>38.1967</v>
       </c>
       <c r="E107" t="n">
-        <v>25.3948</v>
+        <v>23.3935</v>
       </c>
       <c r="F107" t="n">
-        <v>23.8179</v>
+        <v>22.8358</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>22.8682</v>
+        <v>22.0568</v>
       </c>
       <c r="C108" t="n">
-        <v>18.4799</v>
+        <v>18.5879</v>
       </c>
       <c r="D108" t="n">
-        <v>39.799</v>
+        <v>39.0595</v>
       </c>
       <c r="E108" t="n">
-        <v>25.1362</v>
+        <v>23.6664</v>
       </c>
       <c r="F108" t="n">
-        <v>23.4056</v>
+        <v>23.1201</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>23.2871</v>
+        <v>22.8463</v>
       </c>
       <c r="C109" t="n">
-        <v>18.6362</v>
+        <v>18.6715</v>
       </c>
       <c r="D109" t="n">
-        <v>40.498</v>
+        <v>39.776</v>
       </c>
       <c r="E109" t="n">
-        <v>25.1161</v>
+        <v>23.8315</v>
       </c>
       <c r="F109" t="n">
-        <v>23.6634</v>
+        <v>23.2324</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>24.7321</v>
+        <v>24.4979</v>
       </c>
       <c r="C110" t="n">
-        <v>18.7308</v>
+        <v>18.664</v>
       </c>
       <c r="D110" t="n">
-        <v>41.1245</v>
+        <v>40.4597</v>
       </c>
       <c r="E110" t="n">
-        <v>25.4622</v>
+        <v>24.0441</v>
       </c>
       <c r="F110" t="n">
-        <v>24.0854</v>
+        <v>23.3727</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>24.6547</v>
+        <v>24.6567</v>
       </c>
       <c r="C111" t="n">
-        <v>18.4908</v>
+        <v>18.7621</v>
       </c>
       <c r="D111" t="n">
-        <v>41.5992</v>
+        <v>41.4068</v>
       </c>
       <c r="E111" t="n">
-        <v>25.7061</v>
+        <v>24.3229</v>
       </c>
       <c r="F111" t="n">
-        <v>24.0558</v>
+        <v>23.6079</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>24.5931</v>
+        <v>24.3119</v>
       </c>
       <c r="C112" t="n">
-        <v>18.8314</v>
+        <v>18.8375</v>
       </c>
       <c r="D112" t="n">
-        <v>42.4063</v>
+        <v>42.1711</v>
       </c>
       <c r="E112" t="n">
-        <v>25.8447</v>
+        <v>24.5748</v>
       </c>
       <c r="F112" t="n">
-        <v>24.1199</v>
+        <v>23.812</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>24.6266</v>
+        <v>24.7281</v>
       </c>
       <c r="C113" t="n">
-        <v>18.792</v>
+        <v>18.8756</v>
       </c>
       <c r="D113" t="n">
-        <v>43.4246</v>
+        <v>43.2909</v>
       </c>
       <c r="E113" t="n">
-        <v>26.07</v>
+        <v>24.8542</v>
       </c>
       <c r="F113" t="n">
-        <v>24.2493</v>
+        <v>24.0873</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>24.7274</v>
+        <v>24.6996</v>
       </c>
       <c r="C114" t="n">
-        <v>18.8685</v>
+        <v>18.9264</v>
       </c>
       <c r="D114" t="n">
-        <v>44.3232</v>
+        <v>44.1375</v>
       </c>
       <c r="E114" t="n">
-        <v>26.3058</v>
+        <v>25.1438</v>
       </c>
       <c r="F114" t="n">
-        <v>24.5932</v>
+        <v>24.3376</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>24.8602</v>
+        <v>24.6276</v>
       </c>
       <c r="C115" t="n">
-        <v>18.9745</v>
+        <v>19.0503</v>
       </c>
       <c r="D115" t="n">
-        <v>45.3281</v>
+        <v>45.1356</v>
       </c>
       <c r="E115" t="n">
-        <v>26.5565</v>
+        <v>25.404</v>
       </c>
       <c r="F115" t="n">
-        <v>25.0009</v>
+        <v>24.6619</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>24.8656</v>
+        <v>24.6246</v>
       </c>
       <c r="C116" t="n">
-        <v>19.1532</v>
+        <v>19.1579</v>
       </c>
       <c r="D116" t="n">
-        <v>46.3224</v>
+        <v>46.2</v>
       </c>
       <c r="E116" t="n">
-        <v>26.6644</v>
+        <v>25.6729</v>
       </c>
       <c r="F116" t="n">
-        <v>25.4768</v>
+        <v>24.9766</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>24.6298</v>
+        <v>24.7779</v>
       </c>
       <c r="C117" t="n">
-        <v>19.0262</v>
+        <v>19.2613</v>
       </c>
       <c r="D117" t="n">
-        <v>47.2852</v>
+        <v>47.1062</v>
       </c>
       <c r="E117" t="n">
-        <v>26.9363</v>
+        <v>26.1091</v>
       </c>
       <c r="F117" t="n">
-        <v>26.0486</v>
+        <v>25.3423</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>24.8415</v>
+        <v>24.8162</v>
       </c>
       <c r="C118" t="n">
-        <v>19.1811</v>
+        <v>19.4646</v>
       </c>
       <c r="D118" t="n">
-        <v>48.5413</v>
+        <v>48.4794</v>
       </c>
       <c r="E118" t="n">
-        <v>27.3186</v>
+        <v>26.5607</v>
       </c>
       <c r="F118" t="n">
-        <v>26.4491</v>
+        <v>25.8369</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>25.2705</v>
+        <v>24.8246</v>
       </c>
       <c r="C119" t="n">
-        <v>19.7628</v>
+        <v>19.67</v>
       </c>
       <c r="D119" t="n">
-        <v>49.4359</v>
+        <v>49.2259</v>
       </c>
       <c r="E119" t="n">
-        <v>27.7395</v>
+        <v>26.9637</v>
       </c>
       <c r="F119" t="n">
-        <v>26.5594</v>
+        <v>26.239</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>25.7897</v>
+        <v>24.9622</v>
       </c>
       <c r="C120" t="n">
-        <v>19.9339</v>
+        <v>19.8346</v>
       </c>
       <c r="D120" t="n">
-        <v>50.9716</v>
+        <v>50.774</v>
       </c>
       <c r="E120" t="n">
-        <v>28.0798</v>
+        <v>27.638</v>
       </c>
       <c r="F120" t="n">
-        <v>27.9629</v>
+        <v>26.909</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>25.5067</v>
+        <v>25.1026</v>
       </c>
       <c r="C121" t="n">
-        <v>20.2259</v>
+        <v>20.1925</v>
       </c>
       <c r="D121" t="n">
-        <v>41.8497</v>
+        <v>41.0901</v>
       </c>
       <c r="E121" t="n">
-        <v>29.8323</v>
+        <v>27.0906</v>
       </c>
       <c r="F121" t="n">
-        <v>27.6134</v>
+        <v>26.6652</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>26.0447</v>
+        <v>25.7511</v>
       </c>
       <c r="C122" t="n">
-        <v>21.0357</v>
+        <v>20.7327</v>
       </c>
       <c r="D122" t="n">
-        <v>43.0172</v>
+        <v>41.8601</v>
       </c>
       <c r="E122" t="n">
-        <v>30.3838</v>
+        <v>27.3664</v>
       </c>
       <c r="F122" t="n">
-        <v>27.903</v>
+        <v>26.9571</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>26.6864</v>
+        <v>26.0311</v>
       </c>
       <c r="C123" t="n">
-        <v>21.1189</v>
+        <v>20.7934</v>
       </c>
       <c r="D123" t="n">
-        <v>43.7232</v>
+        <v>42.6079</v>
       </c>
       <c r="E123" t="n">
-        <v>30.5727</v>
+        <v>27.1434</v>
       </c>
       <c r="F123" t="n">
-        <v>28.0451</v>
+        <v>27.1622</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>32.333</v>
+        <v>31.8244</v>
       </c>
       <c r="C124" t="n">
-        <v>21.5911</v>
+        <v>20.92</v>
       </c>
       <c r="D124" t="n">
-        <v>44.8657</v>
+        <v>43.8551</v>
       </c>
       <c r="E124" t="n">
-        <v>30.8473</v>
+        <v>27.8495</v>
       </c>
       <c r="F124" t="n">
-        <v>28.3659</v>
+        <v>27.3504</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>32.682</v>
+        <v>31.7089</v>
       </c>
       <c r="C125" t="n">
-        <v>21.5765</v>
+        <v>21.0058</v>
       </c>
       <c r="D125" t="n">
-        <v>45.7348</v>
+        <v>44.5952</v>
       </c>
       <c r="E125" t="n">
-        <v>30.9156</v>
+        <v>28.0997</v>
       </c>
       <c r="F125" t="n">
-        <v>28.3883</v>
+        <v>27.6747</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>32.5056</v>
+        <v>32.126</v>
       </c>
       <c r="C126" t="n">
-        <v>21.7516</v>
+        <v>21.178</v>
       </c>
       <c r="D126" t="n">
-        <v>46.3857</v>
+        <v>44.8166</v>
       </c>
       <c r="E126" t="n">
-        <v>30.9405</v>
+        <v>28.4224</v>
       </c>
       <c r="F126" t="n">
-        <v>28.535</v>
+        <v>27.7432</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>32.8232</v>
+        <v>31.9636</v>
       </c>
       <c r="C127" t="n">
-        <v>21.8354</v>
+        <v>21.2658</v>
       </c>
       <c r="D127" t="n">
-        <v>47.2738</v>
+        <v>45.8374</v>
       </c>
       <c r="E127" t="n">
-        <v>30.91</v>
+        <v>28.6381</v>
       </c>
       <c r="F127" t="n">
-        <v>29.0612</v>
+        <v>28.1457</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>32.125</v>
+        <v>31.9302</v>
       </c>
       <c r="C128" t="n">
-        <v>21.801</v>
+        <v>21.4457</v>
       </c>
       <c r="D128" t="n">
-        <v>48.1389</v>
+        <v>46.6385</v>
       </c>
       <c r="E128" t="n">
-        <v>30.639</v>
+        <v>29.0064</v>
       </c>
       <c r="F128" t="n">
-        <v>28.9198</v>
+        <v>28.4755</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>32.0404</v>
+        <v>31.8845</v>
       </c>
       <c r="C129" t="n">
-        <v>21.9751</v>
+        <v>21.6179</v>
       </c>
       <c r="D129" t="n">
-        <v>49.4636</v>
+        <v>47.8457</v>
       </c>
       <c r="E129" t="n">
-        <v>30.5292</v>
+        <v>29.336</v>
       </c>
       <c r="F129" t="n">
-        <v>29.7007</v>
+        <v>28.7439</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>32.1547</v>
+        <v>31.9304</v>
       </c>
       <c r="C130" t="n">
-        <v>22.1939</v>
+        <v>21.831</v>
       </c>
       <c r="D130" t="n">
-        <v>50.5096</v>
+        <v>48.8102</v>
       </c>
       <c r="E130" t="n">
-        <v>31.464</v>
+        <v>29.6962</v>
       </c>
       <c r="F130" t="n">
-        <v>29.9708</v>
+        <v>29.2359</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>32.2799</v>
+        <v>31.9364</v>
       </c>
       <c r="C131" t="n">
-        <v>22.3788</v>
+        <v>22.0025</v>
       </c>
       <c r="D131" t="n">
-        <v>51.5654</v>
+        <v>49.8588</v>
       </c>
       <c r="E131" t="n">
-        <v>31.3799</v>
+        <v>29.9795</v>
       </c>
       <c r="F131" t="n">
-        <v>29.921</v>
+        <v>29.7609</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>32.239</v>
+        <v>31.9426</v>
       </c>
       <c r="C132" t="n">
-        <v>22.5936</v>
+        <v>22.2966</v>
       </c>
       <c r="D132" t="n">
-        <v>52.1884</v>
+        <v>50.9884</v>
       </c>
       <c r="E132" t="n">
-        <v>32.1705</v>
+        <v>30.5415</v>
       </c>
       <c r="F132" t="n">
-        <v>30.7765</v>
+        <v>30.1309</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>32.4966</v>
+        <v>31.983</v>
       </c>
       <c r="C133" t="n">
-        <v>22.9235</v>
+        <v>22.6035</v>
       </c>
       <c r="D133" t="n">
-        <v>53.7327</v>
+        <v>51.9934</v>
       </c>
       <c r="E133" t="n">
-        <v>32.7181</v>
+        <v>31.0745</v>
       </c>
       <c r="F133" t="n">
-        <v>31.7651</v>
+        <v>30.8641</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>32.4879</v>
+        <v>32.176</v>
       </c>
       <c r="C134" t="n">
-        <v>23.2877</v>
+        <v>22.9387</v>
       </c>
       <c r="D134" t="n">
-        <v>55.1313</v>
+        <v>53.3216</v>
       </c>
       <c r="E134" t="n">
-        <v>32.7507</v>
+        <v>31.7304</v>
       </c>
       <c r="F134" t="n">
-        <v>32.1399</v>
+        <v>31.6592</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>32.7969</v>
+        <v>32.3467</v>
       </c>
       <c r="C135" t="n">
-        <v>23.7946</v>
+        <v>23.383</v>
       </c>
       <c r="D135" t="n">
-        <v>44.2533</v>
+        <v>43.2284</v>
       </c>
       <c r="E135" t="n">
-        <v>32.495</v>
+        <v>28.7404</v>
       </c>
       <c r="F135" t="n">
-        <v>30.0205</v>
+        <v>29.1569</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>33.2076</v>
+        <v>32.3211</v>
       </c>
       <c r="C136" t="n">
-        <v>23.5154</v>
+        <v>23.1049</v>
       </c>
       <c r="D136" t="n">
-        <v>45.1875</v>
+        <v>43.4619</v>
       </c>
       <c r="E136" t="n">
-        <v>32.7208</v>
+        <v>29.2463</v>
       </c>
       <c r="F136" t="n">
-        <v>30.3352</v>
+        <v>29.373</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>33.6712</v>
+        <v>32.0947</v>
       </c>
       <c r="C137" t="n">
-        <v>23.7419</v>
+        <v>22.7932</v>
       </c>
       <c r="D137" t="n">
-        <v>45.8587</v>
+        <v>44.2272</v>
       </c>
       <c r="E137" t="n">
-        <v>32.8828</v>
+        <v>29.4284</v>
       </c>
       <c r="F137" t="n">
-        <v>30.7729</v>
+        <v>29.6896</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>38.2838</v>
+        <v>37.0639</v>
       </c>
       <c r="C138" t="n">
-        <v>24.1692</v>
+        <v>23.3288</v>
       </c>
       <c r="D138" t="n">
-        <v>46.7377</v>
+        <v>45.3178</v>
       </c>
       <c r="E138" t="n">
-        <v>33.1523</v>
+        <v>30.0245</v>
       </c>
       <c r="F138" t="n">
-        <v>31.0012</v>
+        <v>29.871</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>38.2953</v>
+        <v>37.1815</v>
       </c>
       <c r="C139" t="n">
-        <v>24.3523</v>
+        <v>23.4751</v>
       </c>
       <c r="D139" t="n">
-        <v>47.0155</v>
+        <v>45.3381</v>
       </c>
       <c r="E139" t="n">
-        <v>33.4822</v>
+        <v>30.1855</v>
       </c>
       <c r="F139" t="n">
-        <v>31.0425</v>
+        <v>30.2102</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>38.3036</v>
+        <v>37.1694</v>
       </c>
       <c r="C140" t="n">
-        <v>24.4434</v>
+        <v>23.6395</v>
       </c>
       <c r="D140" t="n">
-        <v>48.1299</v>
+        <v>46.2783</v>
       </c>
       <c r="E140" t="n">
-        <v>33.6456</v>
+        <v>30.4096</v>
       </c>
       <c r="F140" t="n">
-        <v>31.0413</v>
+        <v>30.4388</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>38.3122</v>
+        <v>37.1459</v>
       </c>
       <c r="C141" t="n">
-        <v>24.617</v>
+        <v>23.8109</v>
       </c>
       <c r="D141" t="n">
-        <v>49.1287</v>
+        <v>47.2819</v>
       </c>
       <c r="E141" t="n">
-        <v>33.9678</v>
+        <v>30.6541</v>
       </c>
       <c r="F141" t="n">
-        <v>31.8551</v>
+        <v>30.7039</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>38.2021</v>
+        <v>37.2031</v>
       </c>
       <c r="C142" t="n">
-        <v>24.7992</v>
+        <v>23.9938</v>
       </c>
       <c r="D142" t="n">
-        <v>49.83</v>
+        <v>48.3273</v>
       </c>
       <c r="E142" t="n">
-        <v>34.1938</v>
+        <v>30.9097</v>
       </c>
       <c r="F142" t="n">
-        <v>31.8458</v>
+        <v>31.0287</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>38.3475</v>
+        <v>37.2235</v>
       </c>
       <c r="C143" t="n">
-        <v>25.032</v>
+        <v>24.1645</v>
       </c>
       <c r="D143" t="n">
-        <v>51.2998</v>
+        <v>49.7952</v>
       </c>
       <c r="E143" t="n">
-        <v>34.4099</v>
+        <v>30.6272</v>
       </c>
       <c r="F143" t="n">
-        <v>32.5561</v>
+        <v>31.4422</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Scattered successful looukp.xlsx
+++ b/clang-x64/Scattered successful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>3.35276</v>
+        <v>3.27786</v>
       </c>
       <c r="C2" t="n">
-        <v>2.65439</v>
+        <v>2.67111</v>
       </c>
       <c r="D2" t="n">
-        <v>7.02719</v>
+        <v>6.87493</v>
       </c>
       <c r="E2" t="n">
-        <v>3.25904</v>
+        <v>3.10335</v>
       </c>
       <c r="F2" t="n">
-        <v>3.16295</v>
+        <v>3.15121</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>3.38743</v>
+        <v>3.1935</v>
       </c>
       <c r="C3" t="n">
-        <v>2.69068</v>
+        <v>2.57541</v>
       </c>
       <c r="D3" t="n">
-        <v>7.70156</v>
+        <v>7.64848</v>
       </c>
       <c r="E3" t="n">
-        <v>3.19603</v>
+        <v>3.04763</v>
       </c>
       <c r="F3" t="n">
-        <v>3.36646</v>
+        <v>3.28395</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>3.14915</v>
+        <v>3.12116</v>
       </c>
       <c r="C4" t="n">
-        <v>2.53571</v>
+        <v>2.50914</v>
       </c>
       <c r="D4" t="n">
-        <v>8.513859999999999</v>
+        <v>8.39696</v>
       </c>
       <c r="E4" t="n">
-        <v>3.17469</v>
+        <v>3.04671</v>
       </c>
       <c r="F4" t="n">
-        <v>3.68198</v>
+        <v>3.29249</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.40277</v>
+        <v>3.1765</v>
       </c>
       <c r="C5" t="n">
-        <v>2.69188</v>
+        <v>2.58906</v>
       </c>
       <c r="D5" t="n">
-        <v>9.2033</v>
+        <v>9.139860000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>3.349</v>
+        <v>3.09291</v>
       </c>
       <c r="F5" t="n">
-        <v>3.59396</v>
+        <v>3.28741</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>3.38382</v>
+        <v>3.19267</v>
       </c>
       <c r="C6" t="n">
-        <v>2.69703</v>
+        <v>2.59133</v>
       </c>
       <c r="D6" t="n">
-        <v>9.999040000000001</v>
+        <v>9.95058</v>
       </c>
       <c r="E6" t="n">
-        <v>3.41952</v>
+        <v>3.11514</v>
       </c>
       <c r="F6" t="n">
-        <v>3.25923</v>
+        <v>3.23746</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>3.44872</v>
+        <v>3.23737</v>
       </c>
       <c r="C7" t="n">
-        <v>2.7967</v>
+        <v>2.67891</v>
       </c>
       <c r="D7" t="n">
-        <v>6.13523</v>
+        <v>6.06327</v>
       </c>
       <c r="E7" t="n">
-        <v>3.70437</v>
+        <v>3.64626</v>
       </c>
       <c r="F7" t="n">
-        <v>3.36661</v>
+        <v>3.31346</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>3.46472</v>
+        <v>3.26613</v>
       </c>
       <c r="C8" t="n">
-        <v>3.16871</v>
+        <v>2.90091</v>
       </c>
       <c r="D8" t="n">
-        <v>6.38959</v>
+        <v>6.30256</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8965</v>
+        <v>3.67495</v>
       </c>
       <c r="F8" t="n">
-        <v>3.40448</v>
+        <v>3.33436</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>3.27952</v>
+        <v>3.23183</v>
       </c>
       <c r="C9" t="n">
-        <v>3.20688</v>
+        <v>2.96373</v>
       </c>
       <c r="D9" t="n">
-        <v>7.03595</v>
+        <v>6.97428</v>
       </c>
       <c r="E9" t="n">
-        <v>3.93118</v>
+        <v>3.71473</v>
       </c>
       <c r="F9" t="n">
-        <v>3.42679</v>
+        <v>3.36416</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>4.18588</v>
+        <v>3.99789</v>
       </c>
       <c r="C10" t="n">
-        <v>3.27633</v>
+        <v>2.97738</v>
       </c>
       <c r="D10" t="n">
-        <v>7.4443</v>
+        <v>7.38662</v>
       </c>
       <c r="E10" t="n">
-        <v>3.96545</v>
+        <v>3.74582</v>
       </c>
       <c r="F10" t="n">
-        <v>3.4575</v>
+        <v>3.39457</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>4.83308</v>
+        <v>4.24994</v>
       </c>
       <c r="C11" t="n">
-        <v>3.22917</v>
+        <v>3.00597</v>
       </c>
       <c r="D11" t="n">
-        <v>7.97543</v>
+        <v>7.93093</v>
       </c>
       <c r="E11" t="n">
-        <v>4.23102</v>
+        <v>3.95591</v>
       </c>
       <c r="F11" t="n">
-        <v>3.4513</v>
+        <v>3.41151</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>3.9529</v>
+        <v>3.98674</v>
       </c>
       <c r="C12" t="n">
-        <v>3.25494</v>
+        <v>3.04611</v>
       </c>
       <c r="D12" t="n">
-        <v>8.62487</v>
+        <v>8.54176</v>
       </c>
       <c r="E12" t="n">
-        <v>4.2851</v>
+        <v>3.97761</v>
       </c>
       <c r="F12" t="n">
-        <v>3.4775</v>
+        <v>3.45171</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>4.84135</v>
+        <v>4.31548</v>
       </c>
       <c r="C13" t="n">
-        <v>3.34881</v>
+        <v>3.08151</v>
       </c>
       <c r="D13" t="n">
-        <v>9.087199999999999</v>
+        <v>9.07141</v>
       </c>
       <c r="E13" t="n">
-        <v>4.24184</v>
+        <v>3.85789</v>
       </c>
       <c r="F13" t="n">
-        <v>3.61813</v>
+        <v>3.51538</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>4.84932</v>
+        <v>4.2494</v>
       </c>
       <c r="C14" t="n">
-        <v>3.39409</v>
+        <v>3.11246</v>
       </c>
       <c r="D14" t="n">
-        <v>9.65513</v>
+        <v>9.598649999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>4.11287</v>
+        <v>3.85956</v>
       </c>
       <c r="F14" t="n">
-        <v>3.58085</v>
+        <v>3.51904</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>4.86238</v>
+        <v>4.33225</v>
       </c>
       <c r="C15" t="n">
-        <v>3.39499</v>
+        <v>3.12464</v>
       </c>
       <c r="D15" t="n">
-        <v>10.1527</v>
+        <v>10.1088</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2692</v>
+        <v>3.95198</v>
       </c>
       <c r="F15" t="n">
-        <v>3.66193</v>
+        <v>3.55232</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>4.86307</v>
+        <v>4.27142</v>
       </c>
       <c r="C16" t="n">
-        <v>3.43115</v>
+        <v>3.15078</v>
       </c>
       <c r="D16" t="n">
-        <v>10.6428</v>
+        <v>10.6362</v>
       </c>
       <c r="E16" t="n">
-        <v>4.47095</v>
+        <v>4.09527</v>
       </c>
       <c r="F16" t="n">
-        <v>3.69376</v>
+        <v>3.59801</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>4.88007</v>
+        <v>4.34758</v>
       </c>
       <c r="C17" t="n">
-        <v>3.4584</v>
+        <v>3.18359</v>
       </c>
       <c r="D17" t="n">
-        <v>11.164</v>
+        <v>11.14</v>
       </c>
       <c r="E17" t="n">
-        <v>4.0796</v>
+        <v>3.95198</v>
       </c>
       <c r="F17" t="n">
-        <v>3.66831</v>
+        <v>3.60789</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>4.89666</v>
+        <v>4.3629</v>
       </c>
       <c r="C18" t="n">
-        <v>3.49669</v>
+        <v>3.22094</v>
       </c>
       <c r="D18" t="n">
-        <v>11.5864</v>
+        <v>11.6105</v>
       </c>
       <c r="E18" t="n">
-        <v>4.57679</v>
+        <v>4.133</v>
       </c>
       <c r="F18" t="n">
-        <v>3.65519</v>
+        <v>3.62348</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>4.90626</v>
+        <v>4.37809</v>
       </c>
       <c r="C19" t="n">
-        <v>3.52596</v>
+        <v>3.246</v>
       </c>
       <c r="D19" t="n">
-        <v>12.1267</v>
+        <v>12.0695</v>
       </c>
       <c r="E19" t="n">
-        <v>4.40519</v>
+        <v>3.96877</v>
       </c>
       <c r="F19" t="n">
-        <v>3.74565</v>
+        <v>3.67221</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>4.93078</v>
+        <v>4.39751</v>
       </c>
       <c r="C20" t="n">
-        <v>3.57339</v>
+        <v>3.28691</v>
       </c>
       <c r="D20" t="n">
-        <v>12.5012</v>
+        <v>12.3942</v>
       </c>
       <c r="E20" t="n">
-        <v>4.68119</v>
+        <v>4.27921</v>
       </c>
       <c r="F20" t="n">
-        <v>3.86829</v>
+        <v>3.72833</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>4.95493</v>
+        <v>4.41444</v>
       </c>
       <c r="C21" t="n">
-        <v>3.60729</v>
+        <v>3.31987</v>
       </c>
       <c r="D21" t="n">
-        <v>8.72888</v>
+        <v>8.67193</v>
       </c>
       <c r="E21" t="n">
-        <v>3.8156</v>
+        <v>3.91875</v>
       </c>
       <c r="F21" t="n">
-        <v>4.15666</v>
+        <v>4.03351</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>4.98941</v>
+        <v>4.44622</v>
       </c>
       <c r="C22" t="n">
-        <v>3.09673</v>
+        <v>3.11911</v>
       </c>
       <c r="D22" t="n">
-        <v>9.110189999999999</v>
+        <v>8.99943</v>
       </c>
       <c r="E22" t="n">
-        <v>3.83348</v>
+        <v>3.88374</v>
       </c>
       <c r="F22" t="n">
-        <v>4.3336</v>
+        <v>4.10505</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>5.02378</v>
+        <v>4.51752</v>
       </c>
       <c r="C23" t="n">
-        <v>3.09892</v>
+        <v>3.132</v>
       </c>
       <c r="D23" t="n">
-        <v>9.45173</v>
+        <v>9.393660000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>4.29687</v>
+        <v>4.04634</v>
       </c>
       <c r="F23" t="n">
-        <v>4.26139</v>
+        <v>4.0763</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>4.92528</v>
+        <v>4.68612</v>
       </c>
       <c r="C24" t="n">
-        <v>3.12677</v>
+        <v>3.16738</v>
       </c>
       <c r="D24" t="n">
-        <v>9.792210000000001</v>
+        <v>9.75285</v>
       </c>
       <c r="E24" t="n">
-        <v>4.11011</v>
+        <v>4.07165</v>
       </c>
       <c r="F24" t="n">
-        <v>4.30907</v>
+        <v>4.10851</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>4.94118</v>
+        <v>4.67207</v>
       </c>
       <c r="C25" t="n">
-        <v>3.15927</v>
+        <v>3.16777</v>
       </c>
       <c r="D25" t="n">
-        <v>10.2228</v>
+        <v>10.1525</v>
       </c>
       <c r="E25" t="n">
-        <v>4.07462</v>
+        <v>4.0294</v>
       </c>
       <c r="F25" t="n">
-        <v>4.42513</v>
+        <v>4.20154</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>4.94497</v>
+        <v>4.68019</v>
       </c>
       <c r="C26" t="n">
-        <v>3.16463</v>
+        <v>3.17768</v>
       </c>
       <c r="D26" t="n">
-        <v>10.6263</v>
+        <v>10.5275</v>
       </c>
       <c r="E26" t="n">
-        <v>4.07668</v>
+        <v>3.9828</v>
       </c>
       <c r="F26" t="n">
-        <v>4.11205</v>
+        <v>4.09041</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>4.50249</v>
+        <v>4.60181</v>
       </c>
       <c r="C27" t="n">
-        <v>3.19767</v>
+        <v>3.26139</v>
       </c>
       <c r="D27" t="n">
-        <v>11.04</v>
+        <v>10.9638</v>
       </c>
       <c r="E27" t="n">
-        <v>3.91976</v>
+        <v>4.15867</v>
       </c>
       <c r="F27" t="n">
-        <v>4.14517</v>
+        <v>4.12289</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>4.49518</v>
+        <v>4.62615</v>
       </c>
       <c r="C28" t="n">
-        <v>3.21807</v>
+        <v>3.27484</v>
       </c>
       <c r="D28" t="n">
-        <v>11.437</v>
+        <v>11.3658</v>
       </c>
       <c r="E28" t="n">
-        <v>4.11428</v>
+        <v>4.20665</v>
       </c>
       <c r="F28" t="n">
-        <v>4.16531</v>
+        <v>4.14902</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>4.50459</v>
+        <v>4.64262</v>
       </c>
       <c r="C29" t="n">
-        <v>3.26364</v>
+        <v>3.30096</v>
       </c>
       <c r="D29" t="n">
-        <v>11.8441</v>
+        <v>11.7607</v>
       </c>
       <c r="E29" t="n">
-        <v>4.16562</v>
+        <v>4.25544</v>
       </c>
       <c r="F29" t="n">
-        <v>4.21135</v>
+        <v>4.20398</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>4.96037</v>
+        <v>4.65734</v>
       </c>
       <c r="C30" t="n">
-        <v>3.42804</v>
+        <v>3.33424</v>
       </c>
       <c r="D30" t="n">
-        <v>12.2804</v>
+        <v>12.1754</v>
       </c>
       <c r="E30" t="n">
-        <v>4.21171</v>
+        <v>4.2813</v>
       </c>
       <c r="F30" t="n">
-        <v>4.24838</v>
+        <v>4.22669</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>5.01065</v>
+        <v>4.74856</v>
       </c>
       <c r="C31" t="n">
-        <v>3.27585</v>
+        <v>3.27996</v>
       </c>
       <c r="D31" t="n">
-        <v>12.7398</v>
+        <v>12.6106</v>
       </c>
       <c r="E31" t="n">
-        <v>4.28784</v>
+        <v>4.14726</v>
       </c>
       <c r="F31" t="n">
-        <v>4.29358</v>
+        <v>4.26274</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>4.56781</v>
+        <v>4.66338</v>
       </c>
       <c r="C32" t="n">
-        <v>3.34639</v>
+        <v>3.38758</v>
       </c>
       <c r="D32" t="n">
-        <v>13.0819</v>
+        <v>12.9205</v>
       </c>
       <c r="E32" t="n">
-        <v>4.3056</v>
+        <v>4.36892</v>
       </c>
       <c r="F32" t="n">
-        <v>4.37372</v>
+        <v>4.31121</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.57103</v>
+        <v>4.70644</v>
       </c>
       <c r="C33" t="n">
-        <v>3.3811</v>
+        <v>3.41947</v>
       </c>
       <c r="D33" t="n">
-        <v>13.4937</v>
+        <v>13.3292</v>
       </c>
       <c r="E33" t="n">
-        <v>4.40406</v>
+        <v>4.28202</v>
       </c>
       <c r="F33" t="n">
-        <v>4.49473</v>
+        <v>4.39545</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>4.60817</v>
+        <v>4.71068</v>
       </c>
       <c r="C34" t="n">
-        <v>3.42161</v>
+        <v>3.46335</v>
       </c>
       <c r="D34" t="n">
-        <v>13.7911</v>
+        <v>13.6642</v>
       </c>
       <c r="E34" t="n">
-        <v>4.27655</v>
+        <v>4.18991</v>
       </c>
       <c r="F34" t="n">
-        <v>4.55285</v>
+        <v>4.53534</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>5.06978</v>
+        <v>4.73646</v>
       </c>
       <c r="C35" t="n">
-        <v>3.50283</v>
+        <v>3.42525</v>
       </c>
       <c r="D35" t="n">
-        <v>9.41188</v>
+        <v>9.436030000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>3.99271</v>
+        <v>3.95305</v>
       </c>
       <c r="F35" t="n">
-        <v>4.0808</v>
+        <v>4.08551</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>4.73165</v>
+        <v>4.79456</v>
       </c>
       <c r="C36" t="n">
-        <v>3.48194</v>
+        <v>3.56559</v>
       </c>
       <c r="D36" t="n">
-        <v>9.685639999999999</v>
+        <v>9.69228</v>
       </c>
       <c r="E36" t="n">
-        <v>4.14916</v>
+        <v>4.01088</v>
       </c>
       <c r="F36" t="n">
-        <v>4.1045</v>
+        <v>4.11132</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>4.83012</v>
+        <v>4.79302</v>
       </c>
       <c r="C37" t="n">
-        <v>3.65966</v>
+        <v>3.45661</v>
       </c>
       <c r="D37" t="n">
-        <v>10.0454</v>
+        <v>9.914540000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>4.18726</v>
+        <v>4.04422</v>
       </c>
       <c r="F37" t="n">
-        <v>4.13054</v>
+        <v>4.146</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>4.83317</v>
+        <v>4.87028</v>
       </c>
       <c r="C38" t="n">
-        <v>3.43029</v>
+        <v>3.3503</v>
       </c>
       <c r="D38" t="n">
-        <v>10.2091</v>
+        <v>10.2135</v>
       </c>
       <c r="E38" t="n">
-        <v>4.20851</v>
+        <v>4.06007</v>
       </c>
       <c r="F38" t="n">
-        <v>4.17034</v>
+        <v>4.1657</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>4.75254</v>
+        <v>4.84502</v>
       </c>
       <c r="C39" t="n">
-        <v>3.47439</v>
+        <v>3.26915</v>
       </c>
       <c r="D39" t="n">
-        <v>10.6598</v>
+        <v>10.5195</v>
       </c>
       <c r="E39" t="n">
-        <v>4.25205</v>
+        <v>4.10013</v>
       </c>
       <c r="F39" t="n">
-        <v>4.22606</v>
+        <v>4.18389</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>4.73956</v>
+        <v>4.86004</v>
       </c>
       <c r="C40" t="n">
-        <v>3.49434</v>
+        <v>3.30036</v>
       </c>
       <c r="D40" t="n">
-        <v>11.1597</v>
+        <v>10.8682</v>
       </c>
       <c r="E40" t="n">
-        <v>4.27888</v>
+        <v>4.12299</v>
       </c>
       <c r="F40" t="n">
-        <v>4.22129</v>
+        <v>4.22062</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>4.69747</v>
+        <v>4.45416</v>
       </c>
       <c r="C41" t="n">
-        <v>3.73256</v>
+        <v>3.55086</v>
       </c>
       <c r="D41" t="n">
-        <v>11.5212</v>
+        <v>11.2333</v>
       </c>
       <c r="E41" t="n">
-        <v>4.45215</v>
+        <v>4.44987</v>
       </c>
       <c r="F41" t="n">
-        <v>4.40362</v>
+        <v>4.31753</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>4.62893</v>
+        <v>4.6389</v>
       </c>
       <c r="C42" t="n">
-        <v>3.79592</v>
+        <v>3.51926</v>
       </c>
       <c r="D42" t="n">
-        <v>11.9102</v>
+        <v>11.6047</v>
       </c>
       <c r="E42" t="n">
-        <v>4.39255</v>
+        <v>4.19459</v>
       </c>
       <c r="F42" t="n">
-        <v>4.43869</v>
+        <v>4.29152</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>4.79771</v>
+        <v>4.6579</v>
       </c>
       <c r="C43" t="n">
-        <v>3.79406</v>
+        <v>3.61927</v>
       </c>
       <c r="D43" t="n">
-        <v>12.2183</v>
+        <v>11.9691</v>
       </c>
       <c r="E43" t="n">
-        <v>4.54404</v>
+        <v>4.54858</v>
       </c>
       <c r="F43" t="n">
-        <v>4.49511</v>
+        <v>4.39705</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>4.67926</v>
+        <v>4.71021</v>
       </c>
       <c r="C44" t="n">
-        <v>3.81852</v>
+        <v>3.50685</v>
       </c>
       <c r="D44" t="n">
-        <v>12.5911</v>
+        <v>12.3251</v>
       </c>
       <c r="E44" t="n">
-        <v>4.45903</v>
+        <v>4.27602</v>
       </c>
       <c r="F44" t="n">
-        <v>4.53769</v>
+        <v>4.43958</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>5.00713</v>
+        <v>4.74663</v>
       </c>
       <c r="C45" t="n">
-        <v>3.88959</v>
+        <v>3.6866</v>
       </c>
       <c r="D45" t="n">
-        <v>12.9039</v>
+        <v>12.7223</v>
       </c>
       <c r="E45" t="n">
-        <v>4.69672</v>
+        <v>4.67244</v>
       </c>
       <c r="F45" t="n">
-        <v>4.56179</v>
+        <v>4.47019</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.75168</v>
+        <v>4.64109</v>
       </c>
       <c r="C46" t="n">
-        <v>3.9641</v>
+        <v>3.63875</v>
       </c>
       <c r="D46" t="n">
-        <v>13.3097</v>
+        <v>13.0929</v>
       </c>
       <c r="E46" t="n">
-        <v>4.76607</v>
+        <v>4.73764</v>
       </c>
       <c r="F46" t="n">
-        <v>4.65379</v>
+        <v>4.54553</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.80753</v>
+        <v>4.53762</v>
       </c>
       <c r="C47" t="n">
-        <v>3.93399</v>
+        <v>3.74013</v>
       </c>
       <c r="D47" t="n">
-        <v>13.614</v>
+        <v>13.491</v>
       </c>
       <c r="E47" t="n">
-        <v>4.91588</v>
+        <v>4.69846</v>
       </c>
       <c r="F47" t="n">
-        <v>4.98988</v>
+        <v>4.94318</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>4.80687</v>
+        <v>4.93654</v>
       </c>
       <c r="C48" t="n">
-        <v>4.16548</v>
+        <v>3.51969</v>
       </c>
       <c r="D48" t="n">
-        <v>14.1245</v>
+        <v>13.8641</v>
       </c>
       <c r="E48" t="n">
-        <v>5.14125</v>
+        <v>4.8073</v>
       </c>
       <c r="F48" t="n">
-        <v>5.22671</v>
+        <v>5.16586</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>4.91292</v>
+        <v>4.64407</v>
       </c>
       <c r="C49" t="n">
-        <v>4.04271</v>
+        <v>3.85114</v>
       </c>
       <c r="D49" t="n">
-        <v>14.546</v>
+        <v>14.2185</v>
       </c>
       <c r="E49" t="n">
-        <v>5.47378</v>
+        <v>5.11275</v>
       </c>
       <c r="F49" t="n">
-        <v>5.66089</v>
+        <v>5.64323</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>5.09304</v>
+        <v>4.88639</v>
       </c>
       <c r="C50" t="n">
-        <v>4.18136</v>
+        <v>3.98927</v>
       </c>
       <c r="D50" t="n">
-        <v>11.7729</v>
+        <v>10.5141</v>
       </c>
       <c r="E50" t="n">
-        <v>4.32615</v>
+        <v>4.35185</v>
       </c>
       <c r="F50" t="n">
-        <v>6.41853</v>
+        <v>4.58505</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>5.21625</v>
+        <v>5.34986</v>
       </c>
       <c r="C51" t="n">
-        <v>3.63211</v>
+        <v>3.53581</v>
       </c>
       <c r="D51" t="n">
-        <v>12.1278</v>
+        <v>10.7925</v>
       </c>
       <c r="E51" t="n">
-        <v>4.3801</v>
+        <v>4.40217</v>
       </c>
       <c r="F51" t="n">
-        <v>6.27912</v>
+        <v>4.63748</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>6.01921</v>
+        <v>5.83682</v>
       </c>
       <c r="C52" t="n">
-        <v>3.62887</v>
+        <v>3.57155</v>
       </c>
       <c r="D52" t="n">
-        <v>12.8662</v>
+        <v>11.2396</v>
       </c>
       <c r="E52" t="n">
-        <v>4.41748</v>
+        <v>4.42012</v>
       </c>
       <c r="F52" t="n">
-        <v>5.10549</v>
+        <v>4.59197</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>5.44223</v>
+        <v>5.13661</v>
       </c>
       <c r="C53" t="n">
-        <v>3.59368</v>
+        <v>3.60909</v>
       </c>
       <c r="D53" t="n">
-        <v>13.4815</v>
+        <v>11.7978</v>
       </c>
       <c r="E53" t="n">
-        <v>4.50177</v>
+        <v>4.47514</v>
       </c>
       <c r="F53" t="n">
-        <v>6.56384</v>
+        <v>4.71491</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>5.42145</v>
+        <v>5.15486</v>
       </c>
       <c r="C54" t="n">
-        <v>3.62459</v>
+        <v>3.60839</v>
       </c>
       <c r="D54" t="n">
-        <v>14.5418</v>
+        <v>12.2632</v>
       </c>
       <c r="E54" t="n">
-        <v>4.49353</v>
+        <v>4.51056</v>
       </c>
       <c r="F54" t="n">
-        <v>6.46507</v>
+        <v>4.75984</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>5.4352</v>
+        <v>5.16752</v>
       </c>
       <c r="C55" t="n">
-        <v>3.70441</v>
+        <v>3.63086</v>
       </c>
       <c r="D55" t="n">
-        <v>15.4387</v>
+        <v>12.6996</v>
       </c>
       <c r="E55" t="n">
-        <v>4.87119</v>
+        <v>4.61117</v>
       </c>
       <c r="F55" t="n">
-        <v>4.94623</v>
+        <v>4.72229</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>5.47454</v>
+        <v>5.18003</v>
       </c>
       <c r="C56" t="n">
-        <v>3.64172</v>
+        <v>3.73827</v>
       </c>
       <c r="D56" t="n">
-        <v>14.6661</v>
+        <v>12.2407</v>
       </c>
       <c r="E56" t="n">
-        <v>4.58778</v>
+        <v>4.56799</v>
       </c>
       <c r="F56" t="n">
-        <v>6.71879</v>
+        <v>5.0113</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>5.48281</v>
+        <v>5.14363</v>
       </c>
       <c r="C57" t="n">
-        <v>3.64104</v>
+        <v>3.75404</v>
       </c>
       <c r="D57" t="n">
-        <v>17.8019</v>
+        <v>13.7954</v>
       </c>
       <c r="E57" t="n">
-        <v>4.98745</v>
+        <v>4.70666</v>
       </c>
       <c r="F57" t="n">
-        <v>5.33888</v>
+        <v>5.03273</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>5.47524</v>
+        <v>5.20508</v>
       </c>
       <c r="C58" t="n">
-        <v>3.81454</v>
+        <v>3.68408</v>
       </c>
       <c r="D58" t="n">
-        <v>18.4773</v>
+        <v>14.1103</v>
       </c>
       <c r="E58" t="n">
-        <v>5.04333</v>
+        <v>4.77073</v>
       </c>
       <c r="F58" t="n">
-        <v>5.21705</v>
+        <v>5.05891</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>5.53239</v>
+        <v>5.2601</v>
       </c>
       <c r="C59" t="n">
-        <v>3.71227</v>
+        <v>3.81934</v>
       </c>
       <c r="D59" t="n">
-        <v>18.3551</v>
+        <v>14.6048</v>
       </c>
       <c r="E59" t="n">
-        <v>4.88502</v>
+        <v>4.82137</v>
       </c>
       <c r="F59" t="n">
-        <v>6.0693</v>
+        <v>5.30881</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>5.37081</v>
+        <v>5.27435</v>
       </c>
       <c r="C60" t="n">
-        <v>3.82001</v>
+        <v>3.85748</v>
       </c>
       <c r="D60" t="n">
-        <v>18.1</v>
+        <v>14.9237</v>
       </c>
       <c r="E60" t="n">
-        <v>4.96881</v>
+        <v>4.93106</v>
       </c>
       <c r="F60" t="n">
-        <v>6.15383</v>
+        <v>5.66639</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>5.59978</v>
+        <v>5.27922</v>
       </c>
       <c r="C61" t="n">
-        <v>3.84077</v>
+        <v>3.82651</v>
       </c>
       <c r="D61" t="n">
-        <v>18.6232</v>
+        <v>15.4557</v>
       </c>
       <c r="E61" t="n">
-        <v>5.28948</v>
+        <v>5.07201</v>
       </c>
       <c r="F61" t="n">
-        <v>6.50487</v>
+        <v>5.75833</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>5.37095</v>
+        <v>5.37988</v>
       </c>
       <c r="C62" t="n">
-        <v>3.82687</v>
+        <v>3.98083</v>
       </c>
       <c r="D62" t="n">
-        <v>18.9466</v>
+        <v>15.6011</v>
       </c>
       <c r="E62" t="n">
-        <v>5.49553</v>
+        <v>5.27717</v>
       </c>
       <c r="F62" t="n">
-        <v>6.44343</v>
+        <v>5.9066</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>5.55412</v>
+        <v>5.46205</v>
       </c>
       <c r="C63" t="n">
-        <v>3.99968</v>
+        <v>4.06068</v>
       </c>
       <c r="D63" t="n">
-        <v>18.6477</v>
+        <v>16.0719</v>
       </c>
       <c r="E63" t="n">
-        <v>5.795</v>
+        <v>5.53821</v>
       </c>
       <c r="F63" t="n">
-        <v>7.60281</v>
+        <v>6.15885</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>5.91536</v>
+        <v>5.62974</v>
       </c>
       <c r="C64" t="n">
-        <v>4.12676</v>
+        <v>4.12488</v>
       </c>
       <c r="D64" t="n">
-        <v>12.9591</v>
+        <v>10.9776</v>
       </c>
       <c r="E64" t="n">
-        <v>5.26215</v>
+        <v>5.33825</v>
       </c>
       <c r="F64" t="n">
-        <v>5.60187</v>
+        <v>5.42958</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>6.23023</v>
+        <v>5.91198</v>
       </c>
       <c r="C65" t="n">
-        <v>6.59601</v>
+        <v>7.38707</v>
       </c>
       <c r="D65" t="n">
-        <v>13.902</v>
+        <v>11.5945</v>
       </c>
       <c r="E65" t="n">
-        <v>5.40887</v>
+        <v>5.22668</v>
       </c>
       <c r="F65" t="n">
-        <v>5.74859</v>
+        <v>5.59692</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>6.6663</v>
+        <v>6.33515</v>
       </c>
       <c r="C66" t="n">
-        <v>6.73312</v>
+        <v>7.53495</v>
       </c>
       <c r="D66" t="n">
-        <v>15.4066</v>
+        <v>12.2244</v>
       </c>
       <c r="E66" t="n">
-        <v>5.96234</v>
+        <v>5.15115</v>
       </c>
       <c r="F66" t="n">
-        <v>5.96067</v>
+        <v>5.86853</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>8.52154</v>
+        <v>10.099</v>
       </c>
       <c r="C67" t="n">
-        <v>6.64099</v>
+        <v>7.85157</v>
       </c>
       <c r="D67" t="n">
-        <v>15.8514</v>
+        <v>13.15</v>
       </c>
       <c r="E67" t="n">
-        <v>5.94135</v>
+        <v>5.88097</v>
       </c>
       <c r="F67" t="n">
-        <v>6.10036</v>
+        <v>5.98242</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>8.24175</v>
+        <v>10.3602</v>
       </c>
       <c r="C68" t="n">
-        <v>6.32505</v>
+        <v>8.050230000000001</v>
       </c>
       <c r="D68" t="n">
-        <v>16.7731</v>
+        <v>14.0659</v>
       </c>
       <c r="E68" t="n">
-        <v>6.55969</v>
+        <v>5.41936</v>
       </c>
       <c r="F68" t="n">
-        <v>6.23616</v>
+        <v>6.08772</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>8.87785</v>
+        <v>9.50262</v>
       </c>
       <c r="C69" t="n">
-        <v>6.8849</v>
+        <v>7.30353</v>
       </c>
       <c r="D69" t="n">
-        <v>17.4786</v>
+        <v>14.5943</v>
       </c>
       <c r="E69" t="n">
-        <v>5.82919</v>
+        <v>6.37231</v>
       </c>
       <c r="F69" t="n">
-        <v>6.4245</v>
+        <v>6.26434</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>9.089169999999999</v>
+        <v>8.3912</v>
       </c>
       <c r="C70" t="n">
-        <v>7.03391</v>
+        <v>6.34023</v>
       </c>
       <c r="D70" t="n">
-        <v>17.5186</v>
+        <v>14.8915</v>
       </c>
       <c r="E70" t="n">
-        <v>6.84516</v>
+        <v>5.90727</v>
       </c>
       <c r="F70" t="n">
-        <v>6.44565</v>
+        <v>6.41804</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>9.12818</v>
+        <v>8.24858</v>
       </c>
       <c r="C71" t="n">
-        <v>7.04302</v>
+        <v>6.18668</v>
       </c>
       <c r="D71" t="n">
-        <v>18.2416</v>
+        <v>15.74</v>
       </c>
       <c r="E71" t="n">
-        <v>6.93523</v>
+        <v>5.32282</v>
       </c>
       <c r="F71" t="n">
-        <v>6.47724</v>
+        <v>6.43216</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>9.12504</v>
+        <v>9.98704</v>
       </c>
       <c r="C72" t="n">
-        <v>7.09163</v>
+        <v>7.77687</v>
       </c>
       <c r="D72" t="n">
-        <v>18.929</v>
+        <v>16.56</v>
       </c>
       <c r="E72" t="n">
-        <v>7.02837</v>
+        <v>5.54251</v>
       </c>
       <c r="F72" t="n">
-        <v>6.68087</v>
+        <v>6.68061</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>9.12696</v>
+        <v>9.480560000000001</v>
       </c>
       <c r="C73" t="n">
-        <v>7.02345</v>
+        <v>7.32404</v>
       </c>
       <c r="D73" t="n">
-        <v>19.1502</v>
+        <v>17.1917</v>
       </c>
       <c r="E73" t="n">
-        <v>7.12791</v>
+        <v>5.72367</v>
       </c>
       <c r="F73" t="n">
-        <v>6.8323</v>
+        <v>6.84951</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>7.92502</v>
+        <v>10.8311</v>
       </c>
       <c r="C74" t="n">
-        <v>6.04574</v>
+        <v>8.76844</v>
       </c>
       <c r="D74" t="n">
-        <v>19.6246</v>
+        <v>18.3801</v>
       </c>
       <c r="E74" t="n">
-        <v>6.77293</v>
+        <v>5.551</v>
       </c>
       <c r="F74" t="n">
-        <v>6.88478</v>
+        <v>7.28594</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>8.931789999999999</v>
+        <v>7.5804</v>
       </c>
       <c r="C75" t="n">
-        <v>6.68027</v>
+        <v>5.70785</v>
       </c>
       <c r="D75" t="n">
-        <v>19.5962</v>
+        <v>19.1037</v>
       </c>
       <c r="E75" t="n">
-        <v>6.76698</v>
+        <v>5.74247</v>
       </c>
       <c r="F75" t="n">
-        <v>7.21659</v>
+        <v>7.49944</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>8.43201</v>
+        <v>7.62225</v>
       </c>
       <c r="C76" t="n">
-        <v>6.36369</v>
+        <v>5.7423</v>
       </c>
       <c r="D76" t="n">
-        <v>20.2433</v>
+        <v>20.1274</v>
       </c>
       <c r="E76" t="n">
-        <v>6.66756</v>
+        <v>5.83709</v>
       </c>
       <c r="F76" t="n">
-        <v>8.233790000000001</v>
+        <v>7.79389</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>8.29532</v>
+        <v>7.6089</v>
       </c>
       <c r="C77" t="n">
-        <v>6.32712</v>
+        <v>5.77979</v>
       </c>
       <c r="D77" t="n">
-        <v>23.2555</v>
+        <v>21.6944</v>
       </c>
       <c r="E77" t="n">
-        <v>6.95118</v>
+        <v>6.13128</v>
       </c>
       <c r="F77" t="n">
-        <v>9.601889999999999</v>
+        <v>8.36134</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>9.55219</v>
+        <v>9.8652</v>
       </c>
       <c r="C78" t="n">
-        <v>7.43858</v>
+        <v>7.72862</v>
       </c>
       <c r="D78" t="n">
-        <v>19.8254</v>
+        <v>20.7095</v>
       </c>
       <c r="E78" t="n">
-        <v>11.5094</v>
+        <v>9.68478</v>
       </c>
       <c r="F78" t="n">
-        <v>11.0013</v>
+        <v>11.1794</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>8.386850000000001</v>
+        <v>7.51086</v>
       </c>
       <c r="C79" t="n">
-        <v>12.7305</v>
+        <v>13.4395</v>
       </c>
       <c r="D79" t="n">
-        <v>20.6355</v>
+        <v>21.6665</v>
       </c>
       <c r="E79" t="n">
-        <v>11.7738</v>
+        <v>10.1466</v>
       </c>
       <c r="F79" t="n">
-        <v>10.5571</v>
+        <v>11.0885</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>8.68215</v>
+        <v>7.84885</v>
       </c>
       <c r="C80" t="n">
-        <v>13.029</v>
+        <v>13.572</v>
       </c>
       <c r="D80" t="n">
-        <v>21.8848</v>
+        <v>22.8293</v>
       </c>
       <c r="E80" t="n">
-        <v>11.7866</v>
+        <v>10.3362</v>
       </c>
       <c r="F80" t="n">
-        <v>10.9344</v>
+        <v>11.264</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>16.1238</v>
+        <v>16.7497</v>
       </c>
       <c r="C81" t="n">
-        <v>13.0833</v>
+        <v>13.6589</v>
       </c>
       <c r="D81" t="n">
-        <v>22.8407</v>
+        <v>23.7388</v>
       </c>
       <c r="E81" t="n">
-        <v>11.5267</v>
+        <v>10.6533</v>
       </c>
       <c r="F81" t="n">
-        <v>10.9834</v>
+        <v>11.4213</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>16.1983</v>
+        <v>16.8021</v>
       </c>
       <c r="C82" t="n">
-        <v>13.1504</v>
+        <v>13.7353</v>
       </c>
       <c r="D82" t="n">
-        <v>23.6516</v>
+        <v>24.6489</v>
       </c>
       <c r="E82" t="n">
-        <v>12.0824</v>
+        <v>10.8852</v>
       </c>
       <c r="F82" t="n">
-        <v>11.1942</v>
+        <v>11.5601</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>16.2604</v>
+        <v>16.8765</v>
       </c>
       <c r="C83" t="n">
-        <v>13.1897</v>
+        <v>13.7917</v>
       </c>
       <c r="D83" t="n">
-        <v>25.0328</v>
+        <v>26.2247</v>
       </c>
       <c r="E83" t="n">
-        <v>12.1716</v>
+        <v>11.2066</v>
       </c>
       <c r="F83" t="n">
-        <v>11.2992</v>
+        <v>11.6812</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>16.327</v>
+        <v>16.9233</v>
       </c>
       <c r="C84" t="n">
-        <v>13.2642</v>
+        <v>13.8808</v>
       </c>
       <c r="D84" t="n">
-        <v>25.6509</v>
+        <v>26.4305</v>
       </c>
       <c r="E84" t="n">
-        <v>12.4763</v>
+        <v>11.5373</v>
       </c>
       <c r="F84" t="n">
-        <v>11.3344</v>
+        <v>11.6256</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>16.4127</v>
+        <v>17.035</v>
       </c>
       <c r="C85" t="n">
-        <v>13.331</v>
+        <v>13.9371</v>
       </c>
       <c r="D85" t="n">
-        <v>27.1807</v>
+        <v>28.0427</v>
       </c>
       <c r="E85" t="n">
-        <v>12.4789</v>
+        <v>11.6414</v>
       </c>
       <c r="F85" t="n">
-        <v>12.3812</v>
+        <v>13.1519</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>16.4613</v>
+        <v>17.0289</v>
       </c>
       <c r="C86" t="n">
-        <v>13.3414</v>
+        <v>13.9935</v>
       </c>
       <c r="D86" t="n">
-        <v>28.1064</v>
+        <v>28.7156</v>
       </c>
       <c r="E86" t="n">
-        <v>12.6461</v>
+        <v>11.8987</v>
       </c>
       <c r="F86" t="n">
-        <v>12.5794</v>
+        <v>13.2498</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>16.5086</v>
+        <v>17.0786</v>
       </c>
       <c r="C87" t="n">
-        <v>13.4053</v>
+        <v>14.0304</v>
       </c>
       <c r="D87" t="n">
-        <v>28.8852</v>
+        <v>29.3667</v>
       </c>
       <c r="E87" t="n">
-        <v>12.604</v>
+        <v>12.0984</v>
       </c>
       <c r="F87" t="n">
-        <v>12.2681</v>
+        <v>13.5597</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>16.5517</v>
+        <v>17.149</v>
       </c>
       <c r="C88" t="n">
-        <v>13.433</v>
+        <v>14.0858</v>
       </c>
       <c r="D88" t="n">
-        <v>30.9779</v>
+        <v>30.6092</v>
       </c>
       <c r="E88" t="n">
-        <v>12.5955</v>
+        <v>12.5043</v>
       </c>
       <c r="F88" t="n">
-        <v>15.0049</v>
+        <v>13.7283</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>16.5097</v>
+        <v>17.1848</v>
       </c>
       <c r="C89" t="n">
-        <v>13.2862</v>
+        <v>14.1712</v>
       </c>
       <c r="D89" t="n">
-        <v>30.4941</v>
+        <v>32.3361</v>
       </c>
       <c r="E89" t="n">
-        <v>12.6333</v>
+        <v>12.7506</v>
       </c>
       <c r="F89" t="n">
-        <v>12.3242</v>
+        <v>13.3477</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>16.496</v>
+        <v>17.2348</v>
       </c>
       <c r="C90" t="n">
-        <v>13.227</v>
+        <v>14.2273</v>
       </c>
       <c r="D90" t="n">
-        <v>32.3849</v>
+        <v>33.1278</v>
       </c>
       <c r="E90" t="n">
-        <v>12.8377</v>
+        <v>13.0143</v>
       </c>
       <c r="F90" t="n">
-        <v>12.4784</v>
+        <v>12.7396</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>16.7644</v>
+        <v>17.3976</v>
       </c>
       <c r="C91" t="n">
-        <v>13.6041</v>
+        <v>14.3987</v>
       </c>
       <c r="D91" t="n">
-        <v>33.764</v>
+        <v>34.1459</v>
       </c>
       <c r="E91" t="n">
-        <v>13.1202</v>
+        <v>13.2968</v>
       </c>
       <c r="F91" t="n">
-        <v>13.1563</v>
+        <v>13.341</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>16.8204</v>
+        <v>17.5032</v>
       </c>
       <c r="C92" t="n">
-        <v>13.674</v>
+        <v>14.5251</v>
       </c>
       <c r="D92" t="n">
-        <v>31.2479</v>
+        <v>32.1598</v>
       </c>
       <c r="E92" t="n">
-        <v>18.8075</v>
+        <v>18.1089</v>
       </c>
       <c r="F92" t="n">
-        <v>17.889</v>
+        <v>18.2844</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>17.1121</v>
+        <v>17.6427</v>
       </c>
       <c r="C93" t="n">
-        <v>13.8454</v>
+        <v>14.7005</v>
       </c>
       <c r="D93" t="n">
-        <v>31.9706</v>
+        <v>32.9581</v>
       </c>
       <c r="E93" t="n">
-        <v>18.7497</v>
+        <v>18.0287</v>
       </c>
       <c r="F93" t="n">
-        <v>18.0052</v>
+        <v>18.3883</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>17.2077</v>
+        <v>17.9465</v>
       </c>
       <c r="C94" t="n">
-        <v>17.008</v>
+        <v>17.4189</v>
       </c>
       <c r="D94" t="n">
-        <v>32.7701</v>
+        <v>33.7148</v>
       </c>
       <c r="E94" t="n">
-        <v>18.911</v>
+        <v>18.3896</v>
       </c>
       <c r="F94" t="n">
-        <v>18.1027</v>
+        <v>18.4932</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>21.4618</v>
+        <v>21.688</v>
       </c>
       <c r="C95" t="n">
-        <v>17.1521</v>
+        <v>17.5387</v>
       </c>
       <c r="D95" t="n">
-        <v>33.7568</v>
+        <v>34.6418</v>
       </c>
       <c r="E95" t="n">
-        <v>19.2829</v>
+        <v>18.5033</v>
       </c>
       <c r="F95" t="n">
-        <v>18.223</v>
+        <v>18.6314</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>21.4458</v>
+        <v>21.9567</v>
       </c>
       <c r="C96" t="n">
-        <v>17.1716</v>
+        <v>17.6584</v>
       </c>
       <c r="D96" t="n">
-        <v>34.5941</v>
+        <v>35.431</v>
       </c>
       <c r="E96" t="n">
-        <v>19.3571</v>
+        <v>18.7105</v>
       </c>
       <c r="F96" t="n">
-        <v>18.3008</v>
+        <v>18.7059</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>21.4791</v>
+        <v>21.9843</v>
       </c>
       <c r="C97" t="n">
-        <v>17.2472</v>
+        <v>17.5956</v>
       </c>
       <c r="D97" t="n">
-        <v>35.6018</v>
+        <v>36.5046</v>
       </c>
       <c r="E97" t="n">
-        <v>19.5544</v>
+        <v>18.7704</v>
       </c>
       <c r="F97" t="n">
-        <v>18.4371</v>
+        <v>18.8335</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>21.4862</v>
+        <v>22.0086</v>
       </c>
       <c r="C98" t="n">
-        <v>17.2499</v>
+        <v>17.6871</v>
       </c>
       <c r="D98" t="n">
-        <v>36.3049</v>
+        <v>37.173</v>
       </c>
       <c r="E98" t="n">
-        <v>19.6942</v>
+        <v>18.9897</v>
       </c>
       <c r="F98" t="n">
-        <v>18.5531</v>
+        <v>18.96</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>21.5214</v>
+        <v>21.9832</v>
       </c>
       <c r="C99" t="n">
-        <v>17.2716</v>
+        <v>17.8404</v>
       </c>
       <c r="D99" t="n">
-        <v>37.2918</v>
+        <v>38.3125</v>
       </c>
       <c r="E99" t="n">
-        <v>19.9509</v>
+        <v>19.3794</v>
       </c>
       <c r="F99" t="n">
-        <v>18.7676</v>
+        <v>19.2375</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>21.5106</v>
+        <v>22.0163</v>
       </c>
       <c r="C100" t="n">
-        <v>17.335</v>
+        <v>17.7336</v>
       </c>
       <c r="D100" t="n">
-        <v>38.2997</v>
+        <v>39.3239</v>
       </c>
       <c r="E100" t="n">
-        <v>20.0956</v>
+        <v>19.453</v>
       </c>
       <c r="F100" t="n">
-        <v>18.9424</v>
+        <v>19.4438</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>21.5598</v>
+        <v>22.0943</v>
       </c>
       <c r="C101" t="n">
-        <v>17.3537</v>
+        <v>17.7768</v>
       </c>
       <c r="D101" t="n">
-        <v>39.6882</v>
+        <v>40.6423</v>
       </c>
       <c r="E101" t="n">
-        <v>20.4117</v>
+        <v>19.4001</v>
       </c>
       <c r="F101" t="n">
-        <v>19.0824</v>
+        <v>19.4792</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>21.618</v>
+        <v>22.1274</v>
       </c>
       <c r="C102" t="n">
-        <v>17.4516</v>
+        <v>17.7969</v>
       </c>
       <c r="D102" t="n">
-        <v>40.4941</v>
+        <v>41.5627</v>
       </c>
       <c r="E102" t="n">
-        <v>20.6489</v>
+        <v>19.5812</v>
       </c>
       <c r="F102" t="n">
-        <v>19.2069</v>
+        <v>19.6557</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>21.6119</v>
+        <v>22.1794</v>
       </c>
       <c r="C103" t="n">
-        <v>17.4923</v>
+        <v>17.926</v>
       </c>
       <c r="D103" t="n">
-        <v>41.7952</v>
+        <v>42.8284</v>
       </c>
       <c r="E103" t="n">
-        <v>20.9537</v>
+        <v>19.7431</v>
       </c>
       <c r="F103" t="n">
-        <v>19.5142</v>
+        <v>20.0393</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>21.6458</v>
+        <v>22.1874</v>
       </c>
       <c r="C104" t="n">
-        <v>17.609</v>
+        <v>17.9683</v>
       </c>
       <c r="D104" t="n">
-        <v>42.7554</v>
+        <v>43.8802</v>
       </c>
       <c r="E104" t="n">
-        <v>21.1828</v>
+        <v>19.9488</v>
       </c>
       <c r="F104" t="n">
-        <v>19.7259</v>
+        <v>20.1399</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>21.7336</v>
+        <v>22.2724</v>
       </c>
       <c r="C105" t="n">
-        <v>17.6532</v>
+        <v>18.0831</v>
       </c>
       <c r="D105" t="n">
-        <v>43.8256</v>
+        <v>45.0468</v>
       </c>
       <c r="E105" t="n">
-        <v>21.4651</v>
+        <v>20.117</v>
       </c>
       <c r="F105" t="n">
-        <v>20.0952</v>
+        <v>20.845</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>21.8927</v>
+        <v>22.4189</v>
       </c>
       <c r="C106" t="n">
-        <v>17.8232</v>
+        <v>18.2195</v>
       </c>
       <c r="D106" t="n">
-        <v>45.2285</v>
+        <v>46.6089</v>
       </c>
       <c r="E106" t="n">
-        <v>21.952</v>
+        <v>20.5062</v>
       </c>
       <c r="F106" t="n">
-        <v>20.5061</v>
+        <v>20.9141</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>22.0529</v>
+        <v>22.5441</v>
       </c>
       <c r="C107" t="n">
-        <v>18.0069</v>
+        <v>18.5122</v>
       </c>
       <c r="D107" t="n">
-        <v>38.1967</v>
+        <v>39.6059</v>
       </c>
       <c r="E107" t="n">
-        <v>23.3935</v>
+        <v>23.5386</v>
       </c>
       <c r="F107" t="n">
-        <v>22.8358</v>
+        <v>23.3579</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>22.0568</v>
+        <v>22.8111</v>
       </c>
       <c r="C108" t="n">
-        <v>18.5879</v>
+        <v>18.984</v>
       </c>
       <c r="D108" t="n">
-        <v>39.0595</v>
+        <v>39.969</v>
       </c>
       <c r="E108" t="n">
-        <v>23.6664</v>
+        <v>23.7631</v>
       </c>
       <c r="F108" t="n">
-        <v>23.1201</v>
+        <v>23.5271</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>22.8463</v>
+        <v>23.4172</v>
       </c>
       <c r="C109" t="n">
-        <v>18.6715</v>
+        <v>19.0249</v>
       </c>
       <c r="D109" t="n">
-        <v>39.776</v>
+        <v>40.7756</v>
       </c>
       <c r="E109" t="n">
-        <v>23.8315</v>
+        <v>23.9071</v>
       </c>
       <c r="F109" t="n">
-        <v>23.2324</v>
+        <v>23.6382</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>24.4979</v>
+        <v>25.4117</v>
       </c>
       <c r="C110" t="n">
-        <v>18.664</v>
+        <v>19.0872</v>
       </c>
       <c r="D110" t="n">
-        <v>40.4597</v>
+        <v>41.4817</v>
       </c>
       <c r="E110" t="n">
-        <v>24.0441</v>
+        <v>24.1216</v>
       </c>
       <c r="F110" t="n">
-        <v>23.3727</v>
+        <v>23.9322</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>24.6567</v>
+        <v>25.1375</v>
       </c>
       <c r="C111" t="n">
-        <v>18.7621</v>
+        <v>19.0835</v>
       </c>
       <c r="D111" t="n">
-        <v>41.4068</v>
+        <v>42.8227</v>
       </c>
       <c r="E111" t="n">
-        <v>24.3229</v>
+        <v>24.3047</v>
       </c>
       <c r="F111" t="n">
-        <v>23.6079</v>
+        <v>23.6023</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>24.3119</v>
+        <v>24.6923</v>
       </c>
       <c r="C112" t="n">
-        <v>18.8375</v>
+        <v>19.1704</v>
       </c>
       <c r="D112" t="n">
-        <v>42.1711</v>
+        <v>43.5705</v>
       </c>
       <c r="E112" t="n">
-        <v>24.5748</v>
+        <v>24.2909</v>
       </c>
       <c r="F112" t="n">
-        <v>23.812</v>
+        <v>24.2301</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>24.7281</v>
+        <v>24.9203</v>
       </c>
       <c r="C113" t="n">
-        <v>18.8756</v>
+        <v>19.1814</v>
       </c>
       <c r="D113" t="n">
-        <v>43.2909</v>
+        <v>44.6114</v>
       </c>
       <c r="E113" t="n">
-        <v>24.8542</v>
+        <v>24.606</v>
       </c>
       <c r="F113" t="n">
-        <v>24.0873</v>
+        <v>24.508</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>24.6996</v>
+        <v>25.1044</v>
       </c>
       <c r="C114" t="n">
-        <v>18.9264</v>
+        <v>19.2395</v>
       </c>
       <c r="D114" t="n">
-        <v>44.1375</v>
+        <v>45.5854</v>
       </c>
       <c r="E114" t="n">
-        <v>25.1438</v>
+        <v>25.0011</v>
       </c>
       <c r="F114" t="n">
-        <v>24.3376</v>
+        <v>24.7284</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>24.6276</v>
+        <v>25.3491</v>
       </c>
       <c r="C115" t="n">
-        <v>19.0503</v>
+        <v>19.3661</v>
       </c>
       <c r="D115" t="n">
-        <v>45.1356</v>
+        <v>46.573</v>
       </c>
       <c r="E115" t="n">
-        <v>25.404</v>
+        <v>25.1192</v>
       </c>
       <c r="F115" t="n">
-        <v>24.6619</v>
+        <v>25.0153</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>24.6246</v>
+        <v>25.3311</v>
       </c>
       <c r="C116" t="n">
-        <v>19.1579</v>
+        <v>19.3939</v>
       </c>
       <c r="D116" t="n">
-        <v>46.2</v>
+        <v>47.6618</v>
       </c>
       <c r="E116" t="n">
-        <v>25.6729</v>
+        <v>25.3822</v>
       </c>
       <c r="F116" t="n">
-        <v>24.9766</v>
+        <v>25.4195</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>24.7779</v>
+        <v>25.2926</v>
       </c>
       <c r="C117" t="n">
-        <v>19.2613</v>
+        <v>19.5229</v>
       </c>
       <c r="D117" t="n">
-        <v>47.1062</v>
+        <v>48.7229</v>
       </c>
       <c r="E117" t="n">
-        <v>26.1091</v>
+        <v>25.5936</v>
       </c>
       <c r="F117" t="n">
-        <v>25.3423</v>
+        <v>25.787</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>24.8162</v>
+        <v>25.5323</v>
       </c>
       <c r="C118" t="n">
-        <v>19.4646</v>
+        <v>19.6962</v>
       </c>
       <c r="D118" t="n">
-        <v>48.4794</v>
+        <v>49.9674</v>
       </c>
       <c r="E118" t="n">
-        <v>26.5607</v>
+        <v>25.9219</v>
       </c>
       <c r="F118" t="n">
-        <v>25.8369</v>
+        <v>26.3143</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>24.8246</v>
+        <v>25.5193</v>
       </c>
       <c r="C119" t="n">
-        <v>19.67</v>
+        <v>19.8865</v>
       </c>
       <c r="D119" t="n">
-        <v>49.2259</v>
+        <v>50.9269</v>
       </c>
       <c r="E119" t="n">
-        <v>26.9637</v>
+        <v>26.4406</v>
       </c>
       <c r="F119" t="n">
-        <v>26.239</v>
+        <v>26.8556</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>24.9622</v>
+        <v>25.7678</v>
       </c>
       <c r="C120" t="n">
-        <v>19.8346</v>
+        <v>20.2139</v>
       </c>
       <c r="D120" t="n">
-        <v>50.774</v>
+        <v>57.0067</v>
       </c>
       <c r="E120" t="n">
-        <v>27.638</v>
+        <v>26.6801</v>
       </c>
       <c r="F120" t="n">
-        <v>26.909</v>
+        <v>26.9365</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>25.1026</v>
+        <v>25.2295</v>
       </c>
       <c r="C121" t="n">
-        <v>20.1925</v>
+        <v>20.1721</v>
       </c>
       <c r="D121" t="n">
-        <v>41.0901</v>
+        <v>41.1823</v>
       </c>
       <c r="E121" t="n">
-        <v>27.0906</v>
+        <v>27.0399</v>
       </c>
       <c r="F121" t="n">
-        <v>26.6652</v>
+        <v>26.7671</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>25.7511</v>
+        <v>25.5502</v>
       </c>
       <c r="C122" t="n">
-        <v>20.7327</v>
+        <v>20.6906</v>
       </c>
       <c r="D122" t="n">
-        <v>41.8601</v>
+        <v>41.9633</v>
       </c>
       <c r="E122" t="n">
-        <v>27.3664</v>
+        <v>27.1327</v>
       </c>
       <c r="F122" t="n">
-        <v>26.9571</v>
+        <v>26.8979</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>26.0311</v>
+        <v>25.683</v>
       </c>
       <c r="C123" t="n">
-        <v>20.7934</v>
+        <v>20.8239</v>
       </c>
       <c r="D123" t="n">
-        <v>42.6079</v>
+        <v>42.6682</v>
       </c>
       <c r="E123" t="n">
-        <v>27.1434</v>
+        <v>27.5311</v>
       </c>
       <c r="F123" t="n">
-        <v>27.1622</v>
+        <v>27.1463</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>31.8244</v>
+        <v>31.934</v>
       </c>
       <c r="C124" t="n">
-        <v>20.92</v>
+        <v>20.9254</v>
       </c>
       <c r="D124" t="n">
-        <v>43.8551</v>
+        <v>43.9065</v>
       </c>
       <c r="E124" t="n">
-        <v>27.8495</v>
+        <v>27.7309</v>
       </c>
       <c r="F124" t="n">
-        <v>27.3504</v>
+        <v>27.2736</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>31.7089</v>
+        <v>31.9</v>
       </c>
       <c r="C125" t="n">
-        <v>21.0058</v>
+        <v>21.0231</v>
       </c>
       <c r="D125" t="n">
-        <v>44.5952</v>
+        <v>44.5956</v>
       </c>
       <c r="E125" t="n">
-        <v>28.0997</v>
+        <v>27.9489</v>
       </c>
       <c r="F125" t="n">
-        <v>27.6747</v>
+        <v>27.5826</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>32.126</v>
+        <v>31.7751</v>
       </c>
       <c r="C126" t="n">
-        <v>21.178</v>
+        <v>21.138</v>
       </c>
       <c r="D126" t="n">
-        <v>44.8166</v>
+        <v>44.9308</v>
       </c>
       <c r="E126" t="n">
-        <v>28.4224</v>
+        <v>28.2847</v>
       </c>
       <c r="F126" t="n">
-        <v>27.7432</v>
+        <v>27.8362</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>31.9636</v>
+        <v>31.9624</v>
       </c>
       <c r="C127" t="n">
-        <v>21.2658</v>
+        <v>21.3185</v>
       </c>
       <c r="D127" t="n">
-        <v>45.8374</v>
+        <v>45.8914</v>
       </c>
       <c r="E127" t="n">
-        <v>28.6381</v>
+        <v>28.4767</v>
       </c>
       <c r="F127" t="n">
-        <v>28.1457</v>
+        <v>28.1189</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>31.9302</v>
+        <v>31.8388</v>
       </c>
       <c r="C128" t="n">
-        <v>21.4457</v>
+        <v>21.417</v>
       </c>
       <c r="D128" t="n">
-        <v>46.6385</v>
+        <v>46.7726</v>
       </c>
       <c r="E128" t="n">
-        <v>29.0064</v>
+        <v>28.8165</v>
       </c>
       <c r="F128" t="n">
-        <v>28.4755</v>
+        <v>28.4501</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>31.8845</v>
+        <v>31.6605</v>
       </c>
       <c r="C129" t="n">
-        <v>21.6179</v>
+        <v>21.5977</v>
       </c>
       <c r="D129" t="n">
-        <v>47.8457</v>
+        <v>47.8599</v>
       </c>
       <c r="E129" t="n">
-        <v>29.336</v>
+        <v>29.0632</v>
       </c>
       <c r="F129" t="n">
-        <v>28.7439</v>
+        <v>28.7484</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>31.9304</v>
+        <v>31.9668</v>
       </c>
       <c r="C130" t="n">
-        <v>21.831</v>
+        <v>21.8129</v>
       </c>
       <c r="D130" t="n">
-        <v>48.8102</v>
+        <v>48.6962</v>
       </c>
       <c r="E130" t="n">
-        <v>29.6962</v>
+        <v>29.4585</v>
       </c>
       <c r="F130" t="n">
-        <v>29.2359</v>
+        <v>29.2385</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>31.9364</v>
+        <v>32.0223</v>
       </c>
       <c r="C131" t="n">
-        <v>22.0025</v>
+        <v>21.9916</v>
       </c>
       <c r="D131" t="n">
-        <v>49.8588</v>
+        <v>49.9866</v>
       </c>
       <c r="E131" t="n">
-        <v>29.9795</v>
+        <v>29.6996</v>
       </c>
       <c r="F131" t="n">
-        <v>29.7609</v>
+        <v>29.6364</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>31.9426</v>
+        <v>31.9799</v>
       </c>
       <c r="C132" t="n">
-        <v>22.2966</v>
+        <v>22.3004</v>
       </c>
       <c r="D132" t="n">
-        <v>50.9884</v>
+        <v>50.9979</v>
       </c>
       <c r="E132" t="n">
-        <v>30.5415</v>
+        <v>30.1946</v>
       </c>
       <c r="F132" t="n">
-        <v>30.1309</v>
+        <v>30.2594</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>31.983</v>
+        <v>32.1512</v>
       </c>
       <c r="C133" t="n">
-        <v>22.6035</v>
+        <v>22.609</v>
       </c>
       <c r="D133" t="n">
-        <v>51.9934</v>
+        <v>51.8539</v>
       </c>
       <c r="E133" t="n">
-        <v>31.0745</v>
+        <v>30.6152</v>
       </c>
       <c r="F133" t="n">
-        <v>30.8641</v>
+        <v>30.6829</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>32.176</v>
+        <v>32.1602</v>
       </c>
       <c r="C134" t="n">
-        <v>22.9387</v>
+        <v>22.9637</v>
       </c>
       <c r="D134" t="n">
-        <v>53.3216</v>
+        <v>53.3923</v>
       </c>
       <c r="E134" t="n">
-        <v>31.7304</v>
+        <v>31.2351</v>
       </c>
       <c r="F134" t="n">
-        <v>31.6592</v>
+        <v>31.6032</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>32.3467</v>
+        <v>32.3335</v>
       </c>
       <c r="C135" t="n">
-        <v>23.383</v>
+        <v>23.412</v>
       </c>
       <c r="D135" t="n">
-        <v>43.2284</v>
+        <v>43.2997</v>
       </c>
       <c r="E135" t="n">
-        <v>28.7404</v>
+        <v>29.0396</v>
       </c>
       <c r="F135" t="n">
-        <v>29.1569</v>
+        <v>29.1347</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>32.3211</v>
+        <v>32.1043</v>
       </c>
       <c r="C136" t="n">
-        <v>23.1049</v>
+        <v>23.0511</v>
       </c>
       <c r="D136" t="n">
-        <v>43.4619</v>
+        <v>43.459</v>
       </c>
       <c r="E136" t="n">
-        <v>29.2463</v>
+        <v>29.3752</v>
       </c>
       <c r="F136" t="n">
-        <v>29.373</v>
+        <v>29.2363</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>32.0947</v>
+        <v>32.4311</v>
       </c>
       <c r="C137" t="n">
-        <v>22.7932</v>
+        <v>23.2148</v>
       </c>
       <c r="D137" t="n">
-        <v>44.2272</v>
+        <v>44.0301</v>
       </c>
       <c r="E137" t="n">
-        <v>29.4284</v>
+        <v>29.7094</v>
       </c>
       <c r="F137" t="n">
-        <v>29.6896</v>
+        <v>29.4317</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>37.0639</v>
+        <v>36.7434</v>
       </c>
       <c r="C138" t="n">
-        <v>23.3288</v>
+        <v>23.2828</v>
       </c>
       <c r="D138" t="n">
-        <v>45.3178</v>
+        <v>45.1375</v>
       </c>
       <c r="E138" t="n">
-        <v>30.0245</v>
+        <v>30.0637</v>
       </c>
       <c r="F138" t="n">
-        <v>29.871</v>
+        <v>29.7168</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>37.1815</v>
+        <v>37.2145</v>
       </c>
       <c r="C139" t="n">
-        <v>23.4751</v>
+        <v>23.433</v>
       </c>
       <c r="D139" t="n">
-        <v>45.3381</v>
+        <v>45.3874</v>
       </c>
       <c r="E139" t="n">
-        <v>30.1855</v>
+        <v>30.0748</v>
       </c>
       <c r="F139" t="n">
-        <v>30.2102</v>
+        <v>30.1836</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>37.1694</v>
+        <v>37.2225</v>
       </c>
       <c r="C140" t="n">
-        <v>23.6395</v>
+        <v>23.6819</v>
       </c>
       <c r="D140" t="n">
-        <v>46.2783</v>
+        <v>46.3265</v>
       </c>
       <c r="E140" t="n">
-        <v>30.4096</v>
+        <v>30.4929</v>
       </c>
       <c r="F140" t="n">
-        <v>30.4388</v>
+        <v>30.3887</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>37.1459</v>
+        <v>37.2144</v>
       </c>
       <c r="C141" t="n">
-        <v>23.8109</v>
+        <v>23.7873</v>
       </c>
       <c r="D141" t="n">
-        <v>47.2819</v>
+        <v>47.475</v>
       </c>
       <c r="E141" t="n">
-        <v>30.6541</v>
+        <v>30.7752</v>
       </c>
       <c r="F141" t="n">
-        <v>30.7039</v>
+        <v>30.668</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>37.2031</v>
+        <v>37.269</v>
       </c>
       <c r="C142" t="n">
-        <v>23.9938</v>
+        <v>23.9942</v>
       </c>
       <c r="D142" t="n">
-        <v>48.3273</v>
+        <v>48.364</v>
       </c>
       <c r="E142" t="n">
-        <v>30.9097</v>
+        <v>31.0895</v>
       </c>
       <c r="F142" t="n">
-        <v>31.0287</v>
+        <v>30.8193</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>37.2235</v>
+        <v>37.2898</v>
       </c>
       <c r="C143" t="n">
-        <v>24.1645</v>
+        <v>24.1709</v>
       </c>
       <c r="D143" t="n">
-        <v>49.7952</v>
+        <v>50.0031</v>
       </c>
       <c r="E143" t="n">
-        <v>30.6272</v>
+        <v>31.1598</v>
       </c>
       <c r="F143" t="n">
-        <v>31.4422</v>
+        <v>31.3388</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Scattered successful looukp.xlsx
+++ b/clang-x64/Scattered successful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>3.27786</v>
+        <v>3.42781</v>
       </c>
       <c r="C2" t="n">
-        <v>2.67111</v>
+        <v>2.69649</v>
       </c>
       <c r="D2" t="n">
-        <v>6.87493</v>
+        <v>7.04459</v>
       </c>
       <c r="E2" t="n">
-        <v>3.10335</v>
+        <v>3.56402</v>
       </c>
       <c r="F2" t="n">
-        <v>3.15121</v>
+        <v>3.14901</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>3.1935</v>
+        <v>3.4334</v>
       </c>
       <c r="C3" t="n">
-        <v>2.57541</v>
+        <v>2.81273</v>
       </c>
       <c r="D3" t="n">
-        <v>7.64848</v>
+        <v>7.7454</v>
       </c>
       <c r="E3" t="n">
-        <v>3.04763</v>
+        <v>3.25734</v>
       </c>
       <c r="F3" t="n">
-        <v>3.28395</v>
+        <v>3.45761</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>3.12116</v>
+        <v>3.24415</v>
       </c>
       <c r="C4" t="n">
-        <v>2.50914</v>
+        <v>2.67025</v>
       </c>
       <c r="D4" t="n">
-        <v>8.39696</v>
+        <v>8.595269999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>3.04671</v>
+        <v>3.20234</v>
       </c>
       <c r="F4" t="n">
-        <v>3.29249</v>
+        <v>3.66182</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.1765</v>
+        <v>3.48203</v>
       </c>
       <c r="C5" t="n">
-        <v>2.58906</v>
+        <v>2.86161</v>
       </c>
       <c r="D5" t="n">
-        <v>9.139860000000001</v>
+        <v>9.33647</v>
       </c>
       <c r="E5" t="n">
-        <v>3.09291</v>
+        <v>3.12517</v>
       </c>
       <c r="F5" t="n">
-        <v>3.28741</v>
+        <v>3.6944</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>3.19267</v>
+        <v>3.49062</v>
       </c>
       <c r="C6" t="n">
-        <v>2.59133</v>
+        <v>2.87979</v>
       </c>
       <c r="D6" t="n">
-        <v>9.95058</v>
+        <v>10.0494</v>
       </c>
       <c r="E6" t="n">
-        <v>3.11514</v>
+        <v>3.56725</v>
       </c>
       <c r="F6" t="n">
-        <v>3.23746</v>
+        <v>3.3217</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>3.23737</v>
+        <v>3.50196</v>
       </c>
       <c r="C7" t="n">
-        <v>2.67891</v>
+        <v>2.91102</v>
       </c>
       <c r="D7" t="n">
-        <v>6.06327</v>
+        <v>6.28112</v>
       </c>
       <c r="E7" t="n">
-        <v>3.64626</v>
+        <v>3.10311</v>
       </c>
       <c r="F7" t="n">
-        <v>3.31346</v>
+        <v>3.43052</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>3.26613</v>
+        <v>3.51532</v>
       </c>
       <c r="C8" t="n">
-        <v>2.90091</v>
+        <v>2.66113</v>
       </c>
       <c r="D8" t="n">
-        <v>6.30256</v>
+        <v>6.53373</v>
       </c>
       <c r="E8" t="n">
-        <v>3.67495</v>
+        <v>3.17628</v>
       </c>
       <c r="F8" t="n">
-        <v>3.33436</v>
+        <v>3.46391</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>3.23183</v>
+        <v>3.33879</v>
       </c>
       <c r="C9" t="n">
-        <v>2.96373</v>
+        <v>2.66602</v>
       </c>
       <c r="D9" t="n">
-        <v>6.97428</v>
+        <v>7.22295</v>
       </c>
       <c r="E9" t="n">
-        <v>3.71473</v>
+        <v>3.21732</v>
       </c>
       <c r="F9" t="n">
-        <v>3.36416</v>
+        <v>3.48667</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>3.99789</v>
+        <v>3.59483</v>
       </c>
       <c r="C10" t="n">
-        <v>2.97738</v>
+        <v>2.6765</v>
       </c>
       <c r="D10" t="n">
-        <v>7.38662</v>
+        <v>7.60708</v>
       </c>
       <c r="E10" t="n">
-        <v>3.74582</v>
+        <v>3.25131</v>
       </c>
       <c r="F10" t="n">
-        <v>3.39457</v>
+        <v>3.53869</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>4.24994</v>
+        <v>3.59178</v>
       </c>
       <c r="C11" t="n">
-        <v>3.00597</v>
+        <v>2.68719</v>
       </c>
       <c r="D11" t="n">
-        <v>7.93093</v>
+        <v>8.102690000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>3.95591</v>
+        <v>3.28879</v>
       </c>
       <c r="F11" t="n">
-        <v>3.41151</v>
+        <v>3.45446</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>3.98674</v>
+        <v>3.59697</v>
       </c>
       <c r="C12" t="n">
-        <v>3.04611</v>
+        <v>2.71022</v>
       </c>
       <c r="D12" t="n">
-        <v>8.54176</v>
+        <v>8.76126</v>
       </c>
       <c r="E12" t="n">
-        <v>3.97761</v>
+        <v>3.31053</v>
       </c>
       <c r="F12" t="n">
-        <v>3.45171</v>
+        <v>3.49293</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>4.31548</v>
+        <v>3.61552</v>
       </c>
       <c r="C13" t="n">
-        <v>3.08151</v>
+        <v>2.71286</v>
       </c>
       <c r="D13" t="n">
-        <v>9.07141</v>
+        <v>9.2555</v>
       </c>
       <c r="E13" t="n">
-        <v>3.85789</v>
+        <v>3.34237</v>
       </c>
       <c r="F13" t="n">
-        <v>3.51538</v>
+        <v>3.65645</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>4.2494</v>
+        <v>3.62816</v>
       </c>
       <c r="C14" t="n">
-        <v>3.11246</v>
+        <v>2.73305</v>
       </c>
       <c r="D14" t="n">
-        <v>9.598649999999999</v>
+        <v>9.84623</v>
       </c>
       <c r="E14" t="n">
-        <v>3.85956</v>
+        <v>3.36864</v>
       </c>
       <c r="F14" t="n">
-        <v>3.51904</v>
+        <v>3.64837</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>4.33225</v>
+        <v>3.64927</v>
       </c>
       <c r="C15" t="n">
-        <v>3.12464</v>
+        <v>2.75392</v>
       </c>
       <c r="D15" t="n">
-        <v>10.1088</v>
+        <v>10.2246</v>
       </c>
       <c r="E15" t="n">
-        <v>3.95198</v>
+        <v>3.41821</v>
       </c>
       <c r="F15" t="n">
-        <v>3.55232</v>
+        <v>3.71795</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>4.27142</v>
+        <v>3.6601</v>
       </c>
       <c r="C16" t="n">
-        <v>3.15078</v>
+        <v>2.76899</v>
       </c>
       <c r="D16" t="n">
-        <v>10.6362</v>
+        <v>10.7984</v>
       </c>
       <c r="E16" t="n">
-        <v>4.09527</v>
+        <v>3.44535</v>
       </c>
       <c r="F16" t="n">
-        <v>3.59801</v>
+        <v>3.59604</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>4.34758</v>
+        <v>3.68458</v>
       </c>
       <c r="C17" t="n">
-        <v>3.18359</v>
+        <v>2.79531</v>
       </c>
       <c r="D17" t="n">
-        <v>11.14</v>
+        <v>11.2256</v>
       </c>
       <c r="E17" t="n">
-        <v>3.95198</v>
+        <v>3.45998</v>
       </c>
       <c r="F17" t="n">
-        <v>3.60789</v>
+        <v>3.74377</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>4.3629</v>
+        <v>3.70561</v>
       </c>
       <c r="C18" t="n">
-        <v>3.22094</v>
+        <v>2.83396</v>
       </c>
       <c r="D18" t="n">
-        <v>11.6105</v>
+        <v>11.6108</v>
       </c>
       <c r="E18" t="n">
-        <v>4.133</v>
+        <v>3.4788</v>
       </c>
       <c r="F18" t="n">
-        <v>3.62348</v>
+        <v>3.64108</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>4.37809</v>
+        <v>3.72359</v>
       </c>
       <c r="C19" t="n">
-        <v>3.246</v>
+        <v>2.86529</v>
       </c>
       <c r="D19" t="n">
-        <v>12.0695</v>
+        <v>12.1054</v>
       </c>
       <c r="E19" t="n">
-        <v>3.96877</v>
+        <v>3.54512</v>
       </c>
       <c r="F19" t="n">
-        <v>3.67221</v>
+        <v>3.79557</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>4.39751</v>
+        <v>3.73859</v>
       </c>
       <c r="C20" t="n">
-        <v>3.28691</v>
+        <v>2.88855</v>
       </c>
       <c r="D20" t="n">
-        <v>12.3942</v>
+        <v>12.4104</v>
       </c>
       <c r="E20" t="n">
-        <v>4.27921</v>
+        <v>3.5727</v>
       </c>
       <c r="F20" t="n">
-        <v>3.72833</v>
+        <v>3.86381</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>4.41444</v>
+        <v>3.75887</v>
       </c>
       <c r="C21" t="n">
-        <v>3.31987</v>
+        <v>2.92681</v>
       </c>
       <c r="D21" t="n">
-        <v>8.67193</v>
+        <v>8.43431</v>
       </c>
       <c r="E21" t="n">
-        <v>3.91875</v>
+        <v>3.54022</v>
       </c>
       <c r="F21" t="n">
-        <v>4.03351</v>
+        <v>3.69399</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>4.44622</v>
+        <v>3.79033</v>
       </c>
       <c r="C22" t="n">
-        <v>3.11911</v>
+        <v>2.93358</v>
       </c>
       <c r="D22" t="n">
-        <v>8.99943</v>
+        <v>8.78185</v>
       </c>
       <c r="E22" t="n">
-        <v>3.88374</v>
+        <v>3.59694</v>
       </c>
       <c r="F22" t="n">
-        <v>4.10505</v>
+        <v>3.75359</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>4.51752</v>
+        <v>3.8562</v>
       </c>
       <c r="C23" t="n">
-        <v>3.132</v>
+        <v>2.95689</v>
       </c>
       <c r="D23" t="n">
-        <v>9.393660000000001</v>
+        <v>9.16461</v>
       </c>
       <c r="E23" t="n">
-        <v>4.04634</v>
+        <v>3.61341</v>
       </c>
       <c r="F23" t="n">
-        <v>4.0763</v>
+        <v>3.75107</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>4.68612</v>
+        <v>4.05417</v>
       </c>
       <c r="C24" t="n">
-        <v>3.16738</v>
+        <v>2.96455</v>
       </c>
       <c r="D24" t="n">
-        <v>9.75285</v>
+        <v>9.568899999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>4.07165</v>
+        <v>3.65054</v>
       </c>
       <c r="F24" t="n">
-        <v>4.10851</v>
+        <v>3.78332</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>4.67207</v>
+        <v>4.06891</v>
       </c>
       <c r="C25" t="n">
-        <v>3.16777</v>
+        <v>2.97742</v>
       </c>
       <c r="D25" t="n">
-        <v>10.1525</v>
+        <v>9.953900000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>4.0294</v>
+        <v>3.68952</v>
       </c>
       <c r="F25" t="n">
-        <v>4.20154</v>
+        <v>3.82576</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>4.68019</v>
+        <v>4.07355</v>
       </c>
       <c r="C26" t="n">
-        <v>3.17768</v>
+        <v>2.98514</v>
       </c>
       <c r="D26" t="n">
-        <v>10.5275</v>
+        <v>10.3387</v>
       </c>
       <c r="E26" t="n">
-        <v>3.9828</v>
+        <v>3.72416</v>
       </c>
       <c r="F26" t="n">
-        <v>4.09041</v>
+        <v>3.84182</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>4.60181</v>
+        <v>4.0465</v>
       </c>
       <c r="C27" t="n">
-        <v>3.26139</v>
+        <v>3.05077</v>
       </c>
       <c r="D27" t="n">
-        <v>10.9638</v>
+        <v>10.7251</v>
       </c>
       <c r="E27" t="n">
-        <v>4.15867</v>
+        <v>3.9403</v>
       </c>
       <c r="F27" t="n">
-        <v>4.12289</v>
+        <v>3.87268</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>4.62615</v>
+        <v>4.04298</v>
       </c>
       <c r="C28" t="n">
-        <v>3.27484</v>
+        <v>3.06502</v>
       </c>
       <c r="D28" t="n">
-        <v>11.3658</v>
+        <v>11.1298</v>
       </c>
       <c r="E28" t="n">
-        <v>4.20665</v>
+        <v>3.96652</v>
       </c>
       <c r="F28" t="n">
-        <v>4.14902</v>
+        <v>3.89795</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>4.64262</v>
+        <v>4.06717</v>
       </c>
       <c r="C29" t="n">
-        <v>3.30096</v>
+        <v>3.08892</v>
       </c>
       <c r="D29" t="n">
-        <v>11.7607</v>
+        <v>11.5283</v>
       </c>
       <c r="E29" t="n">
-        <v>4.25544</v>
+        <v>4.00928</v>
       </c>
       <c r="F29" t="n">
-        <v>4.20398</v>
+        <v>3.9442</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>4.65734</v>
+        <v>4.10724</v>
       </c>
       <c r="C30" t="n">
-        <v>3.33424</v>
+        <v>3.04236</v>
       </c>
       <c r="D30" t="n">
-        <v>12.1754</v>
+        <v>11.9089</v>
       </c>
       <c r="E30" t="n">
-        <v>4.2813</v>
+        <v>4.07068</v>
       </c>
       <c r="F30" t="n">
-        <v>4.22669</v>
+        <v>3.96152</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>4.74856</v>
+        <v>4.14352</v>
       </c>
       <c r="C31" t="n">
-        <v>3.27996</v>
+        <v>3.08364</v>
       </c>
       <c r="D31" t="n">
-        <v>12.6106</v>
+        <v>12.3064</v>
       </c>
       <c r="E31" t="n">
-        <v>4.14726</v>
+        <v>3.87779</v>
       </c>
       <c r="F31" t="n">
-        <v>4.26274</v>
+        <v>4.01166</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>4.66338</v>
+        <v>4.11349</v>
       </c>
       <c r="C32" t="n">
-        <v>3.38758</v>
+        <v>3.16508</v>
       </c>
       <c r="D32" t="n">
-        <v>12.9205</v>
+        <v>12.6166</v>
       </c>
       <c r="E32" t="n">
-        <v>4.36892</v>
+        <v>4.12737</v>
       </c>
       <c r="F32" t="n">
-        <v>4.31121</v>
+        <v>4.04552</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.70644</v>
+        <v>4.13895</v>
       </c>
       <c r="C33" t="n">
-        <v>3.41947</v>
+        <v>3.20061</v>
       </c>
       <c r="D33" t="n">
-        <v>13.3292</v>
+        <v>12.9908</v>
       </c>
       <c r="E33" t="n">
-        <v>4.28202</v>
+        <v>3.97193</v>
       </c>
       <c r="F33" t="n">
-        <v>4.39545</v>
+        <v>4.11914</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>4.71068</v>
+        <v>4.16936</v>
       </c>
       <c r="C34" t="n">
-        <v>3.46335</v>
+        <v>3.23493</v>
       </c>
       <c r="D34" t="n">
-        <v>13.6642</v>
+        <v>13.3334</v>
       </c>
       <c r="E34" t="n">
-        <v>4.18991</v>
+        <v>4.57418</v>
       </c>
       <c r="F34" t="n">
-        <v>4.53534</v>
+        <v>4.23461</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>4.73646</v>
+        <v>4.23698</v>
       </c>
       <c r="C35" t="n">
-        <v>3.42525</v>
+        <v>3.22592</v>
       </c>
       <c r="D35" t="n">
-        <v>9.436030000000001</v>
+        <v>9.36314</v>
       </c>
       <c r="E35" t="n">
-        <v>3.95305</v>
+        <v>4.30575</v>
       </c>
       <c r="F35" t="n">
-        <v>4.08551</v>
+        <v>4.30818</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>4.79456</v>
+        <v>4.30108</v>
       </c>
       <c r="C36" t="n">
-        <v>3.56559</v>
+        <v>3.39403</v>
       </c>
       <c r="D36" t="n">
-        <v>9.69228</v>
+        <v>9.59845</v>
       </c>
       <c r="E36" t="n">
-        <v>4.01088</v>
+        <v>4.37549</v>
       </c>
       <c r="F36" t="n">
-        <v>4.11132</v>
+        <v>4.33553</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>4.79302</v>
+        <v>4.75861</v>
       </c>
       <c r="C37" t="n">
-        <v>3.45661</v>
+        <v>3.51141</v>
       </c>
       <c r="D37" t="n">
-        <v>9.914540000000001</v>
+        <v>9.80949</v>
       </c>
       <c r="E37" t="n">
-        <v>4.04422</v>
+        <v>4.41356</v>
       </c>
       <c r="F37" t="n">
-        <v>4.146</v>
+        <v>4.37012</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>4.87028</v>
+        <v>4.88996</v>
       </c>
       <c r="C38" t="n">
-        <v>3.3503</v>
+        <v>3.3292</v>
       </c>
       <c r="D38" t="n">
-        <v>10.2135</v>
+        <v>10.1168</v>
       </c>
       <c r="E38" t="n">
-        <v>4.06007</v>
+        <v>4.4295</v>
       </c>
       <c r="F38" t="n">
-        <v>4.1657</v>
+        <v>4.39228</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>4.84502</v>
+        <v>5.11847</v>
       </c>
       <c r="C39" t="n">
-        <v>3.26915</v>
+        <v>3.56292</v>
       </c>
       <c r="D39" t="n">
-        <v>10.5195</v>
+        <v>10.4388</v>
       </c>
       <c r="E39" t="n">
-        <v>4.10013</v>
+        <v>4.46434</v>
       </c>
       <c r="F39" t="n">
-        <v>4.18389</v>
+        <v>4.41624</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>4.86004</v>
+        <v>5.14056</v>
       </c>
       <c r="C40" t="n">
-        <v>3.30036</v>
+        <v>3.55489</v>
       </c>
       <c r="D40" t="n">
-        <v>10.8682</v>
+        <v>10.758</v>
       </c>
       <c r="E40" t="n">
-        <v>4.12299</v>
+        <v>4.49865</v>
       </c>
       <c r="F40" t="n">
-        <v>4.22062</v>
+        <v>4.44454</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>4.45416</v>
+        <v>5.13784</v>
       </c>
       <c r="C41" t="n">
-        <v>3.55086</v>
+        <v>3.58093</v>
       </c>
       <c r="D41" t="n">
-        <v>11.2333</v>
+        <v>11.1257</v>
       </c>
       <c r="E41" t="n">
-        <v>4.44987</v>
+        <v>4.18609</v>
       </c>
       <c r="F41" t="n">
-        <v>4.31753</v>
+        <v>4.52204</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>4.6389</v>
+        <v>5.18762</v>
       </c>
       <c r="C42" t="n">
-        <v>3.51926</v>
+        <v>3.42442</v>
       </c>
       <c r="D42" t="n">
-        <v>11.6047</v>
+        <v>11.4951</v>
       </c>
       <c r="E42" t="n">
-        <v>4.19459</v>
+        <v>4.57523</v>
       </c>
       <c r="F42" t="n">
-        <v>4.29152</v>
+        <v>4.51223</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>4.6579</v>
+        <v>5.19002</v>
       </c>
       <c r="C43" t="n">
-        <v>3.61927</v>
+        <v>3.45565</v>
       </c>
       <c r="D43" t="n">
-        <v>11.9691</v>
+        <v>11.8697</v>
       </c>
       <c r="E43" t="n">
-        <v>4.54858</v>
+        <v>4.24153</v>
       </c>
       <c r="F43" t="n">
-        <v>4.39705</v>
+        <v>4.60644</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>4.71021</v>
+        <v>5.21128</v>
       </c>
       <c r="C44" t="n">
-        <v>3.50685</v>
+        <v>3.4674</v>
       </c>
       <c r="D44" t="n">
-        <v>12.3251</v>
+        <v>12.2708</v>
       </c>
       <c r="E44" t="n">
-        <v>4.27602</v>
+        <v>4.6753</v>
       </c>
       <c r="F44" t="n">
-        <v>4.43958</v>
+        <v>4.66348</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>4.74663</v>
+        <v>5.22504</v>
       </c>
       <c r="C45" t="n">
-        <v>3.6866</v>
+        <v>3.49097</v>
       </c>
       <c r="D45" t="n">
-        <v>12.7223</v>
+        <v>12.6662</v>
       </c>
       <c r="E45" t="n">
-        <v>4.67244</v>
+        <v>4.2453</v>
       </c>
       <c r="F45" t="n">
-        <v>4.47019</v>
+        <v>4.66092</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.64109</v>
+        <v>5.05593</v>
       </c>
       <c r="C46" t="n">
-        <v>3.63875</v>
+        <v>3.65522</v>
       </c>
       <c r="D46" t="n">
-        <v>13.0929</v>
+        <v>13.0298</v>
       </c>
       <c r="E46" t="n">
-        <v>4.73764</v>
+        <v>4.3324</v>
       </c>
       <c r="F46" t="n">
-        <v>4.54553</v>
+        <v>4.73949</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.53762</v>
+        <v>5.24317</v>
       </c>
       <c r="C47" t="n">
-        <v>3.74013</v>
+        <v>3.76408</v>
       </c>
       <c r="D47" t="n">
-        <v>13.491</v>
+        <v>13.3636</v>
       </c>
       <c r="E47" t="n">
-        <v>4.69846</v>
+        <v>4.56479</v>
       </c>
       <c r="F47" t="n">
-        <v>4.94318</v>
+        <v>4.70646</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>4.93654</v>
+        <v>5.13524</v>
       </c>
       <c r="C48" t="n">
-        <v>3.51969</v>
+        <v>3.57021</v>
       </c>
       <c r="D48" t="n">
-        <v>13.8641</v>
+        <v>13.7533</v>
       </c>
       <c r="E48" t="n">
-        <v>4.8073</v>
+        <v>4.74571</v>
       </c>
       <c r="F48" t="n">
-        <v>5.16586</v>
+        <v>4.86173</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>4.64407</v>
+        <v>5.30118</v>
       </c>
       <c r="C49" t="n">
-        <v>3.85114</v>
+        <v>3.66681</v>
       </c>
       <c r="D49" t="n">
-        <v>14.2185</v>
+        <v>14.0627</v>
       </c>
       <c r="E49" t="n">
-        <v>5.11275</v>
+        <v>5.06377</v>
       </c>
       <c r="F49" t="n">
-        <v>5.64323</v>
+        <v>5.1614</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>4.88639</v>
+        <v>5.47284</v>
       </c>
       <c r="C50" t="n">
-        <v>3.98927</v>
+        <v>3.78299</v>
       </c>
       <c r="D50" t="n">
-        <v>10.5141</v>
+        <v>9.802659999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>4.35185</v>
+        <v>4.60124</v>
       </c>
       <c r="F50" t="n">
-        <v>4.58505</v>
+        <v>4.66463</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>5.34986</v>
+        <v>5.52966</v>
       </c>
       <c r="C51" t="n">
-        <v>3.53581</v>
+        <v>4.75583</v>
       </c>
       <c r="D51" t="n">
-        <v>10.7925</v>
+        <v>10.0377</v>
       </c>
       <c r="E51" t="n">
-        <v>4.40217</v>
+        <v>4.63739</v>
       </c>
       <c r="F51" t="n">
-        <v>4.63748</v>
+        <v>4.74905</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>5.83682</v>
+        <v>6.37491</v>
       </c>
       <c r="C52" t="n">
-        <v>3.57155</v>
+        <v>4.02797</v>
       </c>
       <c r="D52" t="n">
-        <v>11.2396</v>
+        <v>10.2924</v>
       </c>
       <c r="E52" t="n">
-        <v>4.42012</v>
+        <v>4.69094</v>
       </c>
       <c r="F52" t="n">
-        <v>4.59197</v>
+        <v>4.92068</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>5.13661</v>
+        <v>6.50179</v>
       </c>
       <c r="C53" t="n">
-        <v>3.60909</v>
+        <v>4.48538</v>
       </c>
       <c r="D53" t="n">
-        <v>11.7978</v>
+        <v>10.5952</v>
       </c>
       <c r="E53" t="n">
-        <v>4.47514</v>
+        <v>4.74446</v>
       </c>
       <c r="F53" t="n">
-        <v>4.71491</v>
+        <v>4.80277</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>5.15486</v>
+        <v>6.34229</v>
       </c>
       <c r="C54" t="n">
-        <v>3.60839</v>
+        <v>4.80046</v>
       </c>
       <c r="D54" t="n">
-        <v>12.2632</v>
+        <v>10.9921</v>
       </c>
       <c r="E54" t="n">
-        <v>4.51056</v>
+        <v>4.84161</v>
       </c>
       <c r="F54" t="n">
-        <v>4.75984</v>
+        <v>4.84712</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>5.16752</v>
+        <v>6.68074</v>
       </c>
       <c r="C55" t="n">
-        <v>3.63086</v>
+        <v>5.12662</v>
       </c>
       <c r="D55" t="n">
-        <v>12.6996</v>
+        <v>11.3235</v>
       </c>
       <c r="E55" t="n">
-        <v>4.61117</v>
+        <v>4.54694</v>
       </c>
       <c r="F55" t="n">
-        <v>4.72229</v>
+        <v>5.32641</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>5.18003</v>
+        <v>5.21019</v>
       </c>
       <c r="C56" t="n">
-        <v>3.73827</v>
+        <v>3.63726</v>
       </c>
       <c r="D56" t="n">
-        <v>12.2407</v>
+        <v>12.3953</v>
       </c>
       <c r="E56" t="n">
-        <v>4.56799</v>
+        <v>4.66606</v>
       </c>
       <c r="F56" t="n">
-        <v>5.0113</v>
+        <v>4.99003</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>5.14363</v>
+        <v>6.46043</v>
       </c>
       <c r="C57" t="n">
-        <v>3.75404</v>
+        <v>4.45796</v>
       </c>
       <c r="D57" t="n">
-        <v>13.7954</v>
+        <v>12.36</v>
       </c>
       <c r="E57" t="n">
-        <v>4.70666</v>
+        <v>4.63632</v>
       </c>
       <c r="F57" t="n">
-        <v>5.03273</v>
+        <v>5.65296</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>5.20508</v>
+        <v>7.1261</v>
       </c>
       <c r="C58" t="n">
-        <v>3.68408</v>
+        <v>5.3312</v>
       </c>
       <c r="D58" t="n">
-        <v>14.1103</v>
+        <v>12.9064</v>
       </c>
       <c r="E58" t="n">
-        <v>4.77073</v>
+        <v>4.69653</v>
       </c>
       <c r="F58" t="n">
-        <v>5.05891</v>
+        <v>5.91829</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>5.2601</v>
+        <v>6.53424</v>
       </c>
       <c r="C59" t="n">
-        <v>3.81934</v>
+        <v>4.57517</v>
       </c>
       <c r="D59" t="n">
-        <v>14.6048</v>
+        <v>13.4764</v>
       </c>
       <c r="E59" t="n">
-        <v>4.82137</v>
+        <v>4.79352</v>
       </c>
       <c r="F59" t="n">
-        <v>5.30881</v>
+        <v>5.50488</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>5.27435</v>
+        <v>6.02386</v>
       </c>
       <c r="C60" t="n">
-        <v>3.85748</v>
+        <v>4.09823</v>
       </c>
       <c r="D60" t="n">
-        <v>14.9237</v>
+        <v>14.3273</v>
       </c>
       <c r="E60" t="n">
-        <v>4.93106</v>
+        <v>4.90888</v>
       </c>
       <c r="F60" t="n">
-        <v>5.66639</v>
+        <v>5.73878</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>5.27922</v>
+        <v>6.93137</v>
       </c>
       <c r="C61" t="n">
-        <v>3.82651</v>
+        <v>5.04578</v>
       </c>
       <c r="D61" t="n">
-        <v>15.4557</v>
+        <v>15.7659</v>
       </c>
       <c r="E61" t="n">
-        <v>5.07201</v>
+        <v>5.02752</v>
       </c>
       <c r="F61" t="n">
-        <v>5.75833</v>
+        <v>5.70475</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>5.37988</v>
+        <v>5.87926</v>
       </c>
       <c r="C62" t="n">
-        <v>3.98083</v>
+        <v>4.04637</v>
       </c>
       <c r="D62" t="n">
-        <v>15.6011</v>
+        <v>16.5846</v>
       </c>
       <c r="E62" t="n">
-        <v>5.27717</v>
+        <v>5.22259</v>
       </c>
       <c r="F62" t="n">
-        <v>5.9066</v>
+        <v>6.19762</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>5.46205</v>
+        <v>6.34964</v>
       </c>
       <c r="C63" t="n">
-        <v>4.06068</v>
+        <v>4.39265</v>
       </c>
       <c r="D63" t="n">
-        <v>16.0719</v>
+        <v>17.3185</v>
       </c>
       <c r="E63" t="n">
-        <v>5.53821</v>
+        <v>5.49257</v>
       </c>
       <c r="F63" t="n">
-        <v>6.15885</v>
+        <v>6.72661</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>5.62974</v>
+        <v>6.59484</v>
       </c>
       <c r="C64" t="n">
-        <v>4.12488</v>
+        <v>5.19645</v>
       </c>
       <c r="D64" t="n">
-        <v>10.9776</v>
+        <v>15.501</v>
       </c>
       <c r="E64" t="n">
-        <v>5.33825</v>
+        <v>4.65423</v>
       </c>
       <c r="F64" t="n">
-        <v>5.42958</v>
+        <v>6.10768</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>5.91198</v>
+        <v>6.95243</v>
       </c>
       <c r="C65" t="n">
-        <v>7.38707</v>
+        <v>4.47008</v>
       </c>
       <c r="D65" t="n">
-        <v>11.5945</v>
+        <v>16.085</v>
       </c>
       <c r="E65" t="n">
-        <v>5.22668</v>
+        <v>4.69634</v>
       </c>
       <c r="F65" t="n">
-        <v>5.59692</v>
+        <v>6.1924</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>6.33515</v>
+        <v>7.37329</v>
       </c>
       <c r="C66" t="n">
-        <v>7.53495</v>
+        <v>4.51102</v>
       </c>
       <c r="D66" t="n">
-        <v>12.2244</v>
+        <v>16.561</v>
       </c>
       <c r="E66" t="n">
-        <v>5.15115</v>
+        <v>4.6999</v>
       </c>
       <c r="F66" t="n">
-        <v>5.86853</v>
+        <v>6.06586</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>10.099</v>
+        <v>6.46864</v>
       </c>
       <c r="C67" t="n">
-        <v>7.85157</v>
+        <v>4.59586</v>
       </c>
       <c r="D67" t="n">
-        <v>13.15</v>
+        <v>17.5089</v>
       </c>
       <c r="E67" t="n">
-        <v>5.88097</v>
+        <v>4.765</v>
       </c>
       <c r="F67" t="n">
-        <v>5.98242</v>
+        <v>6.15032</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>10.3602</v>
+        <v>6.58266</v>
       </c>
       <c r="C68" t="n">
-        <v>8.050230000000001</v>
+        <v>4.70748</v>
       </c>
       <c r="D68" t="n">
-        <v>14.0659</v>
+        <v>17.3702</v>
       </c>
       <c r="E68" t="n">
-        <v>5.41936</v>
+        <v>4.84524</v>
       </c>
       <c r="F68" t="n">
-        <v>6.08772</v>
+        <v>6.28036</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>9.50262</v>
+        <v>6.78835</v>
       </c>
       <c r="C69" t="n">
-        <v>7.30353</v>
+        <v>4.93219</v>
       </c>
       <c r="D69" t="n">
-        <v>14.5943</v>
+        <v>18.4878</v>
       </c>
       <c r="E69" t="n">
-        <v>6.37231</v>
+        <v>4.84265</v>
       </c>
       <c r="F69" t="n">
-        <v>6.26434</v>
+        <v>6.47061</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>8.3912</v>
+        <v>7.18289</v>
       </c>
       <c r="C70" t="n">
-        <v>6.34023</v>
+        <v>5.38217</v>
       </c>
       <c r="D70" t="n">
-        <v>14.8915</v>
+        <v>19.2741</v>
       </c>
       <c r="E70" t="n">
-        <v>5.90727</v>
+        <v>4.96916</v>
       </c>
       <c r="F70" t="n">
-        <v>6.41804</v>
+        <v>6.62869</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>8.24858</v>
+        <v>7.55742</v>
       </c>
       <c r="C71" t="n">
-        <v>6.18668</v>
+        <v>5.73391</v>
       </c>
       <c r="D71" t="n">
-        <v>15.74</v>
+        <v>19.5658</v>
       </c>
       <c r="E71" t="n">
-        <v>5.32282</v>
+        <v>5.1076</v>
       </c>
       <c r="F71" t="n">
-        <v>6.43216</v>
+        <v>6.70437</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>9.98704</v>
+        <v>7.01083</v>
       </c>
       <c r="C72" t="n">
-        <v>7.77687</v>
+        <v>5.23776</v>
       </c>
       <c r="D72" t="n">
-        <v>16.56</v>
+        <v>19.6606</v>
       </c>
       <c r="E72" t="n">
-        <v>5.54251</v>
+        <v>5.21834</v>
       </c>
       <c r="F72" t="n">
-        <v>6.68061</v>
+        <v>6.82059</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>9.480560000000001</v>
+        <v>6.96059</v>
       </c>
       <c r="C73" t="n">
-        <v>7.32404</v>
+        <v>5.0713</v>
       </c>
       <c r="D73" t="n">
-        <v>17.1917</v>
+        <v>20.282</v>
       </c>
       <c r="E73" t="n">
-        <v>5.72367</v>
+        <v>5.347</v>
       </c>
       <c r="F73" t="n">
-        <v>6.84951</v>
+        <v>7.00678</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>10.8311</v>
+        <v>6.52534</v>
       </c>
       <c r="C74" t="n">
-        <v>8.76844</v>
+        <v>4.81636</v>
       </c>
       <c r="D74" t="n">
-        <v>18.3801</v>
+        <v>20.5769</v>
       </c>
       <c r="E74" t="n">
-        <v>5.551</v>
+        <v>5.64691</v>
       </c>
       <c r="F74" t="n">
-        <v>7.28594</v>
+        <v>7.98487</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>7.5804</v>
+        <v>7.40921</v>
       </c>
       <c r="C75" t="n">
-        <v>5.70785</v>
+        <v>5.54755</v>
       </c>
       <c r="D75" t="n">
-        <v>19.1037</v>
+        <v>22.2813</v>
       </c>
       <c r="E75" t="n">
-        <v>5.74247</v>
+        <v>5.78782</v>
       </c>
       <c r="F75" t="n">
-        <v>7.49944</v>
+        <v>9.08967</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>7.62225</v>
+        <v>7.29736</v>
       </c>
       <c r="C76" t="n">
-        <v>5.7423</v>
+        <v>5.5729</v>
       </c>
       <c r="D76" t="n">
-        <v>20.1274</v>
+        <v>24.8201</v>
       </c>
       <c r="E76" t="n">
-        <v>5.83709</v>
+        <v>5.86591</v>
       </c>
       <c r="F76" t="n">
-        <v>7.79389</v>
+        <v>9.94721</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>7.6089</v>
+        <v>7.27821</v>
       </c>
       <c r="C77" t="n">
-        <v>5.77979</v>
+        <v>5.57934</v>
       </c>
       <c r="D77" t="n">
-        <v>21.6944</v>
+        <v>24.5254</v>
       </c>
       <c r="E77" t="n">
-        <v>6.13128</v>
+        <v>6.14412</v>
       </c>
       <c r="F77" t="n">
-        <v>8.36134</v>
+        <v>10.1213</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>9.8652</v>
+        <v>7.37687</v>
       </c>
       <c r="C78" t="n">
-        <v>7.72862</v>
+        <v>5.58087</v>
       </c>
       <c r="D78" t="n">
-        <v>20.7095</v>
+        <v>21.3485</v>
       </c>
       <c r="E78" t="n">
-        <v>9.68478</v>
+        <v>12.4643</v>
       </c>
       <c r="F78" t="n">
-        <v>11.1794</v>
+        <v>11.0835</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>7.51086</v>
+        <v>7.73288</v>
       </c>
       <c r="C79" t="n">
-        <v>13.4395</v>
+        <v>13.5073</v>
       </c>
       <c r="D79" t="n">
-        <v>21.6665</v>
+        <v>22.2262</v>
       </c>
       <c r="E79" t="n">
-        <v>10.1466</v>
+        <v>12.9051</v>
       </c>
       <c r="F79" t="n">
-        <v>11.0885</v>
+        <v>11.023</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>7.84885</v>
+        <v>8.085789999999999</v>
       </c>
       <c r="C80" t="n">
-        <v>13.572</v>
+        <v>14.676</v>
       </c>
       <c r="D80" t="n">
-        <v>22.8293</v>
+        <v>23.4308</v>
       </c>
       <c r="E80" t="n">
-        <v>10.3362</v>
+        <v>12.9516</v>
       </c>
       <c r="F80" t="n">
-        <v>11.264</v>
+        <v>11.2599</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>16.7497</v>
+        <v>18.0225</v>
       </c>
       <c r="C81" t="n">
-        <v>13.6589</v>
+        <v>14.7239</v>
       </c>
       <c r="D81" t="n">
-        <v>23.7388</v>
+        <v>24.7824</v>
       </c>
       <c r="E81" t="n">
-        <v>10.6533</v>
+        <v>12.0133</v>
       </c>
       <c r="F81" t="n">
-        <v>11.4213</v>
+        <v>11.3137</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>16.8021</v>
+        <v>18.0565</v>
       </c>
       <c r="C82" t="n">
-        <v>13.7353</v>
+        <v>14.7677</v>
       </c>
       <c r="D82" t="n">
-        <v>24.6489</v>
+        <v>25.5437</v>
       </c>
       <c r="E82" t="n">
-        <v>10.8852</v>
+        <v>13.4302</v>
       </c>
       <c r="F82" t="n">
-        <v>11.5601</v>
+        <v>11.3209</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>16.8765</v>
+        <v>18.0955</v>
       </c>
       <c r="C83" t="n">
-        <v>13.7917</v>
+        <v>14.8123</v>
       </c>
       <c r="D83" t="n">
-        <v>26.2247</v>
+        <v>26.4885</v>
       </c>
       <c r="E83" t="n">
-        <v>11.2066</v>
+        <v>13.4869</v>
       </c>
       <c r="F83" t="n">
-        <v>11.6812</v>
+        <v>11.5042</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>16.9233</v>
+        <v>18.1273</v>
       </c>
       <c r="C84" t="n">
-        <v>13.8808</v>
+        <v>14.8594</v>
       </c>
       <c r="D84" t="n">
-        <v>26.4305</v>
+        <v>27.0424</v>
       </c>
       <c r="E84" t="n">
-        <v>11.5373</v>
+        <v>13.7759</v>
       </c>
       <c r="F84" t="n">
-        <v>11.6256</v>
+        <v>11.6882</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>17.035</v>
+        <v>18.4577</v>
       </c>
       <c r="C85" t="n">
-        <v>13.9371</v>
+        <v>15.0768</v>
       </c>
       <c r="D85" t="n">
-        <v>28.0427</v>
+        <v>27.8344</v>
       </c>
       <c r="E85" t="n">
-        <v>11.6414</v>
+        <v>13.5724</v>
       </c>
       <c r="F85" t="n">
-        <v>13.1519</v>
+        <v>14.9606</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>17.0289</v>
+        <v>18.1831</v>
       </c>
       <c r="C86" t="n">
-        <v>13.9935</v>
+        <v>14.9442</v>
       </c>
       <c r="D86" t="n">
-        <v>28.7156</v>
+        <v>29.0784</v>
       </c>
       <c r="E86" t="n">
-        <v>11.8987</v>
+        <v>13.7995</v>
       </c>
       <c r="F86" t="n">
-        <v>13.2498</v>
+        <v>14.9991</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>17.0786</v>
+        <v>18.2156</v>
       </c>
       <c r="C87" t="n">
-        <v>14.0304</v>
+        <v>14.992</v>
       </c>
       <c r="D87" t="n">
-        <v>29.3667</v>
+        <v>29.3154</v>
       </c>
       <c r="E87" t="n">
-        <v>12.0984</v>
+        <v>13.9103</v>
       </c>
       <c r="F87" t="n">
-        <v>13.5597</v>
+        <v>15.0255</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>17.149</v>
+        <v>18.3307</v>
       </c>
       <c r="C88" t="n">
-        <v>14.0858</v>
+        <v>15.0537</v>
       </c>
       <c r="D88" t="n">
-        <v>30.6092</v>
+        <v>32.398</v>
       </c>
       <c r="E88" t="n">
-        <v>12.5043</v>
+        <v>13.2913</v>
       </c>
       <c r="F88" t="n">
-        <v>13.7283</v>
+        <v>15.1497</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>17.1848</v>
+        <v>17.8927</v>
       </c>
       <c r="C89" t="n">
-        <v>14.1712</v>
+        <v>14.6927</v>
       </c>
       <c r="D89" t="n">
-        <v>32.3361</v>
+        <v>32.537</v>
       </c>
       <c r="E89" t="n">
-        <v>12.7506</v>
+        <v>13.4718</v>
       </c>
       <c r="F89" t="n">
-        <v>13.3477</v>
+        <v>14.2783</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>17.2348</v>
+        <v>17.7646</v>
       </c>
       <c r="C90" t="n">
-        <v>14.2273</v>
+        <v>14.611</v>
       </c>
       <c r="D90" t="n">
-        <v>33.1278</v>
+        <v>33.0875</v>
       </c>
       <c r="E90" t="n">
-        <v>13.0143</v>
+        <v>13.716</v>
       </c>
       <c r="F90" t="n">
-        <v>12.7396</v>
+        <v>12.6985</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>17.3976</v>
+        <v>18.4333</v>
       </c>
       <c r="C91" t="n">
-        <v>14.3987</v>
+        <v>15.313</v>
       </c>
       <c r="D91" t="n">
-        <v>34.1459</v>
+        <v>34.1832</v>
       </c>
       <c r="E91" t="n">
-        <v>13.2968</v>
+        <v>13.9694</v>
       </c>
       <c r="F91" t="n">
-        <v>13.341</v>
+        <v>13.0963</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>17.5032</v>
+        <v>18.6449</v>
       </c>
       <c r="C92" t="n">
-        <v>14.5251</v>
+        <v>15.4785</v>
       </c>
       <c r="D92" t="n">
-        <v>32.1598</v>
+        <v>32.2108</v>
       </c>
       <c r="E92" t="n">
-        <v>18.1089</v>
+        <v>18.1138</v>
       </c>
       <c r="F92" t="n">
-        <v>18.2844</v>
+        <v>18.4481</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>17.6427</v>
+        <v>18.5556</v>
       </c>
       <c r="C93" t="n">
-        <v>14.7005</v>
+        <v>15.4329</v>
       </c>
       <c r="D93" t="n">
-        <v>32.9581</v>
+        <v>33.0095</v>
       </c>
       <c r="E93" t="n">
-        <v>18.0287</v>
+        <v>17.999</v>
       </c>
       <c r="F93" t="n">
-        <v>18.3883</v>
+        <v>18.5802</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>17.9465</v>
+        <v>18.5394</v>
       </c>
       <c r="C94" t="n">
-        <v>17.4189</v>
+        <v>17.4323</v>
       </c>
       <c r="D94" t="n">
-        <v>33.7148</v>
+        <v>33.862</v>
       </c>
       <c r="E94" t="n">
-        <v>18.3896</v>
+        <v>18.1989</v>
       </c>
       <c r="F94" t="n">
-        <v>18.4932</v>
+        <v>18.643</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>21.688</v>
+        <v>21.9785</v>
       </c>
       <c r="C95" t="n">
-        <v>17.5387</v>
+        <v>17.6016</v>
       </c>
       <c r="D95" t="n">
-        <v>34.6418</v>
+        <v>34.7106</v>
       </c>
       <c r="E95" t="n">
-        <v>18.5033</v>
+        <v>18.6328</v>
       </c>
       <c r="F95" t="n">
-        <v>18.6314</v>
+        <v>18.8658</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>21.9567</v>
+        <v>22.0411</v>
       </c>
       <c r="C96" t="n">
-        <v>17.6584</v>
+        <v>17.6738</v>
       </c>
       <c r="D96" t="n">
-        <v>35.431</v>
+        <v>35.5007</v>
       </c>
       <c r="E96" t="n">
-        <v>18.7105</v>
+        <v>18.7346</v>
       </c>
       <c r="F96" t="n">
-        <v>18.7059</v>
+        <v>18.9023</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>21.9843</v>
+        <v>22.04</v>
       </c>
       <c r="C97" t="n">
-        <v>17.5956</v>
+        <v>17.6661</v>
       </c>
       <c r="D97" t="n">
-        <v>36.5046</v>
+        <v>36.5841</v>
       </c>
       <c r="E97" t="n">
-        <v>18.7704</v>
+        <v>18.8635</v>
       </c>
       <c r="F97" t="n">
-        <v>18.8335</v>
+        <v>19.0756</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>22.0086</v>
+        <v>22.0654</v>
       </c>
       <c r="C98" t="n">
-        <v>17.6871</v>
+        <v>17.7417</v>
       </c>
       <c r="D98" t="n">
-        <v>37.173</v>
+        <v>37.26</v>
       </c>
       <c r="E98" t="n">
-        <v>18.9897</v>
+        <v>19.0878</v>
       </c>
       <c r="F98" t="n">
-        <v>18.96</v>
+        <v>19.1804</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>21.9832</v>
+        <v>22.0807</v>
       </c>
       <c r="C99" t="n">
-        <v>17.8404</v>
+        <v>17.7946</v>
       </c>
       <c r="D99" t="n">
-        <v>38.3125</v>
+        <v>38.3055</v>
       </c>
       <c r="E99" t="n">
-        <v>19.3794</v>
+        <v>19.143</v>
       </c>
       <c r="F99" t="n">
-        <v>19.2375</v>
+        <v>19.256</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>22.0163</v>
+        <v>22.102</v>
       </c>
       <c r="C100" t="n">
-        <v>17.7336</v>
+        <v>17.7319</v>
       </c>
       <c r="D100" t="n">
-        <v>39.3239</v>
+        <v>39.4286</v>
       </c>
       <c r="E100" t="n">
-        <v>19.453</v>
+        <v>19.3728</v>
       </c>
       <c r="F100" t="n">
-        <v>19.4438</v>
+        <v>19.5171</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>22.0943</v>
+        <v>22.113</v>
       </c>
       <c r="C101" t="n">
-        <v>17.7768</v>
+        <v>17.7542</v>
       </c>
       <c r="D101" t="n">
-        <v>40.6423</v>
+        <v>40.7715</v>
       </c>
       <c r="E101" t="n">
-        <v>19.4001</v>
+        <v>19.472</v>
       </c>
       <c r="F101" t="n">
-        <v>19.4792</v>
+        <v>19.5902</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>22.1274</v>
+        <v>22.112</v>
       </c>
       <c r="C102" t="n">
-        <v>17.7969</v>
+        <v>17.8049</v>
       </c>
       <c r="D102" t="n">
-        <v>41.5627</v>
+        <v>41.6367</v>
       </c>
       <c r="E102" t="n">
-        <v>19.5812</v>
+        <v>19.5827</v>
       </c>
       <c r="F102" t="n">
-        <v>19.6557</v>
+        <v>19.6634</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>22.1794</v>
+        <v>22.1417</v>
       </c>
       <c r="C103" t="n">
-        <v>17.926</v>
+        <v>17.8543</v>
       </c>
       <c r="D103" t="n">
-        <v>42.8284</v>
+        <v>42.98</v>
       </c>
       <c r="E103" t="n">
-        <v>19.7431</v>
+        <v>19.8548</v>
       </c>
       <c r="F103" t="n">
-        <v>20.0393</v>
+        <v>19.9952</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>22.1874</v>
+        <v>22.2063</v>
       </c>
       <c r="C104" t="n">
-        <v>17.9683</v>
+        <v>17.9694</v>
       </c>
       <c r="D104" t="n">
-        <v>43.8802</v>
+        <v>44.0112</v>
       </c>
       <c r="E104" t="n">
-        <v>19.9488</v>
+        <v>20.0052</v>
       </c>
       <c r="F104" t="n">
-        <v>20.1399</v>
+        <v>20.2161</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>22.2724</v>
+        <v>22.2673</v>
       </c>
       <c r="C105" t="n">
-        <v>18.0831</v>
+        <v>18.0574</v>
       </c>
       <c r="D105" t="n">
-        <v>45.0468</v>
+        <v>45.2145</v>
       </c>
       <c r="E105" t="n">
-        <v>20.117</v>
+        <v>20.1996</v>
       </c>
       <c r="F105" t="n">
-        <v>20.845</v>
+        <v>20.8957</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>22.4189</v>
+        <v>22.4081</v>
       </c>
       <c r="C106" t="n">
-        <v>18.2195</v>
+        <v>18.2748</v>
       </c>
       <c r="D106" t="n">
-        <v>46.6089</v>
+        <v>46.4098</v>
       </c>
       <c r="E106" t="n">
-        <v>20.5062</v>
+        <v>20.4948</v>
       </c>
       <c r="F106" t="n">
-        <v>20.9141</v>
+        <v>21.0499</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>22.5441</v>
+        <v>22.5774</v>
       </c>
       <c r="C107" t="n">
-        <v>18.5122</v>
+        <v>18.4267</v>
       </c>
       <c r="D107" t="n">
-        <v>39.6059</v>
+        <v>39.6799</v>
       </c>
       <c r="E107" t="n">
-        <v>23.5386</v>
+        <v>23.2582</v>
       </c>
       <c r="F107" t="n">
-        <v>23.3579</v>
+        <v>23.3488</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>22.8111</v>
+        <v>22.6864</v>
       </c>
       <c r="C108" t="n">
-        <v>18.984</v>
+        <v>18.9985</v>
       </c>
       <c r="D108" t="n">
-        <v>39.969</v>
+        <v>40.5015</v>
       </c>
       <c r="E108" t="n">
-        <v>23.7631</v>
+        <v>23.6695</v>
       </c>
       <c r="F108" t="n">
-        <v>23.5271</v>
+        <v>23.607</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>23.4172</v>
+        <v>23.4624</v>
       </c>
       <c r="C109" t="n">
-        <v>19.0249</v>
+        <v>19.0164</v>
       </c>
       <c r="D109" t="n">
-        <v>40.7756</v>
+        <v>41.298</v>
       </c>
       <c r="E109" t="n">
-        <v>23.9071</v>
+        <v>23.6734</v>
       </c>
       <c r="F109" t="n">
-        <v>23.6382</v>
+        <v>23.699</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>25.4117</v>
+        <v>25.33</v>
       </c>
       <c r="C110" t="n">
-        <v>19.0872</v>
+        <v>19.0735</v>
       </c>
       <c r="D110" t="n">
-        <v>41.4817</v>
+        <v>42.0062</v>
       </c>
       <c r="E110" t="n">
-        <v>24.1216</v>
+        <v>24.1359</v>
       </c>
       <c r="F110" t="n">
-        <v>23.9322</v>
+        <v>23.3741</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>25.1375</v>
+        <v>25.2857</v>
       </c>
       <c r="C111" t="n">
-        <v>19.0835</v>
+        <v>19.117</v>
       </c>
       <c r="D111" t="n">
-        <v>42.8227</v>
+        <v>42.9939</v>
       </c>
       <c r="E111" t="n">
-        <v>24.3047</v>
+        <v>24.4019</v>
       </c>
       <c r="F111" t="n">
-        <v>23.6023</v>
+        <v>24.2543</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>24.6923</v>
+        <v>25.3447</v>
       </c>
       <c r="C112" t="n">
-        <v>19.1704</v>
+        <v>19.232</v>
       </c>
       <c r="D112" t="n">
-        <v>43.5705</v>
+        <v>43.7532</v>
       </c>
       <c r="E112" t="n">
-        <v>24.2909</v>
+        <v>24.7767</v>
       </c>
       <c r="F112" t="n">
-        <v>24.2301</v>
+        <v>24.3376</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>24.9203</v>
+        <v>25.435</v>
       </c>
       <c r="C113" t="n">
-        <v>19.1814</v>
+        <v>19.2559</v>
       </c>
       <c r="D113" t="n">
-        <v>44.6114</v>
+        <v>44.8139</v>
       </c>
       <c r="E113" t="n">
-        <v>24.606</v>
+        <v>24.7892</v>
       </c>
       <c r="F113" t="n">
-        <v>24.508</v>
+        <v>24.4799</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>25.1044</v>
+        <v>25.2673</v>
       </c>
       <c r="C114" t="n">
-        <v>19.2395</v>
+        <v>19.3042</v>
       </c>
       <c r="D114" t="n">
-        <v>45.5854</v>
+        <v>45.7617</v>
       </c>
       <c r="E114" t="n">
-        <v>25.0011</v>
+        <v>24.9391</v>
       </c>
       <c r="F114" t="n">
-        <v>24.7284</v>
+        <v>24.777</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>25.3491</v>
+        <v>25.2437</v>
       </c>
       <c r="C115" t="n">
-        <v>19.3661</v>
+        <v>19.4132</v>
       </c>
       <c r="D115" t="n">
-        <v>46.573</v>
+        <v>46.802</v>
       </c>
       <c r="E115" t="n">
-        <v>25.1192</v>
+        <v>25.1833</v>
       </c>
       <c r="F115" t="n">
-        <v>25.0153</v>
+        <v>25.0733</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>25.3311</v>
+        <v>25.3116</v>
       </c>
       <c r="C116" t="n">
-        <v>19.3939</v>
+        <v>19.463</v>
       </c>
       <c r="D116" t="n">
-        <v>47.6618</v>
+        <v>47.8679</v>
       </c>
       <c r="E116" t="n">
-        <v>25.3822</v>
+        <v>25.4136</v>
       </c>
       <c r="F116" t="n">
-        <v>25.4195</v>
+        <v>25.3984</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>25.2926</v>
+        <v>25.7358</v>
       </c>
       <c r="C117" t="n">
-        <v>19.5229</v>
+        <v>19.6117</v>
       </c>
       <c r="D117" t="n">
-        <v>48.7229</v>
+        <v>48.8627</v>
       </c>
       <c r="E117" t="n">
-        <v>25.5936</v>
+        <v>25.6494</v>
       </c>
       <c r="F117" t="n">
-        <v>25.787</v>
+        <v>25.8057</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>25.5323</v>
+        <v>25.4903</v>
       </c>
       <c r="C118" t="n">
-        <v>19.6962</v>
+        <v>19.7291</v>
       </c>
       <c r="D118" t="n">
-        <v>49.9674</v>
+        <v>50.1551</v>
       </c>
       <c r="E118" t="n">
-        <v>25.9219</v>
+        <v>26.0049</v>
       </c>
       <c r="F118" t="n">
-        <v>26.3143</v>
+        <v>25.7216</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>25.5193</v>
+        <v>25.3936</v>
       </c>
       <c r="C119" t="n">
-        <v>19.8865</v>
+        <v>19.8997</v>
       </c>
       <c r="D119" t="n">
-        <v>50.9269</v>
+        <v>51.1088</v>
       </c>
       <c r="E119" t="n">
-        <v>26.4406</v>
+        <v>26.4238</v>
       </c>
       <c r="F119" t="n">
-        <v>26.8556</v>
+        <v>26.7407</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>25.7678</v>
+        <v>25.7952</v>
       </c>
       <c r="C120" t="n">
-        <v>20.2139</v>
+        <v>20.1854</v>
       </c>
       <c r="D120" t="n">
-        <v>57.0067</v>
+        <v>52.5585</v>
       </c>
       <c r="E120" t="n">
-        <v>26.6801</v>
+        <v>26.8319</v>
       </c>
       <c r="F120" t="n">
-        <v>26.9365</v>
+        <v>27.3987</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>25.2295</v>
+        <v>25.8913</v>
       </c>
       <c r="C121" t="n">
-        <v>20.1721</v>
+        <v>20.4254</v>
       </c>
       <c r="D121" t="n">
-        <v>41.1823</v>
+        <v>42.8465</v>
       </c>
       <c r="E121" t="n">
-        <v>27.0399</v>
+        <v>28.3743</v>
       </c>
       <c r="F121" t="n">
-        <v>26.7671</v>
+        <v>27.3673</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>25.5502</v>
+        <v>25.5885</v>
       </c>
       <c r="C122" t="n">
-        <v>20.6906</v>
+        <v>21.4</v>
       </c>
       <c r="D122" t="n">
-        <v>41.9633</v>
+        <v>43.7685</v>
       </c>
       <c r="E122" t="n">
-        <v>27.1327</v>
+        <v>28.5307</v>
       </c>
       <c r="F122" t="n">
-        <v>26.8979</v>
+        <v>27.7302</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>25.683</v>
+        <v>26.4171</v>
       </c>
       <c r="C123" t="n">
-        <v>20.8239</v>
+        <v>21.492</v>
       </c>
       <c r="D123" t="n">
-        <v>42.6682</v>
+        <v>44.3968</v>
       </c>
       <c r="E123" t="n">
-        <v>27.5311</v>
+        <v>28.7968</v>
       </c>
       <c r="F123" t="n">
-        <v>27.1463</v>
+        <v>27.992</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>31.934</v>
+        <v>32.9661</v>
       </c>
       <c r="C124" t="n">
-        <v>20.9254</v>
+        <v>21.6565</v>
       </c>
       <c r="D124" t="n">
-        <v>43.9065</v>
+        <v>45.1942</v>
       </c>
       <c r="E124" t="n">
-        <v>27.7309</v>
+        <v>29.153</v>
       </c>
       <c r="F124" t="n">
-        <v>27.2736</v>
+        <v>28.0995</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>31.9</v>
+        <v>32.9802</v>
       </c>
       <c r="C125" t="n">
-        <v>21.0231</v>
+        <v>21.7724</v>
       </c>
       <c r="D125" t="n">
-        <v>44.5956</v>
+        <v>46.2758</v>
       </c>
       <c r="E125" t="n">
-        <v>27.9489</v>
+        <v>29.3212</v>
       </c>
       <c r="F125" t="n">
-        <v>27.5826</v>
+        <v>28.286</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>31.7751</v>
+        <v>32.9787</v>
       </c>
       <c r="C126" t="n">
-        <v>21.138</v>
+        <v>21.8913</v>
       </c>
       <c r="D126" t="n">
-        <v>44.9308</v>
+        <v>46.7556</v>
       </c>
       <c r="E126" t="n">
-        <v>28.2847</v>
+        <v>29.625</v>
       </c>
       <c r="F126" t="n">
-        <v>27.8362</v>
+        <v>28.6635</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>31.9624</v>
+        <v>33.0893</v>
       </c>
       <c r="C127" t="n">
-        <v>21.3185</v>
+        <v>22.0689</v>
       </c>
       <c r="D127" t="n">
-        <v>45.8914</v>
+        <v>47.4752</v>
       </c>
       <c r="E127" t="n">
-        <v>28.4767</v>
+        <v>29.8165</v>
       </c>
       <c r="F127" t="n">
-        <v>28.1189</v>
+        <v>28.802</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>31.8388</v>
+        <v>33.1069</v>
       </c>
       <c r="C128" t="n">
-        <v>21.417</v>
+        <v>22.1499</v>
       </c>
       <c r="D128" t="n">
-        <v>46.7726</v>
+        <v>48.3108</v>
       </c>
       <c r="E128" t="n">
-        <v>28.8165</v>
+        <v>30.1592</v>
       </c>
       <c r="F128" t="n">
-        <v>28.4501</v>
+        <v>29.2233</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>31.6605</v>
+        <v>33.1237</v>
       </c>
       <c r="C129" t="n">
-        <v>21.5977</v>
+        <v>22.3334</v>
       </c>
       <c r="D129" t="n">
-        <v>47.8599</v>
+        <v>49.7501</v>
       </c>
       <c r="E129" t="n">
-        <v>29.0632</v>
+        <v>30.3815</v>
       </c>
       <c r="F129" t="n">
-        <v>28.7484</v>
+        <v>29.5271</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>31.9668</v>
+        <v>33.1355</v>
       </c>
       <c r="C130" t="n">
-        <v>21.8129</v>
+        <v>22.5219</v>
       </c>
       <c r="D130" t="n">
-        <v>48.6962</v>
+        <v>50.7107</v>
       </c>
       <c r="E130" t="n">
-        <v>29.4585</v>
+        <v>30.7963</v>
       </c>
       <c r="F130" t="n">
-        <v>29.2385</v>
+        <v>30.0562</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>32.0223</v>
+        <v>33.2982</v>
       </c>
       <c r="C131" t="n">
-        <v>21.9916</v>
+        <v>22.7252</v>
       </c>
       <c r="D131" t="n">
-        <v>49.9866</v>
+        <v>51.9262</v>
       </c>
       <c r="E131" t="n">
-        <v>29.6996</v>
+        <v>30.9989</v>
       </c>
       <c r="F131" t="n">
-        <v>29.6364</v>
+        <v>30.495</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>31.9799</v>
+        <v>33.1965</v>
       </c>
       <c r="C132" t="n">
-        <v>22.3004</v>
+        <v>22.9399</v>
       </c>
       <c r="D132" t="n">
-        <v>50.9979</v>
+        <v>53.0129</v>
       </c>
       <c r="E132" t="n">
-        <v>30.1946</v>
+        <v>31.5065</v>
       </c>
       <c r="F132" t="n">
-        <v>30.2594</v>
+        <v>30.9924</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>32.1512</v>
+        <v>33.2619</v>
       </c>
       <c r="C133" t="n">
-        <v>22.609</v>
+        <v>23.2993</v>
       </c>
       <c r="D133" t="n">
-        <v>51.8539</v>
+        <v>54.0873</v>
       </c>
       <c r="E133" t="n">
-        <v>30.6152</v>
+        <v>31.8782</v>
       </c>
       <c r="F133" t="n">
-        <v>30.6829</v>
+        <v>31.6157</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>32.1602</v>
+        <v>33.3366</v>
       </c>
       <c r="C134" t="n">
-        <v>22.9637</v>
+        <v>23.6474</v>
       </c>
       <c r="D134" t="n">
-        <v>53.3923</v>
+        <v>55.492</v>
       </c>
       <c r="E134" t="n">
-        <v>31.2351</v>
+        <v>32.4593</v>
       </c>
       <c r="F134" t="n">
-        <v>31.6032</v>
+        <v>32.4532</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>32.3335</v>
+        <v>33.6124</v>
       </c>
       <c r="C135" t="n">
-        <v>23.412</v>
+        <v>24.1224</v>
       </c>
       <c r="D135" t="n">
-        <v>43.2997</v>
+        <v>45.0278</v>
       </c>
       <c r="E135" t="n">
-        <v>29.0396</v>
+        <v>30.4918</v>
       </c>
       <c r="F135" t="n">
-        <v>29.1347</v>
+        <v>30.1127</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>32.1043</v>
+        <v>33.2278</v>
       </c>
       <c r="C136" t="n">
-        <v>23.0511</v>
+        <v>24.1724</v>
       </c>
       <c r="D136" t="n">
-        <v>43.459</v>
+        <v>45.4991</v>
       </c>
       <c r="E136" t="n">
-        <v>29.3752</v>
+        <v>31.0572</v>
       </c>
       <c r="F136" t="n">
-        <v>29.2363</v>
+        <v>30.324</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>32.4311</v>
+        <v>34.02</v>
       </c>
       <c r="C137" t="n">
-        <v>23.2148</v>
+        <v>24.2433</v>
       </c>
       <c r="D137" t="n">
-        <v>44.0301</v>
+        <v>46.2304</v>
       </c>
       <c r="E137" t="n">
-        <v>29.7094</v>
+        <v>31.2921</v>
       </c>
       <c r="F137" t="n">
-        <v>29.4317</v>
+        <v>30.5268</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>36.7434</v>
+        <v>38.3904</v>
       </c>
       <c r="C138" t="n">
-        <v>23.2828</v>
+        <v>24.3941</v>
       </c>
       <c r="D138" t="n">
-        <v>45.1375</v>
+        <v>47.0192</v>
       </c>
       <c r="E138" t="n">
-        <v>30.0637</v>
+        <v>31.6044</v>
       </c>
       <c r="F138" t="n">
-        <v>29.7168</v>
+        <v>30.7795</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>37.2145</v>
+        <v>38.4081</v>
       </c>
       <c r="C139" t="n">
-        <v>23.433</v>
+        <v>24.5249</v>
       </c>
       <c r="D139" t="n">
-        <v>45.3874</v>
+        <v>47.26</v>
       </c>
       <c r="E139" t="n">
-        <v>30.0748</v>
+        <v>31.8272</v>
       </c>
       <c r="F139" t="n">
-        <v>30.1836</v>
+        <v>31.1202</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>37.2225</v>
+        <v>38.4614</v>
       </c>
       <c r="C140" t="n">
-        <v>23.6819</v>
+        <v>24.7308</v>
       </c>
       <c r="D140" t="n">
-        <v>46.3265</v>
+        <v>48.3314</v>
       </c>
       <c r="E140" t="n">
-        <v>30.4929</v>
+        <v>32.0538</v>
       </c>
       <c r="F140" t="n">
-        <v>30.3887</v>
+        <v>31.3044</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>37.2144</v>
+        <v>38.4464</v>
       </c>
       <c r="C141" t="n">
-        <v>23.7873</v>
+        <v>24.904</v>
       </c>
       <c r="D141" t="n">
-        <v>47.475</v>
+        <v>49.4144</v>
       </c>
       <c r="E141" t="n">
-        <v>30.7752</v>
+        <v>32.3956</v>
       </c>
       <c r="F141" t="n">
-        <v>30.668</v>
+        <v>31.3581</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>37.269</v>
+        <v>38.5142</v>
       </c>
       <c r="C142" t="n">
-        <v>23.9942</v>
+        <v>25.0803</v>
       </c>
       <c r="D142" t="n">
-        <v>48.364</v>
+        <v>50.304</v>
       </c>
       <c r="E142" t="n">
-        <v>31.0895</v>
+        <v>32.3058</v>
       </c>
       <c r="F142" t="n">
-        <v>30.8193</v>
+        <v>31.9455</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>37.2898</v>
+        <v>39.6619</v>
       </c>
       <c r="C143" t="n">
-        <v>24.1709</v>
+        <v>25.1684</v>
       </c>
       <c r="D143" t="n">
-        <v>50.0031</v>
+        <v>51.3679</v>
       </c>
       <c r="E143" t="n">
-        <v>31.1598</v>
+        <v>32.394</v>
       </c>
       <c r="F143" t="n">
-        <v>31.3388</v>
+        <v>32.1384</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Scattered successful looukp.xlsx
+++ b/clang-x64/Scattered successful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>3.42781</v>
+        <v>3.50914</v>
       </c>
       <c r="C2" t="n">
-        <v>2.69649</v>
+        <v>3.28921</v>
       </c>
       <c r="D2" t="n">
-        <v>7.04459</v>
+        <v>7.53826</v>
       </c>
       <c r="E2" t="n">
-        <v>3.56402</v>
+        <v>4.0728</v>
       </c>
       <c r="F2" t="n">
-        <v>3.14901</v>
+        <v>3.68182</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>3.4334</v>
+        <v>3.12264</v>
       </c>
       <c r="C3" t="n">
-        <v>2.81273</v>
+        <v>3.07569</v>
       </c>
       <c r="D3" t="n">
-        <v>7.7454</v>
+        <v>7.81677</v>
       </c>
       <c r="E3" t="n">
-        <v>3.25734</v>
+        <v>3.80859</v>
       </c>
       <c r="F3" t="n">
-        <v>3.45761</v>
+        <v>3.99805</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>3.24415</v>
+        <v>3.24879</v>
       </c>
       <c r="C4" t="n">
-        <v>2.67025</v>
+        <v>3.1389</v>
       </c>
       <c r="D4" t="n">
-        <v>8.595269999999999</v>
+        <v>9.061640000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>3.20234</v>
+        <v>3.82732</v>
       </c>
       <c r="F4" t="n">
-        <v>3.66182</v>
+        <v>4.03643</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.48203</v>
+        <v>3.53294</v>
       </c>
       <c r="C5" t="n">
-        <v>2.86161</v>
+        <v>3.38482</v>
       </c>
       <c r="D5" t="n">
-        <v>9.33647</v>
+        <v>9.55691</v>
       </c>
       <c r="E5" t="n">
-        <v>3.12517</v>
+        <v>4.11879</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6944</v>
+        <v>3.7658</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>3.49062</v>
+        <v>3.1909</v>
       </c>
       <c r="C6" t="n">
-        <v>2.87979</v>
+        <v>3.10785</v>
       </c>
       <c r="D6" t="n">
-        <v>10.0494</v>
+        <v>10.1929</v>
       </c>
       <c r="E6" t="n">
-        <v>3.56725</v>
+        <v>3.79723</v>
       </c>
       <c r="F6" t="n">
-        <v>3.3217</v>
+        <v>4.10943</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>3.50196</v>
+        <v>3.56578</v>
       </c>
       <c r="C7" t="n">
-        <v>2.91102</v>
+        <v>3.44751</v>
       </c>
       <c r="D7" t="n">
-        <v>6.28112</v>
+        <v>6.69215</v>
       </c>
       <c r="E7" t="n">
-        <v>3.10311</v>
+        <v>4.77961</v>
       </c>
       <c r="F7" t="n">
-        <v>3.43052</v>
+        <v>3.94963</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>3.51532</v>
+        <v>3.30728</v>
       </c>
       <c r="C8" t="n">
-        <v>2.66113</v>
+        <v>3.88597</v>
       </c>
       <c r="D8" t="n">
-        <v>6.53373</v>
+        <v>6.81991</v>
       </c>
       <c r="E8" t="n">
-        <v>3.17628</v>
+        <v>4.83102</v>
       </c>
       <c r="F8" t="n">
-        <v>3.46391</v>
+        <v>3.98013</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>3.33879</v>
+        <v>3.35585</v>
       </c>
       <c r="C9" t="n">
-        <v>2.66602</v>
+        <v>3.89317</v>
       </c>
       <c r="D9" t="n">
-        <v>7.22295</v>
+        <v>7.34504</v>
       </c>
       <c r="E9" t="n">
-        <v>3.21732</v>
+        <v>4.85739</v>
       </c>
       <c r="F9" t="n">
-        <v>3.48667</v>
+        <v>4.0202</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>3.59483</v>
+        <v>4.2444</v>
       </c>
       <c r="C10" t="n">
-        <v>2.6765</v>
+        <v>3.92976</v>
       </c>
       <c r="D10" t="n">
-        <v>7.60708</v>
+        <v>7.6638</v>
       </c>
       <c r="E10" t="n">
-        <v>3.25131</v>
+        <v>4.89434</v>
       </c>
       <c r="F10" t="n">
-        <v>3.53869</v>
+        <v>4.0587</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>3.59178</v>
+        <v>3.98287</v>
       </c>
       <c r="C11" t="n">
-        <v>2.68719</v>
+        <v>3.81154</v>
       </c>
       <c r="D11" t="n">
-        <v>8.102690000000001</v>
+        <v>8.2555</v>
       </c>
       <c r="E11" t="n">
-        <v>3.28879</v>
+        <v>4.92794</v>
       </c>
       <c r="F11" t="n">
-        <v>3.45446</v>
+        <v>4.06706</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>3.59697</v>
+        <v>3.98242</v>
       </c>
       <c r="C12" t="n">
-        <v>2.71022</v>
+        <v>3.82899</v>
       </c>
       <c r="D12" t="n">
-        <v>8.76126</v>
+        <v>8.663500000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>3.31053</v>
+        <v>4.94037</v>
       </c>
       <c r="F12" t="n">
-        <v>3.49293</v>
+        <v>4.09015</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>3.61552</v>
+        <v>4.93154</v>
       </c>
       <c r="C13" t="n">
-        <v>2.71286</v>
+        <v>3.7098</v>
       </c>
       <c r="D13" t="n">
-        <v>9.2555</v>
+        <v>9.25465</v>
       </c>
       <c r="E13" t="n">
-        <v>3.34237</v>
+        <v>4.99001</v>
       </c>
       <c r="F13" t="n">
-        <v>3.65645</v>
+        <v>4.10994</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>3.62816</v>
+        <v>4.87904</v>
       </c>
       <c r="C14" t="n">
-        <v>2.73305</v>
+        <v>3.64677</v>
       </c>
       <c r="D14" t="n">
-        <v>9.84623</v>
+        <v>9.75512</v>
       </c>
       <c r="E14" t="n">
-        <v>3.36864</v>
+        <v>4.99841</v>
       </c>
       <c r="F14" t="n">
-        <v>3.64837</v>
+        <v>4.25187</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>3.64927</v>
+        <v>4.85466</v>
       </c>
       <c r="C15" t="n">
-        <v>2.75392</v>
+        <v>3.85364</v>
       </c>
       <c r="D15" t="n">
-        <v>10.2246</v>
+        <v>10.2526</v>
       </c>
       <c r="E15" t="n">
-        <v>3.41821</v>
+        <v>5.05852</v>
       </c>
       <c r="F15" t="n">
-        <v>3.71795</v>
+        <v>4.27888</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>3.6601</v>
+        <v>4.4958</v>
       </c>
       <c r="C16" t="n">
-        <v>2.76899</v>
+        <v>4.03395</v>
       </c>
       <c r="D16" t="n">
-        <v>10.7984</v>
+        <v>10.6412</v>
       </c>
       <c r="E16" t="n">
-        <v>3.44535</v>
+        <v>5.11489</v>
       </c>
       <c r="F16" t="n">
-        <v>3.59604</v>
+        <v>4.227</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>3.68458</v>
+        <v>4.12175</v>
       </c>
       <c r="C17" t="n">
-        <v>2.79531</v>
+        <v>3.99019</v>
       </c>
       <c r="D17" t="n">
-        <v>11.2256</v>
+        <v>11.1323</v>
       </c>
       <c r="E17" t="n">
-        <v>3.45998</v>
+        <v>4.89671</v>
       </c>
       <c r="F17" t="n">
-        <v>3.74377</v>
+        <v>4.48248</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.70561</v>
+        <v>4.92417</v>
       </c>
       <c r="C18" t="n">
-        <v>2.83396</v>
+        <v>3.75714</v>
       </c>
       <c r="D18" t="n">
-        <v>11.6108</v>
+        <v>11.5903</v>
       </c>
       <c r="E18" t="n">
-        <v>3.4788</v>
+        <v>5.1917</v>
       </c>
       <c r="F18" t="n">
-        <v>3.64108</v>
+        <v>4.37672</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>3.72359</v>
+        <v>4.9176</v>
       </c>
       <c r="C19" t="n">
-        <v>2.86529</v>
+        <v>3.77966</v>
       </c>
       <c r="D19" t="n">
-        <v>12.1054</v>
+        <v>12.2312</v>
       </c>
       <c r="E19" t="n">
-        <v>3.54512</v>
+        <v>5.245</v>
       </c>
       <c r="F19" t="n">
-        <v>3.79557</v>
+        <v>4.30731</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>3.73859</v>
+        <v>4.92417</v>
       </c>
       <c r="C20" t="n">
-        <v>2.88855</v>
+        <v>3.91465</v>
       </c>
       <c r="D20" t="n">
-        <v>12.4104</v>
+        <v>12.533</v>
       </c>
       <c r="E20" t="n">
-        <v>3.5727</v>
+        <v>5.20821</v>
       </c>
       <c r="F20" t="n">
-        <v>3.86381</v>
+        <v>4.47729</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>3.75887</v>
+        <v>4.94363</v>
       </c>
       <c r="C21" t="n">
-        <v>2.92681</v>
+        <v>3.95448</v>
       </c>
       <c r="D21" t="n">
-        <v>8.43431</v>
+        <v>8.69083</v>
       </c>
       <c r="E21" t="n">
-        <v>3.54022</v>
+        <v>4.85839</v>
       </c>
       <c r="F21" t="n">
-        <v>3.69399</v>
+        <v>4.9114</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>3.79033</v>
+        <v>4.89304</v>
       </c>
       <c r="C22" t="n">
-        <v>2.93358</v>
+        <v>3.99458</v>
       </c>
       <c r="D22" t="n">
-        <v>8.78185</v>
+        <v>9.114319999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>3.59694</v>
+        <v>4.78815</v>
       </c>
       <c r="F22" t="n">
-        <v>3.75359</v>
+        <v>4.9259</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>3.8562</v>
+        <v>4.94587</v>
       </c>
       <c r="C23" t="n">
-        <v>2.95689</v>
+        <v>4.0073</v>
       </c>
       <c r="D23" t="n">
-        <v>9.16461</v>
+        <v>9.45354</v>
       </c>
       <c r="E23" t="n">
-        <v>3.61341</v>
+        <v>4.80372</v>
       </c>
       <c r="F23" t="n">
-        <v>3.75107</v>
+        <v>4.99567</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>4.05417</v>
+        <v>5.02627</v>
       </c>
       <c r="C24" t="n">
-        <v>2.96455</v>
+        <v>3.98242</v>
       </c>
       <c r="D24" t="n">
-        <v>9.568899999999999</v>
+        <v>9.784660000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>3.65054</v>
+        <v>4.98657</v>
       </c>
       <c r="F24" t="n">
-        <v>3.78332</v>
+        <v>4.90744</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>4.06891</v>
+        <v>5.0201</v>
       </c>
       <c r="C25" t="n">
-        <v>2.97742</v>
+        <v>4.03054</v>
       </c>
       <c r="D25" t="n">
-        <v>9.953900000000001</v>
+        <v>10.1511</v>
       </c>
       <c r="E25" t="n">
-        <v>3.68952</v>
+        <v>4.90528</v>
       </c>
       <c r="F25" t="n">
-        <v>3.82576</v>
+        <v>5.0202</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>4.07355</v>
+        <v>4.72015</v>
       </c>
       <c r="C26" t="n">
-        <v>2.98514</v>
+        <v>3.99155</v>
       </c>
       <c r="D26" t="n">
-        <v>10.3387</v>
+        <v>10.5697</v>
       </c>
       <c r="E26" t="n">
-        <v>3.72416</v>
+        <v>5.10714</v>
       </c>
       <c r="F26" t="n">
-        <v>3.84182</v>
+        <v>4.82539</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>4.0465</v>
+        <v>5.03112</v>
       </c>
       <c r="C27" t="n">
-        <v>3.05077</v>
+        <v>4.04759</v>
       </c>
       <c r="D27" t="n">
-        <v>10.7251</v>
+        <v>11.0794</v>
       </c>
       <c r="E27" t="n">
-        <v>3.9403</v>
+        <v>5.03466</v>
       </c>
       <c r="F27" t="n">
-        <v>3.87268</v>
+        <v>4.8549</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>4.04298</v>
+        <v>5.03822</v>
       </c>
       <c r="C28" t="n">
-        <v>3.06502</v>
+        <v>4.09676</v>
       </c>
       <c r="D28" t="n">
-        <v>11.1298</v>
+        <v>11.453</v>
       </c>
       <c r="E28" t="n">
-        <v>3.96652</v>
+        <v>5.17706</v>
       </c>
       <c r="F28" t="n">
-        <v>3.89795</v>
+        <v>4.87121</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>4.06717</v>
+        <v>4.64555</v>
       </c>
       <c r="C29" t="n">
-        <v>3.08892</v>
+        <v>4.13176</v>
       </c>
       <c r="D29" t="n">
-        <v>11.5283</v>
+        <v>11.8689</v>
       </c>
       <c r="E29" t="n">
-        <v>4.00928</v>
+        <v>5.22578</v>
       </c>
       <c r="F29" t="n">
-        <v>3.9442</v>
+        <v>4.89448</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>4.10724</v>
+        <v>4.71872</v>
       </c>
       <c r="C30" t="n">
-        <v>3.04236</v>
+        <v>4.13929</v>
       </c>
       <c r="D30" t="n">
-        <v>11.9089</v>
+        <v>12.2594</v>
       </c>
       <c r="E30" t="n">
-        <v>4.07068</v>
+        <v>5.19647</v>
       </c>
       <c r="F30" t="n">
-        <v>3.96152</v>
+        <v>5.06082</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>4.14352</v>
+        <v>4.75719</v>
       </c>
       <c r="C31" t="n">
-        <v>3.08364</v>
+        <v>4.11048</v>
       </c>
       <c r="D31" t="n">
-        <v>12.3064</v>
+        <v>12.618</v>
       </c>
       <c r="E31" t="n">
-        <v>3.87779</v>
+        <v>5.2187</v>
       </c>
       <c r="F31" t="n">
-        <v>4.01166</v>
+        <v>5.15936</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>4.11349</v>
+        <v>4.77117</v>
       </c>
       <c r="C32" t="n">
-        <v>3.16508</v>
+        <v>4.17664</v>
       </c>
       <c r="D32" t="n">
-        <v>12.6166</v>
+        <v>12.9941</v>
       </c>
       <c r="E32" t="n">
-        <v>4.12737</v>
+        <v>5.28882</v>
       </c>
       <c r="F32" t="n">
-        <v>4.04552</v>
+        <v>5.35295</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.13895</v>
+        <v>4.77785</v>
       </c>
       <c r="C33" t="n">
-        <v>3.20061</v>
+        <v>4.02662</v>
       </c>
       <c r="D33" t="n">
-        <v>12.9908</v>
+        <v>13.4293</v>
       </c>
       <c r="E33" t="n">
-        <v>3.97193</v>
+        <v>5.33273</v>
       </c>
       <c r="F33" t="n">
-        <v>4.11914</v>
+        <v>5.01319</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>4.16936</v>
+        <v>4.63155</v>
       </c>
       <c r="C34" t="n">
-        <v>3.23493</v>
+        <v>4.2224</v>
       </c>
       <c r="D34" t="n">
-        <v>13.3334</v>
+        <v>13.9041</v>
       </c>
       <c r="E34" t="n">
-        <v>4.57418</v>
+        <v>5.45705</v>
       </c>
       <c r="F34" t="n">
-        <v>4.23461</v>
+        <v>5.36788</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>4.23698</v>
+        <v>4.82066</v>
       </c>
       <c r="C35" t="n">
-        <v>3.22592</v>
+        <v>4.38339</v>
       </c>
       <c r="D35" t="n">
-        <v>9.36314</v>
+        <v>9.530239999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>4.30575</v>
+        <v>4.91903</v>
       </c>
       <c r="F35" t="n">
-        <v>4.30818</v>
+        <v>4.80907</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>4.30108</v>
+        <v>4.80222</v>
       </c>
       <c r="C36" t="n">
-        <v>3.39403</v>
+        <v>4.45978</v>
       </c>
       <c r="D36" t="n">
-        <v>9.59845</v>
+        <v>9.903729999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>4.37549</v>
+        <v>4.8918</v>
       </c>
       <c r="F36" t="n">
-        <v>4.33553</v>
+        <v>4.84825</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>4.75861</v>
+        <v>5.52141</v>
       </c>
       <c r="C37" t="n">
-        <v>3.51141</v>
+        <v>4.05331</v>
       </c>
       <c r="D37" t="n">
-        <v>9.80949</v>
+        <v>10.1798</v>
       </c>
       <c r="E37" t="n">
-        <v>4.41356</v>
+        <v>5.01162</v>
       </c>
       <c r="F37" t="n">
-        <v>4.37012</v>
+        <v>4.89862</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>4.88996</v>
+        <v>5.12072</v>
       </c>
       <c r="C38" t="n">
-        <v>3.3292</v>
+        <v>3.97979</v>
       </c>
       <c r="D38" t="n">
-        <v>10.1168</v>
+        <v>10.5987</v>
       </c>
       <c r="E38" t="n">
-        <v>4.4295</v>
+        <v>5.05286</v>
       </c>
       <c r="F38" t="n">
-        <v>4.39228</v>
+        <v>4.90789</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>5.11847</v>
+        <v>4.92896</v>
       </c>
       <c r="C39" t="n">
-        <v>3.56292</v>
+        <v>4.34517</v>
       </c>
       <c r="D39" t="n">
-        <v>10.4388</v>
+        <v>10.9217</v>
       </c>
       <c r="E39" t="n">
-        <v>4.46434</v>
+        <v>5.2632</v>
       </c>
       <c r="F39" t="n">
-        <v>4.41624</v>
+        <v>4.87596</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>5.14056</v>
+        <v>4.91063</v>
       </c>
       <c r="C40" t="n">
-        <v>3.55489</v>
+        <v>4.26926</v>
       </c>
       <c r="D40" t="n">
-        <v>10.758</v>
+        <v>11.4444</v>
       </c>
       <c r="E40" t="n">
-        <v>4.49865</v>
+        <v>5.30429</v>
       </c>
       <c r="F40" t="n">
-        <v>4.44454</v>
+        <v>4.9405</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>5.13784</v>
+        <v>4.83225</v>
       </c>
       <c r="C41" t="n">
-        <v>3.58093</v>
+        <v>4.28702</v>
       </c>
       <c r="D41" t="n">
-        <v>11.1257</v>
+        <v>11.9759</v>
       </c>
       <c r="E41" t="n">
-        <v>4.18609</v>
+        <v>5.32765</v>
       </c>
       <c r="F41" t="n">
-        <v>4.52204</v>
+        <v>5.15223</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>5.18762</v>
+        <v>4.94979</v>
       </c>
       <c r="C42" t="n">
-        <v>3.42442</v>
+        <v>4.39498</v>
       </c>
       <c r="D42" t="n">
-        <v>11.4951</v>
+        <v>12.5649</v>
       </c>
       <c r="E42" t="n">
-        <v>4.57523</v>
+        <v>5.34177</v>
       </c>
       <c r="F42" t="n">
-        <v>4.51223</v>
+        <v>5.05472</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>5.19002</v>
+        <v>4.972</v>
       </c>
       <c r="C43" t="n">
-        <v>3.45565</v>
+        <v>4.43773</v>
       </c>
       <c r="D43" t="n">
-        <v>11.8697</v>
+        <v>12.7051</v>
       </c>
       <c r="E43" t="n">
-        <v>4.24153</v>
+        <v>5.21035</v>
       </c>
       <c r="F43" t="n">
-        <v>4.60644</v>
+        <v>5.09973</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>5.21128</v>
+        <v>4.96312</v>
       </c>
       <c r="C44" t="n">
-        <v>3.4674</v>
+        <v>4.42869</v>
       </c>
       <c r="D44" t="n">
-        <v>12.2708</v>
+        <v>13.2244</v>
       </c>
       <c r="E44" t="n">
-        <v>4.6753</v>
+        <v>5.28829</v>
       </c>
       <c r="F44" t="n">
-        <v>4.66348</v>
+        <v>5.22898</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>5.22504</v>
+        <v>5.07169</v>
       </c>
       <c r="C45" t="n">
-        <v>3.49097</v>
+        <v>4.38826</v>
       </c>
       <c r="D45" t="n">
-        <v>12.6662</v>
+        <v>13.6727</v>
       </c>
       <c r="E45" t="n">
-        <v>4.2453</v>
+        <v>5.32496</v>
       </c>
       <c r="F45" t="n">
-        <v>4.66092</v>
+        <v>5.29888</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>5.05593</v>
+        <v>4.96246</v>
       </c>
       <c r="C46" t="n">
-        <v>3.65522</v>
+        <v>4.52624</v>
       </c>
       <c r="D46" t="n">
-        <v>13.0298</v>
+        <v>13.9533</v>
       </c>
       <c r="E46" t="n">
-        <v>4.3324</v>
+        <v>5.58894</v>
       </c>
       <c r="F46" t="n">
-        <v>4.73949</v>
+        <v>5.38366</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>5.24317</v>
+        <v>4.97913</v>
       </c>
       <c r="C47" t="n">
-        <v>3.76408</v>
+        <v>4.54874</v>
       </c>
       <c r="D47" t="n">
-        <v>13.3636</v>
+        <v>14.3551</v>
       </c>
       <c r="E47" t="n">
-        <v>4.56479</v>
+        <v>5.56237</v>
       </c>
       <c r="F47" t="n">
-        <v>4.70646</v>
+        <v>5.74695</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>5.13524</v>
+        <v>4.66573</v>
       </c>
       <c r="C48" t="n">
-        <v>3.57021</v>
+        <v>4.612</v>
       </c>
       <c r="D48" t="n">
-        <v>13.7533</v>
+        <v>14.6916</v>
       </c>
       <c r="E48" t="n">
-        <v>4.74571</v>
+        <v>5.99291</v>
       </c>
       <c r="F48" t="n">
-        <v>4.86173</v>
+        <v>6.02667</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>5.30118</v>
+        <v>4.95208</v>
       </c>
       <c r="C49" t="n">
-        <v>3.66681</v>
+        <v>4.72952</v>
       </c>
       <c r="D49" t="n">
-        <v>14.0627</v>
+        <v>15.4878</v>
       </c>
       <c r="E49" t="n">
-        <v>5.06377</v>
+        <v>6.32987</v>
       </c>
       <c r="F49" t="n">
-        <v>5.1614</v>
+        <v>6.53559</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>5.47284</v>
+        <v>5.20146</v>
       </c>
       <c r="C50" t="n">
-        <v>3.78299</v>
+        <v>4.82645</v>
       </c>
       <c r="D50" t="n">
-        <v>9.802659999999999</v>
+        <v>11.8674</v>
       </c>
       <c r="E50" t="n">
-        <v>4.60124</v>
+        <v>5.19334</v>
       </c>
       <c r="F50" t="n">
-        <v>4.66463</v>
+        <v>6.1628</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>5.52966</v>
+        <v>6.01964</v>
       </c>
       <c r="C51" t="n">
-        <v>4.75583</v>
+        <v>4.13423</v>
       </c>
       <c r="D51" t="n">
-        <v>10.0377</v>
+        <v>12.1769</v>
       </c>
       <c r="E51" t="n">
-        <v>4.63739</v>
+        <v>5.00406</v>
       </c>
       <c r="F51" t="n">
-        <v>4.74905</v>
+        <v>5.85473</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>6.37491</v>
+        <v>6.16114</v>
       </c>
       <c r="C52" t="n">
-        <v>4.02797</v>
+        <v>4.05133</v>
       </c>
       <c r="D52" t="n">
-        <v>10.2924</v>
+        <v>13.9887</v>
       </c>
       <c r="E52" t="n">
-        <v>4.69094</v>
+        <v>5.22427</v>
       </c>
       <c r="F52" t="n">
-        <v>4.92068</v>
+        <v>6.49545</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>6.50179</v>
+        <v>5.14975</v>
       </c>
       <c r="C53" t="n">
-        <v>4.48538</v>
+        <v>4.1674</v>
       </c>
       <c r="D53" t="n">
-        <v>10.5952</v>
+        <v>14.8894</v>
       </c>
       <c r="E53" t="n">
-        <v>4.74446</v>
+        <v>5.24633</v>
       </c>
       <c r="F53" t="n">
-        <v>4.80277</v>
+        <v>6.50984</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>6.34229</v>
+        <v>5.12413</v>
       </c>
       <c r="C54" t="n">
-        <v>4.80046</v>
+        <v>4.18946</v>
       </c>
       <c r="D54" t="n">
-        <v>10.9921</v>
+        <v>15.8705</v>
       </c>
       <c r="E54" t="n">
-        <v>4.84161</v>
+        <v>5.3184</v>
       </c>
       <c r="F54" t="n">
-        <v>4.84712</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>6.68074</v>
+        <v>5.44697</v>
       </c>
       <c r="C55" t="n">
-        <v>5.12662</v>
+        <v>4.18448</v>
       </c>
       <c r="D55" t="n">
-        <v>11.3235</v>
+        <v>16.7264</v>
       </c>
       <c r="E55" t="n">
-        <v>4.54694</v>
+        <v>5.38118</v>
       </c>
       <c r="F55" t="n">
-        <v>5.32641</v>
+        <v>5.72767</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>5.21019</v>
+        <v>5.17129</v>
       </c>
       <c r="C56" t="n">
-        <v>3.63726</v>
+        <v>4.20673</v>
       </c>
       <c r="D56" t="n">
-        <v>12.3953</v>
+        <v>17.8128</v>
       </c>
       <c r="E56" t="n">
-        <v>4.66606</v>
+        <v>5.26509</v>
       </c>
       <c r="F56" t="n">
-        <v>4.99003</v>
+        <v>6.11975</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>6.46043</v>
+        <v>5.14661</v>
       </c>
       <c r="C57" t="n">
-        <v>4.45796</v>
+        <v>4.23527</v>
       </c>
       <c r="D57" t="n">
-        <v>12.36</v>
+        <v>19.2716</v>
       </c>
       <c r="E57" t="n">
-        <v>4.63632</v>
+        <v>5.43383</v>
       </c>
       <c r="F57" t="n">
-        <v>5.65296</v>
+        <v>6.7497</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>7.1261</v>
+        <v>5.1988</v>
       </c>
       <c r="C58" t="n">
-        <v>5.3312</v>
+        <v>4.28167</v>
       </c>
       <c r="D58" t="n">
-        <v>12.9064</v>
+        <v>19.481</v>
       </c>
       <c r="E58" t="n">
-        <v>4.69653</v>
+        <v>5.48817</v>
       </c>
       <c r="F58" t="n">
-        <v>5.91829</v>
+        <v>5.95997</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>6.53424</v>
+        <v>5.22236</v>
       </c>
       <c r="C59" t="n">
-        <v>4.57517</v>
+        <v>4.33223</v>
       </c>
       <c r="D59" t="n">
-        <v>13.4764</v>
+        <v>19.1429</v>
       </c>
       <c r="E59" t="n">
-        <v>4.79352</v>
+        <v>5.50724</v>
       </c>
       <c r="F59" t="n">
-        <v>5.50488</v>
+        <v>7.19081</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>6.02386</v>
+        <v>5.24142</v>
       </c>
       <c r="C60" t="n">
-        <v>4.09823</v>
+        <v>4.32563</v>
       </c>
       <c r="D60" t="n">
-        <v>14.3273</v>
+        <v>20.4837</v>
       </c>
       <c r="E60" t="n">
-        <v>4.90888</v>
+        <v>5.71004</v>
       </c>
       <c r="F60" t="n">
-        <v>5.73878</v>
+        <v>6.29084</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>6.93137</v>
+        <v>5.29568</v>
       </c>
       <c r="C61" t="n">
-        <v>5.04578</v>
+        <v>4.43704</v>
       </c>
       <c r="D61" t="n">
-        <v>15.7659</v>
+        <v>20.8686</v>
       </c>
       <c r="E61" t="n">
-        <v>5.02752</v>
+        <v>5.86922</v>
       </c>
       <c r="F61" t="n">
-        <v>5.70475</v>
+        <v>7.21947</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>5.87926</v>
+        <v>5.27064</v>
       </c>
       <c r="C62" t="n">
-        <v>4.04637</v>
+        <v>4.41163</v>
       </c>
       <c r="D62" t="n">
-        <v>16.5846</v>
+        <v>20.9796</v>
       </c>
       <c r="E62" t="n">
-        <v>5.22259</v>
+        <v>6.02391</v>
       </c>
       <c r="F62" t="n">
-        <v>6.19762</v>
+        <v>7.22003</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>6.34964</v>
+        <v>5.43547</v>
       </c>
       <c r="C63" t="n">
-        <v>4.39265</v>
+        <v>4.54388</v>
       </c>
       <c r="D63" t="n">
-        <v>17.3185</v>
+        <v>20.8278</v>
       </c>
       <c r="E63" t="n">
-        <v>5.49257</v>
+        <v>6.37574</v>
       </c>
       <c r="F63" t="n">
-        <v>6.72661</v>
+        <v>7.61906</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>6.59484</v>
+        <v>5.63384</v>
       </c>
       <c r="C64" t="n">
-        <v>5.19645</v>
+        <v>4.72366</v>
       </c>
       <c r="D64" t="n">
-        <v>15.501</v>
+        <v>15.7723</v>
       </c>
       <c r="E64" t="n">
-        <v>4.65423</v>
+        <v>6.04683</v>
       </c>
       <c r="F64" t="n">
-        <v>6.10768</v>
+        <v>6.3958</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>6.95243</v>
+        <v>5.8561</v>
       </c>
       <c r="C65" t="n">
-        <v>4.47008</v>
+        <v>7.21349</v>
       </c>
       <c r="D65" t="n">
-        <v>16.085</v>
+        <v>14.9077</v>
       </c>
       <c r="E65" t="n">
-        <v>4.69634</v>
+        <v>6.10056</v>
       </c>
       <c r="F65" t="n">
-        <v>6.1924</v>
+        <v>6.40211</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>7.37329</v>
+        <v>6.29695</v>
       </c>
       <c r="C66" t="n">
-        <v>4.51102</v>
+        <v>7.28792</v>
       </c>
       <c r="D66" t="n">
-        <v>16.561</v>
+        <v>16.2966</v>
       </c>
       <c r="E66" t="n">
-        <v>4.6999</v>
+        <v>6.17091</v>
       </c>
       <c r="F66" t="n">
-        <v>6.06586</v>
+        <v>6.5996</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>6.46864</v>
+        <v>8.47709</v>
       </c>
       <c r="C67" t="n">
-        <v>4.59586</v>
+        <v>7.31486</v>
       </c>
       <c r="D67" t="n">
-        <v>17.5089</v>
+        <v>17.4551</v>
       </c>
       <c r="E67" t="n">
-        <v>4.765</v>
+        <v>6.30032</v>
       </c>
       <c r="F67" t="n">
-        <v>6.15032</v>
+        <v>6.77407</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>6.58266</v>
+        <v>8.171989999999999</v>
       </c>
       <c r="C68" t="n">
-        <v>4.70748</v>
+        <v>6.87606</v>
       </c>
       <c r="D68" t="n">
-        <v>17.3702</v>
+        <v>18.5054</v>
       </c>
       <c r="E68" t="n">
-        <v>4.84524</v>
+        <v>6.3738</v>
       </c>
       <c r="F68" t="n">
-        <v>6.28036</v>
+        <v>6.88039</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>6.78835</v>
+        <v>8.45776</v>
       </c>
       <c r="C69" t="n">
-        <v>4.93219</v>
+        <v>7.22707</v>
       </c>
       <c r="D69" t="n">
-        <v>18.4878</v>
+        <v>19.3442</v>
       </c>
       <c r="E69" t="n">
-        <v>4.84265</v>
+        <v>6.51513</v>
       </c>
       <c r="F69" t="n">
-        <v>6.47061</v>
+        <v>6.95297</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>7.18289</v>
+        <v>8.15762</v>
       </c>
       <c r="C70" t="n">
-        <v>5.38217</v>
+        <v>6.91164</v>
       </c>
       <c r="D70" t="n">
-        <v>19.2741</v>
+        <v>19.4274</v>
       </c>
       <c r="E70" t="n">
-        <v>4.96916</v>
+        <v>6.73741</v>
       </c>
       <c r="F70" t="n">
-        <v>6.62869</v>
+        <v>6.96607</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>7.55742</v>
+        <v>8.17882</v>
       </c>
       <c r="C71" t="n">
-        <v>5.73391</v>
+        <v>6.84997</v>
       </c>
       <c r="D71" t="n">
-        <v>19.5658</v>
+        <v>19.3236</v>
       </c>
       <c r="E71" t="n">
-        <v>5.1076</v>
+        <v>6.62433</v>
       </c>
       <c r="F71" t="n">
-        <v>6.70437</v>
+        <v>7.85608</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>7.01083</v>
+        <v>7.43719</v>
       </c>
       <c r="C72" t="n">
-        <v>5.23776</v>
+        <v>6.20583</v>
       </c>
       <c r="D72" t="n">
-        <v>19.6606</v>
+        <v>19.9402</v>
       </c>
       <c r="E72" t="n">
-        <v>5.21834</v>
+        <v>6.7432</v>
       </c>
       <c r="F72" t="n">
-        <v>6.82059</v>
+        <v>8.01436</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>6.96059</v>
+        <v>8.785159999999999</v>
       </c>
       <c r="C73" t="n">
-        <v>5.0713</v>
+        <v>7.55392</v>
       </c>
       <c r="D73" t="n">
-        <v>20.282</v>
+        <v>19.6175</v>
       </c>
       <c r="E73" t="n">
-        <v>5.347</v>
+        <v>6.86662</v>
       </c>
       <c r="F73" t="n">
-        <v>7.00678</v>
+        <v>8.15996</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>6.52534</v>
+        <v>7.67334</v>
       </c>
       <c r="C74" t="n">
-        <v>4.81636</v>
+        <v>6.36725</v>
       </c>
       <c r="D74" t="n">
-        <v>20.5769</v>
+        <v>20.5683</v>
       </c>
       <c r="E74" t="n">
-        <v>5.64691</v>
+        <v>6.30342</v>
       </c>
       <c r="F74" t="n">
-        <v>7.98487</v>
+        <v>7.76215</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>7.40921</v>
+        <v>7.75653</v>
       </c>
       <c r="C75" t="n">
-        <v>5.54755</v>
+        <v>6.44513</v>
       </c>
       <c r="D75" t="n">
-        <v>22.2813</v>
+        <v>21.1876</v>
       </c>
       <c r="E75" t="n">
-        <v>5.78782</v>
+        <v>6.46677</v>
       </c>
       <c r="F75" t="n">
-        <v>9.08967</v>
+        <v>7.70882</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>7.29736</v>
+        <v>7.81491</v>
       </c>
       <c r="C76" t="n">
-        <v>5.5729</v>
+        <v>6.47608</v>
       </c>
       <c r="D76" t="n">
-        <v>24.8201</v>
+        <v>21.3761</v>
       </c>
       <c r="E76" t="n">
-        <v>5.86591</v>
+        <v>6.63168</v>
       </c>
       <c r="F76" t="n">
-        <v>9.94721</v>
+        <v>8.03228</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>7.27821</v>
+        <v>7.78206</v>
       </c>
       <c r="C77" t="n">
-        <v>5.57934</v>
+        <v>6.51057</v>
       </c>
       <c r="D77" t="n">
-        <v>24.5254</v>
+        <v>22.6739</v>
       </c>
       <c r="E77" t="n">
-        <v>6.14412</v>
+        <v>6.89281</v>
       </c>
       <c r="F77" t="n">
-        <v>10.1213</v>
+        <v>9.837719999999999</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>7.37687</v>
+        <v>8.511749999999999</v>
       </c>
       <c r="C78" t="n">
-        <v>5.58087</v>
+        <v>7.13942</v>
       </c>
       <c r="D78" t="n">
-        <v>21.3485</v>
+        <v>20.0294</v>
       </c>
       <c r="E78" t="n">
-        <v>12.4643</v>
+        <v>12.6859</v>
       </c>
       <c r="F78" t="n">
-        <v>11.0835</v>
+        <v>14.0405</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>7.73288</v>
+        <v>8.22315</v>
       </c>
       <c r="C79" t="n">
-        <v>13.5073</v>
+        <v>15.2971</v>
       </c>
       <c r="D79" t="n">
-        <v>22.2262</v>
+        <v>21.2681</v>
       </c>
       <c r="E79" t="n">
-        <v>12.9051</v>
+        <v>11.1829</v>
       </c>
       <c r="F79" t="n">
-        <v>11.023</v>
+        <v>15.5165</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>8.085789999999999</v>
+        <v>9.44689</v>
       </c>
       <c r="C80" t="n">
-        <v>14.676</v>
+        <v>16.7445</v>
       </c>
       <c r="D80" t="n">
-        <v>23.4308</v>
+        <v>22.0779</v>
       </c>
       <c r="E80" t="n">
-        <v>12.9516</v>
+        <v>13.207</v>
       </c>
       <c r="F80" t="n">
-        <v>11.2599</v>
+        <v>13.9361</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>18.0225</v>
+        <v>17.3617</v>
       </c>
       <c r="C81" t="n">
-        <v>14.7239</v>
+        <v>16.5999</v>
       </c>
       <c r="D81" t="n">
-        <v>24.7824</v>
+        <v>22.9107</v>
       </c>
       <c r="E81" t="n">
-        <v>12.0133</v>
+        <v>13.4266</v>
       </c>
       <c r="F81" t="n">
-        <v>11.3137</v>
+        <v>14.3467</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>18.0565</v>
+        <v>17.2506</v>
       </c>
       <c r="C82" t="n">
-        <v>14.7677</v>
+        <v>16.421</v>
       </c>
       <c r="D82" t="n">
-        <v>25.5437</v>
+        <v>24.1288</v>
       </c>
       <c r="E82" t="n">
-        <v>13.4302</v>
+        <v>13.6338</v>
       </c>
       <c r="F82" t="n">
-        <v>11.3209</v>
+        <v>14.2674</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>18.0955</v>
+        <v>17.3353</v>
       </c>
       <c r="C83" t="n">
-        <v>14.8123</v>
+        <v>16.6155</v>
       </c>
       <c r="D83" t="n">
-        <v>26.4885</v>
+        <v>24.6365</v>
       </c>
       <c r="E83" t="n">
-        <v>13.4869</v>
+        <v>13.8898</v>
       </c>
       <c r="F83" t="n">
-        <v>11.5042</v>
+        <v>14.4794</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>18.1273</v>
+        <v>17.3493</v>
       </c>
       <c r="C84" t="n">
-        <v>14.8594</v>
+        <v>16.5276</v>
       </c>
       <c r="D84" t="n">
-        <v>27.0424</v>
+        <v>25.7279</v>
       </c>
       <c r="E84" t="n">
-        <v>13.7759</v>
+        <v>14.1158</v>
       </c>
       <c r="F84" t="n">
-        <v>11.6882</v>
+        <v>14.5321</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>18.4577</v>
+        <v>17.4076</v>
       </c>
       <c r="C85" t="n">
-        <v>15.0768</v>
+        <v>16.6504</v>
       </c>
       <c r="D85" t="n">
-        <v>27.8344</v>
+        <v>27.0711</v>
       </c>
       <c r="E85" t="n">
-        <v>13.5724</v>
+        <v>13.3715</v>
       </c>
       <c r="F85" t="n">
-        <v>14.9606</v>
+        <v>12.7988</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>18.1831</v>
+        <v>17.6148</v>
       </c>
       <c r="C86" t="n">
-        <v>14.9442</v>
+        <v>16.8929</v>
       </c>
       <c r="D86" t="n">
-        <v>29.0784</v>
+        <v>28.3177</v>
       </c>
       <c r="E86" t="n">
-        <v>13.7995</v>
+        <v>13.5866</v>
       </c>
       <c r="F86" t="n">
-        <v>14.9991</v>
+        <v>13.0774</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>18.2156</v>
+        <v>17.609</v>
       </c>
       <c r="C87" t="n">
-        <v>14.992</v>
+        <v>16.865</v>
       </c>
       <c r="D87" t="n">
-        <v>29.3154</v>
+        <v>29.6848</v>
       </c>
       <c r="E87" t="n">
-        <v>13.9103</v>
+        <v>13.409</v>
       </c>
       <c r="F87" t="n">
-        <v>15.0255</v>
+        <v>12.2715</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>18.3307</v>
+        <v>17.0694</v>
       </c>
       <c r="C88" t="n">
-        <v>15.0537</v>
+        <v>16.0496</v>
       </c>
       <c r="D88" t="n">
-        <v>32.398</v>
+        <v>30.9495</v>
       </c>
       <c r="E88" t="n">
-        <v>13.2913</v>
+        <v>13.2797</v>
       </c>
       <c r="F88" t="n">
-        <v>15.1497</v>
+        <v>12.6951</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>17.8927</v>
+        <v>17.5178</v>
       </c>
       <c r="C89" t="n">
-        <v>14.6927</v>
+        <v>16.6681</v>
       </c>
       <c r="D89" t="n">
-        <v>32.537</v>
+        <v>32.3818</v>
       </c>
       <c r="E89" t="n">
-        <v>13.4718</v>
+        <v>13.5532</v>
       </c>
       <c r="F89" t="n">
-        <v>14.2783</v>
+        <v>13.0413</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>17.7646</v>
+        <v>17.1415</v>
       </c>
       <c r="C90" t="n">
-        <v>14.611</v>
+        <v>16.0575</v>
       </c>
       <c r="D90" t="n">
-        <v>33.0875</v>
+        <v>33.0825</v>
       </c>
       <c r="E90" t="n">
-        <v>13.716</v>
+        <v>13.8124</v>
       </c>
       <c r="F90" t="n">
-        <v>12.6985</v>
+        <v>13.1852</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>18.4333</v>
+        <v>17.0094</v>
       </c>
       <c r="C91" t="n">
-        <v>15.313</v>
+        <v>16.0563</v>
       </c>
       <c r="D91" t="n">
-        <v>34.1832</v>
+        <v>33.9506</v>
       </c>
       <c r="E91" t="n">
-        <v>13.9694</v>
+        <v>14.1247</v>
       </c>
       <c r="F91" t="n">
-        <v>13.0963</v>
+        <v>13.6115</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>18.6449</v>
+        <v>17.2124</v>
       </c>
       <c r="C92" t="n">
-        <v>15.4785</v>
+        <v>16.1616</v>
       </c>
       <c r="D92" t="n">
-        <v>32.2108</v>
+        <v>31.7088</v>
       </c>
       <c r="E92" t="n">
-        <v>18.1138</v>
+        <v>20.0479</v>
       </c>
       <c r="F92" t="n">
-        <v>18.4481</v>
+        <v>20.2569</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>18.5556</v>
+        <v>17.3296</v>
       </c>
       <c r="C93" t="n">
-        <v>15.4329</v>
+        <v>16.2816</v>
       </c>
       <c r="D93" t="n">
-        <v>33.0095</v>
+        <v>32.3977</v>
       </c>
       <c r="E93" t="n">
-        <v>17.999</v>
+        <v>20.7127</v>
       </c>
       <c r="F93" t="n">
-        <v>18.5802</v>
+        <v>20.3172</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>18.5394</v>
+        <v>17.5799</v>
       </c>
       <c r="C94" t="n">
-        <v>17.4323</v>
+        <v>20.95</v>
       </c>
       <c r="D94" t="n">
-        <v>33.862</v>
+        <v>33.4358</v>
       </c>
       <c r="E94" t="n">
-        <v>18.1989</v>
+        <v>20.7647</v>
       </c>
       <c r="F94" t="n">
-        <v>18.643</v>
+        <v>20.3738</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>21.9785</v>
+        <v>21.264</v>
       </c>
       <c r="C95" t="n">
-        <v>17.6016</v>
+        <v>20.8739</v>
       </c>
       <c r="D95" t="n">
-        <v>34.7106</v>
+        <v>33.7549</v>
       </c>
       <c r="E95" t="n">
-        <v>18.6328</v>
+        <v>21.2855</v>
       </c>
       <c r="F95" t="n">
-        <v>18.8658</v>
+        <v>20.5198</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>22.0411</v>
+        <v>21.4761</v>
       </c>
       <c r="C96" t="n">
-        <v>17.6738</v>
+        <v>20.8879</v>
       </c>
       <c r="D96" t="n">
-        <v>35.5007</v>
+        <v>34.4142</v>
       </c>
       <c r="E96" t="n">
-        <v>18.7346</v>
+        <v>21.5422</v>
       </c>
       <c r="F96" t="n">
-        <v>18.9023</v>
+        <v>20.6032</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>22.04</v>
+        <v>21.5732</v>
       </c>
       <c r="C97" t="n">
-        <v>17.6661</v>
+        <v>20.93</v>
       </c>
       <c r="D97" t="n">
-        <v>36.5841</v>
+        <v>35.5314</v>
       </c>
       <c r="E97" t="n">
-        <v>18.8635</v>
+        <v>21.7261</v>
       </c>
       <c r="F97" t="n">
-        <v>19.0756</v>
+        <v>20.7149</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>22.0654</v>
+        <v>21.5288</v>
       </c>
       <c r="C98" t="n">
-        <v>17.7417</v>
+        <v>20.9603</v>
       </c>
       <c r="D98" t="n">
-        <v>37.26</v>
+        <v>36.1867</v>
       </c>
       <c r="E98" t="n">
-        <v>19.0878</v>
+        <v>21.9051</v>
       </c>
       <c r="F98" t="n">
-        <v>19.1804</v>
+        <v>20.9015</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>22.0807</v>
+        <v>21.5805</v>
       </c>
       <c r="C99" t="n">
-        <v>17.7946</v>
+        <v>20.9746</v>
       </c>
       <c r="D99" t="n">
-        <v>38.3055</v>
+        <v>37.27</v>
       </c>
       <c r="E99" t="n">
-        <v>19.143</v>
+        <v>22.0796</v>
       </c>
       <c r="F99" t="n">
-        <v>19.256</v>
+        <v>20.9917</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>22.102</v>
+        <v>21.4097</v>
       </c>
       <c r="C100" t="n">
-        <v>17.7319</v>
+        <v>21.0203</v>
       </c>
       <c r="D100" t="n">
-        <v>39.4286</v>
+        <v>38.6015</v>
       </c>
       <c r="E100" t="n">
-        <v>19.3728</v>
+        <v>22.2572</v>
       </c>
       <c r="F100" t="n">
-        <v>19.5171</v>
+        <v>21.1596</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>22.113</v>
+        <v>21.5952</v>
       </c>
       <c r="C101" t="n">
-        <v>17.7542</v>
+        <v>21.0605</v>
       </c>
       <c r="D101" t="n">
-        <v>40.7715</v>
+        <v>39.6024</v>
       </c>
       <c r="E101" t="n">
-        <v>19.472</v>
+        <v>22.4678</v>
       </c>
       <c r="F101" t="n">
-        <v>19.5902</v>
+        <v>21.2953</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>22.112</v>
+        <v>21.6224</v>
       </c>
       <c r="C102" t="n">
-        <v>17.8049</v>
+        <v>21.1153</v>
       </c>
       <c r="D102" t="n">
-        <v>41.6367</v>
+        <v>40.2399</v>
       </c>
       <c r="E102" t="n">
-        <v>19.5827</v>
+        <v>22.7183</v>
       </c>
       <c r="F102" t="n">
-        <v>19.6634</v>
+        <v>21.4962</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>22.1417</v>
+        <v>21.6385</v>
       </c>
       <c r="C103" t="n">
-        <v>17.8543</v>
+        <v>21.1415</v>
       </c>
       <c r="D103" t="n">
-        <v>42.98</v>
+        <v>41.2099</v>
       </c>
       <c r="E103" t="n">
-        <v>19.8548</v>
+        <v>22.8933</v>
       </c>
       <c r="F103" t="n">
-        <v>19.9952</v>
+        <v>21.7336</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>22.2063</v>
+        <v>21.7493</v>
       </c>
       <c r="C104" t="n">
-        <v>17.9694</v>
+        <v>21.2139</v>
       </c>
       <c r="D104" t="n">
-        <v>44.0112</v>
+        <v>42.3416</v>
       </c>
       <c r="E104" t="n">
-        <v>20.0052</v>
+        <v>23.3698</v>
       </c>
       <c r="F104" t="n">
-        <v>20.2161</v>
+        <v>22.9365</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>22.2673</v>
+        <v>21.6582</v>
       </c>
       <c r="C105" t="n">
-        <v>18.0574</v>
+        <v>21.3037</v>
       </c>
       <c r="D105" t="n">
-        <v>45.2145</v>
+        <v>44.1627</v>
       </c>
       <c r="E105" t="n">
-        <v>20.1996</v>
+        <v>23.4451</v>
       </c>
       <c r="F105" t="n">
-        <v>20.8957</v>
+        <v>23.1997</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>22.4081</v>
+        <v>21.9168</v>
       </c>
       <c r="C106" t="n">
-        <v>18.2748</v>
+        <v>21.439</v>
       </c>
       <c r="D106" t="n">
-        <v>46.4098</v>
+        <v>45.1909</v>
       </c>
       <c r="E106" t="n">
-        <v>20.4948</v>
+        <v>23.7764</v>
       </c>
       <c r="F106" t="n">
-        <v>21.0499</v>
+        <v>22.7392</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>22.5774</v>
+        <v>22.1866</v>
       </c>
       <c r="C107" t="n">
-        <v>18.4267</v>
+        <v>21.5437</v>
       </c>
       <c r="D107" t="n">
-        <v>39.6799</v>
+        <v>38.4719</v>
       </c>
       <c r="E107" t="n">
-        <v>23.2582</v>
+        <v>26.815</v>
       </c>
       <c r="F107" t="n">
-        <v>23.3488</v>
+        <v>25.479</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>22.6864</v>
+        <v>22.4488</v>
       </c>
       <c r="C108" t="n">
-        <v>18.9985</v>
+        <v>22.4739</v>
       </c>
       <c r="D108" t="n">
-        <v>40.5015</v>
+        <v>39.0159</v>
       </c>
       <c r="E108" t="n">
-        <v>23.6695</v>
+        <v>27.2669</v>
       </c>
       <c r="F108" t="n">
-        <v>23.607</v>
+        <v>26.1108</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>23.4624</v>
+        <v>23.0385</v>
       </c>
       <c r="C109" t="n">
-        <v>19.0164</v>
+        <v>22.8212</v>
       </c>
       <c r="D109" t="n">
-        <v>41.298</v>
+        <v>39.7839</v>
       </c>
       <c r="E109" t="n">
-        <v>23.6734</v>
+        <v>27.3081</v>
       </c>
       <c r="F109" t="n">
-        <v>23.699</v>
+        <v>25.8662</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>25.33</v>
+        <v>24.747</v>
       </c>
       <c r="C110" t="n">
-        <v>19.0735</v>
+        <v>22.7633</v>
       </c>
       <c r="D110" t="n">
-        <v>42.0062</v>
+        <v>40.7656</v>
       </c>
       <c r="E110" t="n">
-        <v>24.1359</v>
+        <v>27.6922</v>
       </c>
       <c r="F110" t="n">
-        <v>23.3741</v>
+        <v>26.2875</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>25.2857</v>
+        <v>24.8149</v>
       </c>
       <c r="C111" t="n">
-        <v>19.117</v>
+        <v>22.8029</v>
       </c>
       <c r="D111" t="n">
-        <v>42.9939</v>
+        <v>41.486</v>
       </c>
       <c r="E111" t="n">
-        <v>24.4019</v>
+        <v>27.791</v>
       </c>
       <c r="F111" t="n">
-        <v>24.2543</v>
+        <v>26.3842</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>25.3447</v>
+        <v>24.8091</v>
       </c>
       <c r="C112" t="n">
-        <v>19.232</v>
+        <v>22.8635</v>
       </c>
       <c r="D112" t="n">
-        <v>43.7532</v>
+        <v>42.3794</v>
       </c>
       <c r="E112" t="n">
-        <v>24.7767</v>
+        <v>28.151</v>
       </c>
       <c r="F112" t="n">
-        <v>24.3376</v>
+        <v>26.805</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>25.435</v>
+        <v>24.8204</v>
       </c>
       <c r="C113" t="n">
-        <v>19.2559</v>
+        <v>22.9684</v>
       </c>
       <c r="D113" t="n">
-        <v>44.8139</v>
+        <v>43.2616</v>
       </c>
       <c r="E113" t="n">
-        <v>24.7892</v>
+        <v>28.4141</v>
       </c>
       <c r="F113" t="n">
-        <v>24.4799</v>
+        <v>27.0799</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>25.2673</v>
+        <v>24.7975</v>
       </c>
       <c r="C114" t="n">
-        <v>19.3042</v>
+        <v>23.0391</v>
       </c>
       <c r="D114" t="n">
-        <v>45.7617</v>
+        <v>44.3201</v>
       </c>
       <c r="E114" t="n">
-        <v>24.9391</v>
+        <v>28.6903</v>
       </c>
       <c r="F114" t="n">
-        <v>24.777</v>
+        <v>27.3094</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>25.2437</v>
+        <v>24.9197</v>
       </c>
       <c r="C115" t="n">
-        <v>19.4132</v>
+        <v>23.0875</v>
       </c>
       <c r="D115" t="n">
-        <v>46.802</v>
+        <v>45.2676</v>
       </c>
       <c r="E115" t="n">
-        <v>25.1833</v>
+        <v>28.9822</v>
       </c>
       <c r="F115" t="n">
-        <v>25.0733</v>
+        <v>27.5954</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>25.3116</v>
+        <v>24.9202</v>
       </c>
       <c r="C116" t="n">
-        <v>19.463</v>
+        <v>23.2277</v>
       </c>
       <c r="D116" t="n">
-        <v>47.8679</v>
+        <v>46.1543</v>
       </c>
       <c r="E116" t="n">
-        <v>25.4136</v>
+        <v>29.1456</v>
       </c>
       <c r="F116" t="n">
-        <v>25.3984</v>
+        <v>27.9111</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>25.7358</v>
+        <v>24.7771</v>
       </c>
       <c r="C117" t="n">
-        <v>19.6117</v>
+        <v>23.281</v>
       </c>
       <c r="D117" t="n">
-        <v>48.8627</v>
+        <v>47.2076</v>
       </c>
       <c r="E117" t="n">
-        <v>25.6494</v>
+        <v>29.3694</v>
       </c>
       <c r="F117" t="n">
-        <v>25.8057</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>25.4903</v>
+        <v>24.9055</v>
       </c>
       <c r="C118" t="n">
-        <v>19.7291</v>
+        <v>23.4263</v>
       </c>
       <c r="D118" t="n">
-        <v>50.1551</v>
+        <v>48.7935</v>
       </c>
       <c r="E118" t="n">
-        <v>26.0049</v>
+        <v>29.8086</v>
       </c>
       <c r="F118" t="n">
-        <v>25.7216</v>
+        <v>28.7485</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>25.3936</v>
+        <v>24.9831</v>
       </c>
       <c r="C119" t="n">
-        <v>19.8997</v>
+        <v>23.6027</v>
       </c>
       <c r="D119" t="n">
-        <v>51.1088</v>
+        <v>49.7663</v>
       </c>
       <c r="E119" t="n">
-        <v>26.4238</v>
+        <v>30.253</v>
       </c>
       <c r="F119" t="n">
-        <v>26.7407</v>
+        <v>29.368</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>25.7952</v>
+        <v>24.974</v>
       </c>
       <c r="C120" t="n">
-        <v>20.1854</v>
+        <v>23.7579</v>
       </c>
       <c r="D120" t="n">
-        <v>52.5585</v>
+        <v>50.3487</v>
       </c>
       <c r="E120" t="n">
-        <v>26.8319</v>
+        <v>30.7043</v>
       </c>
       <c r="F120" t="n">
-        <v>27.3987</v>
+        <v>30.147</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>25.8913</v>
+        <v>25.3556</v>
       </c>
       <c r="C121" t="n">
-        <v>20.4254</v>
+        <v>24.0289</v>
       </c>
       <c r="D121" t="n">
-        <v>42.8465</v>
+        <v>41.3818</v>
       </c>
       <c r="E121" t="n">
-        <v>28.3743</v>
+        <v>31.176</v>
       </c>
       <c r="F121" t="n">
-        <v>27.3673</v>
+        <v>29.7173</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>25.5885</v>
+        <v>25.532</v>
       </c>
       <c r="C122" t="n">
-        <v>21.4</v>
+        <v>24.5749</v>
       </c>
       <c r="D122" t="n">
-        <v>43.7685</v>
+        <v>42</v>
       </c>
       <c r="E122" t="n">
-        <v>28.5307</v>
+        <v>31.2843</v>
       </c>
       <c r="F122" t="n">
-        <v>27.7302</v>
+        <v>30.2552</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>26.4171</v>
+        <v>25.8646</v>
       </c>
       <c r="C123" t="n">
-        <v>21.492</v>
+        <v>24.6487</v>
       </c>
       <c r="D123" t="n">
-        <v>44.3968</v>
+        <v>43.4104</v>
       </c>
       <c r="E123" t="n">
-        <v>28.7968</v>
+        <v>31.7668</v>
       </c>
       <c r="F123" t="n">
-        <v>27.992</v>
+        <v>30.5041</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>32.9661</v>
+        <v>32.222</v>
       </c>
       <c r="C124" t="n">
-        <v>21.6565</v>
+        <v>24.7353</v>
       </c>
       <c r="D124" t="n">
-        <v>45.1942</v>
+        <v>43.9616</v>
       </c>
       <c r="E124" t="n">
-        <v>29.153</v>
+        <v>32.029</v>
       </c>
       <c r="F124" t="n">
-        <v>28.0995</v>
+        <v>30.693</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>32.9802</v>
+        <v>32.19</v>
       </c>
       <c r="C125" t="n">
-        <v>21.7724</v>
+        <v>24.8434</v>
       </c>
       <c r="D125" t="n">
-        <v>46.2758</v>
+        <v>44.1714</v>
       </c>
       <c r="E125" t="n">
-        <v>29.3212</v>
+        <v>32.1817</v>
       </c>
       <c r="F125" t="n">
-        <v>28.286</v>
+        <v>30.8049</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>32.9787</v>
+        <v>31.5055</v>
       </c>
       <c r="C126" t="n">
-        <v>21.8913</v>
+        <v>24.9922</v>
       </c>
       <c r="D126" t="n">
-        <v>46.7556</v>
+        <v>45.2457</v>
       </c>
       <c r="E126" t="n">
-        <v>29.625</v>
+        <v>32.518</v>
       </c>
       <c r="F126" t="n">
-        <v>28.6635</v>
+        <v>31.2169</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>33.0893</v>
+        <v>32.101</v>
       </c>
       <c r="C127" t="n">
-        <v>22.0689</v>
+        <v>25.1645</v>
       </c>
       <c r="D127" t="n">
-        <v>47.4752</v>
+        <v>45.9805</v>
       </c>
       <c r="E127" t="n">
-        <v>29.8165</v>
+        <v>32.882</v>
       </c>
       <c r="F127" t="n">
-        <v>28.802</v>
+        <v>31.5169</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>33.1069</v>
+        <v>32.2581</v>
       </c>
       <c r="C128" t="n">
-        <v>22.1499</v>
+        <v>25.2825</v>
       </c>
       <c r="D128" t="n">
-        <v>48.3108</v>
+        <v>47.0605</v>
       </c>
       <c r="E128" t="n">
-        <v>30.1592</v>
+        <v>33.186</v>
       </c>
       <c r="F128" t="n">
-        <v>29.2233</v>
+        <v>31.7251</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>33.1237</v>
+        <v>32.1973</v>
       </c>
       <c r="C129" t="n">
-        <v>22.3334</v>
+        <v>25.4321</v>
       </c>
       <c r="D129" t="n">
-        <v>49.7501</v>
+        <v>48.1635</v>
       </c>
       <c r="E129" t="n">
-        <v>30.3815</v>
+        <v>33.483</v>
       </c>
       <c r="F129" t="n">
-        <v>29.5271</v>
+        <v>32.2017</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>33.1355</v>
+        <v>32.0977</v>
       </c>
       <c r="C130" t="n">
-        <v>22.5219</v>
+        <v>25.6347</v>
       </c>
       <c r="D130" t="n">
-        <v>50.7107</v>
+        <v>49.2497</v>
       </c>
       <c r="E130" t="n">
-        <v>30.7963</v>
+        <v>33.7735</v>
       </c>
       <c r="F130" t="n">
-        <v>30.0562</v>
+        <v>32.6066</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>33.2982</v>
+        <v>32.2003</v>
       </c>
       <c r="C131" t="n">
-        <v>22.7252</v>
+        <v>25.8465</v>
       </c>
       <c r="D131" t="n">
-        <v>51.9262</v>
+        <v>50.1889</v>
       </c>
       <c r="E131" t="n">
-        <v>30.9989</v>
+        <v>34.1506</v>
       </c>
       <c r="F131" t="n">
-        <v>30.495</v>
+        <v>33.1185</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>33.1965</v>
+        <v>32.231</v>
       </c>
       <c r="C132" t="n">
-        <v>22.9399</v>
+        <v>26.1545</v>
       </c>
       <c r="D132" t="n">
-        <v>53.0129</v>
+        <v>51.3646</v>
       </c>
       <c r="E132" t="n">
-        <v>31.5065</v>
+        <v>34.5726</v>
       </c>
       <c r="F132" t="n">
-        <v>30.9924</v>
+        <v>33.6637</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>33.2619</v>
+        <v>32.3776</v>
       </c>
       <c r="C133" t="n">
-        <v>23.2993</v>
+        <v>26.4664</v>
       </c>
       <c r="D133" t="n">
-        <v>54.0873</v>
+        <v>52.2998</v>
       </c>
       <c r="E133" t="n">
-        <v>31.8782</v>
+        <v>35.1086</v>
       </c>
       <c r="F133" t="n">
-        <v>31.6157</v>
+        <v>34.3715</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>33.3366</v>
+        <v>32.3235</v>
       </c>
       <c r="C134" t="n">
-        <v>23.6474</v>
+        <v>26.7393</v>
       </c>
       <c r="D134" t="n">
-        <v>55.492</v>
+        <v>53.8676</v>
       </c>
       <c r="E134" t="n">
-        <v>32.4593</v>
+        <v>35.704</v>
       </c>
       <c r="F134" t="n">
-        <v>32.4532</v>
+        <v>35.2097</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>33.6124</v>
+        <v>32.5002</v>
       </c>
       <c r="C135" t="n">
-        <v>24.1224</v>
+        <v>27.2581</v>
       </c>
       <c r="D135" t="n">
-        <v>45.0278</v>
+        <v>43.3362</v>
       </c>
       <c r="E135" t="n">
-        <v>30.4918</v>
+        <v>33.2916</v>
       </c>
       <c r="F135" t="n">
-        <v>30.1127</v>
+        <v>32.5939</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>33.2278</v>
+        <v>32.8583</v>
       </c>
       <c r="C136" t="n">
-        <v>24.1724</v>
+        <v>26.4772</v>
       </c>
       <c r="D136" t="n">
-        <v>45.4991</v>
+        <v>44.0165</v>
       </c>
       <c r="E136" t="n">
-        <v>31.0572</v>
+        <v>33.5886</v>
       </c>
       <c r="F136" t="n">
-        <v>30.324</v>
+        <v>32.604</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>34.02</v>
+        <v>32.8351</v>
       </c>
       <c r="C137" t="n">
-        <v>24.2433</v>
+        <v>26.6499</v>
       </c>
       <c r="D137" t="n">
-        <v>46.2304</v>
+        <v>44.2624</v>
       </c>
       <c r="E137" t="n">
-        <v>31.2921</v>
+        <v>33.9679</v>
       </c>
       <c r="F137" t="n">
-        <v>30.5268</v>
+        <v>33.0307</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>38.3904</v>
+        <v>37.4775</v>
       </c>
       <c r="C138" t="n">
-        <v>24.3941</v>
+        <v>26.7286</v>
       </c>
       <c r="D138" t="n">
-        <v>47.0192</v>
+        <v>45.7043</v>
       </c>
       <c r="E138" t="n">
-        <v>31.6044</v>
+        <v>34.2626</v>
       </c>
       <c r="F138" t="n">
-        <v>30.7795</v>
+        <v>33.1223</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>38.4081</v>
+        <v>37.3888</v>
       </c>
       <c r="C139" t="n">
-        <v>24.5249</v>
+        <v>26.8631</v>
       </c>
       <c r="D139" t="n">
-        <v>47.26</v>
+        <v>45.8135</v>
       </c>
       <c r="E139" t="n">
-        <v>31.8272</v>
+        <v>34.4278</v>
       </c>
       <c r="F139" t="n">
-        <v>31.1202</v>
+        <v>33.4844</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>38.4614</v>
+        <v>37.5294</v>
       </c>
       <c r="C140" t="n">
-        <v>24.7308</v>
+        <v>27.0954</v>
       </c>
       <c r="D140" t="n">
-        <v>48.3314</v>
+        <v>46.7355</v>
       </c>
       <c r="E140" t="n">
-        <v>32.0538</v>
+        <v>34.8213</v>
       </c>
       <c r="F140" t="n">
-        <v>31.3044</v>
+        <v>33.8245</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>38.4464</v>
+        <v>37.5125</v>
       </c>
       <c r="C141" t="n">
-        <v>24.904</v>
+        <v>27.1799</v>
       </c>
       <c r="D141" t="n">
-        <v>49.4144</v>
+        <v>47.455</v>
       </c>
       <c r="E141" t="n">
-        <v>32.3956</v>
+        <v>34.9685</v>
       </c>
       <c r="F141" t="n">
-        <v>31.3581</v>
+        <v>34.1814</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>38.5142</v>
+        <v>37.0314</v>
       </c>
       <c r="C142" t="n">
-        <v>25.0803</v>
+        <v>27.3922</v>
       </c>
       <c r="D142" t="n">
-        <v>50.304</v>
+        <v>48.4312</v>
       </c>
       <c r="E142" t="n">
-        <v>32.3058</v>
+        <v>35.4896</v>
       </c>
       <c r="F142" t="n">
-        <v>31.9455</v>
+        <v>34.4027</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>39.6619</v>
+        <v>37.597</v>
       </c>
       <c r="C143" t="n">
-        <v>25.1684</v>
+        <v>27.6259</v>
       </c>
       <c r="D143" t="n">
-        <v>51.3679</v>
+        <v>49.9431</v>
       </c>
       <c r="E143" t="n">
-        <v>32.394</v>
+        <v>35.8109</v>
       </c>
       <c r="F143" t="n">
-        <v>32.1384</v>
+        <v>34.8584</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Scattered successful looukp.xlsx
+++ b/clang-x64/Scattered successful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>3.50914</v>
+        <v>3.3892</v>
       </c>
       <c r="C2" t="n">
-        <v>3.28921</v>
+        <v>2.76158</v>
       </c>
       <c r="D2" t="n">
-        <v>7.53826</v>
+        <v>7.0188</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0728</v>
+        <v>3.21641</v>
       </c>
       <c r="F2" t="n">
-        <v>3.68182</v>
+        <v>3.30964</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>3.12264</v>
+        <v>3.52455</v>
       </c>
       <c r="C3" t="n">
-        <v>3.07569</v>
+        <v>2.89565</v>
       </c>
       <c r="D3" t="n">
-        <v>7.81677</v>
+        <v>7.54104</v>
       </c>
       <c r="E3" t="n">
-        <v>3.80859</v>
+        <v>3.25213</v>
       </c>
       <c r="F3" t="n">
-        <v>3.99805</v>
+        <v>3.28898</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>3.24879</v>
+        <v>3.58606</v>
       </c>
       <c r="C4" t="n">
-        <v>3.1389</v>
+        <v>2.93699</v>
       </c>
       <c r="D4" t="n">
-        <v>9.061640000000001</v>
+        <v>8.53267</v>
       </c>
       <c r="E4" t="n">
-        <v>3.82732</v>
+        <v>3.24719</v>
       </c>
       <c r="F4" t="n">
-        <v>4.03643</v>
+        <v>3.34186</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.53294</v>
+        <v>3.55291</v>
       </c>
       <c r="C5" t="n">
-        <v>3.38482</v>
+        <v>2.93182</v>
       </c>
       <c r="D5" t="n">
-        <v>9.55691</v>
+        <v>9.18154</v>
       </c>
       <c r="E5" t="n">
-        <v>4.11879</v>
+        <v>3.4131</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7658</v>
+        <v>3.30395</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>3.1909</v>
+        <v>3.48621</v>
       </c>
       <c r="C6" t="n">
-        <v>3.10785</v>
+        <v>2.89048</v>
       </c>
       <c r="D6" t="n">
-        <v>10.1929</v>
+        <v>10.1296</v>
       </c>
       <c r="E6" t="n">
-        <v>3.79723</v>
+        <v>3.53327</v>
       </c>
       <c r="F6" t="n">
-        <v>4.10943</v>
+        <v>3.42957</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>3.56578</v>
+        <v>3.54263</v>
       </c>
       <c r="C7" t="n">
-        <v>3.44751</v>
+        <v>2.92603</v>
       </c>
       <c r="D7" t="n">
-        <v>6.69215</v>
+        <v>5.86349</v>
       </c>
       <c r="E7" t="n">
-        <v>4.77961</v>
+        <v>3.4737</v>
       </c>
       <c r="F7" t="n">
-        <v>3.94963</v>
+        <v>3.46139</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>3.30728</v>
+        <v>3.53499</v>
       </c>
       <c r="C8" t="n">
-        <v>3.88597</v>
+        <v>3.18681</v>
       </c>
       <c r="D8" t="n">
-        <v>6.81991</v>
+        <v>6.32192</v>
       </c>
       <c r="E8" t="n">
-        <v>4.83102</v>
+        <v>3.48193</v>
       </c>
       <c r="F8" t="n">
-        <v>3.98013</v>
+        <v>3.48009</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>3.35585</v>
+        <v>3.57334</v>
       </c>
       <c r="C9" t="n">
-        <v>3.89317</v>
+        <v>3.19951</v>
       </c>
       <c r="D9" t="n">
-        <v>7.34504</v>
+        <v>7.02036</v>
       </c>
       <c r="E9" t="n">
-        <v>4.85739</v>
+        <v>3.52351</v>
       </c>
       <c r="F9" t="n">
-        <v>4.0202</v>
+        <v>3.51399</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>4.2444</v>
+        <v>4.04616</v>
       </c>
       <c r="C10" t="n">
-        <v>3.92976</v>
+        <v>3.22619</v>
       </c>
       <c r="D10" t="n">
-        <v>7.6638</v>
+        <v>7.52441</v>
       </c>
       <c r="E10" t="n">
-        <v>4.89434</v>
+        <v>3.60043</v>
       </c>
       <c r="F10" t="n">
-        <v>4.0587</v>
+        <v>3.55635</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>3.98287</v>
+        <v>4.06125</v>
       </c>
       <c r="C11" t="n">
-        <v>3.81154</v>
+        <v>3.24218</v>
       </c>
       <c r="D11" t="n">
-        <v>8.2555</v>
+        <v>8.03997</v>
       </c>
       <c r="E11" t="n">
-        <v>4.92794</v>
+        <v>3.69502</v>
       </c>
       <c r="F11" t="n">
-        <v>4.06706</v>
+        <v>3.55464</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>3.98242</v>
+        <v>4.06536</v>
       </c>
       <c r="C12" t="n">
-        <v>3.82899</v>
+        <v>3.32371</v>
       </c>
       <c r="D12" t="n">
-        <v>8.663500000000001</v>
+        <v>8.56856</v>
       </c>
       <c r="E12" t="n">
-        <v>4.94037</v>
+        <v>3.72627</v>
       </c>
       <c r="F12" t="n">
-        <v>4.09015</v>
+        <v>3.58566</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>4.93154</v>
+        <v>4.10391</v>
       </c>
       <c r="C13" t="n">
-        <v>3.7098</v>
+        <v>3.25833</v>
       </c>
       <c r="D13" t="n">
-        <v>9.25465</v>
+        <v>9.06377</v>
       </c>
       <c r="E13" t="n">
-        <v>4.99001</v>
+        <v>3.70087</v>
       </c>
       <c r="F13" t="n">
-        <v>4.10994</v>
+        <v>3.53294</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>4.87904</v>
+        <v>4.09583</v>
       </c>
       <c r="C14" t="n">
-        <v>3.64677</v>
+        <v>3.30096</v>
       </c>
       <c r="D14" t="n">
-        <v>9.75512</v>
+        <v>9.62505</v>
       </c>
       <c r="E14" t="n">
-        <v>4.99841</v>
+        <v>3.79239</v>
       </c>
       <c r="F14" t="n">
-        <v>4.25187</v>
+        <v>3.5355</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>4.85466</v>
+        <v>4.10756</v>
       </c>
       <c r="C15" t="n">
-        <v>3.85364</v>
+        <v>3.3144</v>
       </c>
       <c r="D15" t="n">
-        <v>10.2526</v>
+        <v>10.1432</v>
       </c>
       <c r="E15" t="n">
-        <v>5.05852</v>
+        <v>3.76561</v>
       </c>
       <c r="F15" t="n">
-        <v>4.27888</v>
+        <v>3.57513</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>4.4958</v>
+        <v>4.15319</v>
       </c>
       <c r="C16" t="n">
-        <v>4.03395</v>
+        <v>3.33751</v>
       </c>
       <c r="D16" t="n">
-        <v>10.6412</v>
+        <v>10.6952</v>
       </c>
       <c r="E16" t="n">
-        <v>5.11489</v>
+        <v>3.77364</v>
       </c>
       <c r="F16" t="n">
-        <v>4.227</v>
+        <v>3.70302</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>4.12175</v>
+        <v>4.13302</v>
       </c>
       <c r="C17" t="n">
-        <v>3.99019</v>
+        <v>3.37656</v>
       </c>
       <c r="D17" t="n">
-        <v>11.1323</v>
+        <v>11.1927</v>
       </c>
       <c r="E17" t="n">
-        <v>4.89671</v>
+        <v>3.84327</v>
       </c>
       <c r="F17" t="n">
-        <v>4.48248</v>
+        <v>3.63617</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>4.92417</v>
+        <v>4.15149</v>
       </c>
       <c r="C18" t="n">
-        <v>3.75714</v>
+        <v>3.39889</v>
       </c>
       <c r="D18" t="n">
-        <v>11.5903</v>
+        <v>11.682</v>
       </c>
       <c r="E18" t="n">
-        <v>5.1917</v>
+        <v>3.80603</v>
       </c>
       <c r="F18" t="n">
-        <v>4.37672</v>
+        <v>3.78291</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>4.9176</v>
+        <v>4.2142</v>
       </c>
       <c r="C19" t="n">
-        <v>3.77966</v>
+        <v>3.42567</v>
       </c>
       <c r="D19" t="n">
-        <v>12.2312</v>
+        <v>12.2058</v>
       </c>
       <c r="E19" t="n">
-        <v>5.245</v>
+        <v>3.86517</v>
       </c>
       <c r="F19" t="n">
-        <v>4.30731</v>
+        <v>3.90616</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>4.92417</v>
+        <v>4.22658</v>
       </c>
       <c r="C20" t="n">
-        <v>3.91465</v>
+        <v>3.44864</v>
       </c>
       <c r="D20" t="n">
-        <v>12.533</v>
+        <v>12.5929</v>
       </c>
       <c r="E20" t="n">
-        <v>5.20821</v>
+        <v>3.85473</v>
       </c>
       <c r="F20" t="n">
-        <v>4.47729</v>
+        <v>4.07883</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>4.94363</v>
+        <v>4.53582</v>
       </c>
       <c r="C21" t="n">
-        <v>3.95448</v>
+        <v>3.69325</v>
       </c>
       <c r="D21" t="n">
-        <v>8.69083</v>
+        <v>8.668509999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>4.85839</v>
+        <v>3.87362</v>
       </c>
       <c r="F21" t="n">
-        <v>4.9114</v>
+        <v>3.98827</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>4.89304</v>
+        <v>4.63582</v>
       </c>
       <c r="C22" t="n">
-        <v>3.99458</v>
+        <v>3.37158</v>
       </c>
       <c r="D22" t="n">
-        <v>9.114319999999999</v>
+        <v>9.01864</v>
       </c>
       <c r="E22" t="n">
-        <v>4.78815</v>
+        <v>3.84383</v>
       </c>
       <c r="F22" t="n">
-        <v>4.9259</v>
+        <v>4.01927</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>4.94587</v>
+        <v>4.66413</v>
       </c>
       <c r="C23" t="n">
-        <v>4.0073</v>
+        <v>3.17376</v>
       </c>
       <c r="D23" t="n">
-        <v>9.45354</v>
+        <v>9.405469999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>4.80372</v>
+        <v>3.87203</v>
       </c>
       <c r="F23" t="n">
-        <v>4.99567</v>
+        <v>4.19671</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>5.02627</v>
+        <v>4.6288</v>
       </c>
       <c r="C24" t="n">
-        <v>3.98242</v>
+        <v>3.38859</v>
       </c>
       <c r="D24" t="n">
-        <v>9.784660000000001</v>
+        <v>9.812049999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>4.98657</v>
+        <v>3.75901</v>
       </c>
       <c r="F24" t="n">
-        <v>4.90744</v>
+        <v>4.16029</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>5.0201</v>
+        <v>4.51637</v>
       </c>
       <c r="C25" t="n">
-        <v>4.03054</v>
+        <v>3.19165</v>
       </c>
       <c r="D25" t="n">
-        <v>10.1511</v>
+        <v>10.2241</v>
       </c>
       <c r="E25" t="n">
-        <v>4.90528</v>
+        <v>3.80129</v>
       </c>
       <c r="F25" t="n">
-        <v>5.0202</v>
+        <v>4.2107</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>4.72015</v>
+        <v>4.74474</v>
       </c>
       <c r="C26" t="n">
-        <v>3.99155</v>
+        <v>3.33432</v>
       </c>
       <c r="D26" t="n">
-        <v>10.5697</v>
+        <v>10.4814</v>
       </c>
       <c r="E26" t="n">
-        <v>5.10714</v>
+        <v>3.85515</v>
       </c>
       <c r="F26" t="n">
-        <v>4.82539</v>
+        <v>4.15954</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>5.03112</v>
+        <v>4.41192</v>
       </c>
       <c r="C27" t="n">
-        <v>4.04759</v>
+        <v>3.20837</v>
       </c>
       <c r="D27" t="n">
-        <v>11.0794</v>
+        <v>10.8862</v>
       </c>
       <c r="E27" t="n">
-        <v>5.03466</v>
+        <v>3.99947</v>
       </c>
       <c r="F27" t="n">
-        <v>4.8549</v>
+        <v>4.20693</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>5.03822</v>
+        <v>4.72214</v>
       </c>
       <c r="C28" t="n">
-        <v>4.09676</v>
+        <v>3.22458</v>
       </c>
       <c r="D28" t="n">
-        <v>11.453</v>
+        <v>11.3403</v>
       </c>
       <c r="E28" t="n">
-        <v>5.17706</v>
+        <v>3.95941</v>
       </c>
       <c r="F28" t="n">
-        <v>4.87121</v>
+        <v>4.16541</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>4.64555</v>
+        <v>4.46698</v>
       </c>
       <c r="C29" t="n">
-        <v>4.13176</v>
+        <v>3.36992</v>
       </c>
       <c r="D29" t="n">
-        <v>11.8689</v>
+        <v>11.8449</v>
       </c>
       <c r="E29" t="n">
-        <v>5.22578</v>
+        <v>4.08352</v>
       </c>
       <c r="F29" t="n">
-        <v>4.89448</v>
+        <v>4.19879</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>4.71872</v>
+        <v>4.7716</v>
       </c>
       <c r="C30" t="n">
-        <v>4.13929</v>
+        <v>3.28502</v>
       </c>
       <c r="D30" t="n">
-        <v>12.2594</v>
+        <v>12.1501</v>
       </c>
       <c r="E30" t="n">
-        <v>5.19647</v>
+        <v>4.06173</v>
       </c>
       <c r="F30" t="n">
-        <v>5.06082</v>
+        <v>4.31728</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>4.75719</v>
+        <v>4.32593</v>
       </c>
       <c r="C31" t="n">
-        <v>4.11048</v>
+        <v>3.36921</v>
       </c>
       <c r="D31" t="n">
-        <v>12.618</v>
+        <v>12.5959</v>
       </c>
       <c r="E31" t="n">
-        <v>5.2187</v>
+        <v>4.15881</v>
       </c>
       <c r="F31" t="n">
-        <v>5.15936</v>
+        <v>4.29602</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>4.77117</v>
+        <v>4.82225</v>
       </c>
       <c r="C32" t="n">
-        <v>4.17664</v>
+        <v>3.36395</v>
       </c>
       <c r="D32" t="n">
-        <v>12.9941</v>
+        <v>12.9356</v>
       </c>
       <c r="E32" t="n">
-        <v>5.28882</v>
+        <v>4.20531</v>
       </c>
       <c r="F32" t="n">
-        <v>5.35295</v>
+        <v>4.41185</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.77785</v>
+        <v>4.62908</v>
       </c>
       <c r="C33" t="n">
-        <v>4.02662</v>
+        <v>3.39806</v>
       </c>
       <c r="D33" t="n">
-        <v>13.4293</v>
+        <v>13.3451</v>
       </c>
       <c r="E33" t="n">
-        <v>5.33273</v>
+        <v>4.10304</v>
       </c>
       <c r="F33" t="n">
-        <v>5.01319</v>
+        <v>4.41649</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>4.63155</v>
+        <v>4.594</v>
       </c>
       <c r="C34" t="n">
-        <v>4.2224</v>
+        <v>3.41397</v>
       </c>
       <c r="D34" t="n">
-        <v>13.9041</v>
+        <v>13.77</v>
       </c>
       <c r="E34" t="n">
-        <v>5.45705</v>
+        <v>3.95497</v>
       </c>
       <c r="F34" t="n">
-        <v>5.36788</v>
+        <v>4.07328</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>4.82066</v>
+        <v>4.43165</v>
       </c>
       <c r="C35" t="n">
-        <v>4.38339</v>
+        <v>3.4335</v>
       </c>
       <c r="D35" t="n">
-        <v>9.530239999999999</v>
+        <v>9.31902</v>
       </c>
       <c r="E35" t="n">
-        <v>4.91903</v>
+        <v>4.13591</v>
       </c>
       <c r="F35" t="n">
-        <v>4.80907</v>
+        <v>4.16872</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>4.80222</v>
+        <v>4.55758</v>
       </c>
       <c r="C36" t="n">
-        <v>4.45978</v>
+        <v>3.56196</v>
       </c>
       <c r="D36" t="n">
-        <v>9.903729999999999</v>
+        <v>9.53637</v>
       </c>
       <c r="E36" t="n">
-        <v>4.8918</v>
+        <v>4.11197</v>
       </c>
       <c r="F36" t="n">
-        <v>4.84825</v>
+        <v>4.171</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>5.52141</v>
+        <v>5.13904</v>
       </c>
       <c r="C37" t="n">
-        <v>4.05331</v>
+        <v>3.76462</v>
       </c>
       <c r="D37" t="n">
-        <v>10.1798</v>
+        <v>9.77205</v>
       </c>
       <c r="E37" t="n">
-        <v>5.01162</v>
+        <v>4.14591</v>
       </c>
       <c r="F37" t="n">
-        <v>4.89862</v>
+        <v>4.16707</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>5.12072</v>
+        <v>4.62747</v>
       </c>
       <c r="C38" t="n">
-        <v>3.97979</v>
+        <v>3.51241</v>
       </c>
       <c r="D38" t="n">
-        <v>10.5987</v>
+        <v>10.0904</v>
       </c>
       <c r="E38" t="n">
-        <v>5.05286</v>
+        <v>4.00877</v>
       </c>
       <c r="F38" t="n">
-        <v>4.90789</v>
+        <v>4.20959</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>4.92896</v>
+        <v>4.64916</v>
       </c>
       <c r="C39" t="n">
-        <v>4.34517</v>
+        <v>3.91477</v>
       </c>
       <c r="D39" t="n">
-        <v>10.9217</v>
+        <v>10.4394</v>
       </c>
       <c r="E39" t="n">
-        <v>5.2632</v>
+        <v>4.04886</v>
       </c>
       <c r="F39" t="n">
-        <v>4.87596</v>
+        <v>4.22645</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>4.91063</v>
+        <v>4.70514</v>
       </c>
       <c r="C40" t="n">
-        <v>4.26926</v>
+        <v>3.79083</v>
       </c>
       <c r="D40" t="n">
-        <v>11.4444</v>
+        <v>10.7471</v>
       </c>
       <c r="E40" t="n">
-        <v>5.30429</v>
+        <v>4.17862</v>
       </c>
       <c r="F40" t="n">
-        <v>4.9405</v>
+        <v>4.34289</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>4.83225</v>
+        <v>4.68286</v>
       </c>
       <c r="C41" t="n">
-        <v>4.28702</v>
+        <v>3.7449</v>
       </c>
       <c r="D41" t="n">
-        <v>11.9759</v>
+        <v>11.0814</v>
       </c>
       <c r="E41" t="n">
-        <v>5.32765</v>
+        <v>4.18179</v>
       </c>
       <c r="F41" t="n">
-        <v>5.15223</v>
+        <v>4.37431</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>4.94979</v>
+        <v>4.65082</v>
       </c>
       <c r="C42" t="n">
-        <v>4.39498</v>
+        <v>4.04869</v>
       </c>
       <c r="D42" t="n">
-        <v>12.5649</v>
+        <v>11.466</v>
       </c>
       <c r="E42" t="n">
-        <v>5.34177</v>
+        <v>4.39958</v>
       </c>
       <c r="F42" t="n">
-        <v>5.05472</v>
+        <v>4.45531</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>4.972</v>
+        <v>4.6531</v>
       </c>
       <c r="C43" t="n">
-        <v>4.43773</v>
+        <v>4.05362</v>
       </c>
       <c r="D43" t="n">
-        <v>12.7051</v>
+        <v>11.8635</v>
       </c>
       <c r="E43" t="n">
-        <v>5.21035</v>
+        <v>4.4385</v>
       </c>
       <c r="F43" t="n">
-        <v>5.09973</v>
+        <v>4.38384</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>4.96312</v>
+        <v>4.69391</v>
       </c>
       <c r="C44" t="n">
-        <v>4.42869</v>
+        <v>4.03971</v>
       </c>
       <c r="D44" t="n">
-        <v>13.2244</v>
+        <v>12.2532</v>
       </c>
       <c r="E44" t="n">
-        <v>5.28829</v>
+        <v>4.46801</v>
       </c>
       <c r="F44" t="n">
-        <v>5.22898</v>
+        <v>4.5536</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>5.07169</v>
+        <v>4.74566</v>
       </c>
       <c r="C45" t="n">
-        <v>4.38826</v>
+        <v>3.98097</v>
       </c>
       <c r="D45" t="n">
-        <v>13.6727</v>
+        <v>12.6442</v>
       </c>
       <c r="E45" t="n">
-        <v>5.32496</v>
+        <v>4.67344</v>
       </c>
       <c r="F45" t="n">
-        <v>5.29888</v>
+        <v>4.53367</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.96246</v>
+        <v>4.98989</v>
       </c>
       <c r="C46" t="n">
-        <v>4.52624</v>
+        <v>4.33249</v>
       </c>
       <c r="D46" t="n">
-        <v>13.9533</v>
+        <v>13.0231</v>
       </c>
       <c r="E46" t="n">
-        <v>5.58894</v>
+        <v>4.77517</v>
       </c>
       <c r="F46" t="n">
-        <v>5.38366</v>
+        <v>4.60436</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.97913</v>
+        <v>4.79598</v>
       </c>
       <c r="C47" t="n">
-        <v>4.54874</v>
+        <v>4.09218</v>
       </c>
       <c r="D47" t="n">
-        <v>14.3551</v>
+        <v>13.3483</v>
       </c>
       <c r="E47" t="n">
-        <v>5.56237</v>
+        <v>4.9133</v>
       </c>
       <c r="F47" t="n">
-        <v>5.74695</v>
+        <v>4.75417</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>4.66573</v>
+        <v>4.91727</v>
       </c>
       <c r="C48" t="n">
-        <v>4.612</v>
+        <v>4.28678</v>
       </c>
       <c r="D48" t="n">
-        <v>14.6916</v>
+        <v>13.8329</v>
       </c>
       <c r="E48" t="n">
-        <v>5.99291</v>
+        <v>4.47266</v>
       </c>
       <c r="F48" t="n">
-        <v>6.02667</v>
+        <v>4.51318</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>4.95208</v>
+        <v>5.0924</v>
       </c>
       <c r="C49" t="n">
-        <v>4.72952</v>
+        <v>4.52182</v>
       </c>
       <c r="D49" t="n">
-        <v>15.4878</v>
+        <v>14.1221</v>
       </c>
       <c r="E49" t="n">
-        <v>6.32987</v>
+        <v>4.32443</v>
       </c>
       <c r="F49" t="n">
-        <v>6.53559</v>
+        <v>4.47888</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>5.20146</v>
+        <v>5.07977</v>
       </c>
       <c r="C50" t="n">
-        <v>4.82645</v>
+        <v>3.94809</v>
       </c>
       <c r="D50" t="n">
-        <v>11.8674</v>
+        <v>9.97847</v>
       </c>
       <c r="E50" t="n">
-        <v>5.19334</v>
+        <v>4.36937</v>
       </c>
       <c r="F50" t="n">
-        <v>6.1628</v>
+        <v>4.57452</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>6.01964</v>
+        <v>5.56236</v>
       </c>
       <c r="C51" t="n">
-        <v>4.13423</v>
+        <v>3.65905</v>
       </c>
       <c r="D51" t="n">
-        <v>12.1769</v>
+        <v>10.3311</v>
       </c>
       <c r="E51" t="n">
-        <v>5.00406</v>
+        <v>4.35791</v>
       </c>
       <c r="F51" t="n">
-        <v>5.85473</v>
+        <v>4.69366</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>6.16114</v>
+        <v>6.15997</v>
       </c>
       <c r="C52" t="n">
-        <v>4.05133</v>
+        <v>3.73361</v>
       </c>
       <c r="D52" t="n">
-        <v>13.9887</v>
+        <v>10.676</v>
       </c>
       <c r="E52" t="n">
-        <v>5.22427</v>
+        <v>4.39551</v>
       </c>
       <c r="F52" t="n">
-        <v>6.49545</v>
+        <v>4.67788</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>5.14975</v>
+        <v>5.48238</v>
       </c>
       <c r="C53" t="n">
-        <v>4.1674</v>
+        <v>3.68933</v>
       </c>
       <c r="D53" t="n">
-        <v>14.8894</v>
+        <v>11.2609</v>
       </c>
       <c r="E53" t="n">
-        <v>5.24633</v>
+        <v>4.53487</v>
       </c>
       <c r="F53" t="n">
-        <v>6.50984</v>
+        <v>4.44464</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>5.12413</v>
+        <v>5.44048</v>
       </c>
       <c r="C54" t="n">
-        <v>4.18946</v>
+        <v>3.91265</v>
       </c>
       <c r="D54" t="n">
-        <v>15.8705</v>
+        <v>11.6013</v>
       </c>
       <c r="E54" t="n">
-        <v>5.3184</v>
+        <v>4.44397</v>
       </c>
       <c r="F54" t="n">
-        <v>6.3</v>
+        <v>4.60403</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>5.44697</v>
+        <v>5.49556</v>
       </c>
       <c r="C55" t="n">
-        <v>4.18448</v>
+        <v>3.7765</v>
       </c>
       <c r="D55" t="n">
-        <v>16.7264</v>
+        <v>12.2156</v>
       </c>
       <c r="E55" t="n">
-        <v>5.38118</v>
+        <v>4.6383</v>
       </c>
       <c r="F55" t="n">
-        <v>5.72767</v>
+        <v>4.65017</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>5.17129</v>
+        <v>5.55541</v>
       </c>
       <c r="C56" t="n">
-        <v>4.20673</v>
+        <v>3.73534</v>
       </c>
       <c r="D56" t="n">
-        <v>17.8128</v>
+        <v>12.8543</v>
       </c>
       <c r="E56" t="n">
-        <v>5.26509</v>
+        <v>4.53274</v>
       </c>
       <c r="F56" t="n">
-        <v>6.11975</v>
+        <v>4.66663</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>5.14661</v>
+        <v>5.61926</v>
       </c>
       <c r="C57" t="n">
-        <v>4.23527</v>
+        <v>3.76981</v>
       </c>
       <c r="D57" t="n">
-        <v>19.2716</v>
+        <v>13.308</v>
       </c>
       <c r="E57" t="n">
-        <v>5.43383</v>
+        <v>4.63771</v>
       </c>
       <c r="F57" t="n">
-        <v>6.7497</v>
+        <v>4.76169</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>5.1988</v>
+        <v>5.35488</v>
       </c>
       <c r="C58" t="n">
-        <v>4.28167</v>
+        <v>3.81829</v>
       </c>
       <c r="D58" t="n">
-        <v>19.481</v>
+        <v>13.7094</v>
       </c>
       <c r="E58" t="n">
-        <v>5.48817</v>
+        <v>4.70224</v>
       </c>
       <c r="F58" t="n">
-        <v>5.95997</v>
+        <v>4.85108</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>5.22236</v>
+        <v>5.41654</v>
       </c>
       <c r="C59" t="n">
-        <v>4.33223</v>
+        <v>3.92858</v>
       </c>
       <c r="D59" t="n">
-        <v>19.1429</v>
+        <v>14.259</v>
       </c>
       <c r="E59" t="n">
-        <v>5.50724</v>
+        <v>4.79043</v>
       </c>
       <c r="F59" t="n">
-        <v>7.19081</v>
+        <v>4.95951</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>5.24142</v>
+        <v>5.71619</v>
       </c>
       <c r="C60" t="n">
-        <v>4.32563</v>
+        <v>3.88926</v>
       </c>
       <c r="D60" t="n">
-        <v>20.4837</v>
+        <v>14.9463</v>
       </c>
       <c r="E60" t="n">
-        <v>5.71004</v>
+        <v>4.87813</v>
       </c>
       <c r="F60" t="n">
-        <v>6.29084</v>
+        <v>5.48425</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>5.29568</v>
+        <v>5.48913</v>
       </c>
       <c r="C61" t="n">
-        <v>4.43704</v>
+        <v>4.00367</v>
       </c>
       <c r="D61" t="n">
-        <v>20.8686</v>
+        <v>15.8636</v>
       </c>
       <c r="E61" t="n">
-        <v>5.86922</v>
+        <v>5.05215</v>
       </c>
       <c r="F61" t="n">
-        <v>7.21947</v>
+        <v>5.80943</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>5.27064</v>
+        <v>5.54509</v>
       </c>
       <c r="C62" t="n">
-        <v>4.41163</v>
+        <v>4.00123</v>
       </c>
       <c r="D62" t="n">
-        <v>20.9796</v>
+        <v>16.42</v>
       </c>
       <c r="E62" t="n">
-        <v>6.02391</v>
+        <v>5.25179</v>
       </c>
       <c r="F62" t="n">
-        <v>7.22003</v>
+        <v>5.96739</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>5.43547</v>
+        <v>5.83793</v>
       </c>
       <c r="C63" t="n">
-        <v>4.54388</v>
+        <v>4.13856</v>
       </c>
       <c r="D63" t="n">
-        <v>20.8278</v>
+        <v>16.657</v>
       </c>
       <c r="E63" t="n">
-        <v>6.37574</v>
+        <v>4.70498</v>
       </c>
       <c r="F63" t="n">
-        <v>7.61906</v>
+        <v>5.22308</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>5.63384</v>
+        <v>5.80767</v>
       </c>
       <c r="C64" t="n">
-        <v>4.72366</v>
+        <v>4.38242</v>
       </c>
       <c r="D64" t="n">
-        <v>15.7723</v>
+        <v>11.5212</v>
       </c>
       <c r="E64" t="n">
-        <v>6.04683</v>
+        <v>4.57535</v>
       </c>
       <c r="F64" t="n">
-        <v>6.3958</v>
+        <v>5.69492</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>5.8561</v>
+        <v>6.01008</v>
       </c>
       <c r="C65" t="n">
-        <v>7.21349</v>
+        <v>4.58703</v>
       </c>
       <c r="D65" t="n">
-        <v>14.9077</v>
+        <v>12.1646</v>
       </c>
       <c r="E65" t="n">
-        <v>6.10056</v>
+        <v>4.65248</v>
       </c>
       <c r="F65" t="n">
-        <v>6.40211</v>
+        <v>5.5503</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>6.29695</v>
+        <v>6.53285</v>
       </c>
       <c r="C66" t="n">
-        <v>7.28792</v>
+        <v>4.54057</v>
       </c>
       <c r="D66" t="n">
-        <v>16.2966</v>
+        <v>13.3904</v>
       </c>
       <c r="E66" t="n">
-        <v>6.17091</v>
+        <v>4.63657</v>
       </c>
       <c r="F66" t="n">
-        <v>6.5996</v>
+        <v>5.80095</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>8.47709</v>
+        <v>6.48252</v>
       </c>
       <c r="C67" t="n">
-        <v>7.31486</v>
+        <v>4.56927</v>
       </c>
       <c r="D67" t="n">
-        <v>17.4551</v>
+        <v>14.9003</v>
       </c>
       <c r="E67" t="n">
-        <v>6.30032</v>
+        <v>4.74679</v>
       </c>
       <c r="F67" t="n">
-        <v>6.77407</v>
+        <v>5.9723</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>8.171989999999999</v>
+        <v>6.37951</v>
       </c>
       <c r="C68" t="n">
-        <v>6.87606</v>
+        <v>4.49072</v>
       </c>
       <c r="D68" t="n">
-        <v>18.5054</v>
+        <v>15.855</v>
       </c>
       <c r="E68" t="n">
-        <v>6.3738</v>
+        <v>4.91761</v>
       </c>
       <c r="F68" t="n">
-        <v>6.88039</v>
+        <v>6.06305</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>8.45776</v>
+        <v>6.94003</v>
       </c>
       <c r="C69" t="n">
-        <v>7.22707</v>
+        <v>5.15544</v>
       </c>
       <c r="D69" t="n">
-        <v>19.3442</v>
+        <v>16.2412</v>
       </c>
       <c r="E69" t="n">
-        <v>6.51513</v>
+        <v>4.79837</v>
       </c>
       <c r="F69" t="n">
-        <v>6.95297</v>
+        <v>6.03825</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>8.15762</v>
+        <v>7.08593</v>
       </c>
       <c r="C70" t="n">
-        <v>6.91164</v>
+        <v>5.24509</v>
       </c>
       <c r="D70" t="n">
-        <v>19.4274</v>
+        <v>16.6838</v>
       </c>
       <c r="E70" t="n">
-        <v>6.73741</v>
+        <v>4.89972</v>
       </c>
       <c r="F70" t="n">
-        <v>6.96607</v>
+        <v>6.14705</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>8.17882</v>
+        <v>6.58249</v>
       </c>
       <c r="C71" t="n">
-        <v>6.84997</v>
+        <v>4.75772</v>
       </c>
       <c r="D71" t="n">
-        <v>19.3236</v>
+        <v>17.9336</v>
       </c>
       <c r="E71" t="n">
-        <v>6.62433</v>
+        <v>5.17755</v>
       </c>
       <c r="F71" t="n">
-        <v>7.85608</v>
+        <v>6.15112</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>7.43719</v>
+        <v>7.26903</v>
       </c>
       <c r="C72" t="n">
-        <v>6.20583</v>
+        <v>5.4158</v>
       </c>
       <c r="D72" t="n">
-        <v>19.9402</v>
+        <v>17.7166</v>
       </c>
       <c r="E72" t="n">
-        <v>6.7432</v>
+        <v>5.21022</v>
       </c>
       <c r="F72" t="n">
-        <v>8.01436</v>
+        <v>6.42739</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>8.785159999999999</v>
+        <v>7.21938</v>
       </c>
       <c r="C73" t="n">
-        <v>7.55392</v>
+        <v>5.32683</v>
       </c>
       <c r="D73" t="n">
-        <v>19.6175</v>
+        <v>18.7415</v>
       </c>
       <c r="E73" t="n">
-        <v>6.86662</v>
+        <v>5.31137</v>
       </c>
       <c r="F73" t="n">
-        <v>8.15996</v>
+        <v>6.54828</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>7.67334</v>
+        <v>7.18005</v>
       </c>
       <c r="C74" t="n">
-        <v>6.36725</v>
+        <v>5.29046</v>
       </c>
       <c r="D74" t="n">
-        <v>20.5683</v>
+        <v>18.8941</v>
       </c>
       <c r="E74" t="n">
-        <v>6.30342</v>
+        <v>5.31198</v>
       </c>
       <c r="F74" t="n">
-        <v>7.76215</v>
+        <v>6.859</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>7.75653</v>
+        <v>6.85846</v>
       </c>
       <c r="C75" t="n">
-        <v>6.44513</v>
+        <v>5.03262</v>
       </c>
       <c r="D75" t="n">
-        <v>21.1876</v>
+        <v>19.6682</v>
       </c>
       <c r="E75" t="n">
-        <v>6.46677</v>
+        <v>5.45067</v>
       </c>
       <c r="F75" t="n">
-        <v>7.70882</v>
+        <v>7.19709</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>7.81491</v>
+        <v>7.29741</v>
       </c>
       <c r="C76" t="n">
-        <v>6.47608</v>
+        <v>5.1915</v>
       </c>
       <c r="D76" t="n">
-        <v>21.3761</v>
+        <v>20.6826</v>
       </c>
       <c r="E76" t="n">
-        <v>6.63168</v>
+        <v>5.59437</v>
       </c>
       <c r="F76" t="n">
-        <v>8.03228</v>
+        <v>7.53615</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>7.78206</v>
+        <v>7.09547</v>
       </c>
       <c r="C77" t="n">
-        <v>6.51057</v>
+        <v>5.19514</v>
       </c>
       <c r="D77" t="n">
-        <v>22.6739</v>
+        <v>21.0663</v>
       </c>
       <c r="E77" t="n">
-        <v>6.89281</v>
+        <v>11.2084</v>
       </c>
       <c r="F77" t="n">
-        <v>9.837719999999999</v>
+        <v>10.2065</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>8.511749999999999</v>
+        <v>7.13512</v>
       </c>
       <c r="C78" t="n">
-        <v>7.13942</v>
+        <v>5.38058</v>
       </c>
       <c r="D78" t="n">
-        <v>20.0294</v>
+        <v>20.1353</v>
       </c>
       <c r="E78" t="n">
-        <v>12.6859</v>
+        <v>11.2193</v>
       </c>
       <c r="F78" t="n">
-        <v>14.0405</v>
+        <v>10.2358</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>8.22315</v>
+        <v>7.418</v>
       </c>
       <c r="C79" t="n">
-        <v>15.2971</v>
+        <v>14.3877</v>
       </c>
       <c r="D79" t="n">
-        <v>21.2681</v>
+        <v>21.7338</v>
       </c>
       <c r="E79" t="n">
-        <v>11.1829</v>
+        <v>10.5387</v>
       </c>
       <c r="F79" t="n">
-        <v>15.5165</v>
+        <v>10.2794</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>9.44689</v>
+        <v>8.080679999999999</v>
       </c>
       <c r="C80" t="n">
-        <v>16.7445</v>
+        <v>14.0373</v>
       </c>
       <c r="D80" t="n">
-        <v>22.0779</v>
+        <v>22.645</v>
       </c>
       <c r="E80" t="n">
-        <v>13.207</v>
+        <v>10.1674</v>
       </c>
       <c r="F80" t="n">
-        <v>13.9361</v>
+        <v>10.983</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>17.3617</v>
+        <v>18.2293</v>
       </c>
       <c r="C81" t="n">
-        <v>16.5999</v>
+        <v>14.8513</v>
       </c>
       <c r="D81" t="n">
-        <v>22.9107</v>
+        <v>23.6459</v>
       </c>
       <c r="E81" t="n">
-        <v>13.4266</v>
+        <v>10.4635</v>
       </c>
       <c r="F81" t="n">
-        <v>14.3467</v>
+        <v>11.0891</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>17.2506</v>
+        <v>18.2543</v>
       </c>
       <c r="C82" t="n">
-        <v>16.421</v>
+        <v>14.8779</v>
       </c>
       <c r="D82" t="n">
-        <v>24.1288</v>
+        <v>24.2903</v>
       </c>
       <c r="E82" t="n">
-        <v>13.6338</v>
+        <v>12.195</v>
       </c>
       <c r="F82" t="n">
-        <v>14.2674</v>
+        <v>10.7468</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>17.3353</v>
+        <v>17.991</v>
       </c>
       <c r="C83" t="n">
-        <v>16.6155</v>
+        <v>14.5811</v>
       </c>
       <c r="D83" t="n">
-        <v>24.6365</v>
+        <v>25.4154</v>
       </c>
       <c r="E83" t="n">
-        <v>13.8898</v>
+        <v>12.6507</v>
       </c>
       <c r="F83" t="n">
-        <v>14.4794</v>
+        <v>10.8971</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>17.3493</v>
+        <v>18.0481</v>
       </c>
       <c r="C84" t="n">
-        <v>16.5276</v>
+        <v>14.6271</v>
       </c>
       <c r="D84" t="n">
-        <v>25.7279</v>
+        <v>26.4116</v>
       </c>
       <c r="E84" t="n">
-        <v>14.1158</v>
+        <v>12.347</v>
       </c>
       <c r="F84" t="n">
-        <v>14.5321</v>
+        <v>10.8876</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>17.4076</v>
+        <v>18.5012</v>
       </c>
       <c r="C85" t="n">
-        <v>16.6504</v>
+        <v>14.993</v>
       </c>
       <c r="D85" t="n">
-        <v>27.0711</v>
+        <v>27.4198</v>
       </c>
       <c r="E85" t="n">
-        <v>13.3715</v>
+        <v>12.3074</v>
       </c>
       <c r="F85" t="n">
-        <v>12.7988</v>
+        <v>13.1997</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>17.6148</v>
+        <v>18.1119</v>
       </c>
       <c r="C86" t="n">
-        <v>16.8929</v>
+        <v>14.7234</v>
       </c>
       <c r="D86" t="n">
-        <v>28.3177</v>
+        <v>28.38</v>
       </c>
       <c r="E86" t="n">
-        <v>13.5866</v>
+        <v>12.4897</v>
       </c>
       <c r="F86" t="n">
-        <v>13.0774</v>
+        <v>13.2849</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>17.609</v>
+        <v>18.1551</v>
       </c>
       <c r="C87" t="n">
-        <v>16.865</v>
+        <v>14.7595</v>
       </c>
       <c r="D87" t="n">
-        <v>29.6848</v>
+        <v>29.0521</v>
       </c>
       <c r="E87" t="n">
-        <v>13.409</v>
+        <v>12.061</v>
       </c>
       <c r="F87" t="n">
-        <v>12.2715</v>
+        <v>11.2508</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>17.0694</v>
+        <v>18.1568</v>
       </c>
       <c r="C88" t="n">
-        <v>16.0496</v>
+        <v>14.7451</v>
       </c>
       <c r="D88" t="n">
-        <v>30.9495</v>
+        <v>30.6862</v>
       </c>
       <c r="E88" t="n">
-        <v>13.2797</v>
+        <v>11.7549</v>
       </c>
       <c r="F88" t="n">
-        <v>12.6951</v>
+        <v>14.014</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>17.5178</v>
+        <v>17.7829</v>
       </c>
       <c r="C89" t="n">
-        <v>16.6681</v>
+        <v>14.3839</v>
       </c>
       <c r="D89" t="n">
-        <v>32.3818</v>
+        <v>31.424</v>
       </c>
       <c r="E89" t="n">
-        <v>13.5532</v>
+        <v>11.852</v>
       </c>
       <c r="F89" t="n">
-        <v>13.0413</v>
+        <v>11.6769</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>17.1415</v>
+        <v>18.6205</v>
       </c>
       <c r="C90" t="n">
-        <v>16.0575</v>
+        <v>15.2147</v>
       </c>
       <c r="D90" t="n">
-        <v>33.0825</v>
+        <v>32.7287</v>
       </c>
       <c r="E90" t="n">
-        <v>13.8124</v>
+        <v>12.0755</v>
       </c>
       <c r="F90" t="n">
-        <v>13.1852</v>
+        <v>12.0073</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>17.0094</v>
+        <v>18.2008</v>
       </c>
       <c r="C91" t="n">
-        <v>16.0563</v>
+        <v>14.7885</v>
       </c>
       <c r="D91" t="n">
-        <v>33.9506</v>
+        <v>33.8622</v>
       </c>
       <c r="E91" t="n">
-        <v>14.1247</v>
+        <v>17.6001</v>
       </c>
       <c r="F91" t="n">
-        <v>13.6115</v>
+        <v>17.9513</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>17.2124</v>
+        <v>18.2714</v>
       </c>
       <c r="C92" t="n">
-        <v>16.1616</v>
+        <v>14.9418</v>
       </c>
       <c r="D92" t="n">
-        <v>31.7088</v>
+        <v>32.0694</v>
       </c>
       <c r="E92" t="n">
-        <v>20.0479</v>
+        <v>17.685</v>
       </c>
       <c r="F92" t="n">
-        <v>20.2569</v>
+        <v>18.2825</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>17.3296</v>
+        <v>18.3643</v>
       </c>
       <c r="C93" t="n">
-        <v>16.2816</v>
+        <v>14.9663</v>
       </c>
       <c r="D93" t="n">
-        <v>32.3977</v>
+        <v>32.7774</v>
       </c>
       <c r="E93" t="n">
-        <v>20.7127</v>
+        <v>17.8605</v>
       </c>
       <c r="F93" t="n">
-        <v>20.3172</v>
+        <v>18.3038</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>17.5799</v>
+        <v>18.5881</v>
       </c>
       <c r="C94" t="n">
-        <v>20.95</v>
+        <v>18.5338</v>
       </c>
       <c r="D94" t="n">
-        <v>33.4358</v>
+        <v>33.3131</v>
       </c>
       <c r="E94" t="n">
-        <v>20.7647</v>
+        <v>17.9993</v>
       </c>
       <c r="F94" t="n">
-        <v>20.3738</v>
+        <v>18.3712</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>21.264</v>
+        <v>23.0471</v>
       </c>
       <c r="C95" t="n">
-        <v>20.8739</v>
+        <v>18.6796</v>
       </c>
       <c r="D95" t="n">
-        <v>33.7549</v>
+        <v>34.2113</v>
       </c>
       <c r="E95" t="n">
-        <v>21.2855</v>
+        <v>18.567</v>
       </c>
       <c r="F95" t="n">
-        <v>20.5198</v>
+        <v>18.5906</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>21.4761</v>
+        <v>23.0723</v>
       </c>
       <c r="C96" t="n">
-        <v>20.8879</v>
+        <v>18.8244</v>
       </c>
       <c r="D96" t="n">
-        <v>34.4142</v>
+        <v>35.2865</v>
       </c>
       <c r="E96" t="n">
-        <v>21.5422</v>
+        <v>18.6836</v>
       </c>
       <c r="F96" t="n">
-        <v>20.6032</v>
+        <v>18.6979</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>21.5732</v>
+        <v>23.1051</v>
       </c>
       <c r="C97" t="n">
-        <v>20.93</v>
+        <v>18.7244</v>
       </c>
       <c r="D97" t="n">
-        <v>35.5314</v>
+        <v>36.1549</v>
       </c>
       <c r="E97" t="n">
-        <v>21.7261</v>
+        <v>18.7843</v>
       </c>
       <c r="F97" t="n">
-        <v>20.7149</v>
+        <v>18.8662</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>21.5288</v>
+        <v>23.0533</v>
       </c>
       <c r="C98" t="n">
-        <v>20.9603</v>
+        <v>18.7357</v>
       </c>
       <c r="D98" t="n">
-        <v>36.1867</v>
+        <v>37.0491</v>
       </c>
       <c r="E98" t="n">
-        <v>21.9051</v>
+        <v>18.9167</v>
       </c>
       <c r="F98" t="n">
-        <v>20.9015</v>
+        <v>18.6321</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>21.5805</v>
+        <v>23.1254</v>
       </c>
       <c r="C99" t="n">
-        <v>20.9746</v>
+        <v>18.7542</v>
       </c>
       <c r="D99" t="n">
-        <v>37.27</v>
+        <v>38.3548</v>
       </c>
       <c r="E99" t="n">
-        <v>22.0796</v>
+        <v>19.058</v>
       </c>
       <c r="F99" t="n">
-        <v>20.9917</v>
+        <v>18.8945</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>21.4097</v>
+        <v>23.0679</v>
       </c>
       <c r="C100" t="n">
-        <v>21.0203</v>
+        <v>18.7982</v>
       </c>
       <c r="D100" t="n">
-        <v>38.6015</v>
+        <v>39.1623</v>
       </c>
       <c r="E100" t="n">
-        <v>22.2572</v>
+        <v>19.2235</v>
       </c>
       <c r="F100" t="n">
-        <v>21.1596</v>
+        <v>18.9767</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>21.5952</v>
+        <v>23.0846</v>
       </c>
       <c r="C101" t="n">
-        <v>21.0605</v>
+        <v>18.7918</v>
       </c>
       <c r="D101" t="n">
-        <v>39.6024</v>
+        <v>39.9994</v>
       </c>
       <c r="E101" t="n">
-        <v>22.4678</v>
+        <v>19.3405</v>
       </c>
       <c r="F101" t="n">
-        <v>21.2953</v>
+        <v>19.3205</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>21.6224</v>
+        <v>23.135</v>
       </c>
       <c r="C102" t="n">
-        <v>21.1153</v>
+        <v>18.8487</v>
       </c>
       <c r="D102" t="n">
-        <v>40.2399</v>
+        <v>41.0949</v>
       </c>
       <c r="E102" t="n">
-        <v>22.7183</v>
+        <v>19.5568</v>
       </c>
       <c r="F102" t="n">
-        <v>21.4962</v>
+        <v>19.4131</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>21.6385</v>
+        <v>23.1571</v>
       </c>
       <c r="C103" t="n">
-        <v>21.1415</v>
+        <v>18.8678</v>
       </c>
       <c r="D103" t="n">
-        <v>41.2099</v>
+        <v>42.2868</v>
       </c>
       <c r="E103" t="n">
-        <v>22.8933</v>
+        <v>19.7611</v>
       </c>
       <c r="F103" t="n">
-        <v>21.7336</v>
+        <v>19.5712</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>21.7493</v>
+        <v>23.2753</v>
       </c>
       <c r="C104" t="n">
-        <v>21.2139</v>
+        <v>18.9557</v>
       </c>
       <c r="D104" t="n">
-        <v>42.3416</v>
+        <v>43.2862</v>
       </c>
       <c r="E104" t="n">
-        <v>23.3698</v>
+        <v>20.1785</v>
       </c>
       <c r="F104" t="n">
-        <v>22.9365</v>
+        <v>19.9037</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>21.6582</v>
+        <v>23.3474</v>
       </c>
       <c r="C105" t="n">
-        <v>21.3037</v>
+        <v>19.0446</v>
       </c>
       <c r="D105" t="n">
-        <v>44.1627</v>
+        <v>44.6012</v>
       </c>
       <c r="E105" t="n">
-        <v>23.4451</v>
+        <v>22.6342</v>
       </c>
       <c r="F105" t="n">
-        <v>23.1997</v>
+        <v>22.3749</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>21.9168</v>
+        <v>23.3807</v>
       </c>
       <c r="C106" t="n">
-        <v>21.439</v>
+        <v>19.1548</v>
       </c>
       <c r="D106" t="n">
-        <v>45.1909</v>
+        <v>45.165</v>
       </c>
       <c r="E106" t="n">
-        <v>23.7764</v>
+        <v>22.8497</v>
       </c>
       <c r="F106" t="n">
-        <v>22.7392</v>
+        <v>22.948</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>22.1866</v>
+        <v>23.565</v>
       </c>
       <c r="C107" t="n">
-        <v>21.5437</v>
+        <v>19.3687</v>
       </c>
       <c r="D107" t="n">
-        <v>38.4719</v>
+        <v>38.8617</v>
       </c>
       <c r="E107" t="n">
-        <v>26.815</v>
+        <v>22.9264</v>
       </c>
       <c r="F107" t="n">
-        <v>25.479</v>
+        <v>22.7733</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>22.4488</v>
+        <v>23.8462</v>
       </c>
       <c r="C108" t="n">
-        <v>22.4739</v>
+        <v>20.0205</v>
       </c>
       <c r="D108" t="n">
-        <v>39.0159</v>
+        <v>39.5032</v>
       </c>
       <c r="E108" t="n">
-        <v>27.2669</v>
+        <v>22.787</v>
       </c>
       <c r="F108" t="n">
-        <v>26.1108</v>
+        <v>22.9559</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>23.0385</v>
+        <v>24.2809</v>
       </c>
       <c r="C109" t="n">
-        <v>22.8212</v>
+        <v>20.1397</v>
       </c>
       <c r="D109" t="n">
-        <v>39.7839</v>
+        <v>40.414</v>
       </c>
       <c r="E109" t="n">
-        <v>27.3081</v>
+        <v>23.6102</v>
       </c>
       <c r="F109" t="n">
-        <v>25.8662</v>
+        <v>23.1694</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>24.747</v>
+        <v>25.8186</v>
       </c>
       <c r="C110" t="n">
-        <v>22.7633</v>
+        <v>20.2009</v>
       </c>
       <c r="D110" t="n">
-        <v>40.7656</v>
+        <v>40.8227</v>
       </c>
       <c r="E110" t="n">
-        <v>27.6922</v>
+        <v>23.6808</v>
       </c>
       <c r="F110" t="n">
-        <v>26.2875</v>
+        <v>23.2715</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>24.8149</v>
+        <v>26.1902</v>
       </c>
       <c r="C111" t="n">
-        <v>22.8029</v>
+        <v>20.2257</v>
       </c>
       <c r="D111" t="n">
-        <v>41.486</v>
+        <v>41.9459</v>
       </c>
       <c r="E111" t="n">
-        <v>27.791</v>
+        <v>24.0877</v>
       </c>
       <c r="F111" t="n">
-        <v>26.3842</v>
+        <v>23.7688</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>24.8091</v>
+        <v>26.2105</v>
       </c>
       <c r="C112" t="n">
-        <v>22.8635</v>
+        <v>20.2757</v>
       </c>
       <c r="D112" t="n">
-        <v>42.3794</v>
+        <v>42.9624</v>
       </c>
       <c r="E112" t="n">
-        <v>28.151</v>
+        <v>24.1717</v>
       </c>
       <c r="F112" t="n">
-        <v>26.805</v>
+        <v>23.8859</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>24.8204</v>
+        <v>26.2158</v>
       </c>
       <c r="C113" t="n">
-        <v>22.9684</v>
+        <v>20.3786</v>
       </c>
       <c r="D113" t="n">
-        <v>43.2616</v>
+        <v>43.8469</v>
       </c>
       <c r="E113" t="n">
-        <v>28.4141</v>
+        <v>24.3563</v>
       </c>
       <c r="F113" t="n">
-        <v>27.0799</v>
+        <v>24.1517</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>24.7975</v>
+        <v>26.1584</v>
       </c>
       <c r="C114" t="n">
-        <v>23.0391</v>
+        <v>20.394</v>
       </c>
       <c r="D114" t="n">
-        <v>44.3201</v>
+        <v>44.6487</v>
       </c>
       <c r="E114" t="n">
-        <v>28.6903</v>
+        <v>24.6316</v>
       </c>
       <c r="F114" t="n">
-        <v>27.3094</v>
+        <v>24.3292</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>24.9197</v>
+        <v>26.3163</v>
       </c>
       <c r="C115" t="n">
-        <v>23.0875</v>
+        <v>20.4639</v>
       </c>
       <c r="D115" t="n">
-        <v>45.2676</v>
+        <v>45.6806</v>
       </c>
       <c r="E115" t="n">
-        <v>28.9822</v>
+        <v>24.8523</v>
       </c>
       <c r="F115" t="n">
-        <v>27.5954</v>
+        <v>24.6825</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>24.9202</v>
+        <v>26.3531</v>
       </c>
       <c r="C116" t="n">
-        <v>23.2277</v>
+        <v>20.5704</v>
       </c>
       <c r="D116" t="n">
-        <v>46.1543</v>
+        <v>46.7409</v>
       </c>
       <c r="E116" t="n">
-        <v>29.1456</v>
+        <v>25.1098</v>
       </c>
       <c r="F116" t="n">
-        <v>27.9111</v>
+        <v>25.0487</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>24.7771</v>
+        <v>26.3886</v>
       </c>
       <c r="C117" t="n">
-        <v>23.281</v>
+        <v>20.6705</v>
       </c>
       <c r="D117" t="n">
-        <v>47.2076</v>
+        <v>47.7211</v>
       </c>
       <c r="E117" t="n">
-        <v>29.3694</v>
+        <v>25.3756</v>
       </c>
       <c r="F117" t="n">
-        <v>27.99</v>
+        <v>25.4924</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>24.9055</v>
+        <v>26.5198</v>
       </c>
       <c r="C118" t="n">
-        <v>23.4263</v>
+        <v>20.8411</v>
       </c>
       <c r="D118" t="n">
-        <v>48.7935</v>
+        <v>48.9008</v>
       </c>
       <c r="E118" t="n">
-        <v>29.8086</v>
+        <v>25.7795</v>
       </c>
       <c r="F118" t="n">
-        <v>28.7485</v>
+        <v>25.661</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>24.9831</v>
+        <v>26.5342</v>
       </c>
       <c r="C119" t="n">
-        <v>23.6027</v>
+        <v>20.9898</v>
       </c>
       <c r="D119" t="n">
-        <v>49.7663</v>
+        <v>50.335</v>
       </c>
       <c r="E119" t="n">
-        <v>30.253</v>
+        <v>26.6343</v>
       </c>
       <c r="F119" t="n">
-        <v>29.368</v>
+        <v>26.3026</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>24.974</v>
+        <v>26.3919</v>
       </c>
       <c r="C120" t="n">
-        <v>23.7579</v>
+        <v>21.216</v>
       </c>
       <c r="D120" t="n">
-        <v>50.3487</v>
+        <v>51.2362</v>
       </c>
       <c r="E120" t="n">
-        <v>30.7043</v>
+        <v>26.9363</v>
       </c>
       <c r="F120" t="n">
-        <v>30.147</v>
+        <v>26.837</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>25.3556</v>
+        <v>26.8782</v>
       </c>
       <c r="C121" t="n">
-        <v>24.0289</v>
+        <v>21.4641</v>
       </c>
       <c r="D121" t="n">
-        <v>41.3818</v>
+        <v>41.8947</v>
       </c>
       <c r="E121" t="n">
-        <v>31.176</v>
+        <v>27.1283</v>
       </c>
       <c r="F121" t="n">
-        <v>29.7173</v>
+        <v>26.7988</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>25.532</v>
+        <v>27.0981</v>
       </c>
       <c r="C122" t="n">
-        <v>24.5749</v>
+        <v>21.9743</v>
       </c>
       <c r="D122" t="n">
-        <v>42</v>
+        <v>42.911</v>
       </c>
       <c r="E122" t="n">
-        <v>31.2843</v>
+        <v>27.4818</v>
       </c>
       <c r="F122" t="n">
-        <v>30.2552</v>
+        <v>27.2084</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>25.8646</v>
+        <v>27.3963</v>
       </c>
       <c r="C123" t="n">
-        <v>24.6487</v>
+        <v>22.0827</v>
       </c>
       <c r="D123" t="n">
-        <v>43.4104</v>
+        <v>43.3094</v>
       </c>
       <c r="E123" t="n">
-        <v>31.7668</v>
+        <v>27.6213</v>
       </c>
       <c r="F123" t="n">
-        <v>30.5041</v>
+        <v>27.376</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>32.222</v>
+        <v>33.817</v>
       </c>
       <c r="C124" t="n">
-        <v>24.7353</v>
+        <v>22.1758</v>
       </c>
       <c r="D124" t="n">
-        <v>43.9616</v>
+        <v>44.0503</v>
       </c>
       <c r="E124" t="n">
-        <v>32.029</v>
+        <v>27.9922</v>
       </c>
       <c r="F124" t="n">
-        <v>30.693</v>
+        <v>27.6328</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>32.19</v>
+        <v>33.8391</v>
       </c>
       <c r="C125" t="n">
-        <v>24.8434</v>
+        <v>22.277</v>
       </c>
       <c r="D125" t="n">
-        <v>44.1714</v>
+        <v>44.6192</v>
       </c>
       <c r="E125" t="n">
-        <v>32.1817</v>
+        <v>28.2382</v>
       </c>
       <c r="F125" t="n">
-        <v>30.8049</v>
+        <v>27.8899</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>31.5055</v>
+        <v>32.9386</v>
       </c>
       <c r="C126" t="n">
-        <v>24.9922</v>
+        <v>22.427</v>
       </c>
       <c r="D126" t="n">
-        <v>45.2457</v>
+        <v>45.9701</v>
       </c>
       <c r="E126" t="n">
-        <v>32.518</v>
+        <v>28.5728</v>
       </c>
       <c r="F126" t="n">
-        <v>31.2169</v>
+        <v>27.991</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>32.101</v>
+        <v>33.5877</v>
       </c>
       <c r="C127" t="n">
-        <v>25.1645</v>
+        <v>22.5331</v>
       </c>
       <c r="D127" t="n">
-        <v>45.9805</v>
+        <v>46.1715</v>
       </c>
       <c r="E127" t="n">
-        <v>32.882</v>
+        <v>28.7927</v>
       </c>
       <c r="F127" t="n">
-        <v>31.5169</v>
+        <v>28.4368</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>32.2581</v>
+        <v>33.858</v>
       </c>
       <c r="C128" t="n">
-        <v>25.2825</v>
+        <v>22.6853</v>
       </c>
       <c r="D128" t="n">
-        <v>47.0605</v>
+        <v>47.8274</v>
       </c>
       <c r="E128" t="n">
-        <v>33.186</v>
+        <v>29.0221</v>
       </c>
       <c r="F128" t="n">
-        <v>31.7251</v>
+        <v>28.5708</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>32.1973</v>
+        <v>33.6884</v>
       </c>
       <c r="C129" t="n">
-        <v>25.4321</v>
+        <v>22.8453</v>
       </c>
       <c r="D129" t="n">
-        <v>48.1635</v>
+        <v>48.7474</v>
       </c>
       <c r="E129" t="n">
-        <v>33.483</v>
+        <v>29.2379</v>
       </c>
       <c r="F129" t="n">
-        <v>32.2017</v>
+        <v>29.1362</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>32.0977</v>
+        <v>33.9891</v>
       </c>
       <c r="C130" t="n">
-        <v>25.6347</v>
+        <v>23.0378</v>
       </c>
       <c r="D130" t="n">
-        <v>49.2497</v>
+        <v>49.6649</v>
       </c>
       <c r="E130" t="n">
-        <v>33.7735</v>
+        <v>29.6035</v>
       </c>
       <c r="F130" t="n">
-        <v>32.6066</v>
+        <v>29.3753</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>32.2003</v>
+        <v>33.9096</v>
       </c>
       <c r="C131" t="n">
-        <v>25.8465</v>
+        <v>23.3005</v>
       </c>
       <c r="D131" t="n">
-        <v>50.1889</v>
+        <v>51.0016</v>
       </c>
       <c r="E131" t="n">
-        <v>34.1506</v>
+        <v>29.9562</v>
       </c>
       <c r="F131" t="n">
-        <v>33.1185</v>
+        <v>29.9061</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>32.231</v>
+        <v>34.0766</v>
       </c>
       <c r="C132" t="n">
-        <v>26.1545</v>
+        <v>23.5196</v>
       </c>
       <c r="D132" t="n">
-        <v>51.3646</v>
+        <v>51.8887</v>
       </c>
       <c r="E132" t="n">
-        <v>34.5726</v>
+        <v>30.3991</v>
       </c>
       <c r="F132" t="n">
-        <v>33.6637</v>
+        <v>30.4494</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>32.3776</v>
+        <v>34.2303</v>
       </c>
       <c r="C133" t="n">
-        <v>26.4664</v>
+        <v>23.8363</v>
       </c>
       <c r="D133" t="n">
-        <v>52.2998</v>
+        <v>53.4891</v>
       </c>
       <c r="E133" t="n">
-        <v>35.1086</v>
+        <v>30.8036</v>
       </c>
       <c r="F133" t="n">
-        <v>34.3715</v>
+        <v>31.1938</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>32.3235</v>
+        <v>33.8273</v>
       </c>
       <c r="C134" t="n">
-        <v>26.7393</v>
+        <v>24.2165</v>
       </c>
       <c r="D134" t="n">
-        <v>53.8676</v>
+        <v>54.3206</v>
       </c>
       <c r="E134" t="n">
-        <v>35.704</v>
+        <v>29.2991</v>
       </c>
       <c r="F134" t="n">
-        <v>35.2097</v>
+        <v>29.3162</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>32.5002</v>
+        <v>34.2702</v>
       </c>
       <c r="C135" t="n">
-        <v>27.2581</v>
+        <v>24.6067</v>
       </c>
       <c r="D135" t="n">
-        <v>43.3362</v>
+        <v>43.2197</v>
       </c>
       <c r="E135" t="n">
-        <v>33.2916</v>
+        <v>29.5463</v>
       </c>
       <c r="F135" t="n">
-        <v>32.5939</v>
+        <v>29.6111</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>32.8583</v>
+        <v>34.5904</v>
       </c>
       <c r="C136" t="n">
-        <v>26.4772</v>
+        <v>23.9185</v>
       </c>
       <c r="D136" t="n">
-        <v>44.0165</v>
+        <v>44.4198</v>
       </c>
       <c r="E136" t="n">
-        <v>33.5886</v>
+        <v>29.8207</v>
       </c>
       <c r="F136" t="n">
-        <v>32.604</v>
+        <v>29.7277</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>32.8351</v>
+        <v>34.9658</v>
       </c>
       <c r="C137" t="n">
-        <v>26.6499</v>
+        <v>24.008</v>
       </c>
       <c r="D137" t="n">
-        <v>44.2624</v>
+        <v>45.1582</v>
       </c>
       <c r="E137" t="n">
-        <v>33.9679</v>
+        <v>30.1553</v>
       </c>
       <c r="F137" t="n">
-        <v>33.0307</v>
+        <v>29.7387</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>37.4775</v>
+        <v>39.316</v>
       </c>
       <c r="C138" t="n">
-        <v>26.7286</v>
+        <v>24.5816</v>
       </c>
       <c r="D138" t="n">
-        <v>45.7043</v>
+        <v>45.5421</v>
       </c>
       <c r="E138" t="n">
-        <v>34.2626</v>
+        <v>30.3522</v>
       </c>
       <c r="F138" t="n">
-        <v>33.1223</v>
+        <v>30.363</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>37.3888</v>
+        <v>39.3359</v>
       </c>
       <c r="C139" t="n">
-        <v>26.8631</v>
+        <v>24.7338</v>
       </c>
       <c r="D139" t="n">
-        <v>45.8135</v>
+        <v>46.0673</v>
       </c>
       <c r="E139" t="n">
-        <v>34.4278</v>
+        <v>30.6433</v>
       </c>
       <c r="F139" t="n">
-        <v>33.4844</v>
+        <v>30.4495</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>37.5294</v>
+        <v>39.3726</v>
       </c>
       <c r="C140" t="n">
-        <v>27.0954</v>
+        <v>24.8222</v>
       </c>
       <c r="D140" t="n">
-        <v>46.7355</v>
+        <v>46.967</v>
       </c>
       <c r="E140" t="n">
-        <v>34.8213</v>
+        <v>30.8995</v>
       </c>
       <c r="F140" t="n">
-        <v>33.8245</v>
+        <v>30.751</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>37.5125</v>
+        <v>39.3649</v>
       </c>
       <c r="C141" t="n">
-        <v>27.1799</v>
+        <v>25.0315</v>
       </c>
       <c r="D141" t="n">
-        <v>47.455</v>
+        <v>48.6943</v>
       </c>
       <c r="E141" t="n">
-        <v>34.9685</v>
+        <v>31.1146</v>
       </c>
       <c r="F141" t="n">
-        <v>34.1814</v>
+        <v>30.9877</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>37.0314</v>
+        <v>38.758</v>
       </c>
       <c r="C142" t="n">
-        <v>27.3922</v>
+        <v>25.2117</v>
       </c>
       <c r="D142" t="n">
-        <v>48.4312</v>
+        <v>49.6504</v>
       </c>
       <c r="E142" t="n">
-        <v>35.4896</v>
+        <v>31.4687</v>
       </c>
       <c r="F142" t="n">
-        <v>34.4027</v>
+        <v>31.1121</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>37.597</v>
+        <v>38.7789</v>
       </c>
       <c r="C143" t="n">
-        <v>27.6259</v>
+        <v>25.4025</v>
       </c>
       <c r="D143" t="n">
-        <v>49.9431</v>
+        <v>50.5036</v>
       </c>
       <c r="E143" t="n">
-        <v>35.8109</v>
+        <v>31.4498</v>
       </c>
       <c r="F143" t="n">
-        <v>34.8584</v>
+        <v>31.6685</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Scattered successful looukp.xlsx
+++ b/clang-x64/Scattered successful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>5.08765</v>
+        <v>12.2246</v>
       </c>
       <c r="C2" t="n">
-        <v>4.92265</v>
+        <v>17.0513</v>
       </c>
       <c r="D2" t="n">
-        <v>7.36635</v>
+        <v>25.2051</v>
       </c>
       <c r="E2" t="n">
-        <v>4.57181</v>
+        <v>14.1639</v>
       </c>
       <c r="F2" t="n">
-        <v>4.88283</v>
+        <v>17.009</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>4.58211</v>
+        <v>12.6524</v>
       </c>
       <c r="C3" t="n">
-        <v>4.98558</v>
+        <v>17.669</v>
       </c>
       <c r="D3" t="n">
-        <v>8.05251</v>
+        <v>25.7718</v>
       </c>
       <c r="E3" t="n">
-        <v>4.66628</v>
+        <v>14.3515</v>
       </c>
       <c r="F3" t="n">
-        <v>4.92265</v>
+        <v>17.7165</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>4.63644</v>
+        <v>12.546</v>
       </c>
       <c r="C4" t="n">
-        <v>5.08802</v>
+        <v>17.8017</v>
       </c>
       <c r="D4" t="n">
-        <v>8.93915</v>
+        <v>26.2806</v>
       </c>
       <c r="E4" t="n">
-        <v>4.60515</v>
+        <v>14.5548</v>
       </c>
       <c r="F4" t="n">
-        <v>4.76153</v>
+        <v>17.0913</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>4.65471</v>
+        <v>12.9739</v>
       </c>
       <c r="C5" t="n">
-        <v>5.06127</v>
+        <v>17.6029</v>
       </c>
       <c r="D5" t="n">
-        <v>9.65856</v>
+        <v>26.8461</v>
       </c>
       <c r="E5" t="n">
-        <v>4.61737</v>
+        <v>14.635</v>
       </c>
       <c r="F5" t="n">
-        <v>4.96204</v>
+        <v>17.5858</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>4.63073</v>
+        <v>12.817</v>
       </c>
       <c r="C6" t="n">
-        <v>5.1062</v>
+        <v>18.3159</v>
       </c>
       <c r="D6" t="n">
-        <v>10.3758</v>
+        <v>27.4259</v>
       </c>
       <c r="E6" t="n">
-        <v>4.64217</v>
+        <v>14.8374</v>
       </c>
       <c r="F6" t="n">
-        <v>5.02337</v>
+        <v>17.5974</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>4.63977</v>
+        <v>13.004</v>
       </c>
       <c r="C7" t="n">
-        <v>5.15549</v>
+        <v>18.0892</v>
       </c>
       <c r="D7" t="n">
-        <v>6.04566</v>
+        <v>24.1448</v>
       </c>
       <c r="E7" t="n">
-        <v>4.7074</v>
+        <v>15.5398</v>
       </c>
       <c r="F7" t="n">
-        <v>5.15791</v>
+        <v>18.0434</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>4.72931</v>
+        <v>13.2856</v>
       </c>
       <c r="C8" t="n">
-        <v>5.19208</v>
+        <v>17.9883</v>
       </c>
       <c r="D8" t="n">
-        <v>6.46623</v>
+        <v>24.1262</v>
       </c>
       <c r="E8" t="n">
-        <v>4.98078</v>
+        <v>15.8234</v>
       </c>
       <c r="F8" t="n">
-        <v>5.26348</v>
+        <v>18.9962</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77251</v>
+        <v>13.1217</v>
       </c>
       <c r="C9" t="n">
-        <v>5.17962</v>
+        <v>18.2457</v>
       </c>
       <c r="D9" t="n">
-        <v>6.99979</v>
+        <v>24.2378</v>
       </c>
       <c r="E9" t="n">
-        <v>4.88042</v>
+        <v>14.3527</v>
       </c>
       <c r="F9" t="n">
-        <v>4.81301</v>
+        <v>18.4926</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>5.39842</v>
+        <v>14.388</v>
       </c>
       <c r="C10" t="n">
-        <v>5.15688</v>
+        <v>19.6504</v>
       </c>
       <c r="D10" t="n">
-        <v>7.11797</v>
+        <v>25.0814</v>
       </c>
       <c r="E10" t="n">
-        <v>4.95105</v>
+        <v>15.2096</v>
       </c>
       <c r="F10" t="n">
-        <v>4.82632</v>
+        <v>18.9696</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>5.50298</v>
+        <v>14.7034</v>
       </c>
       <c r="C11" t="n">
-        <v>5.1811</v>
+        <v>20.0842</v>
       </c>
       <c r="D11" t="n">
-        <v>7.76206</v>
+        <v>25.0515</v>
       </c>
       <c r="E11" t="n">
-        <v>4.95988</v>
+        <v>14.4604</v>
       </c>
       <c r="F11" t="n">
-        <v>4.84461</v>
+        <v>18.9604</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>5.50052</v>
+        <v>13.932</v>
       </c>
       <c r="C12" t="n">
-        <v>5.20653</v>
+        <v>19.4361</v>
       </c>
       <c r="D12" t="n">
-        <v>8.35173</v>
+        <v>25.9148</v>
       </c>
       <c r="E12" t="n">
-        <v>4.98531</v>
+        <v>14.7342</v>
       </c>
       <c r="F12" t="n">
-        <v>4.86862</v>
+        <v>18.7495</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>5.4946</v>
+        <v>14.467</v>
       </c>
       <c r="C13" t="n">
-        <v>5.21133</v>
+        <v>19.3993</v>
       </c>
       <c r="D13" t="n">
-        <v>8.938370000000001</v>
+        <v>25.977</v>
       </c>
       <c r="E13" t="n">
-        <v>5.19808</v>
+        <v>14.5564</v>
       </c>
       <c r="F13" t="n">
-        <v>4.90776</v>
+        <v>18.3647</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>5.60141</v>
+        <v>14.5984</v>
       </c>
       <c r="C14" t="n">
-        <v>5.21205</v>
+        <v>19.4829</v>
       </c>
       <c r="D14" t="n">
-        <v>9.537929999999999</v>
+        <v>26.527</v>
       </c>
       <c r="E14" t="n">
-        <v>5.10355</v>
+        <v>14.7457</v>
       </c>
       <c r="F14" t="n">
-        <v>4.94648</v>
+        <v>19.134</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>5.57804</v>
+        <v>14.6598</v>
       </c>
       <c r="C15" t="n">
-        <v>5.23316</v>
+        <v>19.9591</v>
       </c>
       <c r="D15" t="n">
-        <v>9.94788</v>
+        <v>27.3652</v>
       </c>
       <c r="E15" t="n">
-        <v>5.08706</v>
+        <v>14.8729</v>
       </c>
       <c r="F15" t="n">
-        <v>4.97045</v>
+        <v>18.7509</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>5.59386</v>
+        <v>14.7052</v>
       </c>
       <c r="C16" t="n">
-        <v>5.26336</v>
+        <v>19.5729</v>
       </c>
       <c r="D16" t="n">
-        <v>10.4647</v>
+        <v>27.4572</v>
       </c>
       <c r="E16" t="n">
-        <v>5.17513</v>
+        <v>15.2148</v>
       </c>
       <c r="F16" t="n">
-        <v>5.01522</v>
+        <v>19.0951</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>5.61311</v>
+        <v>14.8912</v>
       </c>
       <c r="C17" t="n">
-        <v>5.29118</v>
+        <v>19.6166</v>
       </c>
       <c r="D17" t="n">
-        <v>10.9133</v>
+        <v>28.2825</v>
       </c>
       <c r="E17" t="n">
-        <v>5.16373</v>
+        <v>15.2477</v>
       </c>
       <c r="F17" t="n">
-        <v>5.03577</v>
+        <v>19.5945</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>5.83532</v>
+        <v>15.1101</v>
       </c>
       <c r="C18" t="n">
-        <v>5.32872</v>
+        <v>20.2596</v>
       </c>
       <c r="D18" t="n">
-        <v>11.4402</v>
+        <v>28.9862</v>
       </c>
       <c r="E18" t="n">
-        <v>5.29173</v>
+        <v>15.4004</v>
       </c>
       <c r="F18" t="n">
-        <v>5.08449</v>
+        <v>19.6821</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>5.59667</v>
+        <v>15.0716</v>
       </c>
       <c r="C19" t="n">
-        <v>5.38199</v>
+        <v>20.2129</v>
       </c>
       <c r="D19" t="n">
-        <v>11.8697</v>
+        <v>29.4335</v>
       </c>
       <c r="E19" t="n">
-        <v>5.3107</v>
+        <v>15.7521</v>
       </c>
       <c r="F19" t="n">
-        <v>5.19376</v>
+        <v>20.6507</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>5.57896</v>
+        <v>15.1828</v>
       </c>
       <c r="C20" t="n">
-        <v>5.3725</v>
+        <v>20.2154</v>
       </c>
       <c r="D20" t="n">
-        <v>12.2139</v>
+        <v>29.889</v>
       </c>
       <c r="E20" t="n">
-        <v>5.27632</v>
+        <v>15.8705</v>
       </c>
       <c r="F20" t="n">
-        <v>5.21549</v>
+        <v>20.8845</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>5.61837</v>
+        <v>15.0805</v>
       </c>
       <c r="C21" t="n">
-        <v>5.4018</v>
+        <v>20.2925</v>
       </c>
       <c r="D21" t="n">
-        <v>8.46785</v>
+        <v>25.3273</v>
       </c>
       <c r="E21" t="n">
-        <v>5.62325</v>
+        <v>16.2117</v>
       </c>
       <c r="F21" t="n">
-        <v>5.6118</v>
+        <v>19.6959</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>5.66505</v>
+        <v>15.3204</v>
       </c>
       <c r="C22" t="n">
-        <v>5.62667</v>
+        <v>20.635</v>
       </c>
       <c r="D22" t="n">
-        <v>8.82687</v>
+        <v>26.0802</v>
       </c>
       <c r="E22" t="n">
-        <v>5.94174</v>
+        <v>16.9212</v>
       </c>
       <c r="F22" t="n">
-        <v>6.21226</v>
+        <v>21.8607</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>5.73568</v>
+        <v>16.0697</v>
       </c>
       <c r="C23" t="n">
-        <v>5.97542</v>
+        <v>20.8746</v>
       </c>
       <c r="D23" t="n">
-        <v>9.21528</v>
+        <v>26.2242</v>
       </c>
       <c r="E23" t="n">
-        <v>5.50005</v>
+        <v>16.0866</v>
       </c>
       <c r="F23" t="n">
-        <v>5.51306</v>
+        <v>21.0678</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>6.01521</v>
+        <v>16.1344</v>
       </c>
       <c r="C24" t="n">
-        <v>6.0179</v>
+        <v>21.6398</v>
       </c>
       <c r="D24" t="n">
-        <v>9.558059999999999</v>
+        <v>26.8834</v>
       </c>
       <c r="E24" t="n">
-        <v>5.52828</v>
+        <v>15.825</v>
       </c>
       <c r="F24" t="n">
-        <v>5.54933</v>
+        <v>20.9484</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>6.04991</v>
+        <v>16.1443</v>
       </c>
       <c r="C25" t="n">
-        <v>6.03123</v>
+        <v>21.5597</v>
       </c>
       <c r="D25" t="n">
-        <v>9.93618</v>
+        <v>27.319</v>
       </c>
       <c r="E25" t="n">
-        <v>5.59205</v>
+        <v>16.1957</v>
       </c>
       <c r="F25" t="n">
-        <v>5.57372</v>
+        <v>20.9851</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>6.04214</v>
+        <v>16.9273</v>
       </c>
       <c r="C26" t="n">
-        <v>6.03327</v>
+        <v>21.5892</v>
       </c>
       <c r="D26" t="n">
-        <v>10.3507</v>
+        <v>27.5792</v>
       </c>
       <c r="E26" t="n">
-        <v>5.60069</v>
+        <v>16.2594</v>
       </c>
       <c r="F26" t="n">
-        <v>5.59521</v>
+        <v>21.7892</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>6.06188</v>
+        <v>16.9158</v>
       </c>
       <c r="C27" t="n">
-        <v>6.03904</v>
+        <v>21.903</v>
       </c>
       <c r="D27" t="n">
-        <v>10.7412</v>
+        <v>28.3114</v>
       </c>
       <c r="E27" t="n">
-        <v>5.67555</v>
+        <v>16.6371</v>
       </c>
       <c r="F27" t="n">
-        <v>5.61699</v>
+        <v>21.3887</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>6.08285</v>
+        <v>17.019</v>
       </c>
       <c r="C28" t="n">
-        <v>6.09346</v>
+        <v>21.9392</v>
       </c>
       <c r="D28" t="n">
-        <v>11.1435</v>
+        <v>28.7278</v>
       </c>
       <c r="E28" t="n">
-        <v>5.65063</v>
+        <v>16.7772</v>
       </c>
       <c r="F28" t="n">
-        <v>5.62894</v>
+        <v>21.8564</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>6.09766</v>
+        <v>16.2148</v>
       </c>
       <c r="C29" t="n">
-        <v>6.06648</v>
+        <v>21.6824</v>
       </c>
       <c r="D29" t="n">
-        <v>11.5154</v>
+        <v>29.0497</v>
       </c>
       <c r="E29" t="n">
-        <v>5.7989</v>
+        <v>16.5672</v>
       </c>
       <c r="F29" t="n">
-        <v>5.67287</v>
+        <v>21.4507</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>6.1138</v>
+        <v>16.9983</v>
       </c>
       <c r="C30" t="n">
-        <v>6.10295</v>
+        <v>21.4997</v>
       </c>
       <c r="D30" t="n">
-        <v>11.9141</v>
+        <v>29.5999</v>
       </c>
       <c r="E30" t="n">
-        <v>5.79513</v>
+        <v>16.6645</v>
       </c>
       <c r="F30" t="n">
-        <v>5.71038</v>
+        <v>21.3873</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>6.13901</v>
+        <v>16.9365</v>
       </c>
       <c r="C31" t="n">
-        <v>6.11881</v>
+        <v>21.3288</v>
       </c>
       <c r="D31" t="n">
-        <v>12.2853</v>
+        <v>30.1176</v>
       </c>
       <c r="E31" t="n">
-        <v>5.80221</v>
+        <v>16.4546</v>
       </c>
       <c r="F31" t="n">
-        <v>5.77847</v>
+        <v>21.7841</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>6.15276</v>
+        <v>17.0936</v>
       </c>
       <c r="C32" t="n">
-        <v>6.18786</v>
+        <v>21.8102</v>
       </c>
       <c r="D32" t="n">
-        <v>12.6122</v>
+        <v>30.9687</v>
       </c>
       <c r="E32" t="n">
-        <v>5.83629</v>
+        <v>17.6842</v>
       </c>
       <c r="F32" t="n">
-        <v>5.83382</v>
+        <v>22.1728</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>6.18048</v>
+        <v>17.1069</v>
       </c>
       <c r="C33" t="n">
-        <v>6.2145</v>
+        <v>21.9175</v>
       </c>
       <c r="D33" t="n">
-        <v>12.9874</v>
+        <v>31.5484</v>
       </c>
       <c r="E33" t="n">
-        <v>5.90417</v>
+        <v>17.0682</v>
       </c>
       <c r="F33" t="n">
-        <v>5.89927</v>
+        <v>22.7309</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>6.21944</v>
+        <v>17.1961</v>
       </c>
       <c r="C34" t="n">
-        <v>6.2203</v>
+        <v>22.5181</v>
       </c>
       <c r="D34" t="n">
-        <v>13.317</v>
+        <v>32.1231</v>
       </c>
       <c r="E34" t="n">
-        <v>5.99517</v>
+        <v>17.574</v>
       </c>
       <c r="F34" t="n">
-        <v>6.02268</v>
+        <v>22.2182</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>6.22164</v>
+        <v>17.2866</v>
       </c>
       <c r="C35" t="n">
-        <v>6.2539</v>
+        <v>22.792</v>
       </c>
       <c r="D35" t="n">
-        <v>9.39554</v>
+        <v>26.9526</v>
       </c>
       <c r="E35" t="n">
-        <v>6.345</v>
+        <v>18.6312</v>
       </c>
       <c r="F35" t="n">
-        <v>6.31959</v>
+        <v>22.6353</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>6.29726</v>
+        <v>17.4743</v>
       </c>
       <c r="C36" t="n">
-        <v>6.41156</v>
+        <v>22.7477</v>
       </c>
       <c r="D36" t="n">
-        <v>9.62424</v>
+        <v>27.0017</v>
       </c>
       <c r="E36" t="n">
-        <v>6.99972</v>
+        <v>18.7164</v>
       </c>
       <c r="F36" t="n">
-        <v>6.9931</v>
+        <v>23.7128</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>6.53888</v>
+        <v>17.7017</v>
       </c>
       <c r="C37" t="n">
-        <v>6.66495</v>
+        <v>22.9158</v>
       </c>
       <c r="D37" t="n">
-        <v>9.777609999999999</v>
+        <v>27.3297</v>
       </c>
       <c r="E37" t="n">
-        <v>5.9826</v>
+        <v>17.286</v>
       </c>
       <c r="F37" t="n">
-        <v>6.01933</v>
+        <v>24.1392</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>6.68413</v>
+        <v>18.2469</v>
       </c>
       <c r="C38" t="n">
-        <v>6.89486</v>
+        <v>24.0206</v>
       </c>
       <c r="D38" t="n">
-        <v>10.067</v>
+        <v>28.3995</v>
       </c>
       <c r="E38" t="n">
-        <v>6.09185</v>
+        <v>17.7578</v>
       </c>
       <c r="F38" t="n">
-        <v>6.04724</v>
+        <v>23.6928</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>6.68471</v>
+        <v>17.7434</v>
       </c>
       <c r="C39" t="n">
-        <v>6.90239</v>
+        <v>23.8772</v>
       </c>
       <c r="D39" t="n">
-        <v>10.4002</v>
+        <v>28.9624</v>
       </c>
       <c r="E39" t="n">
-        <v>6.13058</v>
+        <v>17.4352</v>
       </c>
       <c r="F39" t="n">
-        <v>6.07921</v>
+        <v>23.7407</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>6.6956</v>
+        <v>18.8004</v>
       </c>
       <c r="C40" t="n">
-        <v>6.91018</v>
+        <v>24.422</v>
       </c>
       <c r="D40" t="n">
-        <v>10.732</v>
+        <v>29.1492</v>
       </c>
       <c r="E40" t="n">
-        <v>6.17003</v>
+        <v>18.0388</v>
       </c>
       <c r="F40" t="n">
-        <v>6.11484</v>
+        <v>23.927</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>6.70406</v>
+        <v>18.6783</v>
       </c>
       <c r="C41" t="n">
-        <v>6.92243</v>
+        <v>24.4677</v>
       </c>
       <c r="D41" t="n">
-        <v>11.1096</v>
+        <v>29.6739</v>
       </c>
       <c r="E41" t="n">
-        <v>6.23534</v>
+        <v>17.9381</v>
       </c>
       <c r="F41" t="n">
-        <v>6.1426</v>
+        <v>23.4739</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>6.72532</v>
+        <v>17.7082</v>
       </c>
       <c r="C42" t="n">
-        <v>6.93932</v>
+        <v>24.054</v>
       </c>
       <c r="D42" t="n">
-        <v>11.4471</v>
+        <v>30.1068</v>
       </c>
       <c r="E42" t="n">
-        <v>6.26077</v>
+        <v>18.1563</v>
       </c>
       <c r="F42" t="n">
-        <v>6.17842</v>
+        <v>24.6463</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>6.7374</v>
+        <v>18.4093</v>
       </c>
       <c r="C43" t="n">
-        <v>6.95499</v>
+        <v>24.2582</v>
       </c>
       <c r="D43" t="n">
-        <v>11.8603</v>
+        <v>31.8175</v>
       </c>
       <c r="E43" t="n">
-        <v>6.31464</v>
+        <v>18.505</v>
       </c>
       <c r="F43" t="n">
-        <v>6.23214</v>
+        <v>23.9333</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>6.75055</v>
+        <v>18.7409</v>
       </c>
       <c r="C44" t="n">
-        <v>6.95792</v>
+        <v>24.295</v>
       </c>
       <c r="D44" t="n">
-        <v>12.2533</v>
+        <v>31.3409</v>
       </c>
       <c r="E44" t="n">
-        <v>6.35102</v>
+        <v>18.8825</v>
       </c>
       <c r="F44" t="n">
-        <v>6.27752</v>
+        <v>23.8157</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>6.77096</v>
+        <v>18.4943</v>
       </c>
       <c r="C45" t="n">
-        <v>6.99144</v>
+        <v>24.4261</v>
       </c>
       <c r="D45" t="n">
-        <v>12.6353</v>
+        <v>32.2858</v>
       </c>
       <c r="E45" t="n">
-        <v>6.41213</v>
+        <v>18.6571</v>
       </c>
       <c r="F45" t="n">
-        <v>6.27823</v>
+        <v>23.9433</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>6.7916</v>
+        <v>18.4928</v>
       </c>
       <c r="C46" t="n">
-        <v>7.02437</v>
+        <v>24.3438</v>
       </c>
       <c r="D46" t="n">
-        <v>12.9746</v>
+        <v>32.9142</v>
       </c>
       <c r="E46" t="n">
-        <v>6.48558</v>
+        <v>18.7251</v>
       </c>
       <c r="F46" t="n">
-        <v>6.38293</v>
+        <v>24.6843</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>6.79738</v>
+        <v>18.5033</v>
       </c>
       <c r="C47" t="n">
-        <v>7.06668</v>
+        <v>24.1443</v>
       </c>
       <c r="D47" t="n">
-        <v>13.3077</v>
+        <v>33.3618</v>
       </c>
       <c r="E47" t="n">
-        <v>6.64228</v>
+        <v>18.9783</v>
       </c>
       <c r="F47" t="n">
-        <v>6.55677</v>
+        <v>24.5275</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>6.86444</v>
+        <v>19.4271</v>
       </c>
       <c r="C48" t="n">
-        <v>7.10979</v>
+        <v>24.7899</v>
       </c>
       <c r="D48" t="n">
-        <v>13.6798</v>
+        <v>34.5155</v>
       </c>
       <c r="E48" t="n">
-        <v>6.86998</v>
+        <v>19.3521</v>
       </c>
       <c r="F48" t="n">
-        <v>6.72696</v>
+        <v>25.5278</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>6.93623</v>
+        <v>19.0347</v>
       </c>
       <c r="C49" t="n">
-        <v>7.1786</v>
+        <v>24.6959</v>
       </c>
       <c r="D49" t="n">
-        <v>13.9915</v>
+        <v>35.6923</v>
       </c>
       <c r="E49" t="n">
-        <v>7.21305</v>
+        <v>19.9305</v>
       </c>
       <c r="F49" t="n">
-        <v>7.14408</v>
+        <v>26.0097</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>7.08651</v>
+        <v>18.1652</v>
       </c>
       <c r="C50" t="n">
-        <v>7.23885</v>
+        <v>24.786</v>
       </c>
       <c r="D50" t="n">
-        <v>9.816409999999999</v>
+        <v>30.0932</v>
       </c>
       <c r="E50" t="n">
-        <v>7.64697</v>
+        <v>20.4904</v>
       </c>
       <c r="F50" t="n">
-        <v>7.64688</v>
+        <v>25.2395</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>7.43591</v>
+        <v>19.2728</v>
       </c>
       <c r="C51" t="n">
-        <v>7.68187</v>
+        <v>24.3396</v>
       </c>
       <c r="D51" t="n">
-        <v>10.0142</v>
+        <v>32.1872</v>
       </c>
       <c r="E51" t="n">
-        <v>6.51089</v>
+        <v>19.09</v>
       </c>
       <c r="F51" t="n">
-        <v>6.32239</v>
+        <v>25.2704</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>7.88546</v>
+        <v>19.9932</v>
       </c>
       <c r="C52" t="n">
-        <v>8.406370000000001</v>
+        <v>26.0182</v>
       </c>
       <c r="D52" t="n">
-        <v>10.2601</v>
+        <v>32.4551</v>
       </c>
       <c r="E52" t="n">
-        <v>6.44022</v>
+        <v>19.1897</v>
       </c>
       <c r="F52" t="n">
-        <v>6.35389</v>
+        <v>25.2972</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>7.41505</v>
+        <v>20.8765</v>
       </c>
       <c r="C53" t="n">
-        <v>7.56462</v>
+        <v>25.9138</v>
       </c>
       <c r="D53" t="n">
-        <v>10.5423</v>
+        <v>35.0284</v>
       </c>
       <c r="E53" t="n">
-        <v>6.43541</v>
+        <v>18.8209</v>
       </c>
       <c r="F53" t="n">
-        <v>6.38422</v>
+        <v>25.3311</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>7.4219</v>
+        <v>21.1089</v>
       </c>
       <c r="C54" t="n">
-        <v>7.58701</v>
+        <v>26.3705</v>
       </c>
       <c r="D54" t="n">
-        <v>10.8877</v>
+        <v>34.6783</v>
       </c>
       <c r="E54" t="n">
-        <v>6.65003</v>
+        <v>19.3945</v>
       </c>
       <c r="F54" t="n">
-        <v>6.42808</v>
+        <v>25.3407</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>7.4195</v>
+        <v>20.9173</v>
       </c>
       <c r="C55" t="n">
-        <v>7.60045</v>
+        <v>25.9912</v>
       </c>
       <c r="D55" t="n">
-        <v>11.2492</v>
+        <v>40.1837</v>
       </c>
       <c r="E55" t="n">
-        <v>6.67068</v>
+        <v>19.0256</v>
       </c>
       <c r="F55" t="n">
-        <v>6.472</v>
+        <v>25.7799</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>7.43884</v>
+        <v>20.1825</v>
       </c>
       <c r="C56" t="n">
-        <v>7.60592</v>
+        <v>26.2117</v>
       </c>
       <c r="D56" t="n">
-        <v>11.6175</v>
+        <v>38.1972</v>
       </c>
       <c r="E56" t="n">
-        <v>6.71998</v>
+        <v>19.7641</v>
       </c>
       <c r="F56" t="n">
-        <v>6.53251</v>
+        <v>25.6847</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>7.40122</v>
+        <v>20.5099</v>
       </c>
       <c r="C57" t="n">
-        <v>7.62358</v>
+        <v>26.0139</v>
       </c>
       <c r="D57" t="n">
-        <v>12.0638</v>
+        <v>36.9767</v>
       </c>
       <c r="E57" t="n">
-        <v>6.65609</v>
+        <v>19.8753</v>
       </c>
       <c r="F57" t="n">
-        <v>6.60637</v>
+        <v>25.6002</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>7.45337</v>
+        <v>20.9154</v>
       </c>
       <c r="C58" t="n">
-        <v>7.59781</v>
+        <v>26.4327</v>
       </c>
       <c r="D58" t="n">
-        <v>12.4435</v>
+        <v>41.5426</v>
       </c>
       <c r="E58" t="n">
-        <v>6.8519</v>
+        <v>19.8987</v>
       </c>
       <c r="F58" t="n">
-        <v>6.65232</v>
+        <v>25.9609</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>7.46518</v>
+        <v>20.9978</v>
       </c>
       <c r="C59" t="n">
-        <v>7.64422</v>
+        <v>26.0663</v>
       </c>
       <c r="D59" t="n">
-        <v>12.7692</v>
+        <v>44.4199</v>
       </c>
       <c r="E59" t="n">
-        <v>6.93356</v>
+        <v>20.0611</v>
       </c>
       <c r="F59" t="n">
-        <v>6.76855</v>
+        <v>25.707</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>7.46681</v>
+        <v>20.3603</v>
       </c>
       <c r="C60" t="n">
-        <v>7.67959</v>
+        <v>26.5125</v>
       </c>
       <c r="D60" t="n">
-        <v>13.1256</v>
+        <v>47.4476</v>
       </c>
       <c r="E60" t="n">
-        <v>7.07264</v>
+        <v>20.2677</v>
       </c>
       <c r="F60" t="n">
-        <v>6.9368</v>
+        <v>26.2943</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>7.5382</v>
+        <v>21.1555</v>
       </c>
       <c r="C61" t="n">
-        <v>7.69555</v>
+        <v>26.1392</v>
       </c>
       <c r="D61" t="n">
-        <v>13.5583</v>
+        <v>48.754</v>
       </c>
       <c r="E61" t="n">
-        <v>7.20513</v>
+        <v>20.3461</v>
       </c>
       <c r="F61" t="n">
-        <v>7.1526</v>
+        <v>25.7588</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>7.60505</v>
+        <v>21.0925</v>
       </c>
       <c r="C62" t="n">
-        <v>7.80956</v>
+        <v>26.4722</v>
       </c>
       <c r="D62" t="n">
-        <v>13.9904</v>
+        <v>54.714</v>
       </c>
       <c r="E62" t="n">
-        <v>7.53493</v>
+        <v>20.8572</v>
       </c>
       <c r="F62" t="n">
-        <v>7.41612</v>
+        <v>26.0076</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>7.72328</v>
+        <v>21.2013</v>
       </c>
       <c r="C63" t="n">
-        <v>7.95244</v>
+        <v>26.4649</v>
       </c>
       <c r="D63" t="n">
-        <v>14.4074</v>
+        <v>54.2994</v>
       </c>
       <c r="E63" t="n">
-        <v>7.83172</v>
+        <v>21.3304</v>
       </c>
       <c r="F63" t="n">
-        <v>7.8467</v>
+        <v>26.9114</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>7.87333</v>
+        <v>21.2587</v>
       </c>
       <c r="C64" t="n">
-        <v>8.147640000000001</v>
+        <v>26.8807</v>
       </c>
       <c r="D64" t="n">
-        <v>10.8898</v>
+        <v>58.6508</v>
       </c>
       <c r="E64" t="n">
-        <v>8.195959999999999</v>
+        <v>21.9689</v>
       </c>
       <c r="F64" t="n">
-        <v>8.363659999999999</v>
+        <v>27.3983</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>8.137639999999999</v>
+        <v>21.6698</v>
       </c>
       <c r="C65" t="n">
-        <v>8.54585</v>
+        <v>27.0566</v>
       </c>
       <c r="D65" t="n">
-        <v>11.108</v>
+        <v>61.4104</v>
       </c>
       <c r="E65" t="n">
-        <v>8.843389999999999</v>
+        <v>22.2927</v>
       </c>
       <c r="F65" t="n">
-        <v>9.1228</v>
+        <v>28.4567</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>8.58291</v>
+        <v>22.2485</v>
       </c>
       <c r="C66" t="n">
-        <v>9.059699999999999</v>
+        <v>27.9883</v>
       </c>
       <c r="D66" t="n">
-        <v>11.589</v>
+        <v>64.5089</v>
       </c>
       <c r="E66" t="n">
-        <v>6.92845</v>
+        <v>19.6264</v>
       </c>
       <c r="F66" t="n">
-        <v>7.00451</v>
+        <v>28.2938</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>8.604089999999999</v>
+        <v>21.9351</v>
       </c>
       <c r="C67" t="n">
-        <v>8.576269999999999</v>
+        <v>32.355</v>
       </c>
       <c r="D67" t="n">
-        <v>12.2469</v>
+        <v>67.89830000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>7.02751</v>
+        <v>19.9461</v>
       </c>
       <c r="F67" t="n">
-        <v>7.09578</v>
+        <v>27.7483</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>8.467180000000001</v>
+        <v>21.9599</v>
       </c>
       <c r="C68" t="n">
-        <v>8.62604</v>
+        <v>31.2684</v>
       </c>
       <c r="D68" t="n">
-        <v>12.7926</v>
+        <v>71.06180000000001</v>
       </c>
       <c r="E68" t="n">
-        <v>7.02476</v>
+        <v>19.8477</v>
       </c>
       <c r="F68" t="n">
-        <v>7.15993</v>
+        <v>29.5588</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>8.47148</v>
+        <v>23.1957</v>
       </c>
       <c r="C69" t="n">
-        <v>8.68268</v>
+        <v>31.4685</v>
       </c>
       <c r="D69" t="n">
-        <v>13.3232</v>
+        <v>77.7133</v>
       </c>
       <c r="E69" t="n">
-        <v>7.08103</v>
+        <v>20.2669</v>
       </c>
       <c r="F69" t="n">
-        <v>7.25903</v>
+        <v>29.7182</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>8.561859999999999</v>
+        <v>23.6186</v>
       </c>
       <c r="C70" t="n">
-        <v>8.66962</v>
+        <v>32.1435</v>
       </c>
       <c r="D70" t="n">
-        <v>14.0868</v>
+        <v>76.6669</v>
       </c>
       <c r="E70" t="n">
-        <v>7.13624</v>
+        <v>19.9552</v>
       </c>
       <c r="F70" t="n">
-        <v>7.31106</v>
+        <v>29.7144</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>8.503349999999999</v>
+        <v>23.4037</v>
       </c>
       <c r="C71" t="n">
-        <v>8.877090000000001</v>
+        <v>30.7551</v>
       </c>
       <c r="D71" t="n">
-        <v>15.0176</v>
+        <v>80.9359</v>
       </c>
       <c r="E71" t="n">
-        <v>7.22934</v>
+        <v>20.0491</v>
       </c>
       <c r="F71" t="n">
-        <v>7.41562</v>
+        <v>34.1743</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>8.751810000000001</v>
+        <v>23.7689</v>
       </c>
       <c r="C72" t="n">
-        <v>8.947150000000001</v>
+        <v>33.6829</v>
       </c>
       <c r="D72" t="n">
-        <v>15.7969</v>
+        <v>85.2102</v>
       </c>
       <c r="E72" t="n">
-        <v>7.30987</v>
+        <v>19.7153</v>
       </c>
       <c r="F72" t="n">
-        <v>7.55202</v>
+        <v>28.7992</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>8.619809999999999</v>
+        <v>23.3694</v>
       </c>
       <c r="C73" t="n">
-        <v>8.99145</v>
+        <v>32.4466</v>
       </c>
       <c r="D73" t="n">
-        <v>16.6073</v>
+        <v>88.2179</v>
       </c>
       <c r="E73" t="n">
-        <v>7.41247</v>
+        <v>20.3325</v>
       </c>
       <c r="F73" t="n">
-        <v>7.73996</v>
+        <v>29.2025</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>8.4818</v>
+        <v>23.2417</v>
       </c>
       <c r="C74" t="n">
-        <v>9.109069999999999</v>
+        <v>32.7573</v>
       </c>
       <c r="D74" t="n">
-        <v>17.5128</v>
+        <v>92.2088</v>
       </c>
       <c r="E74" t="n">
-        <v>7.51749</v>
+        <v>20.4387</v>
       </c>
       <c r="F74" t="n">
-        <v>7.96819</v>
+        <v>28.0311</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>8.52383</v>
+        <v>23.2726</v>
       </c>
       <c r="C75" t="n">
-        <v>9.056319999999999</v>
+        <v>32.7857</v>
       </c>
       <c r="D75" t="n">
-        <v>18.4737</v>
+        <v>96.40689999999999</v>
       </c>
       <c r="E75" t="n">
-        <v>7.69005</v>
+        <v>20.6694</v>
       </c>
       <c r="F75" t="n">
-        <v>8.22856</v>
+        <v>29.3338</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>8.605359999999999</v>
+        <v>23.3593</v>
       </c>
       <c r="C76" t="n">
-        <v>9.23573</v>
+        <v>32.8775</v>
       </c>
       <c r="D76" t="n">
-        <v>19.14</v>
+        <v>100.442</v>
       </c>
       <c r="E76" t="n">
-        <v>7.90698</v>
+        <v>21.1592</v>
       </c>
       <c r="F76" t="n">
-        <v>8.637890000000001</v>
+        <v>31.4941</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>8.820690000000001</v>
+        <v>23.4469</v>
       </c>
       <c r="C77" t="n">
-        <v>9.42184</v>
+        <v>33.2108</v>
       </c>
       <c r="D77" t="n">
-        <v>20.185</v>
+        <v>104.626</v>
       </c>
       <c r="E77" t="n">
-        <v>8.20016</v>
+        <v>21.013</v>
       </c>
       <c r="F77" t="n">
-        <v>9.07437</v>
+        <v>30.1186</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>8.972939999999999</v>
+        <v>23.6095</v>
       </c>
       <c r="C78" t="n">
-        <v>9.82798</v>
+        <v>34.2015</v>
       </c>
       <c r="D78" t="n">
-        <v>20.1168</v>
+        <v>99.0818</v>
       </c>
       <c r="E78" t="n">
-        <v>8.55078</v>
+        <v>21.5701</v>
       </c>
       <c r="F78" t="n">
-        <v>9.542719999999999</v>
+        <v>31.1671</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>9.184139999999999</v>
+        <v>24.0026</v>
       </c>
       <c r="C79" t="n">
-        <v>10.2318</v>
+        <v>33.3097</v>
       </c>
       <c r="D79" t="n">
-        <v>20.8274</v>
+        <v>99.9068</v>
       </c>
       <c r="E79" t="n">
-        <v>9.21477</v>
+        <v>22.8572</v>
       </c>
       <c r="F79" t="n">
-        <v>10.3943</v>
+        <v>32.8196</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>9.56903</v>
+        <v>24.6985</v>
       </c>
       <c r="C80" t="n">
-        <v>10.8748</v>
+        <v>35.7959</v>
       </c>
       <c r="D80" t="n">
-        <v>21.6737</v>
+        <v>103.469</v>
       </c>
       <c r="E80" t="n">
-        <v>11.8216</v>
+        <v>27.059</v>
       </c>
       <c r="F80" t="n">
-        <v>12.4205</v>
+        <v>57.5039</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>21.2802</v>
+        <v>45.0016</v>
       </c>
       <c r="C81" t="n">
-        <v>17.0509</v>
+        <v>65.20910000000001</v>
       </c>
       <c r="D81" t="n">
-        <v>22.9515</v>
+        <v>107.058</v>
       </c>
       <c r="E81" t="n">
-        <v>12.1536</v>
+        <v>28.2574</v>
       </c>
       <c r="F81" t="n">
-        <v>12.4518</v>
+        <v>60.6027</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>21.4301</v>
+        <v>44.2102</v>
       </c>
       <c r="C82" t="n">
-        <v>17.1075</v>
+        <v>66.28440000000001</v>
       </c>
       <c r="D82" t="n">
-        <v>23.8585</v>
+        <v>107.746</v>
       </c>
       <c r="E82" t="n">
-        <v>12.4575</v>
+        <v>30.4666</v>
       </c>
       <c r="F82" t="n">
-        <v>12.5723</v>
+        <v>58.7642</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>21.9814</v>
+        <v>38.5318</v>
       </c>
       <c r="C83" t="n">
-        <v>17.1241</v>
+        <v>63.4704</v>
       </c>
       <c r="D83" t="n">
-        <v>24.8767</v>
+        <v>111.737</v>
       </c>
       <c r="E83" t="n">
-        <v>12.49</v>
+        <v>27.8373</v>
       </c>
       <c r="F83" t="n">
-        <v>12.7455</v>
+        <v>59.3812</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>21.6587</v>
+        <v>43.7841</v>
       </c>
       <c r="C84" t="n">
-        <v>17.2238</v>
+        <v>65.49720000000001</v>
       </c>
       <c r="D84" t="n">
-        <v>26.0695</v>
+        <v>112.87</v>
       </c>
       <c r="E84" t="n">
-        <v>12.9492</v>
+        <v>29.7487</v>
       </c>
       <c r="F84" t="n">
-        <v>12.7333</v>
+        <v>59.7156</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>21.6732</v>
+        <v>44.1697</v>
       </c>
       <c r="C85" t="n">
-        <v>17.2646</v>
+        <v>64.152</v>
       </c>
       <c r="D85" t="n">
-        <v>26.5555</v>
+        <v>116.566</v>
       </c>
       <c r="E85" t="n">
-        <v>13.1692</v>
+        <v>30.3962</v>
       </c>
       <c r="F85" t="n">
-        <v>12.2832</v>
+        <v>58.1798</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>21.7714</v>
+        <v>40.2435</v>
       </c>
       <c r="C86" t="n">
-        <v>17.3731</v>
+        <v>64.5043</v>
       </c>
       <c r="D86" t="n">
-        <v>28.0755</v>
+        <v>119.901</v>
       </c>
       <c r="E86" t="n">
-        <v>13.4304</v>
+        <v>29.7328</v>
       </c>
       <c r="F86" t="n">
-        <v>12.4429</v>
+        <v>59.6763</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>21.8227</v>
+        <v>44.5354</v>
       </c>
       <c r="C87" t="n">
-        <v>17.4353</v>
+        <v>64.1932</v>
       </c>
       <c r="D87" t="n">
-        <v>28.7345</v>
+        <v>136.731</v>
       </c>
       <c r="E87" t="n">
-        <v>13.5763</v>
+        <v>30.461</v>
       </c>
       <c r="F87" t="n">
-        <v>12.6418</v>
+        <v>60.8267</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>21.8189</v>
+        <v>46.8278</v>
       </c>
       <c r="C88" t="n">
-        <v>17.1697</v>
+        <v>64.0454</v>
       </c>
       <c r="D88" t="n">
-        <v>30.1396</v>
+        <v>128.254</v>
       </c>
       <c r="E88" t="n">
-        <v>13.8178</v>
+        <v>32.5633</v>
       </c>
       <c r="F88" t="n">
-        <v>13.2765</v>
+        <v>58.4714</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>21.8592</v>
+        <v>44.5403</v>
       </c>
       <c r="C89" t="n">
-        <v>17.3438</v>
+        <v>63.9768</v>
       </c>
       <c r="D89" t="n">
-        <v>31.3091</v>
+        <v>134.93</v>
       </c>
       <c r="E89" t="n">
-        <v>14.1699</v>
+        <v>31.7359</v>
       </c>
       <c r="F89" t="n">
-        <v>13.5373</v>
+        <v>61.1912</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>21.8681</v>
+        <v>41.3935</v>
       </c>
       <c r="C90" t="n">
-        <v>17.7375</v>
+        <v>66.29770000000001</v>
       </c>
       <c r="D90" t="n">
-        <v>32.452</v>
+        <v>134.953</v>
       </c>
       <c r="E90" t="n">
-        <v>14.393</v>
+        <v>28.1647</v>
       </c>
       <c r="F90" t="n">
-        <v>13.7072</v>
+        <v>59.3979</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>21.9183</v>
+        <v>43.0715</v>
       </c>
       <c r="C91" t="n">
-        <v>17.7873</v>
+        <v>64.47490000000001</v>
       </c>
       <c r="D91" t="n">
-        <v>33.7114</v>
+        <v>140.746</v>
       </c>
       <c r="E91" t="n">
-        <v>14.7733</v>
+        <v>33.0106</v>
       </c>
       <c r="F91" t="n">
-        <v>13.652</v>
+        <v>60.9128</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>22.0483</v>
+        <v>44.5833</v>
       </c>
       <c r="C92" t="n">
-        <v>17.7829</v>
+        <v>65.91419999999999</v>
       </c>
       <c r="D92" t="n">
-        <v>32.0212</v>
+        <v>123.819</v>
       </c>
       <c r="E92" t="n">
-        <v>14.8314</v>
+        <v>33.9565</v>
       </c>
       <c r="F92" t="n">
-        <v>14.3141</v>
+        <v>61.5944</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>22.1729</v>
+        <v>45.1165</v>
       </c>
       <c r="C93" t="n">
-        <v>18.3873</v>
+        <v>64.092</v>
       </c>
       <c r="D93" t="n">
-        <v>32.7134</v>
+        <v>125.78</v>
       </c>
       <c r="E93" t="n">
-        <v>15.3372</v>
+        <v>30.982</v>
       </c>
       <c r="F93" t="n">
-        <v>15.1439</v>
+        <v>62.4255</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>22.3072</v>
+        <v>40.6542</v>
       </c>
       <c r="C94" t="n">
-        <v>18.998</v>
+        <v>67.15860000000001</v>
       </c>
       <c r="D94" t="n">
-        <v>33.4336</v>
+        <v>126.972</v>
       </c>
       <c r="E94" t="n">
-        <v>23.6021</v>
+        <v>52.3676</v>
       </c>
       <c r="F94" t="n">
-        <v>23.2065</v>
+        <v>85.2319</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>29.921</v>
+        <v>72.9457</v>
       </c>
       <c r="C95" t="n">
-        <v>26.6679</v>
+        <v>91.43389999999999</v>
       </c>
       <c r="D95" t="n">
-        <v>34.1108</v>
+        <v>131.419</v>
       </c>
       <c r="E95" t="n">
-        <v>23.7445</v>
+        <v>57.0656</v>
       </c>
       <c r="F95" t="n">
-        <v>23.3183</v>
+        <v>84.95350000000001</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>29.8974</v>
+        <v>72.9517</v>
       </c>
       <c r="C96" t="n">
-        <v>26.7033</v>
+        <v>89.8785</v>
       </c>
       <c r="D96" t="n">
-        <v>35.0325</v>
+        <v>133.125</v>
       </c>
       <c r="E96" t="n">
-        <v>24.0385</v>
+        <v>57.77</v>
       </c>
       <c r="F96" t="n">
-        <v>23.4758</v>
+        <v>85.8085</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>29.8999</v>
+        <v>72.6803</v>
       </c>
       <c r="C97" t="n">
-        <v>26.7559</v>
+        <v>90.2281</v>
       </c>
       <c r="D97" t="n">
-        <v>36.1915</v>
+        <v>135.831</v>
       </c>
       <c r="E97" t="n">
-        <v>24.1977</v>
+        <v>57.7606</v>
       </c>
       <c r="F97" t="n">
-        <v>23.5799</v>
+        <v>84.5629</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>29.9432</v>
+        <v>72.2885</v>
       </c>
       <c r="C98" t="n">
-        <v>26.7744</v>
+        <v>89.459</v>
       </c>
       <c r="D98" t="n">
-        <v>36.8011</v>
+        <v>138.726</v>
       </c>
       <c r="E98" t="n">
-        <v>24.4391</v>
+        <v>58.0845</v>
       </c>
       <c r="F98" t="n">
-        <v>23.6594</v>
+        <v>92.3189</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>29.9356</v>
+        <v>72.81480000000001</v>
       </c>
       <c r="C99" t="n">
-        <v>26.8203</v>
+        <v>89.5108</v>
       </c>
       <c r="D99" t="n">
-        <v>37.7519</v>
+        <v>142.382</v>
       </c>
       <c r="E99" t="n">
-        <v>24.4003</v>
+        <v>58.8629</v>
       </c>
       <c r="F99" t="n">
-        <v>23.7966</v>
+        <v>85.3656</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>30.0183</v>
+        <v>72.8402</v>
       </c>
       <c r="C100" t="n">
-        <v>26.8524</v>
+        <v>90.7757</v>
       </c>
       <c r="D100" t="n">
-        <v>38.857</v>
+        <v>145.341</v>
       </c>
       <c r="E100" t="n">
-        <v>24.6199</v>
+        <v>59.7491</v>
       </c>
       <c r="F100" t="n">
-        <v>23.9691</v>
+        <v>93.0377</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>29.9914</v>
+        <v>67.66419999999999</v>
       </c>
       <c r="C101" t="n">
-        <v>26.9355</v>
+        <v>89.611</v>
       </c>
       <c r="D101" t="n">
-        <v>39.6803</v>
+        <v>148.267</v>
       </c>
       <c r="E101" t="n">
-        <v>25.0596</v>
+        <v>58.7738</v>
       </c>
       <c r="F101" t="n">
-        <v>24.1258</v>
+        <v>87.3293</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>29.9826</v>
+        <v>71.5622</v>
       </c>
       <c r="C102" t="n">
-        <v>26.9816</v>
+        <v>89.08929999999999</v>
       </c>
       <c r="D102" t="n">
-        <v>40.8413</v>
+        <v>154.802</v>
       </c>
       <c r="E102" t="n">
-        <v>25.3567</v>
+        <v>60.9188</v>
       </c>
       <c r="F102" t="n">
-        <v>24.295</v>
+        <v>86.70869999999999</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>30.0459</v>
+        <v>67.4486</v>
       </c>
       <c r="C103" t="n">
-        <v>27.0898</v>
+        <v>90.6973</v>
       </c>
       <c r="D103" t="n">
-        <v>41.8984</v>
+        <v>156.963</v>
       </c>
       <c r="E103" t="n">
-        <v>25.6195</v>
+        <v>61.4233</v>
       </c>
       <c r="F103" t="n">
-        <v>24.4341</v>
+        <v>87.3446</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>30.0924</v>
+        <v>72.45099999999999</v>
       </c>
       <c r="C104" t="n">
-        <v>27.1197</v>
+        <v>89.0185</v>
       </c>
       <c r="D104" t="n">
-        <v>43.0874</v>
+        <v>178.619</v>
       </c>
       <c r="E104" t="n">
-        <v>25.8727</v>
+        <v>61.7118</v>
       </c>
       <c r="F104" t="n">
-        <v>24.8674</v>
+        <v>86.68470000000001</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>30.167</v>
+        <v>71.2122</v>
       </c>
       <c r="C105" t="n">
-        <v>27.4284</v>
+        <v>90.6469</v>
       </c>
       <c r="D105" t="n">
-        <v>44.1338</v>
+        <v>180.298</v>
       </c>
       <c r="E105" t="n">
-        <v>26.0309</v>
+        <v>62.3603</v>
       </c>
       <c r="F105" t="n">
-        <v>25.2308</v>
+        <v>89.9132</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>30.2864</v>
+        <v>71.8167</v>
       </c>
       <c r="C106" t="n">
-        <v>27.5327</v>
+        <v>91.9058</v>
       </c>
       <c r="D106" t="n">
-        <v>45.4685</v>
+        <v>183.255</v>
       </c>
       <c r="E106" t="n">
-        <v>26.5386</v>
+        <v>62.9726</v>
       </c>
       <c r="F106" t="n">
-        <v>25.5444</v>
+        <v>88.7255</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>30.4499</v>
+        <v>72.3237</v>
       </c>
       <c r="C107" t="n">
-        <v>27.9487</v>
+        <v>92.5226</v>
       </c>
       <c r="D107" t="n">
-        <v>38.5288</v>
+        <v>139.575</v>
       </c>
       <c r="E107" t="n">
-        <v>26.9956</v>
+        <v>60.1689</v>
       </c>
       <c r="F107" t="n">
-        <v>26.2139</v>
+        <v>90.4033</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>30.6155</v>
+        <v>69.41379999999999</v>
       </c>
       <c r="C108" t="n">
-        <v>28.483</v>
+        <v>93.8477</v>
       </c>
       <c r="D108" t="n">
-        <v>39.1404</v>
+        <v>142.242</v>
       </c>
       <c r="E108" t="n">
-        <v>29.6292</v>
+        <v>77.1683</v>
       </c>
       <c r="F108" t="n">
-        <v>28.9932</v>
+        <v>107.272</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>30.8754</v>
+        <v>71.7704</v>
       </c>
       <c r="C109" t="n">
-        <v>29.4455</v>
+        <v>93.2146</v>
       </c>
       <c r="D109" t="n">
-        <v>40.1823</v>
+        <v>143.034</v>
       </c>
       <c r="E109" t="n">
-        <v>30.2894</v>
+        <v>77.4833</v>
       </c>
       <c r="F109" t="n">
-        <v>29.2678</v>
+        <v>108.64</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>33.8152</v>
+        <v>86.7865</v>
       </c>
       <c r="C110" t="n">
-        <v>33.7764</v>
+        <v>110.6</v>
       </c>
       <c r="D110" t="n">
-        <v>40.9089</v>
+        <v>146.336</v>
       </c>
       <c r="E110" t="n">
-        <v>30.5922</v>
+        <v>78.6498</v>
       </c>
       <c r="F110" t="n">
-        <v>29.5537</v>
+        <v>109.984</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>33.9609</v>
+        <v>88.22580000000001</v>
       </c>
       <c r="C111" t="n">
-        <v>33.6154</v>
+        <v>112.782</v>
       </c>
       <c r="D111" t="n">
-        <v>41.5856</v>
+        <v>148.935</v>
       </c>
       <c r="E111" t="n">
-        <v>30.824</v>
+        <v>76.79989999999999</v>
       </c>
       <c r="F111" t="n">
-        <v>29.7209</v>
+        <v>110.091</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>34.0407</v>
+        <v>88.27549999999999</v>
       </c>
       <c r="C112" t="n">
-        <v>33.7478</v>
+        <v>112.625</v>
       </c>
       <c r="D112" t="n">
-        <v>41.8706</v>
+        <v>150.924</v>
       </c>
       <c r="E112" t="n">
-        <v>31.1119</v>
+        <v>79.15219999999999</v>
       </c>
       <c r="F112" t="n">
-        <v>29.3176</v>
+        <v>109.902</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>33.9002</v>
+        <v>88.584</v>
       </c>
       <c r="C113" t="n">
-        <v>33.8267</v>
+        <v>113.541</v>
       </c>
       <c r="D113" t="n">
-        <v>43.5028</v>
+        <v>155.654</v>
       </c>
       <c r="E113" t="n">
-        <v>31.4207</v>
+        <v>79.3441</v>
       </c>
       <c r="F113" t="n">
-        <v>30.1533</v>
+        <v>111.477</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>34.3096</v>
+        <v>87.4297</v>
       </c>
       <c r="C114" t="n">
-        <v>33.7527</v>
+        <v>111.169</v>
       </c>
       <c r="D114" t="n">
-        <v>44.2905</v>
+        <v>158.377</v>
       </c>
       <c r="E114" t="n">
-        <v>31.515</v>
+        <v>79.95229999999999</v>
       </c>
       <c r="F114" t="n">
-        <v>30.2169</v>
+        <v>110.915</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>34.0053</v>
+        <v>88.2064</v>
       </c>
       <c r="C115" t="n">
-        <v>33.8709</v>
+        <v>112.355</v>
       </c>
       <c r="D115" t="n">
-        <v>45.2833</v>
+        <v>161.807</v>
       </c>
       <c r="E115" t="n">
-        <v>32.027</v>
+        <v>79.05889999999999</v>
       </c>
       <c r="F115" t="n">
-        <v>30.7942</v>
+        <v>112.076</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>33.497</v>
+        <v>86.96550000000001</v>
       </c>
       <c r="C116" t="n">
-        <v>34.1105</v>
+        <v>113.463</v>
       </c>
       <c r="D116" t="n">
-        <v>45.6286</v>
+        <v>165.974</v>
       </c>
       <c r="E116" t="n">
-        <v>32.277</v>
+        <v>81.0951</v>
       </c>
       <c r="F116" t="n">
-        <v>30.9402</v>
+        <v>111.088</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>34.159</v>
+        <v>88.2204</v>
       </c>
       <c r="C117" t="n">
-        <v>34.1331</v>
+        <v>114.986</v>
       </c>
       <c r="D117" t="n">
-        <v>46.8362</v>
+        <v>170.535</v>
       </c>
       <c r="E117" t="n">
-        <v>32.4579</v>
+        <v>79.98650000000001</v>
       </c>
       <c r="F117" t="n">
-        <v>31.3345</v>
+        <v>114.375</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>34.1987</v>
+        <v>89.2576</v>
       </c>
       <c r="C118" t="n">
-        <v>34.3041</v>
+        <v>111.644</v>
       </c>
       <c r="D118" t="n">
-        <v>48.7162</v>
+        <v>180.536</v>
       </c>
       <c r="E118" t="n">
-        <v>33.1597</v>
+        <v>82.6388</v>
       </c>
       <c r="F118" t="n">
-        <v>31.7865</v>
+        <v>112.061</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>34.179</v>
+        <v>88.52030000000001</v>
       </c>
       <c r="C119" t="n">
-        <v>34.5332</v>
+        <v>113.596</v>
       </c>
       <c r="D119" t="n">
-        <v>49.8348</v>
+        <v>178.914</v>
       </c>
       <c r="E119" t="n">
-        <v>33.5726</v>
+        <v>83.1528</v>
       </c>
       <c r="F119" t="n">
-        <v>32.2437</v>
+        <v>115.174</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>34.432</v>
+        <v>88.1712</v>
       </c>
       <c r="C120" t="n">
-        <v>34.7174</v>
+        <v>114.307</v>
       </c>
       <c r="D120" t="n">
-        <v>51.0287</v>
+        <v>195.461</v>
       </c>
       <c r="E120" t="n">
-        <v>34.1489</v>
+        <v>83.82250000000001</v>
       </c>
       <c r="F120" t="n">
-        <v>33.3987</v>
+        <v>113.588</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>34.5646</v>
+        <v>89.30840000000001</v>
       </c>
       <c r="C121" t="n">
-        <v>35.1232</v>
+        <v>114.187</v>
       </c>
       <c r="D121" t="n">
-        <v>41.7292</v>
+        <v>145.728</v>
       </c>
       <c r="E121" t="n">
-        <v>34.7698</v>
+        <v>85.964</v>
       </c>
       <c r="F121" t="n">
-        <v>34.1889</v>
+        <v>117.724</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>34.8426</v>
+        <v>90.2076</v>
       </c>
       <c r="C122" t="n">
-        <v>35.7719</v>
+        <v>112.168</v>
       </c>
       <c r="D122" t="n">
-        <v>42.1413</v>
+        <v>148.693</v>
       </c>
       <c r="E122" t="n">
-        <v>35.6622</v>
+        <v>86.48099999999999</v>
       </c>
       <c r="F122" t="n">
-        <v>35.0182</v>
+        <v>119.221</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>35.1542</v>
+        <v>102.939</v>
       </c>
       <c r="C123" t="n">
-        <v>36.0892</v>
+        <v>114.724</v>
       </c>
       <c r="D123" t="n">
-        <v>42.8431</v>
+        <v>151.443</v>
       </c>
       <c r="E123" t="n">
-        <v>34.183</v>
+        <v>92.6429</v>
       </c>
       <c r="F123" t="n">
-        <v>33.8778</v>
+        <v>133.421</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>43.2891</v>
+        <v>112.815</v>
       </c>
       <c r="C124" t="n">
-        <v>43.297</v>
+        <v>134.441</v>
       </c>
       <c r="D124" t="n">
-        <v>44.2278</v>
+        <v>153.504</v>
       </c>
       <c r="E124" t="n">
-        <v>34.8581</v>
+        <v>92.9992</v>
       </c>
       <c r="F124" t="n">
-        <v>34.0459</v>
+        <v>132.888</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>43.2927</v>
+        <v>110.934</v>
       </c>
       <c r="C125" t="n">
-        <v>43.3197</v>
+        <v>137.126</v>
       </c>
       <c r="D125" t="n">
-        <v>44.4342</v>
+        <v>156.234</v>
       </c>
       <c r="E125" t="n">
-        <v>35.2444</v>
+        <v>93.3648</v>
       </c>
       <c r="F125" t="n">
-        <v>34.1246</v>
+        <v>133.656</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>43.27</v>
+        <v>112.148</v>
       </c>
       <c r="C126" t="n">
-        <v>43.7362</v>
+        <v>137.292</v>
       </c>
       <c r="D126" t="n">
-        <v>44.9856</v>
+        <v>158.944</v>
       </c>
       <c r="E126" t="n">
-        <v>35.5942</v>
+        <v>93.5427</v>
       </c>
       <c r="F126" t="n">
-        <v>34.4045</v>
+        <v>134.036</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>43.5803</v>
+        <v>109.144</v>
       </c>
       <c r="C127" t="n">
-        <v>44.216</v>
+        <v>136.729</v>
       </c>
       <c r="D127" t="n">
-        <v>46.7846</v>
+        <v>161.715</v>
       </c>
       <c r="E127" t="n">
-        <v>36.0444</v>
+        <v>92.7508</v>
       </c>
       <c r="F127" t="n">
-        <v>34.9697</v>
+        <v>132.689</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>43.5917</v>
+        <v>111.181</v>
       </c>
       <c r="C128" t="n">
-        <v>44.2576</v>
+        <v>137.494</v>
       </c>
       <c r="D128" t="n">
-        <v>47.6935</v>
+        <v>165.622</v>
       </c>
       <c r="E128" t="n">
-        <v>36.3705</v>
+        <v>94.95569999999999</v>
       </c>
       <c r="F128" t="n">
-        <v>34.9786</v>
+        <v>133.271</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>43.3762</v>
+        <v>108.457</v>
       </c>
       <c r="C129" t="n">
-        <v>43.6904</v>
+        <v>137.418</v>
       </c>
       <c r="D129" t="n">
-        <v>48.6391</v>
+        <v>176.896</v>
       </c>
       <c r="E129" t="n">
-        <v>36.6965</v>
+        <v>95.7569</v>
       </c>
       <c r="F129" t="n">
-        <v>35.5692</v>
+        <v>135.285</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>43.4455</v>
+        <v>112.027</v>
       </c>
       <c r="C130" t="n">
-        <v>44.5812</v>
+        <v>142.441</v>
       </c>
       <c r="D130" t="n">
-        <v>49.3308</v>
+        <v>183.493</v>
       </c>
       <c r="E130" t="n">
-        <v>36.6359</v>
+        <v>99.9935</v>
       </c>
       <c r="F130" t="n">
-        <v>36.0601</v>
+        <v>139.773</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>43.5428</v>
+        <v>115.436</v>
       </c>
       <c r="C131" t="n">
-        <v>44.5574</v>
+        <v>136.431</v>
       </c>
       <c r="D131" t="n">
-        <v>50.5301</v>
+        <v>183.281</v>
       </c>
       <c r="E131" t="n">
-        <v>37.5419</v>
+        <v>96.89449999999999</v>
       </c>
       <c r="F131" t="n">
-        <v>36.4253</v>
+        <v>136.053</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>42.5473</v>
+        <v>115.147</v>
       </c>
       <c r="C132" t="n">
-        <v>44.6327</v>
+        <v>136.211</v>
       </c>
       <c r="D132" t="n">
-        <v>51.6288</v>
+        <v>186.76</v>
       </c>
       <c r="E132" t="n">
-        <v>38.0901</v>
+        <v>97.301</v>
       </c>
       <c r="F132" t="n">
-        <v>37.0842</v>
+        <v>136.918</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>43.8417</v>
+        <v>110.881</v>
       </c>
       <c r="C133" t="n">
-        <v>44.9601</v>
+        <v>139.257</v>
       </c>
       <c r="D133" t="n">
-        <v>52.892</v>
+        <v>191.686</v>
       </c>
       <c r="E133" t="n">
-        <v>38.575</v>
+        <v>97.3524</v>
       </c>
       <c r="F133" t="n">
-        <v>37.7808</v>
+        <v>137.857</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>43.6968</v>
+        <v>113.402</v>
       </c>
       <c r="C134" t="n">
-        <v>45.2612</v>
+        <v>149.884</v>
       </c>
       <c r="D134" t="n">
-        <v>53.8773</v>
+        <v>194.718</v>
       </c>
       <c r="E134" t="n">
-        <v>39.2795</v>
+        <v>98.8318</v>
       </c>
       <c r="F134" t="n">
-        <v>38.7985</v>
+        <v>142.884</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>42.957</v>
+        <v>119.137</v>
       </c>
       <c r="C135" t="n">
-        <v>45.4029</v>
+        <v>143.335</v>
       </c>
       <c r="D135" t="n">
-        <v>43.3707</v>
+        <v>156.311</v>
       </c>
       <c r="E135" t="n">
-        <v>40.1109</v>
+        <v>105.473</v>
       </c>
       <c r="F135" t="n">
-        <v>40.0714</v>
+        <v>142.631</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>44.0003</v>
+        <v>116.299</v>
       </c>
       <c r="C136" t="n">
-        <v>46.1662</v>
+        <v>144.884</v>
       </c>
       <c r="D136" t="n">
-        <v>43.784</v>
+        <v>159.44</v>
       </c>
       <c r="E136" t="n">
-        <v>41.2711</v>
+        <v>108.387</v>
       </c>
       <c r="F136" t="n">
-        <v>41.4874</v>
+        <v>145.106</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>44.4298</v>
+        <v>116.812</v>
       </c>
       <c r="C137" t="n">
-        <v>47.0242</v>
+        <v>146.531</v>
       </c>
       <c r="D137" t="n">
-        <v>44.7834</v>
+        <v>164.087</v>
       </c>
       <c r="E137" t="n">
-        <v>36.9645</v>
+        <v>108.302</v>
       </c>
       <c r="F137" t="n">
-        <v>36.1637</v>
+        <v>154.436</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>49.5879</v>
+        <v>139.303</v>
       </c>
       <c r="C138" t="n">
-        <v>50.0676</v>
+        <v>158.772</v>
       </c>
       <c r="D138" t="n">
-        <v>45.2057</v>
+        <v>166.484</v>
       </c>
       <c r="E138" t="n">
-        <v>37.3694</v>
+        <v>109.773</v>
       </c>
       <c r="F138" t="n">
-        <v>36.4293</v>
+        <v>153.163</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>49.247</v>
+        <v>139.691</v>
       </c>
       <c r="C139" t="n">
-        <v>50.1245</v>
+        <v>159.048</v>
       </c>
       <c r="D139" t="n">
-        <v>46.3953</v>
+        <v>169.2</v>
       </c>
       <c r="E139" t="n">
-        <v>37.6632</v>
+        <v>110.345</v>
       </c>
       <c r="F139" t="n">
-        <v>36.6948</v>
+        <v>154.69</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>49.3307</v>
+        <v>139.65</v>
       </c>
       <c r="C140" t="n">
-        <v>49.6105</v>
+        <v>159.461</v>
       </c>
       <c r="D140" t="n">
-        <v>47.5014</v>
+        <v>171.337</v>
       </c>
       <c r="E140" t="n">
-        <v>38.0285</v>
+        <v>110.397</v>
       </c>
       <c r="F140" t="n">
-        <v>37.0949</v>
+        <v>154.153</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>49.7133</v>
+        <v>139.069</v>
       </c>
       <c r="C141" t="n">
-        <v>50.2909</v>
+        <v>158.768</v>
       </c>
       <c r="D141" t="n">
-        <v>47.8598</v>
+        <v>174.479</v>
       </c>
       <c r="E141" t="n">
-        <v>38.5706</v>
+        <v>110.217</v>
       </c>
       <c r="F141" t="n">
-        <v>37.5623</v>
+        <v>148.722</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>49.7858</v>
+        <v>134.795</v>
       </c>
       <c r="C142" t="n">
-        <v>50.3661</v>
+        <v>153.595</v>
       </c>
       <c r="D142" t="n">
-        <v>49.3062</v>
+        <v>173.074</v>
       </c>
       <c r="E142" t="n">
-        <v>38.9728</v>
+        <v>102.316</v>
       </c>
       <c r="F142" t="n">
-        <v>37.9786</v>
+        <v>149.594</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>49.8851</v>
+        <v>134.238</v>
       </c>
       <c r="C143" t="n">
-        <v>50.5508</v>
+        <v>153.853</v>
       </c>
       <c r="D143" t="n">
-        <v>49.5605</v>
+        <v>175.72</v>
       </c>
       <c r="E143" t="n">
-        <v>39.2054</v>
+        <v>104.159</v>
       </c>
       <c r="F143" t="n">
-        <v>38.4143</v>
+        <v>149.717</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Scattered successful looukp.xlsx
+++ b/clang-x64/Scattered successful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>12.2246</v>
+        <v>4.98335</v>
       </c>
       <c r="C2" t="n">
-        <v>17.0513</v>
+        <v>4.99801</v>
       </c>
       <c r="D2" t="n">
-        <v>25.2051</v>
+        <v>8.55658</v>
       </c>
       <c r="E2" t="n">
-        <v>14.1639</v>
+        <v>4.33143</v>
       </c>
       <c r="F2" t="n">
-        <v>17.009</v>
+        <v>5.07967</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>12.6524</v>
+        <v>4.63368</v>
       </c>
       <c r="C3" t="n">
-        <v>17.669</v>
+        <v>5.08457</v>
       </c>
       <c r="D3" t="n">
-        <v>25.7718</v>
+        <v>9.227449999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>14.3515</v>
+        <v>4.78417</v>
       </c>
       <c r="F3" t="n">
-        <v>17.7165</v>
+        <v>5.06601</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>12.546</v>
+        <v>4.6853</v>
       </c>
       <c r="C4" t="n">
-        <v>17.8017</v>
+        <v>5.14757</v>
       </c>
       <c r="D4" t="n">
-        <v>26.2806</v>
+        <v>10.0915</v>
       </c>
       <c r="E4" t="n">
-        <v>14.5548</v>
+        <v>4.19729</v>
       </c>
       <c r="F4" t="n">
-        <v>17.0913</v>
+        <v>5.04964</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>12.9739</v>
+        <v>4.62007</v>
       </c>
       <c r="C5" t="n">
-        <v>17.6029</v>
+        <v>5.34358</v>
       </c>
       <c r="D5" t="n">
-        <v>26.8461</v>
+        <v>10.8732</v>
       </c>
       <c r="E5" t="n">
-        <v>14.635</v>
+        <v>4.6925</v>
       </c>
       <c r="F5" t="n">
-        <v>17.5858</v>
+        <v>4.88638</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>12.817</v>
+        <v>4.7488</v>
       </c>
       <c r="C6" t="n">
-        <v>18.3159</v>
+        <v>5.17582</v>
       </c>
       <c r="D6" t="n">
-        <v>27.4259</v>
+        <v>11.6137</v>
       </c>
       <c r="E6" t="n">
-        <v>14.8374</v>
+        <v>4.54198</v>
       </c>
       <c r="F6" t="n">
-        <v>17.5974</v>
+        <v>5.21839</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>13.004</v>
+        <v>4.77349</v>
       </c>
       <c r="C7" t="n">
-        <v>18.0892</v>
+        <v>5.21566</v>
       </c>
       <c r="D7" t="n">
-        <v>24.1448</v>
+        <v>6.60849</v>
       </c>
       <c r="E7" t="n">
-        <v>15.5398</v>
+        <v>4.52218</v>
       </c>
       <c r="F7" t="n">
-        <v>18.0434</v>
+        <v>5.20342</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>13.2856</v>
+        <v>4.70486</v>
       </c>
       <c r="C8" t="n">
-        <v>17.9883</v>
+        <v>5.24484</v>
       </c>
       <c r="D8" t="n">
-        <v>24.1262</v>
+        <v>7.15211</v>
       </c>
       <c r="E8" t="n">
-        <v>15.8234</v>
+        <v>4.57957</v>
       </c>
       <c r="F8" t="n">
-        <v>18.9962</v>
+        <v>5.50687</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>13.1217</v>
+        <v>5.01262</v>
       </c>
       <c r="C9" t="n">
-        <v>18.2457</v>
+        <v>5.34956</v>
       </c>
       <c r="D9" t="n">
-        <v>24.2378</v>
+        <v>7.46576</v>
       </c>
       <c r="E9" t="n">
-        <v>14.3527</v>
+        <v>5.07751</v>
       </c>
       <c r="F9" t="n">
-        <v>18.4926</v>
+        <v>4.28321</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>14.388</v>
+        <v>5.34318</v>
       </c>
       <c r="C10" t="n">
-        <v>19.6504</v>
+        <v>4.67805</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0814</v>
+        <v>7.7044</v>
       </c>
       <c r="E10" t="n">
-        <v>15.2096</v>
+        <v>5.69684</v>
       </c>
       <c r="F10" t="n">
-        <v>18.9696</v>
+        <v>4.40423</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>14.7034</v>
+        <v>5.89328</v>
       </c>
       <c r="C11" t="n">
-        <v>20.0842</v>
+        <v>4.68665</v>
       </c>
       <c r="D11" t="n">
-        <v>25.0515</v>
+        <v>8.130940000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>14.4604</v>
+        <v>5.28324</v>
       </c>
       <c r="F11" t="n">
-        <v>18.9604</v>
+        <v>4.33192</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>13.932</v>
+        <v>5.03088</v>
       </c>
       <c r="C12" t="n">
-        <v>19.4361</v>
+        <v>4.70036</v>
       </c>
       <c r="D12" t="n">
-        <v>25.9148</v>
+        <v>8.678559999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>14.7342</v>
+        <v>5.55601</v>
       </c>
       <c r="F12" t="n">
-        <v>18.7495</v>
+        <v>4.35177</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>14.467</v>
+        <v>5.31675</v>
       </c>
       <c r="C13" t="n">
-        <v>19.3993</v>
+        <v>4.73654</v>
       </c>
       <c r="D13" t="n">
-        <v>25.977</v>
+        <v>9.179550000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>14.5564</v>
+        <v>5.59962</v>
       </c>
       <c r="F13" t="n">
-        <v>18.3647</v>
+        <v>4.40162</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>14.5984</v>
+        <v>5.7911</v>
       </c>
       <c r="C14" t="n">
-        <v>19.4829</v>
+        <v>4.768</v>
       </c>
       <c r="D14" t="n">
-        <v>26.527</v>
+        <v>9.74221</v>
       </c>
       <c r="E14" t="n">
-        <v>14.7457</v>
+        <v>5.80579</v>
       </c>
       <c r="F14" t="n">
-        <v>19.134</v>
+        <v>4.48691</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>14.6598</v>
+        <v>5.11178</v>
       </c>
       <c r="C15" t="n">
-        <v>19.9591</v>
+        <v>4.74699</v>
       </c>
       <c r="D15" t="n">
-        <v>27.3652</v>
+        <v>10.2384</v>
       </c>
       <c r="E15" t="n">
-        <v>14.8729</v>
+        <v>5.51826</v>
       </c>
       <c r="F15" t="n">
-        <v>18.7509</v>
+        <v>4.46134</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>14.7052</v>
+        <v>5.54767</v>
       </c>
       <c r="C16" t="n">
-        <v>19.5729</v>
+        <v>4.79541</v>
       </c>
       <c r="D16" t="n">
-        <v>27.4572</v>
+        <v>10.7125</v>
       </c>
       <c r="E16" t="n">
-        <v>15.2148</v>
+        <v>6.10781</v>
       </c>
       <c r="F16" t="n">
-        <v>19.0951</v>
+        <v>4.62111</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>14.8912</v>
+        <v>5.94968</v>
       </c>
       <c r="C17" t="n">
-        <v>19.6166</v>
+        <v>4.8157</v>
       </c>
       <c r="D17" t="n">
-        <v>28.2825</v>
+        <v>11.237</v>
       </c>
       <c r="E17" t="n">
-        <v>15.2477</v>
+        <v>5.82417</v>
       </c>
       <c r="F17" t="n">
-        <v>19.5945</v>
+        <v>4.54509</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>15.1101</v>
+        <v>5.74341</v>
       </c>
       <c r="C18" t="n">
-        <v>20.2596</v>
+        <v>4.83034</v>
       </c>
       <c r="D18" t="n">
-        <v>28.9862</v>
+        <v>11.745</v>
       </c>
       <c r="E18" t="n">
-        <v>15.4004</v>
+        <v>6.14183</v>
       </c>
       <c r="F18" t="n">
-        <v>19.6821</v>
+        <v>4.69651</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>15.0716</v>
+        <v>5.21113</v>
       </c>
       <c r="C19" t="n">
-        <v>20.2129</v>
+        <v>4.85061</v>
       </c>
       <c r="D19" t="n">
-        <v>29.4335</v>
+        <v>12.2591</v>
       </c>
       <c r="E19" t="n">
-        <v>15.7521</v>
+        <v>5.64148</v>
       </c>
       <c r="F19" t="n">
-        <v>20.6507</v>
+        <v>4.58703</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>15.1828</v>
+        <v>6.10958</v>
       </c>
       <c r="C20" t="n">
-        <v>20.2154</v>
+        <v>4.87845</v>
       </c>
       <c r="D20" t="n">
-        <v>29.889</v>
+        <v>12.67</v>
       </c>
       <c r="E20" t="n">
-        <v>15.8705</v>
+        <v>6.17671</v>
       </c>
       <c r="F20" t="n">
-        <v>20.8845</v>
+        <v>4.64857</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>15.0805</v>
+        <v>6.0787</v>
       </c>
       <c r="C21" t="n">
-        <v>20.2925</v>
+        <v>5.44829</v>
       </c>
       <c r="D21" t="n">
-        <v>25.3273</v>
+        <v>8.77155</v>
       </c>
       <c r="E21" t="n">
-        <v>16.2117</v>
+        <v>6.18794</v>
       </c>
       <c r="F21" t="n">
-        <v>19.6959</v>
+        <v>5.80241</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>15.3204</v>
+        <v>6.26783</v>
       </c>
       <c r="C22" t="n">
-        <v>20.635</v>
+        <v>6.25137</v>
       </c>
       <c r="D22" t="n">
-        <v>26.0802</v>
+        <v>9.046860000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>16.9212</v>
+        <v>6.6127</v>
       </c>
       <c r="F22" t="n">
-        <v>21.8607</v>
+        <v>5.67417</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>16.0697</v>
+        <v>6.42491</v>
       </c>
       <c r="C23" t="n">
-        <v>20.8746</v>
+        <v>5.0899</v>
       </c>
       <c r="D23" t="n">
-        <v>26.2242</v>
+        <v>9.33999</v>
       </c>
       <c r="E23" t="n">
-        <v>16.0866</v>
+        <v>5.67279</v>
       </c>
       <c r="F23" t="n">
-        <v>21.0678</v>
+        <v>5.52859</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>16.1344</v>
+        <v>6.08396</v>
       </c>
       <c r="C24" t="n">
-        <v>21.6398</v>
+        <v>6.25944</v>
       </c>
       <c r="D24" t="n">
-        <v>26.8834</v>
+        <v>9.70495</v>
       </c>
       <c r="E24" t="n">
-        <v>15.825</v>
+        <v>5.55766</v>
       </c>
       <c r="F24" t="n">
-        <v>20.9484</v>
+        <v>5.50479</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>16.1443</v>
+        <v>6.08183</v>
       </c>
       <c r="C25" t="n">
-        <v>21.5597</v>
+        <v>6.26575</v>
       </c>
       <c r="D25" t="n">
-        <v>27.319</v>
+        <v>10.1466</v>
       </c>
       <c r="E25" t="n">
-        <v>16.1957</v>
+        <v>5.59128</v>
       </c>
       <c r="F25" t="n">
-        <v>20.9851</v>
+        <v>5.61243</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>16.9273</v>
+        <v>6.22563</v>
       </c>
       <c r="C26" t="n">
-        <v>21.5892</v>
+        <v>6.30084</v>
       </c>
       <c r="D26" t="n">
-        <v>27.5792</v>
+        <v>10.4517</v>
       </c>
       <c r="E26" t="n">
-        <v>16.2594</v>
+        <v>5.64816</v>
       </c>
       <c r="F26" t="n">
-        <v>21.7892</v>
+        <v>5.32811</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>16.9158</v>
+        <v>6.21734</v>
       </c>
       <c r="C27" t="n">
-        <v>21.903</v>
+        <v>6.31174</v>
       </c>
       <c r="D27" t="n">
-        <v>28.3114</v>
+        <v>10.9733</v>
       </c>
       <c r="E27" t="n">
-        <v>16.6371</v>
+        <v>5.69149</v>
       </c>
       <c r="F27" t="n">
-        <v>21.3887</v>
+        <v>5.34957</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>17.019</v>
+        <v>6.11972</v>
       </c>
       <c r="C28" t="n">
-        <v>21.9392</v>
+        <v>6.29896</v>
       </c>
       <c r="D28" t="n">
-        <v>28.7278</v>
+        <v>11.3625</v>
       </c>
       <c r="E28" t="n">
-        <v>16.7772</v>
+        <v>5.73666</v>
       </c>
       <c r="F28" t="n">
-        <v>21.8564</v>
+        <v>5.70597</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>16.2148</v>
+        <v>6.25199</v>
       </c>
       <c r="C29" t="n">
-        <v>21.6824</v>
+        <v>6.33819</v>
       </c>
       <c r="D29" t="n">
-        <v>29.0497</v>
+        <v>11.7822</v>
       </c>
       <c r="E29" t="n">
-        <v>16.5672</v>
+        <v>5.78184</v>
       </c>
       <c r="F29" t="n">
-        <v>21.4507</v>
+        <v>5.45078</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>16.9983</v>
+        <v>6.08005</v>
       </c>
       <c r="C30" t="n">
-        <v>21.4997</v>
+        <v>6.43753</v>
       </c>
       <c r="D30" t="n">
-        <v>29.5999</v>
+        <v>12.2262</v>
       </c>
       <c r="E30" t="n">
-        <v>16.6645</v>
+        <v>5.84476</v>
       </c>
       <c r="F30" t="n">
-        <v>21.3873</v>
+        <v>5.79203</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>16.9365</v>
+        <v>5.89349</v>
       </c>
       <c r="C31" t="n">
-        <v>21.3288</v>
+        <v>6.20155</v>
       </c>
       <c r="D31" t="n">
-        <v>30.1176</v>
+        <v>12.7249</v>
       </c>
       <c r="E31" t="n">
-        <v>16.4546</v>
+        <v>5.98992</v>
       </c>
       <c r="F31" t="n">
-        <v>21.7841</v>
+        <v>5.95877</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>17.0936</v>
+        <v>6.13532</v>
       </c>
       <c r="C32" t="n">
-        <v>21.8102</v>
+        <v>6.23598</v>
       </c>
       <c r="D32" t="n">
-        <v>30.9687</v>
+        <v>13.0755</v>
       </c>
       <c r="E32" t="n">
-        <v>17.6842</v>
+        <v>5.93573</v>
       </c>
       <c r="F32" t="n">
-        <v>22.1728</v>
+        <v>5.57711</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>17.1069</v>
+        <v>6.17598</v>
       </c>
       <c r="C33" t="n">
-        <v>21.9175</v>
+        <v>6.51661</v>
       </c>
       <c r="D33" t="n">
-        <v>31.5484</v>
+        <v>13.523</v>
       </c>
       <c r="E33" t="n">
-        <v>17.0682</v>
+        <v>6.10265</v>
       </c>
       <c r="F33" t="n">
-        <v>22.7309</v>
+        <v>6.10522</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>17.1961</v>
+        <v>6.2329</v>
       </c>
       <c r="C34" t="n">
-        <v>22.5181</v>
+        <v>6.30154</v>
       </c>
       <c r="D34" t="n">
-        <v>32.1231</v>
+        <v>13.8435</v>
       </c>
       <c r="E34" t="n">
-        <v>17.574</v>
+        <v>6.07203</v>
       </c>
       <c r="F34" t="n">
-        <v>22.2182</v>
+        <v>5.85272</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>17.2866</v>
+        <v>6.50505</v>
       </c>
       <c r="C35" t="n">
-        <v>22.792</v>
+        <v>6.55091</v>
       </c>
       <c r="D35" t="n">
-        <v>26.9526</v>
+        <v>9.52155</v>
       </c>
       <c r="E35" t="n">
-        <v>18.6312</v>
+        <v>6.4108</v>
       </c>
       <c r="F35" t="n">
-        <v>22.6353</v>
+        <v>6.26477</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>17.4743</v>
+        <v>6.07637</v>
       </c>
       <c r="C36" t="n">
-        <v>22.7477</v>
+        <v>6.7261</v>
       </c>
       <c r="D36" t="n">
-        <v>27.0017</v>
+        <v>9.88279</v>
       </c>
       <c r="E36" t="n">
-        <v>18.7164</v>
+        <v>7.04309</v>
       </c>
       <c r="F36" t="n">
-        <v>23.7128</v>
+        <v>6.62287</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>17.7017</v>
+        <v>6.61134</v>
       </c>
       <c r="C37" t="n">
-        <v>22.9158</v>
+        <v>6.63146</v>
       </c>
       <c r="D37" t="n">
-        <v>27.3297</v>
+        <v>10.0942</v>
       </c>
       <c r="E37" t="n">
-        <v>17.286</v>
+        <v>5.6932</v>
       </c>
       <c r="F37" t="n">
-        <v>24.1392</v>
+        <v>5.4793</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>18.2469</v>
+        <v>6.38998</v>
       </c>
       <c r="C38" t="n">
-        <v>24.0206</v>
+        <v>6.58966</v>
       </c>
       <c r="D38" t="n">
-        <v>28.3995</v>
+        <v>10.2028</v>
       </c>
       <c r="E38" t="n">
-        <v>17.7578</v>
+        <v>5.87404</v>
       </c>
       <c r="F38" t="n">
-        <v>23.6928</v>
+        <v>5.47201</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>17.7434</v>
+        <v>6.47146</v>
       </c>
       <c r="C39" t="n">
-        <v>23.8772</v>
+        <v>6.54088</v>
       </c>
       <c r="D39" t="n">
-        <v>28.9624</v>
+        <v>10.7738</v>
       </c>
       <c r="E39" t="n">
-        <v>17.4352</v>
+        <v>5.93744</v>
       </c>
       <c r="F39" t="n">
-        <v>23.7407</v>
+        <v>5.64062</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>18.8004</v>
+        <v>6.45561</v>
       </c>
       <c r="C40" t="n">
-        <v>24.422</v>
+        <v>6.67353</v>
       </c>
       <c r="D40" t="n">
-        <v>29.1492</v>
+        <v>11.3408</v>
       </c>
       <c r="E40" t="n">
-        <v>18.0388</v>
+        <v>5.96848</v>
       </c>
       <c r="F40" t="n">
-        <v>23.927</v>
+        <v>5.65069</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>18.6783</v>
+        <v>6.47442</v>
       </c>
       <c r="C41" t="n">
-        <v>24.4677</v>
+        <v>6.57353</v>
       </c>
       <c r="D41" t="n">
-        <v>29.6739</v>
+        <v>11.6966</v>
       </c>
       <c r="E41" t="n">
-        <v>17.9381</v>
+        <v>6.0022</v>
       </c>
       <c r="F41" t="n">
-        <v>23.4739</v>
+        <v>5.79345</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>17.7082</v>
+        <v>6.49878</v>
       </c>
       <c r="C42" t="n">
-        <v>24.054</v>
+        <v>6.71675</v>
       </c>
       <c r="D42" t="n">
-        <v>30.1068</v>
+        <v>12.3515</v>
       </c>
       <c r="E42" t="n">
-        <v>18.1563</v>
+        <v>6.05621</v>
       </c>
       <c r="F42" t="n">
-        <v>24.6463</v>
+        <v>5.78541</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>18.4093</v>
+        <v>6.53646</v>
       </c>
       <c r="C43" t="n">
-        <v>24.2582</v>
+        <v>6.74587</v>
       </c>
       <c r="D43" t="n">
-        <v>31.8175</v>
+        <v>13.367</v>
       </c>
       <c r="E43" t="n">
-        <v>18.505</v>
+        <v>6.1002</v>
       </c>
       <c r="F43" t="n">
-        <v>23.9333</v>
+        <v>5.84556</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>18.7409</v>
+        <v>6.51414</v>
       </c>
       <c r="C44" t="n">
-        <v>24.295</v>
+        <v>6.75587</v>
       </c>
       <c r="D44" t="n">
-        <v>31.3409</v>
+        <v>13.7066</v>
       </c>
       <c r="E44" t="n">
-        <v>18.8825</v>
+        <v>6.20016</v>
       </c>
       <c r="F44" t="n">
-        <v>23.8157</v>
+        <v>6.09881</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>18.4943</v>
+        <v>6.5783</v>
       </c>
       <c r="C45" t="n">
-        <v>24.4261</v>
+        <v>7.00465</v>
       </c>
       <c r="D45" t="n">
-        <v>32.2858</v>
+        <v>13.9326</v>
       </c>
       <c r="E45" t="n">
-        <v>18.6571</v>
+        <v>6.24357</v>
       </c>
       <c r="F45" t="n">
-        <v>23.9433</v>
+        <v>6.03173</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>18.4928</v>
+        <v>6.56845</v>
       </c>
       <c r="C46" t="n">
-        <v>24.3438</v>
+        <v>6.86066</v>
       </c>
       <c r="D46" t="n">
-        <v>32.9142</v>
+        <v>14.4523</v>
       </c>
       <c r="E46" t="n">
-        <v>18.7251</v>
+        <v>6.32199</v>
       </c>
       <c r="F46" t="n">
-        <v>24.6843</v>
+        <v>6.07882</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>18.5033</v>
+        <v>6.60915</v>
       </c>
       <c r="C47" t="n">
-        <v>24.1443</v>
+        <v>6.93618</v>
       </c>
       <c r="D47" t="n">
-        <v>33.3618</v>
+        <v>15.8124</v>
       </c>
       <c r="E47" t="n">
-        <v>18.9783</v>
+        <v>6.48969</v>
       </c>
       <c r="F47" t="n">
-        <v>24.5275</v>
+        <v>6.3334</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>19.4271</v>
+        <v>6.70572</v>
       </c>
       <c r="C48" t="n">
-        <v>24.7899</v>
+        <v>7.1528</v>
       </c>
       <c r="D48" t="n">
-        <v>34.5155</v>
+        <v>15.9303</v>
       </c>
       <c r="E48" t="n">
-        <v>19.3521</v>
+        <v>6.3789</v>
       </c>
       <c r="F48" t="n">
-        <v>25.5278</v>
+        <v>6.5947</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>19.0347</v>
+        <v>6.81396</v>
       </c>
       <c r="C49" t="n">
-        <v>24.6959</v>
+        <v>7.13651</v>
       </c>
       <c r="D49" t="n">
-        <v>35.6923</v>
+        <v>16.9529</v>
       </c>
       <c r="E49" t="n">
-        <v>19.9305</v>
+        <v>6.95969</v>
       </c>
       <c r="F49" t="n">
-        <v>26.0097</v>
+        <v>7.19232</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>18.1652</v>
+        <v>6.81567</v>
       </c>
       <c r="C50" t="n">
-        <v>24.786</v>
+        <v>7.36417</v>
       </c>
       <c r="D50" t="n">
-        <v>30.0932</v>
+        <v>14.066</v>
       </c>
       <c r="E50" t="n">
-        <v>20.4904</v>
+        <v>7.18437</v>
       </c>
       <c r="F50" t="n">
-        <v>25.2395</v>
+        <v>7.78762</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>19.2728</v>
+        <v>6.99723</v>
       </c>
       <c r="C51" t="n">
-        <v>24.3396</v>
+        <v>7.6821</v>
       </c>
       <c r="D51" t="n">
-        <v>32.1872</v>
+        <v>15.4539</v>
       </c>
       <c r="E51" t="n">
-        <v>19.09</v>
+        <v>5.868</v>
       </c>
       <c r="F51" t="n">
-        <v>25.2704</v>
+        <v>6.35317</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>19.9932</v>
+        <v>7.73079</v>
       </c>
       <c r="C52" t="n">
-        <v>26.0182</v>
+        <v>9.023529999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>32.4551</v>
+        <v>16.2271</v>
       </c>
       <c r="E52" t="n">
-        <v>19.1897</v>
+        <v>5.67596</v>
       </c>
       <c r="F52" t="n">
-        <v>25.2972</v>
+        <v>6.08463</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>20.8765</v>
+        <v>6.68534</v>
       </c>
       <c r="C53" t="n">
-        <v>25.9138</v>
+        <v>8.33778</v>
       </c>
       <c r="D53" t="n">
-        <v>35.0284</v>
+        <v>16.2565</v>
       </c>
       <c r="E53" t="n">
-        <v>18.8209</v>
+        <v>5.77524</v>
       </c>
       <c r="F53" t="n">
-        <v>25.3311</v>
+        <v>6.5808</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>21.1089</v>
+        <v>6.41372</v>
       </c>
       <c r="C54" t="n">
-        <v>26.3705</v>
+        <v>7.76859</v>
       </c>
       <c r="D54" t="n">
-        <v>34.6783</v>
+        <v>17.0997</v>
       </c>
       <c r="E54" t="n">
-        <v>19.3945</v>
+        <v>5.8257</v>
       </c>
       <c r="F54" t="n">
-        <v>25.3407</v>
+        <v>6.76175</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>20.9173</v>
+        <v>6.43461</v>
       </c>
       <c r="C55" t="n">
-        <v>25.9912</v>
+        <v>8.38504</v>
       </c>
       <c r="D55" t="n">
-        <v>40.1837</v>
+        <v>17.6525</v>
       </c>
       <c r="E55" t="n">
-        <v>19.0256</v>
+        <v>5.82392</v>
       </c>
       <c r="F55" t="n">
-        <v>25.7799</v>
+        <v>6.30462</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>20.1825</v>
+        <v>6.54713</v>
       </c>
       <c r="C56" t="n">
-        <v>26.2117</v>
+        <v>8.373139999999999</v>
       </c>
       <c r="D56" t="n">
-        <v>38.1972</v>
+        <v>18.5582</v>
       </c>
       <c r="E56" t="n">
-        <v>19.7641</v>
+        <v>5.87282</v>
       </c>
       <c r="F56" t="n">
-        <v>25.6847</v>
+        <v>6.90966</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>20.5099</v>
+        <v>6.43482</v>
       </c>
       <c r="C57" t="n">
-        <v>26.0139</v>
+        <v>8.10802</v>
       </c>
       <c r="D57" t="n">
-        <v>36.9767</v>
+        <v>20.1403</v>
       </c>
       <c r="E57" t="n">
-        <v>19.8753</v>
+        <v>5.95346</v>
       </c>
       <c r="F57" t="n">
-        <v>25.6002</v>
+        <v>7.13548</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>20.9154</v>
+        <v>6.53635</v>
       </c>
       <c r="C58" t="n">
-        <v>26.4327</v>
+        <v>8.251060000000001</v>
       </c>
       <c r="D58" t="n">
-        <v>41.5426</v>
+        <v>20.3016</v>
       </c>
       <c r="E58" t="n">
-        <v>19.8987</v>
+        <v>6.00572</v>
       </c>
       <c r="F58" t="n">
-        <v>25.9609</v>
+        <v>6.32966</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>20.9978</v>
+        <v>6.46313</v>
       </c>
       <c r="C59" t="n">
-        <v>26.0663</v>
+        <v>8.253450000000001</v>
       </c>
       <c r="D59" t="n">
-        <v>44.4199</v>
+        <v>20.6678</v>
       </c>
       <c r="E59" t="n">
-        <v>20.0611</v>
+        <v>6.08586</v>
       </c>
       <c r="F59" t="n">
-        <v>25.707</v>
+        <v>6.35543</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>20.3603</v>
+        <v>6.34067</v>
       </c>
       <c r="C60" t="n">
-        <v>26.5125</v>
+        <v>7.19656</v>
       </c>
       <c r="D60" t="n">
-        <v>47.4476</v>
+        <v>20.6327</v>
       </c>
       <c r="E60" t="n">
-        <v>20.2677</v>
+        <v>6.17978</v>
       </c>
       <c r="F60" t="n">
-        <v>26.2943</v>
+        <v>6.93794</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>21.1555</v>
+        <v>6.56452</v>
       </c>
       <c r="C61" t="n">
-        <v>26.1392</v>
+        <v>8.26741</v>
       </c>
       <c r="D61" t="n">
-        <v>48.754</v>
+        <v>21.573</v>
       </c>
       <c r="E61" t="n">
-        <v>20.3461</v>
+        <v>6.35241</v>
       </c>
       <c r="F61" t="n">
-        <v>25.7588</v>
+        <v>6.66729</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>21.0925</v>
+        <v>6.67426</v>
       </c>
       <c r="C62" t="n">
-        <v>26.4722</v>
+        <v>7.33701</v>
       </c>
       <c r="D62" t="n">
-        <v>54.714</v>
+        <v>21.2483</v>
       </c>
       <c r="E62" t="n">
-        <v>20.8572</v>
+        <v>6.63242</v>
       </c>
       <c r="F62" t="n">
-        <v>26.0076</v>
+        <v>8.15138</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>21.2013</v>
+        <v>6.73671</v>
       </c>
       <c r="C63" t="n">
-        <v>26.4649</v>
+        <v>7.47529</v>
       </c>
       <c r="D63" t="n">
-        <v>54.2994</v>
+        <v>21.6179</v>
       </c>
       <c r="E63" t="n">
-        <v>21.3304</v>
+        <v>6.92604</v>
       </c>
       <c r="F63" t="n">
-        <v>26.9114</v>
+        <v>8.558260000000001</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>21.2587</v>
+        <v>6.93412</v>
       </c>
       <c r="C64" t="n">
-        <v>26.8807</v>
+        <v>7.76453</v>
       </c>
       <c r="D64" t="n">
-        <v>58.6508</v>
+        <v>14.7132</v>
       </c>
       <c r="E64" t="n">
-        <v>21.9689</v>
+        <v>7.30127</v>
       </c>
       <c r="F64" t="n">
-        <v>27.3983</v>
+        <v>8.33963</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>21.6698</v>
+        <v>7.17893</v>
       </c>
       <c r="C65" t="n">
-        <v>27.0566</v>
+        <v>9.09872</v>
       </c>
       <c r="D65" t="n">
-        <v>61.4104</v>
+        <v>15.286</v>
       </c>
       <c r="E65" t="n">
-        <v>22.2927</v>
+        <v>7.90904</v>
       </c>
       <c r="F65" t="n">
-        <v>28.4567</v>
+        <v>9.52894</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>22.2485</v>
+        <v>7.60247</v>
       </c>
       <c r="C66" t="n">
-        <v>27.9883</v>
+        <v>8.78931</v>
       </c>
       <c r="D66" t="n">
-        <v>64.5089</v>
+        <v>15.9301</v>
       </c>
       <c r="E66" t="n">
-        <v>19.6264</v>
+        <v>6.20712</v>
       </c>
       <c r="F66" t="n">
-        <v>28.2938</v>
+        <v>7.1338</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>21.9351</v>
+        <v>8.68004</v>
       </c>
       <c r="C67" t="n">
-        <v>32.355</v>
+        <v>8.31329</v>
       </c>
       <c r="D67" t="n">
-        <v>67.89830000000001</v>
+        <v>16.9587</v>
       </c>
       <c r="E67" t="n">
-        <v>19.9461</v>
+        <v>6.20953</v>
       </c>
       <c r="F67" t="n">
-        <v>27.7483</v>
+        <v>7.19491</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>21.9599</v>
+        <v>8.418480000000001</v>
       </c>
       <c r="C68" t="n">
-        <v>31.2684</v>
+        <v>8.48305</v>
       </c>
       <c r="D68" t="n">
-        <v>71.06180000000001</v>
+        <v>18.2635</v>
       </c>
       <c r="E68" t="n">
-        <v>19.8477</v>
+        <v>6.27605</v>
       </c>
       <c r="F68" t="n">
-        <v>29.5588</v>
+        <v>7.31097</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>23.1957</v>
+        <v>8.504350000000001</v>
       </c>
       <c r="C69" t="n">
-        <v>31.4685</v>
+        <v>8.57483</v>
       </c>
       <c r="D69" t="n">
-        <v>77.7133</v>
+        <v>19.4116</v>
       </c>
       <c r="E69" t="n">
-        <v>20.2669</v>
+        <v>6.36939</v>
       </c>
       <c r="F69" t="n">
-        <v>29.7182</v>
+        <v>7.46091</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>23.6186</v>
+        <v>8.50104</v>
       </c>
       <c r="C70" t="n">
-        <v>32.1435</v>
+        <v>8.608890000000001</v>
       </c>
       <c r="D70" t="n">
-        <v>76.6669</v>
+        <v>19.0376</v>
       </c>
       <c r="E70" t="n">
-        <v>19.9552</v>
+        <v>6.47293</v>
       </c>
       <c r="F70" t="n">
-        <v>29.7144</v>
+        <v>7.34495</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>23.4037</v>
+        <v>8.53027</v>
       </c>
       <c r="C71" t="n">
-        <v>30.7551</v>
+        <v>8.612349999999999</v>
       </c>
       <c r="D71" t="n">
-        <v>80.9359</v>
+        <v>19.9843</v>
       </c>
       <c r="E71" t="n">
-        <v>20.0491</v>
+        <v>6.57208</v>
       </c>
       <c r="F71" t="n">
-        <v>34.1743</v>
+        <v>7.12107</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>23.7689</v>
+        <v>10.5082</v>
       </c>
       <c r="C72" t="n">
-        <v>33.6829</v>
+        <v>8.685829999999999</v>
       </c>
       <c r="D72" t="n">
-        <v>85.2102</v>
+        <v>20.3066</v>
       </c>
       <c r="E72" t="n">
-        <v>19.7153</v>
+        <v>6.67204</v>
       </c>
       <c r="F72" t="n">
-        <v>28.7992</v>
+        <v>7.24862</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>23.3694</v>
+        <v>8.55996</v>
       </c>
       <c r="C73" t="n">
-        <v>32.4466</v>
+        <v>8.756729999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>88.2179</v>
+        <v>20.8671</v>
       </c>
       <c r="E73" t="n">
-        <v>20.3325</v>
+        <v>6.79358</v>
       </c>
       <c r="F73" t="n">
-        <v>29.2025</v>
+        <v>7.40584</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>23.2417</v>
+        <v>10.9903</v>
       </c>
       <c r="C74" t="n">
-        <v>32.7573</v>
+        <v>8.88622</v>
       </c>
       <c r="D74" t="n">
-        <v>92.2088</v>
+        <v>21.3666</v>
       </c>
       <c r="E74" t="n">
-        <v>20.4387</v>
+        <v>8.00249</v>
       </c>
       <c r="F74" t="n">
-        <v>28.0311</v>
+        <v>16.6076</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>23.2726</v>
+        <v>10.8208</v>
       </c>
       <c r="C75" t="n">
-        <v>32.7857</v>
+        <v>8.65893</v>
       </c>
       <c r="D75" t="n">
-        <v>96.40689999999999</v>
+        <v>26.3032</v>
       </c>
       <c r="E75" t="n">
-        <v>20.6694</v>
+        <v>8.02721</v>
       </c>
       <c r="F75" t="n">
-        <v>29.3338</v>
+        <v>8.05646</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>23.3593</v>
+        <v>11.1075</v>
       </c>
       <c r="C76" t="n">
-        <v>32.8775</v>
+        <v>8.779439999999999</v>
       </c>
       <c r="D76" t="n">
-        <v>100.442</v>
+        <v>24.0059</v>
       </c>
       <c r="E76" t="n">
-        <v>21.1592</v>
+        <v>8.394740000000001</v>
       </c>
       <c r="F76" t="n">
-        <v>31.4941</v>
+        <v>8.42015</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>23.4469</v>
+        <v>11.258</v>
       </c>
       <c r="C77" t="n">
-        <v>33.2108</v>
+        <v>9.34066</v>
       </c>
       <c r="D77" t="n">
-        <v>104.626</v>
+        <v>21.9853</v>
       </c>
       <c r="E77" t="n">
-        <v>21.013</v>
+        <v>8.66412</v>
       </c>
       <c r="F77" t="n">
-        <v>30.1186</v>
+        <v>9.05804</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>23.6095</v>
+        <v>11.3519</v>
       </c>
       <c r="C78" t="n">
-        <v>34.2015</v>
+        <v>9.38219</v>
       </c>
       <c r="D78" t="n">
-        <v>99.0818</v>
+        <v>20.9003</v>
       </c>
       <c r="E78" t="n">
-        <v>21.5701</v>
+        <v>9.0947</v>
       </c>
       <c r="F78" t="n">
-        <v>31.1671</v>
+        <v>9.34587</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>24.0026</v>
+        <v>9.891909999999999</v>
       </c>
       <c r="C79" t="n">
-        <v>33.3097</v>
+        <v>9.80025</v>
       </c>
       <c r="D79" t="n">
-        <v>99.9068</v>
+        <v>21.6101</v>
       </c>
       <c r="E79" t="n">
-        <v>22.8572</v>
+        <v>9.600160000000001</v>
       </c>
       <c r="F79" t="n">
-        <v>32.8196</v>
+        <v>10.2999</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>24.6985</v>
+        <v>11.8403</v>
       </c>
       <c r="C80" t="n">
-        <v>35.7959</v>
+        <v>10.5607</v>
       </c>
       <c r="D80" t="n">
-        <v>103.469</v>
+        <v>23.0925</v>
       </c>
       <c r="E80" t="n">
-        <v>27.059</v>
+        <v>10.5327</v>
       </c>
       <c r="F80" t="n">
-        <v>57.5039</v>
+        <v>13.264</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>45.0016</v>
+        <v>20.1525</v>
       </c>
       <c r="C81" t="n">
-        <v>65.20910000000001</v>
+        <v>17.2405</v>
       </c>
       <c r="D81" t="n">
-        <v>107.058</v>
+        <v>23.7098</v>
       </c>
       <c r="E81" t="n">
-        <v>28.2574</v>
+        <v>11.4065</v>
       </c>
       <c r="F81" t="n">
-        <v>60.6027</v>
+        <v>13.6497</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>44.2102</v>
+        <v>20.2431</v>
       </c>
       <c r="C82" t="n">
-        <v>66.28440000000001</v>
+        <v>16.9954</v>
       </c>
       <c r="D82" t="n">
-        <v>107.746</v>
+        <v>25.2264</v>
       </c>
       <c r="E82" t="n">
-        <v>30.4666</v>
+        <v>11.5293</v>
       </c>
       <c r="F82" t="n">
-        <v>58.7642</v>
+        <v>13.6282</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>38.5318</v>
+        <v>20.3843</v>
       </c>
       <c r="C83" t="n">
-        <v>63.4704</v>
+        <v>17.0534</v>
       </c>
       <c r="D83" t="n">
-        <v>111.737</v>
+        <v>26.1536</v>
       </c>
       <c r="E83" t="n">
-        <v>27.8373</v>
+        <v>11.9257</v>
       </c>
       <c r="F83" t="n">
-        <v>59.3812</v>
+        <v>13.8501</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>43.7841</v>
+        <v>20.4356</v>
       </c>
       <c r="C84" t="n">
-        <v>65.49720000000001</v>
+        <v>17.44</v>
       </c>
       <c r="D84" t="n">
-        <v>112.87</v>
+        <v>26.9807</v>
       </c>
       <c r="E84" t="n">
-        <v>29.7487</v>
+        <v>12.3316</v>
       </c>
       <c r="F84" t="n">
-        <v>59.7156</v>
+        <v>14.06</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>44.1697</v>
+        <v>20.5566</v>
       </c>
       <c r="C85" t="n">
-        <v>64.152</v>
+        <v>16.5153</v>
       </c>
       <c r="D85" t="n">
-        <v>116.566</v>
+        <v>27.7483</v>
       </c>
       <c r="E85" t="n">
-        <v>30.3962</v>
+        <v>12.8004</v>
       </c>
       <c r="F85" t="n">
-        <v>58.1798</v>
+        <v>13.1841</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>40.2435</v>
+        <v>20.466</v>
       </c>
       <c r="C86" t="n">
-        <v>64.5043</v>
+        <v>16.5413</v>
       </c>
       <c r="D86" t="n">
-        <v>119.901</v>
+        <v>29.4324</v>
       </c>
       <c r="E86" t="n">
-        <v>29.7328</v>
+        <v>13.1864</v>
       </c>
       <c r="F86" t="n">
-        <v>59.6763</v>
+        <v>13.5131</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>44.5354</v>
+        <v>20.6084</v>
       </c>
       <c r="C87" t="n">
-        <v>64.1932</v>
+        <v>16.6436</v>
       </c>
       <c r="D87" t="n">
-        <v>136.731</v>
+        <v>29.9029</v>
       </c>
       <c r="E87" t="n">
-        <v>30.461</v>
+        <v>13.2322</v>
       </c>
       <c r="F87" t="n">
-        <v>60.8267</v>
+        <v>13.1104</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>46.8278</v>
+        <v>20.5422</v>
       </c>
       <c r="C88" t="n">
-        <v>64.0454</v>
+        <v>16.7847</v>
       </c>
       <c r="D88" t="n">
-        <v>128.254</v>
+        <v>31.2649</v>
       </c>
       <c r="E88" t="n">
-        <v>32.5633</v>
+        <v>13.7194</v>
       </c>
       <c r="F88" t="n">
-        <v>58.4714</v>
+        <v>14.2354</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>44.5403</v>
+        <v>20.6911</v>
       </c>
       <c r="C89" t="n">
-        <v>63.9768</v>
+        <v>16.902</v>
       </c>
       <c r="D89" t="n">
-        <v>134.93</v>
+        <v>32.4646</v>
       </c>
       <c r="E89" t="n">
-        <v>31.7359</v>
+        <v>14.1705</v>
       </c>
       <c r="F89" t="n">
-        <v>61.1912</v>
+        <v>14.728</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>41.3935</v>
+        <v>20.6908</v>
       </c>
       <c r="C90" t="n">
-        <v>66.29770000000001</v>
+        <v>17.1437</v>
       </c>
       <c r="D90" t="n">
-        <v>134.953</v>
+        <v>33.3649</v>
       </c>
       <c r="E90" t="n">
-        <v>28.1647</v>
+        <v>14.4777</v>
       </c>
       <c r="F90" t="n">
-        <v>59.3979</v>
+        <v>13.8288</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>43.0715</v>
+        <v>20.8927</v>
       </c>
       <c r="C91" t="n">
-        <v>64.47490000000001</v>
+        <v>17.4496</v>
       </c>
       <c r="D91" t="n">
-        <v>140.746</v>
+        <v>34.7116</v>
       </c>
       <c r="E91" t="n">
-        <v>33.0106</v>
+        <v>14.8369</v>
       </c>
       <c r="F91" t="n">
-        <v>60.9128</v>
+        <v>14.2013</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>44.5833</v>
+        <v>20.9439</v>
       </c>
       <c r="C92" t="n">
-        <v>65.91419999999999</v>
+        <v>17.3836</v>
       </c>
       <c r="D92" t="n">
-        <v>123.819</v>
+        <v>33.1497</v>
       </c>
       <c r="E92" t="n">
-        <v>33.9565</v>
+        <v>15.3623</v>
       </c>
       <c r="F92" t="n">
-        <v>61.5944</v>
+        <v>16.1591</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>45.1165</v>
+        <v>20.9837</v>
       </c>
       <c r="C93" t="n">
-        <v>64.092</v>
+        <v>18.3935</v>
       </c>
       <c r="D93" t="n">
-        <v>125.78</v>
+        <v>33.7783</v>
       </c>
       <c r="E93" t="n">
-        <v>30.982</v>
+        <v>15.85</v>
       </c>
       <c r="F93" t="n">
-        <v>62.4255</v>
+        <v>18.8129</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>40.6542</v>
+        <v>21.2685</v>
       </c>
       <c r="C94" t="n">
-        <v>67.15860000000001</v>
+        <v>19.7671</v>
       </c>
       <c r="D94" t="n">
-        <v>126.972</v>
+        <v>34.4502</v>
       </c>
       <c r="E94" t="n">
-        <v>52.3676</v>
+        <v>23.0609</v>
       </c>
       <c r="F94" t="n">
-        <v>85.2319</v>
+        <v>22.874</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>72.9457</v>
+        <v>28.2567</v>
       </c>
       <c r="C95" t="n">
-        <v>91.43389999999999</v>
+        <v>25.8325</v>
       </c>
       <c r="D95" t="n">
-        <v>131.419</v>
+        <v>35.6945</v>
       </c>
       <c r="E95" t="n">
-        <v>57.0656</v>
+        <v>23.3308</v>
       </c>
       <c r="F95" t="n">
-        <v>84.95350000000001</v>
+        <v>22.9938</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>72.9517</v>
+        <v>28.4768</v>
       </c>
       <c r="C96" t="n">
-        <v>89.8785</v>
+        <v>25.5901</v>
       </c>
       <c r="D96" t="n">
-        <v>133.125</v>
+        <v>36.3938</v>
       </c>
       <c r="E96" t="n">
-        <v>57.77</v>
+        <v>23.5067</v>
       </c>
       <c r="F96" t="n">
-        <v>85.8085</v>
+        <v>23.17</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>72.6803</v>
+        <v>28.5353</v>
       </c>
       <c r="C97" t="n">
-        <v>90.2281</v>
+        <v>25.783</v>
       </c>
       <c r="D97" t="n">
-        <v>135.831</v>
+        <v>37.4032</v>
       </c>
       <c r="E97" t="n">
-        <v>57.7606</v>
+        <v>23.6422</v>
       </c>
       <c r="F97" t="n">
-        <v>84.5629</v>
+        <v>23.3787</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>72.2885</v>
+        <v>28.5023</v>
       </c>
       <c r="C98" t="n">
-        <v>89.459</v>
+        <v>25.8585</v>
       </c>
       <c r="D98" t="n">
-        <v>138.726</v>
+        <v>38.0974</v>
       </c>
       <c r="E98" t="n">
-        <v>58.0845</v>
+        <v>23.8888</v>
       </c>
       <c r="F98" t="n">
-        <v>92.3189</v>
+        <v>23.4064</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>72.81480000000001</v>
+        <v>28.5755</v>
       </c>
       <c r="C99" t="n">
-        <v>89.5108</v>
+        <v>25.8716</v>
       </c>
       <c r="D99" t="n">
-        <v>142.382</v>
+        <v>38.8767</v>
       </c>
       <c r="E99" t="n">
-        <v>58.8629</v>
+        <v>24.054</v>
       </c>
       <c r="F99" t="n">
-        <v>85.3656</v>
+        <v>23.5292</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>72.8402</v>
+        <v>28.4997</v>
       </c>
       <c r="C100" t="n">
-        <v>90.7757</v>
+        <v>25.8974</v>
       </c>
       <c r="D100" t="n">
-        <v>145.341</v>
+        <v>39.9206</v>
       </c>
       <c r="E100" t="n">
-        <v>59.7491</v>
+        <v>24.2688</v>
       </c>
       <c r="F100" t="n">
-        <v>93.0377</v>
+        <v>23.6613</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>67.66419999999999</v>
+        <v>28.521</v>
       </c>
       <c r="C101" t="n">
-        <v>89.611</v>
+        <v>25.9897</v>
       </c>
       <c r="D101" t="n">
-        <v>148.267</v>
+        <v>40.8666</v>
       </c>
       <c r="E101" t="n">
-        <v>58.7738</v>
+        <v>24.4049</v>
       </c>
       <c r="F101" t="n">
-        <v>87.3293</v>
+        <v>23.8141</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>71.5622</v>
+        <v>28.6516</v>
       </c>
       <c r="C102" t="n">
-        <v>89.08929999999999</v>
+        <v>26.0509</v>
       </c>
       <c r="D102" t="n">
-        <v>154.802</v>
+        <v>41.8801</v>
       </c>
       <c r="E102" t="n">
-        <v>60.9188</v>
+        <v>24.8118</v>
       </c>
       <c r="F102" t="n">
-        <v>86.70869999999999</v>
+        <v>24.0899</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>67.4486</v>
+        <v>28.6059</v>
       </c>
       <c r="C103" t="n">
-        <v>90.6973</v>
+        <v>26.273</v>
       </c>
       <c r="D103" t="n">
-        <v>156.963</v>
+        <v>42.8955</v>
       </c>
       <c r="E103" t="n">
-        <v>61.4233</v>
+        <v>24.6977</v>
       </c>
       <c r="F103" t="n">
-        <v>87.3446</v>
+        <v>24.3661</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>72.45099999999999</v>
+        <v>28.6429</v>
       </c>
       <c r="C104" t="n">
-        <v>89.0185</v>
+        <v>26.3509</v>
       </c>
       <c r="D104" t="n">
-        <v>178.619</v>
+        <v>44.3236</v>
       </c>
       <c r="E104" t="n">
-        <v>61.7118</v>
+        <v>25.0908</v>
       </c>
       <c r="F104" t="n">
-        <v>86.68470000000001</v>
+        <v>24.6665</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>71.2122</v>
+        <v>28.7289</v>
       </c>
       <c r="C105" t="n">
-        <v>90.6469</v>
+        <v>26.5401</v>
       </c>
       <c r="D105" t="n">
-        <v>180.298</v>
+        <v>45.3779</v>
       </c>
       <c r="E105" t="n">
-        <v>62.3603</v>
+        <v>25.2913</v>
       </c>
       <c r="F105" t="n">
-        <v>89.9132</v>
+        <v>25.7025</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>71.8167</v>
+        <v>28.8346</v>
       </c>
       <c r="C106" t="n">
-        <v>91.9058</v>
+        <v>26.7619</v>
       </c>
       <c r="D106" t="n">
-        <v>183.255</v>
+        <v>47.2464</v>
       </c>
       <c r="E106" t="n">
-        <v>62.9726</v>
+        <v>25.5403</v>
       </c>
       <c r="F106" t="n">
-        <v>88.7255</v>
+        <v>25.3724</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>72.3237</v>
+        <v>28.9155</v>
       </c>
       <c r="C107" t="n">
-        <v>92.5226</v>
+        <v>27.1496</v>
       </c>
       <c r="D107" t="n">
-        <v>139.575</v>
+        <v>40.5468</v>
       </c>
       <c r="E107" t="n">
-        <v>60.1689</v>
+        <v>26.0939</v>
       </c>
       <c r="F107" t="n">
-        <v>90.4033</v>
+        <v>25.9742</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>69.41379999999999</v>
+        <v>29.2635</v>
       </c>
       <c r="C108" t="n">
-        <v>93.8477</v>
+        <v>27.6533</v>
       </c>
       <c r="D108" t="n">
-        <v>142.242</v>
+        <v>41.2824</v>
       </c>
       <c r="E108" t="n">
-        <v>77.1683</v>
+        <v>29.9162</v>
       </c>
       <c r="F108" t="n">
-        <v>107.272</v>
+        <v>29.0754</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>71.7704</v>
+        <v>29.5871</v>
       </c>
       <c r="C109" t="n">
-        <v>93.2146</v>
+        <v>28.5433</v>
       </c>
       <c r="D109" t="n">
-        <v>143.034</v>
+        <v>41.845</v>
       </c>
       <c r="E109" t="n">
-        <v>77.4833</v>
+        <v>30.1652</v>
       </c>
       <c r="F109" t="n">
-        <v>108.64</v>
+        <v>29.8387</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>86.7865</v>
+        <v>32.8967</v>
       </c>
       <c r="C110" t="n">
-        <v>110.6</v>
+        <v>32.2586</v>
       </c>
       <c r="D110" t="n">
-        <v>146.336</v>
+        <v>42.759</v>
       </c>
       <c r="E110" t="n">
-        <v>78.6498</v>
+        <v>30.5346</v>
       </c>
       <c r="F110" t="n">
-        <v>109.984</v>
+        <v>30.1272</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>88.22580000000001</v>
+        <v>33.063</v>
       </c>
       <c r="C111" t="n">
-        <v>112.782</v>
+        <v>32.3993</v>
       </c>
       <c r="D111" t="n">
-        <v>148.935</v>
+        <v>43.5669</v>
       </c>
       <c r="E111" t="n">
-        <v>76.79989999999999</v>
+        <v>30.7435</v>
       </c>
       <c r="F111" t="n">
-        <v>110.091</v>
+        <v>30.4049</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>88.27549999999999</v>
+        <v>33.0892</v>
       </c>
       <c r="C112" t="n">
-        <v>112.625</v>
+        <v>32.3433</v>
       </c>
       <c r="D112" t="n">
-        <v>150.924</v>
+        <v>44.5292</v>
       </c>
       <c r="E112" t="n">
-        <v>79.15219999999999</v>
+        <v>31.0135</v>
       </c>
       <c r="F112" t="n">
-        <v>109.902</v>
+        <v>30.5803</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>88.584</v>
+        <v>32.9222</v>
       </c>
       <c r="C113" t="n">
-        <v>113.541</v>
+        <v>32.3793</v>
       </c>
       <c r="D113" t="n">
-        <v>155.654</v>
+        <v>45.2139</v>
       </c>
       <c r="E113" t="n">
-        <v>79.3441</v>
+        <v>31.3181</v>
       </c>
       <c r="F113" t="n">
-        <v>111.477</v>
+        <v>30.8795</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>87.4297</v>
+        <v>32.8727</v>
       </c>
       <c r="C114" t="n">
-        <v>111.169</v>
+        <v>32.5226</v>
       </c>
       <c r="D114" t="n">
-        <v>158.377</v>
+        <v>46.1366</v>
       </c>
       <c r="E114" t="n">
-        <v>79.95229999999999</v>
+        <v>31.5154</v>
       </c>
       <c r="F114" t="n">
-        <v>110.915</v>
+        <v>31.1852</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>88.2064</v>
+        <v>33.022</v>
       </c>
       <c r="C115" t="n">
-        <v>112.355</v>
+        <v>32.9524</v>
       </c>
       <c r="D115" t="n">
-        <v>161.807</v>
+        <v>47.2104</v>
       </c>
       <c r="E115" t="n">
-        <v>79.05889999999999</v>
+        <v>31.7591</v>
       </c>
       <c r="F115" t="n">
-        <v>112.076</v>
+        <v>31.4007</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>86.96550000000001</v>
+        <v>32.9969</v>
       </c>
       <c r="C116" t="n">
-        <v>113.463</v>
+        <v>32.7887</v>
       </c>
       <c r="D116" t="n">
-        <v>165.974</v>
+        <v>48.0645</v>
       </c>
       <c r="E116" t="n">
-        <v>81.0951</v>
+        <v>32.0457</v>
       </c>
       <c r="F116" t="n">
-        <v>111.088</v>
+        <v>31.7307</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>88.2204</v>
+        <v>33.1538</v>
       </c>
       <c r="C117" t="n">
-        <v>114.986</v>
+        <v>32.7977</v>
       </c>
       <c r="D117" t="n">
-        <v>170.535</v>
+        <v>49.3176</v>
       </c>
       <c r="E117" t="n">
-        <v>79.98650000000001</v>
+        <v>32.3827</v>
       </c>
       <c r="F117" t="n">
-        <v>114.375</v>
+        <v>32.0751</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>89.2576</v>
+        <v>33.0345</v>
       </c>
       <c r="C118" t="n">
-        <v>111.644</v>
+        <v>32.8154</v>
       </c>
       <c r="D118" t="n">
-        <v>180.536</v>
+        <v>50.3334</v>
       </c>
       <c r="E118" t="n">
-        <v>82.6388</v>
+        <v>32.5996</v>
       </c>
       <c r="F118" t="n">
-        <v>112.061</v>
+        <v>32.1542</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>88.52030000000001</v>
+        <v>32.991</v>
       </c>
       <c r="C119" t="n">
-        <v>113.596</v>
+        <v>32.9603</v>
       </c>
       <c r="D119" t="n">
-        <v>178.914</v>
+        <v>51.4686</v>
       </c>
       <c r="E119" t="n">
-        <v>83.1528</v>
+        <v>33.0497</v>
       </c>
       <c r="F119" t="n">
-        <v>115.174</v>
+        <v>33.0482</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>88.1712</v>
+        <v>33.291</v>
       </c>
       <c r="C120" t="n">
-        <v>114.307</v>
+        <v>33.4837</v>
       </c>
       <c r="D120" t="n">
-        <v>195.461</v>
+        <v>52.7793</v>
       </c>
       <c r="E120" t="n">
-        <v>83.82250000000001</v>
+        <v>33.5677</v>
       </c>
       <c r="F120" t="n">
-        <v>113.588</v>
+        <v>33.1985</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>89.30840000000001</v>
+        <v>33.5657</v>
       </c>
       <c r="C121" t="n">
-        <v>114.187</v>
+        <v>33.9457</v>
       </c>
       <c r="D121" t="n">
-        <v>145.728</v>
+        <v>43.7134</v>
       </c>
       <c r="E121" t="n">
-        <v>85.964</v>
+        <v>34.1048</v>
       </c>
       <c r="F121" t="n">
-        <v>117.724</v>
+        <v>34.5044</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>90.2076</v>
+        <v>33.5872</v>
       </c>
       <c r="C122" t="n">
-        <v>112.168</v>
+        <v>34.2648</v>
       </c>
       <c r="D122" t="n">
-        <v>148.693</v>
+        <v>44.4983</v>
       </c>
       <c r="E122" t="n">
-        <v>86.48099999999999</v>
+        <v>34.9403</v>
       </c>
       <c r="F122" t="n">
-        <v>119.221</v>
+        <v>35.7517</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>102.939</v>
+        <v>34.1306</v>
       </c>
       <c r="C123" t="n">
-        <v>114.724</v>
+        <v>35.0234</v>
       </c>
       <c r="D123" t="n">
-        <v>151.443</v>
+        <v>45.1118</v>
       </c>
       <c r="E123" t="n">
-        <v>92.6429</v>
+        <v>36.1031</v>
       </c>
       <c r="F123" t="n">
-        <v>133.421</v>
+        <v>34.221</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>112.815</v>
+        <v>42.4247</v>
       </c>
       <c r="C124" t="n">
-        <v>134.441</v>
+        <v>41.2091</v>
       </c>
       <c r="D124" t="n">
-        <v>153.504</v>
+        <v>45.951</v>
       </c>
       <c r="E124" t="n">
-        <v>92.9992</v>
+        <v>36.4253</v>
       </c>
       <c r="F124" t="n">
-        <v>132.888</v>
+        <v>34.5143</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>110.934</v>
+        <v>42.1616</v>
       </c>
       <c r="C125" t="n">
-        <v>137.126</v>
+        <v>41.3122</v>
       </c>
       <c r="D125" t="n">
-        <v>156.234</v>
+        <v>46.7442</v>
       </c>
       <c r="E125" t="n">
-        <v>93.3648</v>
+        <v>36.8643</v>
       </c>
       <c r="F125" t="n">
-        <v>133.656</v>
+        <v>34.9536</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>112.148</v>
+        <v>42.5497</v>
       </c>
       <c r="C126" t="n">
-        <v>137.292</v>
+        <v>41.2691</v>
       </c>
       <c r="D126" t="n">
-        <v>158.944</v>
+        <v>47.3597</v>
       </c>
       <c r="E126" t="n">
-        <v>93.5427</v>
+        <v>37.1426</v>
       </c>
       <c r="F126" t="n">
-        <v>134.036</v>
+        <v>35.2599</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>109.144</v>
+        <v>42.4668</v>
       </c>
       <c r="C127" t="n">
-        <v>136.729</v>
+        <v>41.4526</v>
       </c>
       <c r="D127" t="n">
-        <v>161.715</v>
+        <v>48.2464</v>
       </c>
       <c r="E127" t="n">
-        <v>92.7508</v>
+        <v>37.4848</v>
       </c>
       <c r="F127" t="n">
-        <v>132.689</v>
+        <v>35.5487</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>111.181</v>
+        <v>42.5309</v>
       </c>
       <c r="C128" t="n">
-        <v>137.494</v>
+        <v>41.4753</v>
       </c>
       <c r="D128" t="n">
-        <v>165.622</v>
+        <v>49.2541</v>
       </c>
       <c r="E128" t="n">
-        <v>94.95569999999999</v>
+        <v>37.8143</v>
       </c>
       <c r="F128" t="n">
-        <v>133.271</v>
+        <v>35.7496</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>108.457</v>
+        <v>42.5065</v>
       </c>
       <c r="C129" t="n">
-        <v>137.418</v>
+        <v>41.6871</v>
       </c>
       <c r="D129" t="n">
-        <v>176.896</v>
+        <v>50.1871</v>
       </c>
       <c r="E129" t="n">
-        <v>95.7569</v>
+        <v>38.2018</v>
       </c>
       <c r="F129" t="n">
-        <v>135.285</v>
+        <v>36.2089</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>112.027</v>
+        <v>42.5674</v>
       </c>
       <c r="C130" t="n">
-        <v>142.441</v>
+        <v>41.7119</v>
       </c>
       <c r="D130" t="n">
-        <v>183.493</v>
+        <v>51.1545</v>
       </c>
       <c r="E130" t="n">
-        <v>99.9935</v>
+        <v>38.5883</v>
       </c>
       <c r="F130" t="n">
-        <v>139.773</v>
+        <v>36.6981</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>115.436</v>
+        <v>42.5821</v>
       </c>
       <c r="C131" t="n">
-        <v>136.431</v>
+        <v>41.8853</v>
       </c>
       <c r="D131" t="n">
-        <v>183.281</v>
+        <v>52.3162</v>
       </c>
       <c r="E131" t="n">
-        <v>96.89449999999999</v>
+        <v>38.9777</v>
       </c>
       <c r="F131" t="n">
-        <v>136.053</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>115.147</v>
+        <v>42.6328</v>
       </c>
       <c r="C132" t="n">
-        <v>136.211</v>
+        <v>42.0411</v>
       </c>
       <c r="D132" t="n">
-        <v>186.76</v>
+        <v>53.5106</v>
       </c>
       <c r="E132" t="n">
-        <v>97.301</v>
+        <v>39.4499</v>
       </c>
       <c r="F132" t="n">
-        <v>136.918</v>
+        <v>37.68</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>110.881</v>
+        <v>42.7574</v>
       </c>
       <c r="C133" t="n">
-        <v>139.257</v>
+        <v>42.2177</v>
       </c>
       <c r="D133" t="n">
-        <v>191.686</v>
+        <v>54.7791</v>
       </c>
       <c r="E133" t="n">
-        <v>97.3524</v>
+        <v>39.957</v>
       </c>
       <c r="F133" t="n">
-        <v>137.857</v>
+        <v>38.3295</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>113.402</v>
+        <v>42.7324</v>
       </c>
       <c r="C134" t="n">
-        <v>149.884</v>
+        <v>42.6116</v>
       </c>
       <c r="D134" t="n">
-        <v>194.718</v>
+        <v>55.7861</v>
       </c>
       <c r="E134" t="n">
-        <v>98.8318</v>
+        <v>40.5698</v>
       </c>
       <c r="F134" t="n">
-        <v>142.884</v>
+        <v>39.2085</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>119.137</v>
+        <v>43.0311</v>
       </c>
       <c r="C135" t="n">
-        <v>143.335</v>
+        <v>43.0421</v>
       </c>
       <c r="D135" t="n">
-        <v>156.311</v>
+        <v>45.7088</v>
       </c>
       <c r="E135" t="n">
-        <v>105.473</v>
+        <v>41.4242</v>
       </c>
       <c r="F135" t="n">
-        <v>142.631</v>
+        <v>40.2754</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>116.299</v>
+        <v>43.2292</v>
       </c>
       <c r="C136" t="n">
-        <v>144.884</v>
+        <v>43.6476</v>
       </c>
       <c r="D136" t="n">
-        <v>159.44</v>
+        <v>46.2723</v>
       </c>
       <c r="E136" t="n">
-        <v>108.387</v>
+        <v>42.4459</v>
       </c>
       <c r="F136" t="n">
-        <v>145.106</v>
+        <v>41.7464</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>116.812</v>
+        <v>43.6075</v>
       </c>
       <c r="C137" t="n">
-        <v>146.531</v>
+        <v>44.5253</v>
       </c>
       <c r="D137" t="n">
-        <v>164.087</v>
+        <v>46.7207</v>
       </c>
       <c r="E137" t="n">
-        <v>108.302</v>
+        <v>39.3995</v>
       </c>
       <c r="F137" t="n">
-        <v>154.436</v>
+        <v>36.9457</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>139.303</v>
+        <v>50.165</v>
       </c>
       <c r="C138" t="n">
-        <v>158.772</v>
+        <v>46.3272</v>
       </c>
       <c r="D138" t="n">
-        <v>166.484</v>
+        <v>47.3853</v>
       </c>
       <c r="E138" t="n">
-        <v>109.773</v>
+        <v>39.7544</v>
       </c>
       <c r="F138" t="n">
-        <v>153.163</v>
+        <v>37.2175</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>139.691</v>
+        <v>50.1511</v>
       </c>
       <c r="C139" t="n">
-        <v>159.048</v>
+        <v>46.3988</v>
       </c>
       <c r="D139" t="n">
-        <v>169.2</v>
+        <v>48.404</v>
       </c>
       <c r="E139" t="n">
-        <v>110.345</v>
+        <v>40.1344</v>
       </c>
       <c r="F139" t="n">
-        <v>154.69</v>
+        <v>37.4782</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>139.65</v>
+        <v>50.2</v>
       </c>
       <c r="C140" t="n">
-        <v>159.461</v>
+        <v>46.4873</v>
       </c>
       <c r="D140" t="n">
-        <v>171.337</v>
+        <v>49.3198</v>
       </c>
       <c r="E140" t="n">
-        <v>110.397</v>
+        <v>40.4762</v>
       </c>
       <c r="F140" t="n">
-        <v>154.153</v>
+        <v>37.7455</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>139.069</v>
+        <v>50.2208</v>
       </c>
       <c r="C141" t="n">
-        <v>158.768</v>
+        <v>46.6131</v>
       </c>
       <c r="D141" t="n">
-        <v>174.479</v>
+        <v>50.1148</v>
       </c>
       <c r="E141" t="n">
-        <v>110.217</v>
+        <v>40.8352</v>
       </c>
       <c r="F141" t="n">
-        <v>148.722</v>
+        <v>38.042</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>134.795</v>
+        <v>50.3101</v>
       </c>
       <c r="C142" t="n">
-        <v>153.595</v>
+        <v>46.6973</v>
       </c>
       <c r="D142" t="n">
-        <v>173.074</v>
+        <v>51.0376</v>
       </c>
       <c r="E142" t="n">
-        <v>102.316</v>
+        <v>41.275</v>
       </c>
       <c r="F142" t="n">
-        <v>149.594</v>
+        <v>38.3739</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>134.238</v>
+        <v>50.2535</v>
       </c>
       <c r="C143" t="n">
-        <v>153.853</v>
+        <v>46.8141</v>
       </c>
       <c r="D143" t="n">
-        <v>175.72</v>
+        <v>52.0915</v>
       </c>
       <c r="E143" t="n">
-        <v>104.159</v>
+        <v>41.6197</v>
       </c>
       <c r="F143" t="n">
-        <v>149.717</v>
+        <v>38.8288</v>
       </c>
     </row>
   </sheetData>
